--- a/output/100_model_iteration.xlsx
+++ b/output/100_model_iteration.xlsx
@@ -1253,307 +1253,307 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.89741599493373</v>
+        <v>12.07275613491221</v>
       </c>
       <c r="C3" t="n">
-        <v>12.04158564530237</v>
+        <v>12.00020497956837</v>
       </c>
       <c r="D3" t="n">
-        <v>11.94720042101609</v>
+        <v>12.01649217398183</v>
       </c>
       <c r="E3" t="n">
-        <v>12.045198476854</v>
+        <v>11.99154596481691</v>
       </c>
       <c r="F3" t="n">
-        <v>11.99843783370073</v>
+        <v>11.96977080073672</v>
       </c>
       <c r="G3" t="n">
-        <v>12.02806697941489</v>
+        <v>12.01495083008616</v>
       </c>
       <c r="H3" t="n">
-        <v>11.93123720334503</v>
+        <v>12.08292704112821</v>
       </c>
       <c r="I3" t="n">
-        <v>11.95282583536142</v>
+        <v>12.00323857997449</v>
       </c>
       <c r="J3" t="n">
-        <v>11.96635431872594</v>
+        <v>11.91164151916827</v>
       </c>
       <c r="K3" t="n">
-        <v>11.99783896760114</v>
+        <v>12.00241391190293</v>
       </c>
       <c r="L3" t="n">
-        <v>11.98409449974168</v>
+        <v>12.05210016321486</v>
       </c>
       <c r="M3" t="n">
-        <v>11.96107251607709</v>
+        <v>11.89247780398137</v>
       </c>
       <c r="N3" t="n">
-        <v>12.01382182022627</v>
+        <v>11.93077578192404</v>
       </c>
       <c r="O3" t="n">
-        <v>11.96544129336099</v>
+        <v>11.90579030285095</v>
       </c>
       <c r="P3" t="n">
-        <v>11.90457293569769</v>
+        <v>12.03954361007754</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.00149106906093</v>
+        <v>12.11332195005169</v>
       </c>
       <c r="R3" t="n">
-        <v>11.8952365150303</v>
+        <v>11.99431449334289</v>
       </c>
       <c r="S3" t="n">
-        <v>12.02657472290444</v>
+        <v>12.02485666442201</v>
       </c>
       <c r="T3" t="n">
-        <v>11.90658551849139</v>
+        <v>12.03404582293376</v>
       </c>
       <c r="U3" t="n">
-        <v>11.95432790934892</v>
+        <v>11.89694475603569</v>
       </c>
       <c r="V3" t="n">
-        <v>12.01636454678027</v>
+        <v>11.95415119476215</v>
       </c>
       <c r="W3" t="n">
-        <v>11.9021480188682</v>
+        <v>12.08615699107518</v>
       </c>
       <c r="X3" t="n">
-        <v>11.97013404738729</v>
+        <v>12.07590754504284</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.99039732000294</v>
+        <v>11.95550600659401</v>
       </c>
       <c r="Z3" t="n">
-        <v>12.0632528171351</v>
+        <v>11.949262091195</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.10049050755718</v>
+        <v>12.06715035552096</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.00276734107645</v>
+        <v>12.00663542703119</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.11486329394736</v>
+        <v>11.92440423932347</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.01917234521442</v>
+        <v>11.90041032543168</v>
       </c>
       <c r="AE3" t="n">
-        <v>12.00825531074319</v>
+        <v>11.93377011242199</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.01250627830258</v>
+        <v>11.97389414109456</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.93374065999086</v>
+        <v>11.98520387464748</v>
       </c>
       <c r="AH3" t="n">
-        <v>12.03498830072984</v>
+        <v>11.92802688835214</v>
       </c>
       <c r="AI3" t="n">
-        <v>12.10201221649876</v>
+        <v>11.97435556251555</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12.04736813928039</v>
+        <v>12.01286952495315</v>
       </c>
       <c r="AK3" t="n">
-        <v>11.93111939362052</v>
+        <v>11.91828795112602</v>
       </c>
       <c r="AL3" t="n">
-        <v>11.93233676077379</v>
+        <v>11.8852030534929</v>
       </c>
       <c r="AM3" t="n">
-        <v>11.91854320552912</v>
+        <v>12.067160172998</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.96176955694711</v>
+        <v>12.0564100356365</v>
       </c>
       <c r="AO3" t="n">
-        <v>11.96852398115233</v>
+        <v>12.01322295412668</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.96349743290658</v>
+        <v>12.00792151652375</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.97399231586498</v>
+        <v>11.96358579019996</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.95322835192016</v>
+        <v>11.92270581579513</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.94250766698979</v>
+        <v>12.07873497843107</v>
       </c>
       <c r="AT3" t="n">
-        <v>11.93328905604691</v>
+        <v>12.01555951366279</v>
       </c>
       <c r="AU3" t="n">
-        <v>12.00411233543127</v>
+        <v>11.8822676278572</v>
       </c>
       <c r="AV3" t="n">
-        <v>11.91506781865609</v>
+        <v>12.01662961866042</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.91790506952136</v>
+        <v>11.99457956522304</v>
       </c>
       <c r="AX3" t="n">
-        <v>11.93866903346618</v>
+        <v>11.91235819499237</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.88947365600637</v>
+        <v>11.87467871810337</v>
       </c>
       <c r="AZ3" t="n">
-        <v>12.08476290933515</v>
+        <v>11.99005370830646</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.03891529154682</v>
+        <v>11.9389733752545</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.01596203022153</v>
+        <v>12.08706019896309</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.97921521365157</v>
+        <v>11.91565686727863</v>
       </c>
       <c r="BD3" t="n">
-        <v>12.0323670343595</v>
+        <v>11.95407265494581</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.04790810051772</v>
+        <v>12.00601692597751</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.04491377001977</v>
+        <v>12.0040730655231</v>
       </c>
       <c r="BG3" t="n">
-        <v>12.18678613076048</v>
+        <v>11.989484294638</v>
       </c>
       <c r="BH3" t="n">
-        <v>12.0869718416697</v>
+        <v>11.92785017376538</v>
       </c>
       <c r="BI3" t="n">
-        <v>12.06285030057636</v>
+        <v>12.01442068632586</v>
       </c>
       <c r="BJ3" t="n">
-        <v>12.11907499159857</v>
+        <v>11.99786842003226</v>
       </c>
       <c r="BK3" t="n">
-        <v>11.91186732114024</v>
+        <v>11.99505080412107</v>
       </c>
       <c r="BL3" t="n">
-        <v>11.98037367594258</v>
+        <v>12.06967344712088</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.06148567126746</v>
+        <v>12.07280522229742</v>
       </c>
       <c r="BN3" t="n">
-        <v>11.91559796241638</v>
+        <v>12.05277756913079</v>
       </c>
       <c r="BO3" t="n">
-        <v>11.91979002511351</v>
+        <v>11.97479734898246</v>
       </c>
       <c r="BP3" t="n">
-        <v>12.05128531262033</v>
+        <v>11.96312436877897</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11.95081325256771</v>
+        <v>12.03507665802322</v>
       </c>
       <c r="BR3" t="n">
-        <v>12.01668852352267</v>
+        <v>12.01102383926917</v>
       </c>
       <c r="BS3" t="n">
-        <v>11.99835929388439</v>
+        <v>11.96300655905446</v>
       </c>
       <c r="BT3" t="n">
-        <v>11.93919917722648</v>
+        <v>11.95594779306093</v>
       </c>
       <c r="BU3" t="n">
-        <v>11.96129831804907</v>
+        <v>11.93191460926096</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.95157901577703</v>
+        <v>11.96208371621247</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.89578629374468</v>
+        <v>12.09357900371928</v>
       </c>
       <c r="BX3" t="n">
-        <v>11.8949812606272</v>
+        <v>11.8823363501965</v>
       </c>
       <c r="BY3" t="n">
-        <v>12.07785140549725</v>
+        <v>11.94191861836724</v>
       </c>
       <c r="BZ3" t="n">
-        <v>11.95756767677293</v>
+        <v>12.03808080599821</v>
       </c>
       <c r="CA3" t="n">
-        <v>11.96432210097815</v>
+        <v>12.03536136485745</v>
       </c>
       <c r="CB3" t="n">
-        <v>12.00169723607883</v>
+        <v>12.13395828679496</v>
       </c>
       <c r="CC3" t="n">
-        <v>11.89970346708462</v>
+        <v>11.98942538977574</v>
       </c>
       <c r="CD3" t="n">
-        <v>12.1114762643677</v>
+        <v>11.9755925646229</v>
       </c>
       <c r="CE3" t="n">
-        <v>12.05470179463111</v>
+        <v>12.05667510751665</v>
       </c>
       <c r="CF3" t="n">
-        <v>11.87283303241939</v>
+        <v>12.0832019304854</v>
       </c>
       <c r="CG3" t="n">
-        <v>11.93991585305057</v>
+        <v>11.98003988172314</v>
       </c>
       <c r="CH3" t="n">
-        <v>11.98143396346317</v>
+        <v>11.95206988962915</v>
       </c>
       <c r="CI3" t="n">
-        <v>11.98732444968865</v>
+        <v>12.04798664033406</v>
       </c>
       <c r="CJ3" t="n">
-        <v>11.97358979930624</v>
+        <v>11.99239026784257</v>
       </c>
       <c r="CK3" t="n">
-        <v>12.06476470859964</v>
+        <v>12.07089081427414</v>
       </c>
       <c r="CL3" t="n">
-        <v>11.99343092040907</v>
+        <v>12.09722128770204</v>
       </c>
       <c r="CM3" t="n">
-        <v>11.93781491296349</v>
+        <v>11.99079983656169</v>
       </c>
       <c r="CN3" t="n">
-        <v>11.92194005258581</v>
+        <v>11.92620083762225</v>
       </c>
       <c r="CO3" t="n">
-        <v>11.98939593734461</v>
+        <v>11.94482459157181</v>
       </c>
       <c r="CP3" t="n">
-        <v>11.94064234635172</v>
+        <v>11.92685860858409</v>
       </c>
       <c r="CQ3" t="n">
-        <v>11.9460714111562</v>
+        <v>11.92816433303074</v>
       </c>
       <c r="CR3" t="n">
-        <v>11.94224259510964</v>
+        <v>11.97135141454056</v>
       </c>
       <c r="CS3" t="n">
-        <v>11.96237824052374</v>
+        <v>11.98455592116268</v>
       </c>
       <c r="CT3" t="n">
-        <v>11.99311676114371</v>
+        <v>11.98667649620385</v>
       </c>
       <c r="CU3" t="n">
-        <v>12.00783315923037</v>
+        <v>11.95268839068282</v>
       </c>
       <c r="CV3" t="n">
-        <v>11.91179859880095</v>
+        <v>11.98134560616979</v>
       </c>
       <c r="CW3" t="n">
-        <v>12.03364330637502</v>
+        <v>12.02231393786801</v>
       </c>
       <c r="CX3" t="n">
-        <v>11.98498199966632</v>
+        <v>11.99086443556062</v>
       </c>
     </row>
     <row r="4">
@@ -1561,307 +1561,307 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.77278795298556</v>
+        <v>13.0598954173151</v>
       </c>
       <c r="C4" t="n">
-        <v>12.9766378243219</v>
+        <v>12.96716973945932</v>
       </c>
       <c r="D4" t="n">
-        <v>12.77344038202921</v>
+        <v>13.01820287898862</v>
       </c>
       <c r="E4" t="n">
-        <v>12.95138334392297</v>
+        <v>13.00782353142669</v>
       </c>
       <c r="F4" t="n">
-        <v>12.84707446843522</v>
+        <v>12.80196496748134</v>
       </c>
       <c r="G4" t="n">
-        <v>12.91335925859542</v>
+        <v>12.96625046888413</v>
       </c>
       <c r="H4" t="n">
-        <v>12.71083213584109</v>
+        <v>13.13661777186416</v>
       </c>
       <c r="I4" t="n">
-        <v>12.75087367685661</v>
+        <v>12.91597810882386</v>
       </c>
       <c r="J4" t="n">
-        <v>12.87305704663722</v>
+        <v>12.64791371527181</v>
       </c>
       <c r="K4" t="n">
-        <v>12.92964010297224</v>
+        <v>12.96168918042905</v>
       </c>
       <c r="L4" t="n">
-        <v>12.85503244250754</v>
+        <v>13.02849212125256</v>
       </c>
       <c r="M4" t="n">
-        <v>12.94084267244946</v>
+        <v>12.65504253863694</v>
       </c>
       <c r="N4" t="n">
-        <v>12.91399326806168</v>
+        <v>12.72008070349772</v>
       </c>
       <c r="O4" t="n">
-        <v>12.80781109055243</v>
+        <v>12.69380700384971</v>
       </c>
       <c r="P4" t="n">
-        <v>12.87006150112329</v>
+        <v>12.92854422554993</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.89852453863463</v>
+        <v>13.19798329164159</v>
       </c>
       <c r="R4" t="n">
-        <v>12.83549456435245</v>
+        <v>13.02289034103031</v>
       </c>
       <c r="S4" t="n">
-        <v>13.10380030241145</v>
+        <v>12.96496341211036</v>
       </c>
       <c r="T4" t="n">
-        <v>12.72005806744791</v>
+        <v>13.04482840491653</v>
       </c>
       <c r="U4" t="n">
-        <v>12.77482668083305</v>
+        <v>12.73042605531134</v>
       </c>
       <c r="V4" t="n">
-        <v>12.85289633951949</v>
+        <v>12.86840706493838</v>
       </c>
       <c r="W4" t="n">
-        <v>12.69648134286293</v>
+        <v>13.03580841073596</v>
       </c>
       <c r="X4" t="n">
-        <v>12.78229034716413</v>
+        <v>13.07202639586967</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.82173450619826</v>
+        <v>12.7659013079954</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.97314869800112</v>
+        <v>12.7888024820929</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.01879880144425</v>
+        <v>13.03960878241585</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.9659004930069</v>
+        <v>12.90313314824121</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.16253071065628</v>
+        <v>12.7869348690969</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.90019388670251</v>
+        <v>12.677722045778</v>
       </c>
       <c r="AE4" t="n">
-        <v>13.01993972553969</v>
+        <v>12.9145714688922</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.91652760981875</v>
+        <v>12.92834085099798</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.76630796278129</v>
+        <v>12.77818002258695</v>
       </c>
       <c r="AH4" t="n">
-        <v>13.00354488849169</v>
+        <v>12.69523567354788</v>
       </c>
       <c r="AI4" t="n">
-        <v>13.07679880481791</v>
+        <v>13.02229360294584</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13.05455285065042</v>
+        <v>13.03272687249457</v>
       </c>
       <c r="AK4" t="n">
-        <v>12.82797440066388</v>
+        <v>12.79571838078321</v>
       </c>
       <c r="AL4" t="n">
-        <v>12.79637061165775</v>
+        <v>12.82196724829008</v>
       </c>
       <c r="AM4" t="n">
-        <v>12.69845635660721</v>
+        <v>13.11768716666757</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.8178780117</v>
+        <v>12.98618392727585</v>
       </c>
       <c r="AO4" t="n">
-        <v>12.8865144401738</v>
+        <v>12.90111339036216</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.85443641039611</v>
+        <v>12.92453384723579</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.97655437365727</v>
+        <v>12.95110901040358</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.85378003172632</v>
+        <v>12.86450461199473</v>
       </c>
       <c r="AS4" t="n">
-        <v>12.95139709650616</v>
+        <v>13.07642155480993</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.83193829031008</v>
+        <v>12.98947795674407</v>
       </c>
       <c r="AU4" t="n">
-        <v>12.95673932156148</v>
+        <v>12.65863709738206</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.79665456252522</v>
+        <v>12.98112211853797</v>
       </c>
       <c r="AW4" t="n">
-        <v>12.79132056974835</v>
+        <v>12.93269689053537</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.84877920245307</v>
+        <v>12.73882276879558</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.69387394921715</v>
+        <v>12.71977883959509</v>
       </c>
       <c r="AZ4" t="n">
-        <v>13.05030052038903</v>
+        <v>12.8978105103756</v>
       </c>
       <c r="BA4" t="n">
-        <v>13.02473654911533</v>
+        <v>12.73687926662299</v>
       </c>
       <c r="BB4" t="n">
-        <v>12.87666488974041</v>
+        <v>13.02798290097868</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.84555408060838</v>
+        <v>12.76353956826169</v>
       </c>
       <c r="BD4" t="n">
-        <v>12.96130313694434</v>
+        <v>12.91036704756793</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.92030808239682</v>
+        <v>12.94712593663913</v>
       </c>
       <c r="BF4" t="n">
-        <v>12.90159922747603</v>
+        <v>12.98891123661283</v>
       </c>
       <c r="BG4" t="n">
-        <v>13.3075256992403</v>
+        <v>12.97528084245459</v>
       </c>
       <c r="BH4" t="n">
-        <v>13.10428442847489</v>
+        <v>12.71468428872405</v>
       </c>
       <c r="BI4" t="n">
-        <v>12.9713329021729</v>
+        <v>13.032077229765</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13.07324600795663</v>
+        <v>13.0434049948444</v>
       </c>
       <c r="BK4" t="n">
-        <v>12.69843420515086</v>
+        <v>12.85781847953028</v>
       </c>
       <c r="BL4" t="n">
-        <v>12.99360037099003</v>
+        <v>13.06040927498924</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.92720482589904</v>
+        <v>13.05630216739519</v>
       </c>
       <c r="BN4" t="n">
-        <v>12.72433844685031</v>
+        <v>13.08425465436702</v>
       </c>
       <c r="BO4" t="n">
-        <v>12.73390590287609</v>
+        <v>12.86056000422809</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.08355923593081</v>
+        <v>12.84081015941285</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12.93345149497668</v>
+        <v>12.95233683210329</v>
       </c>
       <c r="BR4" t="n">
-        <v>13.08093634348848</v>
+        <v>13.00621187713636</v>
       </c>
       <c r="BS4" t="n">
-        <v>12.90678444939474</v>
+        <v>12.86174114904296</v>
       </c>
       <c r="BT4" t="n">
-        <v>12.72960426944375</v>
+        <v>13.00129447273219</v>
       </c>
       <c r="BU4" t="n">
-        <v>12.97354444202151</v>
+        <v>12.70767016792176</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.97604869169626</v>
+        <v>12.73690311816876</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.68534546869686</v>
+        <v>13.06473245909722</v>
       </c>
       <c r="BX4" t="n">
-        <v>12.65223199979788</v>
+        <v>12.72711392448931</v>
       </c>
       <c r="BY4" t="n">
-        <v>13.11971758814463</v>
+        <v>12.83964539878626</v>
       </c>
       <c r="BZ4" t="n">
-        <v>12.7706703511342</v>
+        <v>12.85361883207127</v>
       </c>
       <c r="CA4" t="n">
-        <v>12.83594920112878</v>
+        <v>13.08717956951612</v>
       </c>
       <c r="CB4" t="n">
-        <v>12.90473877696679</v>
+        <v>13.06185142158692</v>
       </c>
       <c r="CC4" t="n">
-        <v>12.76082776249243</v>
+        <v>12.9708630420005</v>
       </c>
       <c r="CD4" t="n">
-        <v>13.29085862601081</v>
+        <v>12.86309204587184</v>
       </c>
       <c r="CE4" t="n">
-        <v>12.89846662688205</v>
+        <v>12.97408850741948</v>
       </c>
       <c r="CF4" t="n">
-        <v>12.57620025997175</v>
+        <v>13.00067486878251</v>
       </c>
       <c r="CG4" t="n">
-        <v>12.85280300589054</v>
+        <v>12.88476418452671</v>
       </c>
       <c r="CH4" t="n">
-        <v>12.93569573509922</v>
+        <v>12.81169377253786</v>
       </c>
       <c r="CI4" t="n">
-        <v>12.92656887602675</v>
+        <v>13.24233106146069</v>
       </c>
       <c r="CJ4" t="n">
-        <v>12.90020429379558</v>
+        <v>12.84571643018527</v>
       </c>
       <c r="CK4" t="n">
-        <v>13.07005537094473</v>
+        <v>13.02398511262629</v>
       </c>
       <c r="CL4" t="n">
-        <v>12.94916205148436</v>
+        <v>13.05043425980864</v>
       </c>
       <c r="CM4" t="n">
-        <v>12.77832010288781</v>
+        <v>12.84698461837034</v>
       </c>
       <c r="CN4" t="n">
-        <v>12.72854320964135</v>
+        <v>12.80849208471616</v>
       </c>
       <c r="CO4" t="n">
-        <v>12.89762469537126</v>
+        <v>12.73869892561823</v>
       </c>
       <c r="CP4" t="n">
-        <v>12.86581036931185</v>
+        <v>12.68585144249201</v>
       </c>
       <c r="CQ4" t="n">
-        <v>12.97454281482028</v>
+        <v>12.74961452865543</v>
       </c>
       <c r="CR4" t="n">
-        <v>12.80571584422549</v>
+        <v>12.84595535760828</v>
       </c>
       <c r="CS4" t="n">
-        <v>12.77189228489766</v>
+        <v>12.90395242748183</v>
       </c>
       <c r="CT4" t="n">
-        <v>12.83159810632488</v>
+        <v>13.00362695977267</v>
       </c>
       <c r="CU4" t="n">
-        <v>12.94947033517022</v>
+        <v>12.91921410577512</v>
       </c>
       <c r="CV4" t="n">
-        <v>12.7669799050294</v>
+        <v>12.93178847559217</v>
       </c>
       <c r="CW4" t="n">
-        <v>13.06690834875503</v>
+        <v>12.9748032920085</v>
       </c>
       <c r="CX4" t="n">
-        <v>12.89179016131667</v>
+        <v>12.91015174974516</v>
       </c>
     </row>
     <row r="5">
@@ -1869,307 +1869,307 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.86056464143399</v>
+        <v>14.24784879061232</v>
       </c>
       <c r="C5" t="n">
-        <v>14.23672673632303</v>
+        <v>14.19263507487201</v>
       </c>
       <c r="D5" t="n">
-        <v>13.83525639353753</v>
+        <v>14.34803694451572</v>
       </c>
       <c r="E5" t="n">
-        <v>14.15381638019025</v>
+        <v>14.31316279208769</v>
       </c>
       <c r="F5" t="n">
-        <v>13.8781912992396</v>
+        <v>13.96123583054294</v>
       </c>
       <c r="G5" t="n">
-        <v>14.02448403863531</v>
+        <v>14.34141026950796</v>
       </c>
       <c r="H5" t="n">
-        <v>13.74021788887649</v>
+        <v>14.474923287141</v>
       </c>
       <c r="I5" t="n">
-        <v>13.85193840893023</v>
+        <v>14.17011677414972</v>
       </c>
       <c r="J5" t="n">
-        <v>14.07692593893253</v>
+        <v>13.5655356879224</v>
       </c>
       <c r="K5" t="n">
-        <v>14.13016887060883</v>
+        <v>14.15286858151551</v>
       </c>
       <c r="L5" t="n">
-        <v>13.93829293695391</v>
+        <v>14.36221163247428</v>
       </c>
       <c r="M5" t="n">
-        <v>14.10148742116647</v>
+        <v>13.73045624656507</v>
       </c>
       <c r="N5" t="n">
-        <v>14.1051920575984</v>
+        <v>13.67013914967443</v>
       </c>
       <c r="O5" t="n">
-        <v>13.80162150271341</v>
+        <v>13.61165535224007</v>
       </c>
       <c r="P5" t="n">
-        <v>14.09723648959445</v>
+        <v>14.12454816516104</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.04877796886124</v>
+        <v>14.59436179981944</v>
       </c>
       <c r="R5" t="n">
-        <v>14.0313398842028</v>
+        <v>14.29445708565912</v>
       </c>
       <c r="S5" t="n">
-        <v>14.33500377839402</v>
+        <v>14.22267596891255</v>
       </c>
       <c r="T5" t="n">
-        <v>13.77202790444761</v>
+        <v>14.39280597233462</v>
       </c>
       <c r="U5" t="n">
-        <v>13.7960831467105</v>
+        <v>13.68431801332736</v>
       </c>
       <c r="V5" t="n">
-        <v>13.87131707390944</v>
+        <v>13.98674528038131</v>
       </c>
       <c r="W5" t="n">
-        <v>13.65663061672308</v>
+        <v>14.3442891257696</v>
       </c>
       <c r="X5" t="n">
-        <v>13.78007930353491</v>
+        <v>14.31805346343197</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.88450818307595</v>
+        <v>13.75931687940621</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.05512813919008</v>
+        <v>13.82127326567696</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.21267881417011</v>
+        <v>14.31703657558805</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.07237901299701</v>
+        <v>14.031908550514</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.52276686015759</v>
+        <v>13.87606102270822</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.13962279721766</v>
+        <v>13.61922332226429</v>
       </c>
       <c r="AE5" t="n">
-        <v>14.25083304113909</v>
+        <v>13.99797359980913</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.11746239038911</v>
+        <v>14.07151363992609</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.82198097440598</v>
+        <v>13.71779224345444</v>
       </c>
       <c r="AH5" t="n">
-        <v>14.1610376363804</v>
+        <v>13.71408871389769</v>
       </c>
       <c r="AI5" t="n">
-        <v>14.3716357100679</v>
+        <v>14.32298463714005</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.3740930959056</v>
+        <v>14.40058590003955</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.90557893613921</v>
+        <v>13.85672721718964</v>
       </c>
       <c r="AL5" t="n">
-        <v>13.92085495664146</v>
+        <v>13.9058347657497</v>
       </c>
       <c r="AM5" t="n">
-        <v>13.64359792161645</v>
+        <v>14.47430087328964</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.04470392435386</v>
+        <v>14.26373205109</v>
       </c>
       <c r="AO5" t="n">
-        <v>13.95171319319501</v>
+        <v>14.05437457409498</v>
       </c>
       <c r="AP5" t="n">
-        <v>14.00390197295626</v>
+        <v>14.15695389400622</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.18563850116553</v>
+        <v>14.1750037418005</v>
       </c>
       <c r="AR5" t="n">
-        <v>14.05519323326515</v>
+        <v>13.97568883253383</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.17899781525644</v>
+        <v>14.264489734425</v>
       </c>
       <c r="AT5" t="n">
-        <v>13.8818518781336</v>
+        <v>14.26887751206668</v>
       </c>
       <c r="AU5" t="n">
-        <v>14.09088513725628</v>
+        <v>13.56054436479255</v>
       </c>
       <c r="AV5" t="n">
-        <v>13.82661029764357</v>
+        <v>14.31873997859577</v>
       </c>
       <c r="AW5" t="n">
-        <v>13.89651384631843</v>
+        <v>14.17569292250098</v>
       </c>
       <c r="AX5" t="n">
-        <v>14.01375015130266</v>
+        <v>13.67352649347123</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.78821501270216</v>
+        <v>13.74433668325593</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.3196501547405</v>
+        <v>14.10458687815754</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.30254375195012</v>
+        <v>13.87381899922315</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.93269521800588</v>
+        <v>14.20991634306389</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.86715463486272</v>
+        <v>13.9189661838846</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.05860099391875</v>
+        <v>14.1061404610368</v>
       </c>
       <c r="BE5" t="n">
-        <v>14.0136101497631</v>
+        <v>14.11045138923385</v>
       </c>
       <c r="BF5" t="n">
-        <v>14.12396707333206</v>
+        <v>14.19218961324712</v>
       </c>
       <c r="BG5" t="n">
-        <v>14.73438734339626</v>
+        <v>14.22578274969583</v>
       </c>
       <c r="BH5" t="n">
-        <v>14.44838335435096</v>
+        <v>13.77477493424514</v>
       </c>
       <c r="BI5" t="n">
-        <v>14.19643395800627</v>
+        <v>14.30419667577398</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14.27958857344362</v>
+        <v>14.19203954358107</v>
       </c>
       <c r="BK5" t="n">
-        <v>13.77481747450144</v>
+        <v>13.92853577021456</v>
       </c>
       <c r="BL5" t="n">
-        <v>14.29773346190188</v>
+        <v>14.34107899443992</v>
       </c>
       <c r="BM5" t="n">
-        <v>14.06033400896317</v>
+        <v>14.21361978999082</v>
       </c>
       <c r="BN5" t="n">
-        <v>13.72266762626214</v>
+        <v>14.36155999653551</v>
       </c>
       <c r="BO5" t="n">
-        <v>13.77651807651393</v>
+        <v>14.02725437040189</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.55251280235266</v>
+        <v>14.03168391645993</v>
       </c>
       <c r="BQ5" t="n">
-        <v>14.05340502326946</v>
+        <v>14.11785740017961</v>
       </c>
       <c r="BR5" t="n">
-        <v>14.57175542291502</v>
+        <v>14.22100185215237</v>
       </c>
       <c r="BS5" t="n">
-        <v>14.08273996195983</v>
+        <v>13.95608207426726</v>
       </c>
       <c r="BT5" t="n">
-        <v>13.83044471671495</v>
+        <v>14.14741136580681</v>
       </c>
       <c r="BU5" t="n">
-        <v>14.24994417535425</v>
+        <v>13.77572109065107</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.16926410321494</v>
+        <v>13.84738886087526</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.69539340139976</v>
+        <v>14.26174590509363</v>
       </c>
       <c r="BX5" t="n">
-        <v>13.61464959338224</v>
+        <v>13.75168980073618</v>
       </c>
       <c r="BY5" t="n">
-        <v>14.44804194010192</v>
+        <v>13.93319539937027</v>
       </c>
       <c r="BZ5" t="n">
-        <v>13.82278774270607</v>
+        <v>13.92873906763741</v>
       </c>
       <c r="CA5" t="n">
-        <v>14.0666486391548</v>
+        <v>14.45848775956584</v>
       </c>
       <c r="CB5" t="n">
-        <v>14.09411660239182</v>
+        <v>14.20256531804922</v>
       </c>
       <c r="CC5" t="n">
-        <v>13.9112549083341</v>
+        <v>14.22452205770877</v>
       </c>
       <c r="CD5" t="n">
-        <v>14.69364799377915</v>
+        <v>13.97434365202142</v>
       </c>
       <c r="CE5" t="n">
-        <v>13.96856705423728</v>
+        <v>14.17671532061473</v>
       </c>
       <c r="CF5" t="n">
-        <v>13.47704917647136</v>
+        <v>14.28899705352086</v>
       </c>
       <c r="CG5" t="n">
-        <v>14.06941819274864</v>
+        <v>13.98757312898885</v>
       </c>
       <c r="CH5" t="n">
-        <v>14.15003390684267</v>
+        <v>13.92868232225343</v>
       </c>
       <c r="CI5" t="n">
-        <v>14.14866335644383</v>
+        <v>14.67310868978149</v>
       </c>
       <c r="CJ5" t="n">
-        <v>13.98550996332645</v>
+        <v>13.91491849193581</v>
       </c>
       <c r="CK5" t="n">
-        <v>14.33512376965363</v>
+        <v>14.21911250128582</v>
       </c>
       <c r="CL5" t="n">
-        <v>14.24432686174383</v>
+        <v>14.22233240971886</v>
       </c>
       <c r="CM5" t="n">
-        <v>13.81651124172862</v>
+        <v>13.91667630374014</v>
       </c>
       <c r="CN5" t="n">
-        <v>13.80782028104718</v>
+        <v>13.9398639207951</v>
       </c>
       <c r="CO5" t="n">
-        <v>14.0162601551708</v>
+        <v>13.70920898642766</v>
       </c>
       <c r="CP5" t="n">
-        <v>13.99127292633753</v>
+        <v>13.7040788461013</v>
       </c>
       <c r="CQ5" t="n">
-        <v>14.1398798797216</v>
+        <v>13.77688897923332</v>
       </c>
       <c r="CR5" t="n">
-        <v>13.85596552248203</v>
+        <v>13.99550849924859</v>
       </c>
       <c r="CS5" t="n">
-        <v>13.8726328746297</v>
+        <v>14.10269152095434</v>
       </c>
       <c r="CT5" t="n">
-        <v>13.96340466822523</v>
+        <v>14.27753724328618</v>
       </c>
       <c r="CU5" t="n">
-        <v>14.16278291724853</v>
+        <v>14.19277013748023</v>
       </c>
       <c r="CV5" t="n">
-        <v>13.92586857535661</v>
+        <v>14.09928270348933</v>
       </c>
       <c r="CW5" t="n">
-        <v>14.27775663386161</v>
+        <v>14.18140384143527</v>
       </c>
       <c r="CX5" t="n">
-        <v>14.04470054952782</v>
+        <v>14.07647772391497</v>
       </c>
     </row>
     <row r="6">
@@ -2177,307 +2177,307 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.18926214466178</v>
+        <v>15.60658945935367</v>
       </c>
       <c r="C6" t="n">
-        <v>15.71420127404402</v>
+        <v>15.56111195269313</v>
       </c>
       <c r="D6" t="n">
-        <v>15.06823920845073</v>
+        <v>15.86165375300003</v>
       </c>
       <c r="E6" t="n">
-        <v>15.54969401737285</v>
+        <v>15.92227290771522</v>
       </c>
       <c r="F6" t="n">
-        <v>15.05250175757974</v>
+        <v>15.25087558441776</v>
       </c>
       <c r="G6" t="n">
-        <v>15.34893335824828</v>
+        <v>15.9675267956803</v>
       </c>
       <c r="H6" t="n">
-        <v>14.95377240526517</v>
+        <v>16.01827829273913</v>
       </c>
       <c r="I6" t="n">
-        <v>15.12092087282725</v>
+        <v>15.66233652052307</v>
       </c>
       <c r="J6" t="n">
-        <v>15.33285326832701</v>
+        <v>14.62161989919663</v>
       </c>
       <c r="K6" t="n">
-        <v>15.52159929087999</v>
+        <v>15.63957632596985</v>
       </c>
       <c r="L6" t="n">
-        <v>15.16524668870835</v>
+        <v>15.96833767084097</v>
       </c>
       <c r="M6" t="n">
-        <v>15.46632031678371</v>
+        <v>14.86280723370989</v>
       </c>
       <c r="N6" t="n">
-        <v>15.35012263339096</v>
+        <v>14.93070289613144</v>
       </c>
       <c r="O6" t="n">
-        <v>14.94764901197602</v>
+        <v>14.75971086829307</v>
       </c>
       <c r="P6" t="n">
-        <v>15.56429334750946</v>
+        <v>15.52260448792753</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.43415813312418</v>
+        <v>16.14819145781469</v>
       </c>
       <c r="R6" t="n">
-        <v>15.45180327427689</v>
+        <v>15.81554703132375</v>
       </c>
       <c r="S6" t="n">
-        <v>15.78294970424998</v>
+        <v>15.70600844928407</v>
       </c>
       <c r="T6" t="n">
-        <v>14.99824309424981</v>
+        <v>15.93591329461495</v>
       </c>
       <c r="U6" t="n">
-        <v>15.12771841745236</v>
+        <v>14.83475357263752</v>
       </c>
       <c r="V6" t="n">
-        <v>15.19810735886243</v>
+        <v>15.25512091011173</v>
       </c>
       <c r="W6" t="n">
-        <v>14.81402503470254</v>
+        <v>15.84952768616812</v>
       </c>
       <c r="X6" t="n">
-        <v>14.99970549217135</v>
+        <v>15.73807895651393</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.09278544217116</v>
+        <v>14.84509977991646</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.33984855005732</v>
+        <v>15.12351531322054</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.59106828464754</v>
+        <v>15.91088095814466</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.56040938740236</v>
+        <v>15.32524274193967</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.22195376281113</v>
+        <v>15.17630472955119</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.48563534384315</v>
+        <v>14.70461741616213</v>
       </c>
       <c r="AE6" t="n">
-        <v>15.70941628402046</v>
+        <v>15.37105025593739</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.59758213577849</v>
+        <v>15.37245821855763</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.05965132133408</v>
+        <v>14.8058256971197</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.62971222938635</v>
+        <v>14.87326773158964</v>
       </c>
       <c r="AI6" t="n">
-        <v>15.95220599712203</v>
+        <v>15.81691259677618</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15.9202066989329</v>
+        <v>15.95936760772475</v>
       </c>
       <c r="AK6" t="n">
-        <v>15.14657903696864</v>
+        <v>15.05375810922772</v>
       </c>
       <c r="AL6" t="n">
-        <v>15.25731452050231</v>
+        <v>15.24271422431108</v>
       </c>
       <c r="AM6" t="n">
-        <v>14.76162941231763</v>
+        <v>16.08741705415042</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.37019150512783</v>
+        <v>15.86362574571965</v>
       </c>
       <c r="AO6" t="n">
-        <v>15.25247130774344</v>
+        <v>15.34268629726694</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.37799759804816</v>
+        <v>15.62369373086518</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.58934453230439</v>
+        <v>15.71972159831436</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.39327238487653</v>
+        <v>15.26612903115984</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.55160435010924</v>
+        <v>15.69537979810593</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.1501189915753</v>
+        <v>15.77851026710328</v>
       </c>
       <c r="AU6" t="n">
-        <v>15.33947164458525</v>
+        <v>14.69628960141293</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.09104361099057</v>
+        <v>15.90965046920312</v>
       </c>
       <c r="AW6" t="n">
-        <v>15.26739433100343</v>
+        <v>15.65468866326682</v>
       </c>
       <c r="AX6" t="n">
-        <v>15.37699016240447</v>
+        <v>14.91857368097628</v>
       </c>
       <c r="AY6" t="n">
-        <v>15.12654174389664</v>
+        <v>15.06134308056354</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.9529508991979</v>
+        <v>15.56903602591515</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.72064616622074</v>
+        <v>15.26408053675224</v>
       </c>
       <c r="BB6" t="n">
-        <v>15.25771165567172</v>
+        <v>15.64210074334892</v>
       </c>
       <c r="BC6" t="n">
-        <v>15.11182829603515</v>
+        <v>15.27285601679453</v>
       </c>
       <c r="BD6" t="n">
-        <v>15.34478855235574</v>
+        <v>15.45684736967473</v>
       </c>
       <c r="BE6" t="n">
-        <v>15.30040930781107</v>
+        <v>15.4738365159095</v>
       </c>
       <c r="BF6" t="n">
-        <v>15.63227908028726</v>
+        <v>15.72990512262538</v>
       </c>
       <c r="BG6" t="n">
-        <v>16.3657572631374</v>
+        <v>15.71375024193945</v>
       </c>
       <c r="BH6" t="n">
-        <v>16.00953155382566</v>
+        <v>14.96117246756597</v>
       </c>
       <c r="BI6" t="n">
-        <v>15.51671627747738</v>
+        <v>15.84963325003953</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15.68325437290252</v>
+        <v>15.70293350118126</v>
       </c>
       <c r="BK6" t="n">
-        <v>15.0258213594906</v>
+        <v>15.21177438591566</v>
       </c>
       <c r="BL6" t="n">
-        <v>15.67857556131817</v>
+        <v>15.84018462473185</v>
       </c>
       <c r="BM6" t="n">
-        <v>15.39718791614116</v>
+        <v>15.60094975283983</v>
       </c>
       <c r="BN6" t="n">
-        <v>14.9002478930188</v>
+        <v>15.7563537753199</v>
       </c>
       <c r="BO6" t="n">
-        <v>15.0443858159399</v>
+        <v>15.3979543864292</v>
       </c>
       <c r="BP6" t="n">
-        <v>16.33068823133523</v>
+        <v>15.42854821560325</v>
       </c>
       <c r="BQ6" t="n">
-        <v>15.48269421642772</v>
+        <v>15.46190350923645</v>
       </c>
       <c r="BR6" t="n">
-        <v>16.14864343365367</v>
+        <v>15.62436764788496</v>
       </c>
       <c r="BS6" t="n">
-        <v>15.38483580219768</v>
+        <v>15.22276420089976</v>
       </c>
       <c r="BT6" t="n">
-        <v>15.11799227414158</v>
+        <v>15.57756051074058</v>
       </c>
       <c r="BU6" t="n">
-        <v>15.69430382027778</v>
+        <v>14.98780039391213</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.50396226903572</v>
+        <v>15.13133101678349</v>
       </c>
       <c r="BW6" t="n">
-        <v>14.94562759029031</v>
+        <v>15.72630324339516</v>
       </c>
       <c r="BX6" t="n">
-        <v>14.842077140785</v>
+        <v>15.07006618544012</v>
       </c>
       <c r="BY6" t="n">
-        <v>16.00341674457243</v>
+        <v>15.22632985945991</v>
       </c>
       <c r="BZ6" t="n">
-        <v>15.03370755735239</v>
+        <v>15.18119054809242</v>
       </c>
       <c r="CA6" t="n">
-        <v>15.45652924906079</v>
+        <v>16.0626757682289</v>
       </c>
       <c r="CB6" t="n">
-        <v>15.47370470294369</v>
+        <v>15.47252856823409</v>
       </c>
       <c r="CC6" t="n">
-        <v>15.34183485209093</v>
+        <v>15.66878490828919</v>
       </c>
       <c r="CD6" t="n">
-        <v>16.33212334118334</v>
+        <v>15.34387323074777</v>
       </c>
       <c r="CE6" t="n">
-        <v>15.23701763556752</v>
+        <v>15.55141559229608</v>
       </c>
       <c r="CF6" t="n">
-        <v>14.48908210593978</v>
+        <v>15.78277751793589</v>
       </c>
       <c r="CG6" t="n">
-        <v>15.30770493920754</v>
+        <v>15.32270651298269</v>
       </c>
       <c r="CH6" t="n">
-        <v>15.55288522873371</v>
+        <v>15.2812132326813</v>
       </c>
       <c r="CI6" t="n">
-        <v>15.52950651504474</v>
+        <v>16.34055813279553</v>
       </c>
       <c r="CJ6" t="n">
-        <v>15.25216748503785</v>
+        <v>15.2713303820274</v>
       </c>
       <c r="CK6" t="n">
-        <v>15.83244035045578</v>
+        <v>15.60928894368737</v>
       </c>
       <c r="CL6" t="n">
-        <v>15.83830118707467</v>
+        <v>15.71448656155091</v>
       </c>
       <c r="CM6" t="n">
-        <v>15.11930527760004</v>
+        <v>15.18668209188114</v>
       </c>
       <c r="CN6" t="n">
-        <v>15.20277906340933</v>
+        <v>15.30071045839592</v>
       </c>
       <c r="CO6" t="n">
-        <v>15.28798466020537</v>
+        <v>14.91150959942677</v>
       </c>
       <c r="CP6" t="n">
-        <v>15.29699136409806</v>
+        <v>14.93853580062546</v>
       </c>
       <c r="CQ6" t="n">
-        <v>15.55292609263108</v>
+        <v>14.95688424315016</v>
       </c>
       <c r="CR6" t="n">
-        <v>14.98822379190868</v>
+        <v>15.30964147604281</v>
       </c>
       <c r="CS6" t="n">
-        <v>15.08147543947539</v>
+        <v>15.50521466060867</v>
       </c>
       <c r="CT6" t="n">
-        <v>15.3236560778391</v>
+        <v>15.84522151815689</v>
       </c>
       <c r="CU6" t="n">
-        <v>15.69047558439887</v>
+        <v>15.66965254458394</v>
       </c>
       <c r="CV6" t="n">
-        <v>15.22880554910963</v>
+        <v>15.466600041653</v>
       </c>
       <c r="CW6" t="n">
-        <v>15.79225510562163</v>
+        <v>15.66199611850671</v>
       </c>
       <c r="CX6" t="n">
-        <v>15.40002977324614</v>
+        <v>15.45893692357867</v>
       </c>
     </row>
     <row r="7">
@@ -2485,307 +2485,307 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.75522066788716</v>
+        <v>17.1251871765696</v>
       </c>
       <c r="C7" t="n">
-        <v>17.38224629551528</v>
+        <v>17.11370979507502</v>
       </c>
       <c r="D7" t="n">
-        <v>16.60403095771237</v>
+        <v>17.54047610812333</v>
       </c>
       <c r="E7" t="n">
-        <v>17.11209930436558</v>
+        <v>17.66321940448429</v>
       </c>
       <c r="F7" t="n">
-        <v>16.28247711122554</v>
+        <v>16.77480931811331</v>
       </c>
       <c r="G7" t="n">
-        <v>16.80223796930261</v>
+        <v>17.82416837852911</v>
       </c>
       <c r="H7" t="n">
-        <v>16.41718706512314</v>
+        <v>17.82617386206327</v>
       </c>
       <c r="I7" t="n">
-        <v>16.60284765505767</v>
+        <v>17.49974247434916</v>
       </c>
       <c r="J7" t="n">
-        <v>16.9006701495188</v>
+        <v>15.94069708914556</v>
       </c>
       <c r="K7" t="n">
-        <v>17.07504718522459</v>
+        <v>17.3731429617902</v>
       </c>
       <c r="L7" t="n">
-        <v>16.56787549200357</v>
+        <v>17.79831685536199</v>
       </c>
       <c r="M7" t="n">
-        <v>16.97831019749614</v>
+        <v>16.15750300131166</v>
       </c>
       <c r="N7" t="n">
-        <v>16.71189596459859</v>
+        <v>16.41195736243278</v>
       </c>
       <c r="O7" t="n">
-        <v>16.34688362809249</v>
+        <v>15.99697957218819</v>
       </c>
       <c r="P7" t="n">
-        <v>17.2752758091859</v>
+        <v>17.28834568435269</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.04149470488872</v>
+        <v>17.95155186305254</v>
       </c>
       <c r="R7" t="n">
-        <v>17.02696205985067</v>
+        <v>17.59418256788272</v>
       </c>
       <c r="S7" t="n">
-        <v>17.42830113503449</v>
+        <v>17.32731498090916</v>
       </c>
       <c r="T7" t="n">
-        <v>16.42101666913508</v>
+        <v>17.72762830296926</v>
       </c>
       <c r="U7" t="n">
-        <v>16.51886813542072</v>
+        <v>16.16051030346092</v>
       </c>
       <c r="V7" t="n">
-        <v>16.64290585004643</v>
+        <v>16.75751138088362</v>
       </c>
       <c r="W7" t="n">
-        <v>16.13091359912595</v>
+        <v>17.50658481263041</v>
       </c>
       <c r="X7" t="n">
-        <v>16.35733706350716</v>
+        <v>17.52307504980654</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.50188064603752</v>
+        <v>16.0792738527446</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.78739002588279</v>
+        <v>16.53752937751188</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.24594747423987</v>
+        <v>17.60916342073468</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.11924781209728</v>
+        <v>16.87215136071606</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.06670181693951</v>
+        <v>16.62585582186976</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.11604983388681</v>
+        <v>15.94003548133652</v>
       </c>
       <c r="AE7" t="n">
-        <v>17.34737338449641</v>
+        <v>16.85119718035559</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.2511978915748</v>
+        <v>16.93641969603582</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.54888051729708</v>
+        <v>16.13118893248097</v>
       </c>
       <c r="AH7" t="n">
-        <v>17.21034927301983</v>
+        <v>16.28496701272989</v>
       </c>
       <c r="AI7" t="n">
-        <v>17.68787899865261</v>
+        <v>17.47407305871601</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17.6426235902161</v>
+        <v>17.78044564580084</v>
       </c>
       <c r="AK7" t="n">
-        <v>16.55401461631365</v>
+        <v>16.39372148713688</v>
       </c>
       <c r="AL7" t="n">
-        <v>16.75362011264974</v>
+        <v>16.73491841282009</v>
       </c>
       <c r="AM7" t="n">
-        <v>16.11559428056264</v>
+        <v>17.82004135616929</v>
       </c>
       <c r="AN7" t="n">
-        <v>16.86270504369073</v>
+        <v>17.54360921665488</v>
       </c>
       <c r="AO7" t="n">
-        <v>16.61480024628734</v>
+        <v>16.9019342508561</v>
       </c>
       <c r="AP7" t="n">
-        <v>16.96531603322695</v>
+        <v>17.29625614965244</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17.26071433667871</v>
+        <v>17.53532142413348</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.88996586581528</v>
+        <v>16.76161056257239</v>
       </c>
       <c r="AS7" t="n">
-        <v>17.1414252529746</v>
+        <v>17.32487492941736</v>
       </c>
       <c r="AT7" t="n">
-        <v>16.637525724986</v>
+        <v>17.46673373219263</v>
       </c>
       <c r="AU7" t="n">
-        <v>16.84329699256181</v>
+        <v>16.04446670836784</v>
       </c>
       <c r="AV7" t="n">
-        <v>16.51472629578225</v>
+        <v>17.61949422662877</v>
       </c>
       <c r="AW7" t="n">
-        <v>16.83481116456649</v>
+        <v>17.40007474170743</v>
       </c>
       <c r="AX7" t="n">
-        <v>16.96381434682696</v>
+        <v>16.27189597888427</v>
       </c>
       <c r="AY7" t="n">
-        <v>16.67568128550751</v>
+        <v>16.60179840254566</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.86404313007043</v>
+        <v>17.31606310546199</v>
       </c>
       <c r="BA7" t="n">
-        <v>17.37273344513076</v>
+        <v>16.8001086652152</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.6328197555175</v>
+        <v>17.28489442301936</v>
       </c>
       <c r="BC7" t="n">
-        <v>16.62804172317885</v>
+        <v>16.74706867290747</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.90538912792002</v>
+        <v>17.19270785191814</v>
       </c>
       <c r="BE7" t="n">
-        <v>16.7747481289973</v>
+        <v>17.00606427381769</v>
       </c>
       <c r="BF7" t="n">
-        <v>17.25495877941963</v>
+        <v>17.50028785931022</v>
       </c>
       <c r="BG7" t="n">
-        <v>18.29503175031909</v>
+        <v>17.40651115445818</v>
       </c>
       <c r="BH7" t="n">
-        <v>17.8165293850618</v>
+        <v>16.38542535131114</v>
       </c>
       <c r="BI7" t="n">
-        <v>17.07350143131034</v>
+        <v>17.560240506909</v>
       </c>
       <c r="BJ7" t="n">
-        <v>17.39823773210299</v>
+        <v>17.26847698925102</v>
       </c>
       <c r="BK7" t="n">
-        <v>16.39377179547481</v>
+        <v>16.70404926970794</v>
       </c>
       <c r="BL7" t="n">
-        <v>17.17698866956741</v>
+        <v>17.50197758778557</v>
       </c>
       <c r="BM7" t="n">
-        <v>16.86427287527215</v>
+        <v>17.15922691018504</v>
       </c>
       <c r="BN7" t="n">
-        <v>16.29266541269762</v>
+        <v>17.35041387615583</v>
       </c>
       <c r="BO7" t="n">
-        <v>16.5332474780709</v>
+        <v>16.97239081571336</v>
       </c>
       <c r="BP7" t="n">
-        <v>18.28721289096644</v>
+        <v>17.06969094383681</v>
       </c>
       <c r="BQ7" t="n">
-        <v>17.1874777289334</v>
+        <v>17.02720610524625</v>
       </c>
       <c r="BR7" t="n">
-        <v>18.01482786913692</v>
+        <v>17.190200614759</v>
       </c>
       <c r="BS7" t="n">
-        <v>16.96925368529907</v>
+        <v>16.66851663599623</v>
       </c>
       <c r="BT7" t="n">
-        <v>16.67187868825854</v>
+        <v>17.25591620874281</v>
       </c>
       <c r="BU7" t="n">
-        <v>17.4061428965738</v>
+        <v>16.38178255408648</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.07481690547734</v>
+        <v>16.52981406127466</v>
       </c>
       <c r="BW7" t="n">
-        <v>16.52027165916142</v>
+        <v>17.27179054502723</v>
       </c>
       <c r="BX7" t="n">
-        <v>16.16341738165409</v>
+        <v>16.46731454724643</v>
       </c>
       <c r="BY7" t="n">
-        <v>17.9436655979485</v>
+        <v>16.7470966675883</v>
       </c>
       <c r="BZ7" t="n">
-        <v>16.39191857497426</v>
+        <v>16.62187554653198</v>
       </c>
       <c r="CA7" t="n">
-        <v>16.98589217502505</v>
+        <v>17.82360015266286</v>
       </c>
       <c r="CB7" t="n">
-        <v>17.00684961781122</v>
+        <v>17.02765776587749</v>
       </c>
       <c r="CC7" t="n">
-        <v>17.02604675480695</v>
+        <v>17.29376911300615</v>
       </c>
       <c r="CD7" t="n">
-        <v>18.13567515463635</v>
+        <v>16.90422029310957</v>
       </c>
       <c r="CE7" t="n">
-        <v>16.76315992266023</v>
+        <v>17.24062793449872</v>
       </c>
       <c r="CF7" t="n">
-        <v>15.8011369564843</v>
+        <v>17.50391978360722</v>
       </c>
       <c r="CG7" t="n">
-        <v>16.80871689318708</v>
+        <v>16.82896489881962</v>
       </c>
       <c r="CH7" t="n">
-        <v>17.21743541843687</v>
+        <v>16.85440068335157</v>
       </c>
       <c r="CI7" t="n">
-        <v>17.21040139609095</v>
+        <v>18.27308705993811</v>
       </c>
       <c r="CJ7" t="n">
-        <v>16.67939871065041</v>
+        <v>16.75469977532517</v>
       </c>
       <c r="CK7" t="n">
-        <v>17.54256728924696</v>
+        <v>17.31720711152299</v>
       </c>
       <c r="CL7" t="n">
-        <v>17.71366935829456</v>
+        <v>17.31884890908792</v>
       </c>
       <c r="CM7" t="n">
-        <v>16.59758747909856</v>
+        <v>16.66116483678963</v>
       </c>
       <c r="CN7" t="n">
-        <v>16.85592034143142</v>
+        <v>16.87847531069296</v>
       </c>
       <c r="CO7" t="n">
-        <v>16.69280432573409</v>
+        <v>16.39596030321665</v>
       </c>
       <c r="CP7" t="n">
-        <v>16.74353451619768</v>
+        <v>16.35284322207123</v>
       </c>
       <c r="CQ7" t="n">
-        <v>17.20281057444349</v>
+        <v>16.25409762458104</v>
       </c>
       <c r="CR7" t="n">
-        <v>16.41034007908803</v>
+        <v>16.78239313944121</v>
       </c>
       <c r="CS7" t="n">
-        <v>16.47513654208548</v>
+        <v>17.17877064788816</v>
       </c>
       <c r="CT7" t="n">
-        <v>16.82451740187085</v>
+        <v>17.61912737880871</v>
       </c>
       <c r="CU7" t="n">
-        <v>17.28569221054456</v>
+        <v>17.36004611972881</v>
       </c>
       <c r="CV7" t="n">
-        <v>16.68344276799888</v>
+        <v>17.02621189707829</v>
       </c>
       <c r="CW7" t="n">
-        <v>17.43792451604282</v>
+        <v>17.33203429676088</v>
       </c>
       <c r="CX7" t="n">
-        <v>16.95544162432452</v>
+        <v>17.04091080727586</v>
       </c>
     </row>
     <row r="8">
@@ -2793,307 +2793,307 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.1069180313899</v>
+        <v>12.3464523864813</v>
       </c>
       <c r="C8" t="n">
-        <v>12.59060574778105</v>
+        <v>12.32576494343418</v>
       </c>
       <c r="D8" t="n">
-        <v>11.82449980602403</v>
+        <v>12.66995615522553</v>
       </c>
       <c r="E8" t="n">
-        <v>12.39748908642182</v>
+        <v>12.69058541462346</v>
       </c>
       <c r="F8" t="n">
-        <v>11.25022520974554</v>
+        <v>12.03600975679925</v>
       </c>
       <c r="G8" t="n">
-        <v>11.80808163647029</v>
+        <v>12.80478229055452</v>
       </c>
       <c r="H8" t="n">
-        <v>11.61483766148571</v>
+        <v>12.72852570820175</v>
       </c>
       <c r="I8" t="n">
-        <v>11.70045047678393</v>
+        <v>12.63537761027703</v>
       </c>
       <c r="J8" t="n">
-        <v>12.09450334772709</v>
+        <v>11.07283745604422</v>
       </c>
       <c r="K8" t="n">
-        <v>12.04742297112946</v>
+        <v>12.39744860352455</v>
       </c>
       <c r="L8" t="n">
-        <v>11.53263770553573</v>
+        <v>12.99884033469219</v>
       </c>
       <c r="M8" t="n">
-        <v>12.15723270669371</v>
+        <v>11.2480416440493</v>
       </c>
       <c r="N8" t="n">
-        <v>11.80961198142143</v>
+        <v>11.56456595411646</v>
       </c>
       <c r="O8" t="n">
-        <v>11.42201137942709</v>
+        <v>11.15996690704012</v>
       </c>
       <c r="P8" t="n">
-        <v>12.59298513802442</v>
+        <v>12.47775875958495</v>
       </c>
       <c r="Q8" t="n">
-        <v>12.29942604794259</v>
+        <v>13.08072891139706</v>
       </c>
       <c r="R8" t="n">
-        <v>12.27011119704112</v>
+        <v>12.61407673931074</v>
       </c>
       <c r="S8" t="n">
-        <v>12.39550018486002</v>
+        <v>12.35025724407251</v>
       </c>
       <c r="T8" t="n">
-        <v>11.48392338928973</v>
+        <v>12.76671627375829</v>
       </c>
       <c r="U8" t="n">
-        <v>11.62627315293227</v>
+        <v>11.26954984032954</v>
       </c>
       <c r="V8" t="n">
-        <v>11.74147360730209</v>
+        <v>11.88346433910772</v>
       </c>
       <c r="W8" t="n">
-        <v>11.30298782092619</v>
+        <v>12.55053298013694</v>
       </c>
       <c r="X8" t="n">
-        <v>11.38471880682866</v>
+        <v>12.69391965616249</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.61747828503678</v>
+        <v>11.13322089158586</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.92917513529605</v>
+        <v>11.7164423783008</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.34176165256182</v>
+        <v>12.69532342636543</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.31934021864597</v>
+        <v>12.02172555822257</v>
       </c>
       <c r="AC8" t="n">
-        <v>13.23181957483364</v>
+        <v>11.82230648154583</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.2421875903757</v>
+        <v>10.90472752752505</v>
       </c>
       <c r="AE8" t="n">
-        <v>12.24599453992754</v>
+        <v>12.02037117114526</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.35995884030517</v>
+        <v>12.22115845610291</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.80614893742574</v>
+        <v>11.22863452422502</v>
       </c>
       <c r="AH8" t="n">
-        <v>12.29361023322159</v>
+        <v>11.45507079826103</v>
       </c>
       <c r="AI8" t="n">
-        <v>12.90896228656501</v>
+        <v>12.65182707616596</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12.85779092761112</v>
+        <v>12.83072803436326</v>
       </c>
       <c r="AK8" t="n">
-        <v>11.67311442715869</v>
+        <v>11.60455046005277</v>
       </c>
       <c r="AL8" t="n">
-        <v>11.84578915634216</v>
+        <v>11.88049933713786</v>
       </c>
       <c r="AM8" t="n">
-        <v>11.31815136874893</v>
+        <v>12.99007270899478</v>
       </c>
       <c r="AN8" t="n">
-        <v>11.89491662854298</v>
+        <v>12.7086501222421</v>
       </c>
       <c r="AO8" t="n">
-        <v>11.69067386385171</v>
+        <v>11.96728635977372</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.93103180175917</v>
+        <v>12.52054389426345</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.22229347629329</v>
+        <v>12.72815471666262</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.886959143501</v>
+        <v>12.12831441267399</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.28031046832717</v>
+        <v>12.43816718256617</v>
       </c>
       <c r="AT8" t="n">
-        <v>11.86336855420045</v>
+        <v>12.4645871594578</v>
       </c>
       <c r="AU8" t="n">
-        <v>11.93071098441451</v>
+        <v>11.32858588468558</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.55433663341401</v>
+        <v>12.53396954494029</v>
       </c>
       <c r="AW8" t="n">
-        <v>12.09189740068816</v>
+        <v>12.46397089477504</v>
       </c>
       <c r="AX8" t="n">
-        <v>12.07567597671577</v>
+        <v>11.38761647186286</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.9164165116566</v>
+        <v>11.82968179520379</v>
       </c>
       <c r="AZ8" t="n">
-        <v>13.03253917042902</v>
+        <v>12.48933632551974</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.47075336155156</v>
+        <v>12.00217106974471</v>
       </c>
       <c r="BB8" t="n">
-        <v>11.65924781402525</v>
+        <v>12.49971977661183</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.79158024073563</v>
+        <v>11.81011448909116</v>
       </c>
       <c r="BD8" t="n">
-        <v>12.20883072900821</v>
+        <v>12.38875909185302</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.90481350542427</v>
+        <v>11.97346087748419</v>
       </c>
       <c r="BF8" t="n">
-        <v>12.5169137622045</v>
+        <v>12.62084816261441</v>
       </c>
       <c r="BG8" t="n">
-        <v>13.56401169709463</v>
+        <v>12.46897008867619</v>
       </c>
       <c r="BH8" t="n">
-        <v>12.81526893262329</v>
+        <v>11.49704544489196</v>
       </c>
       <c r="BI8" t="n">
-        <v>12.33966967333823</v>
+        <v>12.55932571184203</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.45392366336231</v>
+        <v>12.37360469186732</v>
       </c>
       <c r="BK8" t="n">
-        <v>11.41340638850913</v>
+        <v>11.78010395012527</v>
       </c>
       <c r="BL8" t="n">
-        <v>12.27295741268331</v>
+        <v>12.52040085343166</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.98860579350472</v>
+        <v>12.21308300406579</v>
       </c>
       <c r="BN8" t="n">
-        <v>11.33381939247996</v>
+        <v>12.39999279998119</v>
       </c>
       <c r="BO8" t="n">
-        <v>11.90388711726509</v>
+        <v>11.97523729115361</v>
       </c>
       <c r="BP8" t="n">
-        <v>13.45453350650326</v>
+        <v>12.16779442317222</v>
       </c>
       <c r="BQ8" t="n">
-        <v>12.43388142107196</v>
+        <v>12.14408111046973</v>
       </c>
       <c r="BR8" t="n">
-        <v>13.13200942900986</v>
+        <v>12.28243568265255</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.98030400738747</v>
+        <v>11.82232222160727</v>
       </c>
       <c r="BT8" t="n">
-        <v>11.93910144346296</v>
+        <v>12.59970292468783</v>
       </c>
       <c r="BU8" t="n">
-        <v>12.5906034247376</v>
+        <v>11.55256404597541</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.23277871845351</v>
+        <v>11.80253456737764</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.80716328103916</v>
+        <v>12.28505987220295</v>
       </c>
       <c r="BX8" t="n">
-        <v>11.14619942340187</v>
+        <v>11.62710418541893</v>
       </c>
       <c r="BY8" t="n">
-        <v>12.98958437896165</v>
+        <v>12.02122766676188</v>
       </c>
       <c r="BZ8" t="n">
-        <v>11.42562331876023</v>
+        <v>11.7520541020339</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.0225380281218</v>
+        <v>12.96017132902091</v>
       </c>
       <c r="CB8" t="n">
-        <v>11.97441229029209</v>
+        <v>12.1318108180056</v>
       </c>
       <c r="CC8" t="n">
-        <v>12.39146136144908</v>
+        <v>12.4576779775842</v>
       </c>
       <c r="CD8" t="n">
-        <v>13.19254751082194</v>
+        <v>11.94658196292316</v>
       </c>
       <c r="CE8" t="n">
-        <v>12.08250263909028</v>
+        <v>12.36722742267023</v>
       </c>
       <c r="CF8" t="n">
-        <v>11.08305968388326</v>
+        <v>12.59367726207039</v>
       </c>
       <c r="CG8" t="n">
-        <v>11.92551706437828</v>
+        <v>12.04754999473029</v>
       </c>
       <c r="CH8" t="n">
-        <v>12.23609146843359</v>
+        <v>11.99187397859076</v>
       </c>
       <c r="CI8" t="n">
-        <v>12.19868729410637</v>
+        <v>13.21157183824926</v>
       </c>
       <c r="CJ8" t="n">
-        <v>11.71691121987025</v>
+        <v>11.87346871253857</v>
       </c>
       <c r="CK8" t="n">
-        <v>12.61826571266139</v>
+        <v>12.4875000457698</v>
       </c>
       <c r="CL8" t="n">
-        <v>12.7732952966882</v>
+        <v>12.38549958433735</v>
       </c>
       <c r="CM8" t="n">
-        <v>11.81456636448019</v>
+        <v>11.7606800345097</v>
       </c>
       <c r="CN8" t="n">
-        <v>11.98344337316755</v>
+        <v>12.0023891981319</v>
       </c>
       <c r="CO8" t="n">
-        <v>11.91170435501922</v>
+        <v>11.58603849840859</v>
       </c>
       <c r="CP8" t="n">
-        <v>11.96220679583439</v>
+        <v>11.48466145276828</v>
       </c>
       <c r="CQ8" t="n">
-        <v>12.47054202871653</v>
+        <v>11.22685105895166</v>
       </c>
       <c r="CR8" t="n">
-        <v>11.52816933950696</v>
+        <v>11.79294374928671</v>
       </c>
       <c r="CS8" t="n">
-        <v>11.80141923606191</v>
+        <v>12.46229042376149</v>
       </c>
       <c r="CT8" t="n">
-        <v>11.97501239080921</v>
+        <v>12.63897877830554</v>
       </c>
       <c r="CU8" t="n">
-        <v>12.33771463246065</v>
+        <v>12.43491979142257</v>
       </c>
       <c r="CV8" t="n">
-        <v>11.74223435613655</v>
+        <v>11.9842097147066</v>
       </c>
       <c r="CW8" t="n">
-        <v>12.64673327793048</v>
+        <v>12.56090606421266</v>
       </c>
       <c r="CX8" t="n">
-        <v>12.08974848437554</v>
+        <v>12.16060881300296</v>
       </c>
     </row>
     <row r="9">
@@ -3101,307 +3101,307 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.1839993062085</v>
+        <v>14.35266260537566</v>
       </c>
       <c r="C9" t="n">
-        <v>14.72523469226784</v>
+        <v>14.31649803606611</v>
       </c>
       <c r="D9" t="n">
-        <v>13.99495455531426</v>
+        <v>14.79317248829323</v>
       </c>
       <c r="E9" t="n">
-        <v>14.57536464969152</v>
+        <v>14.79876755907192</v>
       </c>
       <c r="F9" t="n">
-        <v>12.90532477842768</v>
+        <v>14.08976158036006</v>
       </c>
       <c r="G9" t="n">
-        <v>13.6657274927538</v>
+        <v>14.98106079263704</v>
       </c>
       <c r="H9" t="n">
-        <v>13.42134119042135</v>
+        <v>14.75678905410541</v>
       </c>
       <c r="I9" t="n">
-        <v>13.61940929735869</v>
+        <v>14.93380536009378</v>
       </c>
       <c r="J9" t="n">
-        <v>14.16930073905788</v>
+        <v>12.91457020224563</v>
       </c>
       <c r="K9" t="n">
-        <v>13.94919311564339</v>
+        <v>14.58214569465878</v>
       </c>
       <c r="L9" t="n">
-        <v>13.31142818267135</v>
+        <v>15.28716320125054</v>
       </c>
       <c r="M9" t="n">
-        <v>14.07217779744709</v>
+        <v>13.03246091604858</v>
       </c>
       <c r="N9" t="n">
-        <v>13.52233709318798</v>
+        <v>13.50391085707053</v>
       </c>
       <c r="O9" t="n">
-        <v>13.21124854909069</v>
+        <v>12.93267138337416</v>
       </c>
       <c r="P9" t="n">
-        <v>14.93483329536723</v>
+        <v>14.71657544701841</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.53046803154389</v>
+        <v>15.33588012769989</v>
       </c>
       <c r="R9" t="n">
-        <v>14.37732123358069</v>
+        <v>14.72578616028443</v>
       </c>
       <c r="S9" t="n">
-        <v>14.50729171932011</v>
+        <v>14.39724309401422</v>
       </c>
       <c r="T9" t="n">
-        <v>13.33784285263729</v>
+        <v>15.1035863256428</v>
       </c>
       <c r="U9" t="n">
-        <v>13.54142253022751</v>
+        <v>13.02868170943536</v>
       </c>
       <c r="V9" t="n">
-        <v>13.50772678814405</v>
+        <v>13.83604356223687</v>
       </c>
       <c r="W9" t="n">
-        <v>13.08683375520286</v>
+        <v>14.61116841891138</v>
       </c>
       <c r="X9" t="n">
-        <v>13.05123985426432</v>
+        <v>14.83277397941703</v>
       </c>
       <c r="Y9" t="n">
-        <v>13.59174248998438</v>
+        <v>12.81108392282449</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.87497670645144</v>
+        <v>13.68970967944229</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.41370817833022</v>
+        <v>14.87792003440779</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.34690993502756</v>
+        <v>14.0571794598148</v>
       </c>
       <c r="AC9" t="n">
-        <v>15.61842696210103</v>
+        <v>13.81100459104926</v>
       </c>
       <c r="AD9" t="n">
-        <v>14.41534337292781</v>
+        <v>12.40708472027844</v>
       </c>
       <c r="AE9" t="n">
-        <v>14.28193148681664</v>
+        <v>14.09195385891351</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.45851497916376</v>
+        <v>14.31322743375118</v>
       </c>
       <c r="AG9" t="n">
-        <v>13.79705409010714</v>
+        <v>12.93642419594474</v>
       </c>
       <c r="AH9" t="n">
-        <v>14.28800823741737</v>
+        <v>13.36078183823551</v>
       </c>
       <c r="AI9" t="n">
-        <v>15.16803638541236</v>
+        <v>14.89248936824549</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.08767081932395</v>
+        <v>15.11010242091962</v>
       </c>
       <c r="AK9" t="n">
-        <v>13.49797296408422</v>
+        <v>13.48542112070038</v>
       </c>
       <c r="AL9" t="n">
-        <v>14.00327171714791</v>
+        <v>13.92607100853347</v>
       </c>
       <c r="AM9" t="n">
-        <v>13.1861423439361</v>
+        <v>15.35385147793904</v>
       </c>
       <c r="AN9" t="n">
-        <v>13.92326798902615</v>
+        <v>14.84180734193199</v>
       </c>
       <c r="AO9" t="n">
-        <v>13.54794977288804</v>
+        <v>13.90981816425785</v>
       </c>
       <c r="AP9" t="n">
-        <v>13.95222309602014</v>
+        <v>14.73738058118207</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.22551504709758</v>
+        <v>14.95895812971555</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.86851522399427</v>
+        <v>14.24132590776575</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.25439316159765</v>
+        <v>14.5286825930221</v>
       </c>
       <c r="AT9" t="n">
-        <v>14.04808946753867</v>
+        <v>14.47181556586998</v>
       </c>
       <c r="AU9" t="n">
-        <v>13.8546269888154</v>
+        <v>13.35311247701245</v>
       </c>
       <c r="AV9" t="n">
-        <v>13.38904947593151</v>
+        <v>14.72931850493181</v>
       </c>
       <c r="AW9" t="n">
-        <v>14.22953331448206</v>
+        <v>14.73433890545539</v>
       </c>
       <c r="AX9" t="n">
-        <v>14.17561139680376</v>
+        <v>13.1751231785641</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.86733566777766</v>
+        <v>13.94202865441597</v>
       </c>
       <c r="AZ9" t="n">
-        <v>15.41319212827735</v>
+        <v>14.8485461016331</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.65303562754416</v>
+        <v>14.04513014658832</v>
       </c>
       <c r="BB9" t="n">
-        <v>13.5401751252285</v>
+        <v>14.75897138495477</v>
       </c>
       <c r="BC9" t="n">
-        <v>13.61039604353821</v>
+        <v>13.80432880829429</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.33899185073519</v>
+        <v>14.5869031286549</v>
       </c>
       <c r="BE9" t="n">
-        <v>13.81024636206747</v>
+        <v>13.84704039853704</v>
       </c>
       <c r="BF9" t="n">
-        <v>14.6928404417552</v>
+        <v>14.68001113302778</v>
       </c>
       <c r="BG9" t="n">
-        <v>16.04213101572445</v>
+        <v>14.60288192810112</v>
       </c>
       <c r="BH9" t="n">
-        <v>14.92010251316035</v>
+        <v>13.32270108975768</v>
       </c>
       <c r="BI9" t="n">
-        <v>14.49394700191383</v>
+        <v>14.69330630610564</v>
       </c>
       <c r="BJ9" t="n">
-        <v>14.51611539551464</v>
+        <v>14.35439925226173</v>
       </c>
       <c r="BK9" t="n">
-        <v>13.17146385674023</v>
+        <v>13.71907854386249</v>
       </c>
       <c r="BL9" t="n">
-        <v>14.20210210233142</v>
+        <v>14.55889215981428</v>
       </c>
       <c r="BM9" t="n">
-        <v>14.01664179257691</v>
+        <v>14.08051335746534</v>
       </c>
       <c r="BN9" t="n">
-        <v>13.12724536306161</v>
+        <v>14.44138535617109</v>
       </c>
       <c r="BO9" t="n">
-        <v>13.98991619123258</v>
+        <v>13.89735213504288</v>
       </c>
       <c r="BP9" t="n">
-        <v>15.91042917951659</v>
+        <v>14.30772048196099</v>
       </c>
       <c r="BQ9" t="n">
-        <v>14.56196933170221</v>
+        <v>14.22461496270739</v>
       </c>
       <c r="BR9" t="n">
-        <v>15.42970655529429</v>
+        <v>14.25023913876768</v>
       </c>
       <c r="BS9" t="n">
-        <v>13.9441310604934</v>
+        <v>13.89188338639288</v>
       </c>
       <c r="BT9" t="n">
-        <v>13.97472544978616</v>
+        <v>14.97930411117633</v>
       </c>
       <c r="BU9" t="n">
-        <v>14.75554738555143</v>
+        <v>13.43206005570349</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.38914546314544</v>
+        <v>13.74408241473418</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.92437079736994</v>
+        <v>14.2114879368105</v>
       </c>
       <c r="BX9" t="n">
-        <v>12.88319057709796</v>
+        <v>13.53674068670669</v>
       </c>
       <c r="BY9" t="n">
-        <v>15.24210984520019</v>
+        <v>14.01608919658159</v>
       </c>
       <c r="BZ9" t="n">
-        <v>13.26452004645124</v>
+        <v>13.72845269369951</v>
       </c>
       <c r="CA9" t="n">
-        <v>14.00041132229816</v>
+        <v>15.13081491749135</v>
       </c>
       <c r="CB9" t="n">
-        <v>13.87884470386462</v>
+        <v>14.10349521329312</v>
       </c>
       <c r="CC9" t="n">
-        <v>14.79171058813401</v>
+        <v>14.66267825048494</v>
       </c>
       <c r="CD9" t="n">
-        <v>15.55158750479492</v>
+        <v>13.98464318008625</v>
       </c>
       <c r="CE9" t="n">
-        <v>14.19197500841178</v>
+        <v>14.43562156573144</v>
       </c>
       <c r="CF9" t="n">
-        <v>12.98720083812886</v>
+        <v>14.67829797762048</v>
       </c>
       <c r="CG9" t="n">
-        <v>13.77211707661484</v>
+        <v>13.98185090285089</v>
       </c>
       <c r="CH9" t="n">
-        <v>14.32618913712943</v>
+        <v>14.1263972765019</v>
       </c>
       <c r="CI9" t="n">
-        <v>14.22793199807519</v>
+        <v>15.55174348622528</v>
       </c>
       <c r="CJ9" t="n">
-        <v>13.49946124466364</v>
+        <v>13.74195766436777</v>
       </c>
       <c r="CK9" t="n">
-        <v>14.72797208158124</v>
+        <v>14.66624359112332</v>
       </c>
       <c r="CL9" t="n">
-        <v>14.95710970814628</v>
+        <v>14.36966479572066</v>
       </c>
       <c r="CM9" t="n">
-        <v>13.71126971770436</v>
+        <v>13.60197384900398</v>
       </c>
       <c r="CN9" t="n">
-        <v>13.96997484182711</v>
+        <v>13.97490994991947</v>
       </c>
       <c r="CO9" t="n">
-        <v>13.81004143706456</v>
+        <v>13.55316613753095</v>
       </c>
       <c r="CP9" t="n">
-        <v>13.94233208619158</v>
+        <v>13.3277969373099</v>
       </c>
       <c r="CQ9" t="n">
-        <v>14.68193660515367</v>
+        <v>12.90668277003185</v>
       </c>
       <c r="CR9" t="n">
-        <v>13.43151231395474</v>
+        <v>13.73240150842119</v>
       </c>
       <c r="CS9" t="n">
-        <v>13.83735780221864</v>
+        <v>14.73407727787267</v>
       </c>
       <c r="CT9" t="n">
-        <v>13.86080588514927</v>
+        <v>14.76674176744188</v>
       </c>
       <c r="CU9" t="n">
-        <v>14.44480413232186</v>
+        <v>14.3992079654694</v>
       </c>
       <c r="CV9" t="n">
-        <v>13.66816747426418</v>
+        <v>13.92127181190416</v>
       </c>
       <c r="CW9" t="n">
-        <v>14.77266313737445</v>
+        <v>14.68462076080824</v>
       </c>
       <c r="CX9" t="n">
-        <v>14.11429607918114</v>
+        <v>14.20211569543162</v>
       </c>
     </row>
     <row r="10">
@@ -3409,307 +3409,307 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16.49564226603263</v>
+        <v>16.54638814960526</v>
       </c>
       <c r="C10" t="n">
-        <v>16.94928402258739</v>
+        <v>16.4770383853013</v>
       </c>
       <c r="D10" t="n">
-        <v>16.32789795038132</v>
+        <v>16.9686946088239</v>
       </c>
       <c r="E10" t="n">
-        <v>16.91007270615456</v>
+        <v>17.173055425793</v>
       </c>
       <c r="F10" t="n">
-        <v>14.83250828808762</v>
+        <v>16.36939513044033</v>
       </c>
       <c r="G10" t="n">
-        <v>15.6717665063614</v>
+        <v>17.3885533571835</v>
       </c>
       <c r="H10" t="n">
-        <v>15.41285713580788</v>
+        <v>16.92881268159161</v>
       </c>
       <c r="I10" t="n">
-        <v>15.68674868713105</v>
+        <v>17.43018482154963</v>
       </c>
       <c r="J10" t="n">
-        <v>16.45386916990655</v>
+        <v>15.02542634168089</v>
       </c>
       <c r="K10" t="n">
-        <v>16.10394198701576</v>
+        <v>16.96650211151913</v>
       </c>
       <c r="L10" t="n">
-        <v>15.29951875546506</v>
+        <v>17.70845690287893</v>
       </c>
       <c r="M10" t="n">
-        <v>16.16563256575963</v>
+        <v>14.97546380339087</v>
       </c>
       <c r="N10" t="n">
-        <v>15.40048526919839</v>
+        <v>15.60273786151087</v>
       </c>
       <c r="O10" t="n">
-        <v>15.19564652362923</v>
+        <v>15.00572195436386</v>
       </c>
       <c r="P10" t="n">
-        <v>17.61707714036834</v>
+        <v>17.19952061170209</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.82797180163895</v>
+        <v>17.69840084982416</v>
       </c>
       <c r="R10" t="n">
-        <v>16.70565222290853</v>
+        <v>17.05510825027532</v>
       </c>
       <c r="S10" t="n">
-        <v>16.74189901043687</v>
+        <v>16.69886035870831</v>
       </c>
       <c r="T10" t="n">
-        <v>15.26355512443604</v>
+        <v>17.58182762238041</v>
       </c>
       <c r="U10" t="n">
-        <v>15.71546454978317</v>
+        <v>15.05899165504491</v>
       </c>
       <c r="V10" t="n">
-        <v>15.49479913129872</v>
+        <v>15.88488951693985</v>
       </c>
       <c r="W10" t="n">
-        <v>15.05755725582559</v>
+        <v>16.83167766234221</v>
       </c>
       <c r="X10" t="n">
-        <v>14.90782601386791</v>
+        <v>17.12578914160122</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.70385083957973</v>
+        <v>14.68775851027494</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.95280533460556</v>
+        <v>15.88988878194443</v>
       </c>
       <c r="AA10" t="n">
-        <v>16.64481633396279</v>
+        <v>17.20409680760021</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.57732596524366</v>
+        <v>16.2586175293822</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.32610740185899</v>
+        <v>15.95583486987152</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.7098844127232</v>
+        <v>14.15633211176235</v>
       </c>
       <c r="AE10" t="n">
-        <v>16.42784457349479</v>
+        <v>16.26183141208283</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.7905525947339</v>
+        <v>16.64858748315902</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.05133814453597</v>
+        <v>14.79863542648817</v>
       </c>
       <c r="AH10" t="n">
-        <v>16.46432904272995</v>
+        <v>15.4667362063345</v>
       </c>
       <c r="AI10" t="n">
-        <v>17.68881241166393</v>
+        <v>17.3242661335234</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.54210128586524</v>
+        <v>17.63248413105696</v>
       </c>
       <c r="AK10" t="n">
-        <v>15.63606668685934</v>
+        <v>15.48367942956276</v>
       </c>
       <c r="AL10" t="n">
-        <v>16.43065702723262</v>
+        <v>16.11848000452729</v>
       </c>
       <c r="AM10" t="n">
-        <v>15.26823682581755</v>
+        <v>17.78112408848345</v>
       </c>
       <c r="AN10" t="n">
-        <v>16.06840250025706</v>
+        <v>17.17430943107707</v>
       </c>
       <c r="AO10" t="n">
-        <v>15.64437830407937</v>
+        <v>16.03471265315219</v>
       </c>
       <c r="AP10" t="n">
-        <v>16.16909638199188</v>
+        <v>17.20232161586798</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16.27218574469534</v>
+        <v>17.42016371749058</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.93857493449372</v>
+        <v>16.64477411082207</v>
       </c>
       <c r="AS10" t="n">
-        <v>16.45413205621967</v>
+        <v>16.78124054753675</v>
       </c>
       <c r="AT10" t="n">
-        <v>16.4136837417076</v>
+        <v>16.59713481063527</v>
       </c>
       <c r="AU10" t="n">
-        <v>15.89504411508274</v>
+        <v>15.54112556372191</v>
       </c>
       <c r="AV10" t="n">
-        <v>15.40556835510169</v>
+        <v>17.12281026791613</v>
       </c>
       <c r="AW10" t="n">
-        <v>16.53314717149401</v>
+        <v>17.14523990504136</v>
       </c>
       <c r="AX10" t="n">
-        <v>16.48220196268595</v>
+        <v>15.25522464693188</v>
       </c>
       <c r="AY10" t="n">
-        <v>15.9033567255464</v>
+        <v>16.25252932740671</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.93462522422881</v>
+        <v>17.49088212640508</v>
       </c>
       <c r="BA10" t="n">
-        <v>16.98214503090706</v>
+        <v>16.38383079735338</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.60258449840219</v>
+        <v>17.19702326814243</v>
       </c>
       <c r="BC10" t="n">
-        <v>15.64891992826647</v>
+        <v>16.03835466476334</v>
       </c>
       <c r="BD10" t="n">
-        <v>16.66251086050573</v>
+        <v>16.84795050821043</v>
       </c>
       <c r="BE10" t="n">
-        <v>15.90472285962244</v>
+        <v>15.85396589288896</v>
       </c>
       <c r="BF10" t="n">
-        <v>17.06405948973459</v>
+        <v>16.8502235287385</v>
       </c>
       <c r="BG10" t="n">
-        <v>18.74667936383931</v>
+        <v>16.88023726706736</v>
       </c>
       <c r="BH10" t="n">
-        <v>17.25158651610136</v>
+        <v>15.30986373977897</v>
       </c>
       <c r="BI10" t="n">
-        <v>16.86666659863285</v>
+        <v>16.92496243101238</v>
       </c>
       <c r="BJ10" t="n">
-        <v>16.76205694278636</v>
+        <v>16.52671616132903</v>
       </c>
       <c r="BK10" t="n">
-        <v>15.06611065049871</v>
+        <v>15.7684906631988</v>
       </c>
       <c r="BL10" t="n">
-        <v>16.31269789465892</v>
+        <v>16.68887786009424</v>
       </c>
       <c r="BM10" t="n">
-        <v>16.21999349806921</v>
+        <v>16.01027534315542</v>
       </c>
       <c r="BN10" t="n">
-        <v>15.07112148993792</v>
+        <v>16.62158510088837</v>
       </c>
       <c r="BO10" t="n">
-        <v>16.20718196065918</v>
+        <v>16.11203775290263</v>
       </c>
       <c r="BP10" t="n">
-        <v>18.42333566869041</v>
+        <v>16.74127700776206</v>
       </c>
       <c r="BQ10" t="n">
-        <v>16.81551060100714</v>
+        <v>16.47412846486066</v>
       </c>
       <c r="BR10" t="n">
-        <v>17.84164994741455</v>
+        <v>16.3625832794697</v>
       </c>
       <c r="BS10" t="n">
-        <v>16.09591128393622</v>
+        <v>16.098072844563</v>
       </c>
       <c r="BT10" t="n">
-        <v>16.24318047829703</v>
+        <v>17.50746665688097</v>
       </c>
       <c r="BU10" t="n">
-        <v>17.15651142601871</v>
+        <v>15.52270418674964</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.86553702661043</v>
+        <v>15.80711640366937</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.19968725843032</v>
+        <v>16.38340254890979</v>
       </c>
       <c r="BX10" t="n">
-        <v>14.86308466364246</v>
+        <v>15.66834062630243</v>
       </c>
       <c r="BY10" t="n">
-        <v>17.59951262360361</v>
+        <v>16.23125803758485</v>
       </c>
       <c r="BZ10" t="n">
-        <v>15.33660410782471</v>
+        <v>15.88406058001414</v>
       </c>
       <c r="CA10" t="n">
-        <v>16.22927294586859</v>
+        <v>17.54183026522051</v>
       </c>
       <c r="CB10" t="n">
-        <v>15.91397572957256</v>
+        <v>16.27599705657979</v>
       </c>
       <c r="CC10" t="n">
-        <v>17.27423719678428</v>
+        <v>17.104034531814</v>
       </c>
       <c r="CD10" t="n">
-        <v>18.02003493439618</v>
+        <v>16.13282427127411</v>
       </c>
       <c r="CE10" t="n">
-        <v>16.6392744425597</v>
+        <v>16.80158303153887</v>
       </c>
       <c r="CF10" t="n">
-        <v>15.1007122876532</v>
+        <v>16.92135454978803</v>
       </c>
       <c r="CG10" t="n">
-        <v>15.71103030187078</v>
+        <v>16.16232454842432</v>
       </c>
       <c r="CH10" t="n">
-        <v>16.69676142105604</v>
+        <v>16.48903313097479</v>
       </c>
       <c r="CI10" t="n">
-        <v>16.49003139336677</v>
+        <v>18.17650348067787</v>
       </c>
       <c r="CJ10" t="n">
-        <v>15.38435424424923</v>
+        <v>15.71123114573552</v>
       </c>
       <c r="CK10" t="n">
-        <v>16.97202210849002</v>
+        <v>16.86818257980487</v>
       </c>
       <c r="CL10" t="n">
-        <v>17.29249161809864</v>
+        <v>16.56094280805312</v>
       </c>
       <c r="CM10" t="n">
-        <v>15.81982054367196</v>
+        <v>15.67404812219808</v>
       </c>
       <c r="CN10" t="n">
-        <v>16.1967397819952</v>
+        <v>16.12553323168006</v>
       </c>
       <c r="CO10" t="n">
-        <v>15.88037664133308</v>
+        <v>15.67619507657416</v>
       </c>
       <c r="CP10" t="n">
-        <v>16.09163247390412</v>
+        <v>15.39717522607598</v>
       </c>
       <c r="CQ10" t="n">
-        <v>17.02333257427175</v>
+        <v>14.69040280750722</v>
       </c>
       <c r="CR10" t="n">
-        <v>15.59449863340672</v>
+        <v>15.83089017040672</v>
       </c>
       <c r="CS10" t="n">
-        <v>16.20032905107414</v>
+        <v>17.09860015632487</v>
       </c>
       <c r="CT10" t="n">
-        <v>15.94147590239116</v>
+        <v>17.10116945252591</v>
       </c>
       <c r="CU10" t="n">
-        <v>16.73337705489426</v>
+        <v>16.5161047131729</v>
       </c>
       <c r="CV10" t="n">
-        <v>15.78792042013852</v>
+        <v>15.94144803409066</v>
       </c>
       <c r="CW10" t="n">
-        <v>17.07509848854116</v>
+        <v>16.90035247354344</v>
       </c>
       <c r="CX10" t="n">
-        <v>16.3244516304026</v>
+        <v>16.42424885334787</v>
       </c>
     </row>
     <row r="11">
@@ -3717,307 +3717,307 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>18.82086757215171</v>
+        <v>19.00786798477715</v>
       </c>
       <c r="C11" t="n">
-        <v>19.31355318426501</v>
+        <v>18.70224909110548</v>
       </c>
       <c r="D11" t="n">
-        <v>18.82125755910542</v>
+        <v>19.32367341136189</v>
       </c>
       <c r="E11" t="n">
-        <v>19.31613404003134</v>
+        <v>19.57178319139215</v>
       </c>
       <c r="F11" t="n">
-        <v>16.85230467308054</v>
+        <v>18.74516876845564</v>
       </c>
       <c r="G11" t="n">
-        <v>17.8096421733784</v>
+        <v>19.94425355855649</v>
       </c>
       <c r="H11" t="n">
-        <v>17.55379793403965</v>
+        <v>19.21355205342945</v>
       </c>
       <c r="I11" t="n">
-        <v>17.887981759761</v>
+        <v>20.16369427818715</v>
       </c>
       <c r="J11" t="n">
-        <v>18.84392792046026</v>
+        <v>17.34942715306169</v>
       </c>
       <c r="K11" t="n">
-        <v>18.34273211392521</v>
+        <v>19.48888352481007</v>
       </c>
       <c r="L11" t="n">
-        <v>17.32282045127672</v>
+        <v>20.22052171369004</v>
       </c>
       <c r="M11" t="n">
-        <v>18.43823600986452</v>
+        <v>17.09547834274289</v>
       </c>
       <c r="N11" t="n">
-        <v>17.45661531747037</v>
+        <v>17.85393732595527</v>
       </c>
       <c r="O11" t="n">
-        <v>17.2889215617805</v>
+        <v>17.13095905958399</v>
       </c>
       <c r="P11" t="n">
-        <v>20.36400666419464</v>
+        <v>19.84990393022214</v>
       </c>
       <c r="Q11" t="n">
-        <v>19.20847195323452</v>
+        <v>20.16965746872936</v>
       </c>
       <c r="R11" t="n">
-        <v>19.24154769225247</v>
+        <v>19.58065750436666</v>
       </c>
       <c r="S11" t="n">
-        <v>19.03622944582145</v>
+        <v>19.12070309477961</v>
       </c>
       <c r="T11" t="n">
-        <v>17.38079378937378</v>
+        <v>20.16380085818956</v>
       </c>
       <c r="U11" t="n">
-        <v>17.95441997732045</v>
+        <v>17.26908128045326</v>
       </c>
       <c r="V11" t="n">
-        <v>17.59974794069981</v>
+        <v>18.07856221201568</v>
       </c>
       <c r="W11" t="n">
-        <v>17.2021669272452</v>
+        <v>19.16548618785664</v>
       </c>
       <c r="X11" t="n">
-        <v>17.01069078806303</v>
+        <v>19.44989917170599</v>
       </c>
       <c r="Y11" t="n">
-        <v>17.90584892928985</v>
+        <v>16.64082334030432</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.18431696881041</v>
+        <v>18.15544196288288</v>
       </c>
       <c r="AA11" t="n">
-        <v>18.93339789586966</v>
+        <v>19.69074910903651</v>
       </c>
       <c r="AB11" t="n">
-        <v>18.94510874541066</v>
+        <v>18.4391796278289</v>
       </c>
       <c r="AC11" t="n">
-        <v>21.07579714915893</v>
+        <v>18.26355817210123</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.0572994737088</v>
+        <v>16.11156319782156</v>
       </c>
       <c r="AE11" t="n">
-        <v>18.72280298605197</v>
+        <v>18.52172688226571</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.25015619236745</v>
+        <v>19.06139091856464</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.38561317565754</v>
+        <v>16.77247279743305</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.68924570659894</v>
+        <v>17.83979810885371</v>
       </c>
       <c r="AI11" t="n">
-        <v>20.24387266529459</v>
+        <v>19.86644730434395</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20.02826076740736</v>
+        <v>20.15450943122965</v>
       </c>
       <c r="AK11" t="n">
-        <v>17.89721558955956</v>
+        <v>17.56634272334789</v>
       </c>
       <c r="AL11" t="n">
-        <v>18.99999217911222</v>
+        <v>18.43748608083351</v>
       </c>
       <c r="AM11" t="n">
-        <v>17.49346329891834</v>
+        <v>20.28774489340372</v>
       </c>
       <c r="AN11" t="n">
-        <v>18.38499217472658</v>
+        <v>19.66258211375055</v>
       </c>
       <c r="AO11" t="n">
-        <v>17.92437476037403</v>
+        <v>18.24717418283092</v>
       </c>
       <c r="AP11" t="n">
-        <v>18.57695073968041</v>
+        <v>19.8705325510277</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18.39716208141402</v>
+        <v>20.04730954237592</v>
       </c>
       <c r="AR11" t="n">
-        <v>18.22943581611651</v>
+        <v>19.16390340117607</v>
       </c>
       <c r="AS11" t="n">
-        <v>18.76038385217259</v>
+        <v>19.11416436874821</v>
       </c>
       <c r="AT11" t="n">
-        <v>18.82212652854991</v>
+        <v>18.76486099571611</v>
       </c>
       <c r="AU11" t="n">
-        <v>18.15982805224319</v>
+        <v>18.00541611753792</v>
       </c>
       <c r="AV11" t="n">
-        <v>17.68703720564892</v>
+        <v>19.55431657728866</v>
       </c>
       <c r="AW11" t="n">
-        <v>18.90706455095999</v>
+        <v>19.64826928706321</v>
       </c>
       <c r="AX11" t="n">
-        <v>18.96616047100547</v>
+        <v>17.43575046572215</v>
       </c>
       <c r="AY11" t="n">
-        <v>18.17141832363296</v>
+        <v>18.70527557169969</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.59936890863464</v>
+        <v>20.3669365440369</v>
       </c>
       <c r="BA11" t="n">
-        <v>19.68008261463505</v>
+        <v>18.77762787920729</v>
       </c>
       <c r="BB11" t="n">
-        <v>17.86366427183551</v>
+        <v>19.71659646127132</v>
       </c>
       <c r="BC11" t="n">
-        <v>17.83345837256633</v>
+        <v>18.48984380934075</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.08261775046923</v>
+        <v>19.22869568488262</v>
       </c>
       <c r="BE11" t="n">
-        <v>18.07783738650777</v>
+        <v>18.0355581096655</v>
       </c>
       <c r="BF11" t="n">
-        <v>19.57156679394321</v>
+        <v>19.09697773843462</v>
       </c>
       <c r="BG11" t="n">
-        <v>21.46910303156928</v>
+        <v>19.22902616272122</v>
       </c>
       <c r="BH11" t="n">
-        <v>19.7868195647745</v>
+        <v>17.446705040916</v>
       </c>
       <c r="BI11" t="n">
-        <v>19.3624836708539</v>
+        <v>19.22725721012782</v>
       </c>
       <c r="BJ11" t="n">
-        <v>19.12592526381515</v>
+        <v>18.91756564988682</v>
       </c>
       <c r="BK11" t="n">
-        <v>17.12323690717889</v>
+        <v>17.97640878770623</v>
       </c>
       <c r="BL11" t="n">
-        <v>18.52832115492047</v>
+        <v>18.95370430221589</v>
       </c>
       <c r="BM11" t="n">
-        <v>18.49846070806121</v>
+        <v>18.04988637283112</v>
       </c>
       <c r="BN11" t="n">
-        <v>17.13809007429629</v>
+        <v>19.01556588986907</v>
       </c>
       <c r="BO11" t="n">
-        <v>18.51676825881639</v>
+        <v>18.48388312204121</v>
       </c>
       <c r="BP11" t="n">
-        <v>21.02703341127648</v>
+        <v>19.32179038897917</v>
       </c>
       <c r="BQ11" t="n">
-        <v>19.18140811455208</v>
+        <v>18.76678474878347</v>
       </c>
       <c r="BR11" t="n">
-        <v>20.31302949429899</v>
+        <v>18.67517529353135</v>
       </c>
       <c r="BS11" t="n">
-        <v>18.37271540093184</v>
+        <v>18.38224155598032</v>
       </c>
       <c r="BT11" t="n">
-        <v>18.55835729050235</v>
+        <v>20.15166533411526</v>
       </c>
       <c r="BU11" t="n">
-        <v>19.63406133034939</v>
+        <v>17.73033003203256</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.42030988646637</v>
+        <v>17.98407077589516</v>
       </c>
       <c r="BW11" t="n">
-        <v>18.67482157204427</v>
+        <v>18.69092254639153</v>
       </c>
       <c r="BX11" t="n">
-        <v>17.12936899761175</v>
+        <v>17.9792868554361</v>
       </c>
       <c r="BY11" t="n">
-        <v>20.02366249615562</v>
+        <v>18.5693060834173</v>
       </c>
       <c r="BZ11" t="n">
-        <v>17.60833756713852</v>
+        <v>18.16489168860955</v>
       </c>
       <c r="CA11" t="n">
-        <v>18.51123679240667</v>
+        <v>20.1179263256465</v>
       </c>
       <c r="CB11" t="n">
-        <v>18.0999973938187</v>
+        <v>18.49969834893368</v>
       </c>
       <c r="CC11" t="n">
-        <v>19.90652041574357</v>
+        <v>19.70201426516748</v>
       </c>
       <c r="CD11" t="n">
-        <v>20.55392821738323</v>
+        <v>18.33555069086971</v>
       </c>
       <c r="CE11" t="n">
-        <v>19.15339843670675</v>
+        <v>19.17532119649575</v>
       </c>
       <c r="CF11" t="n">
-        <v>17.40269912813105</v>
+        <v>19.35095382821319</v>
       </c>
       <c r="CG11" t="n">
-        <v>17.77044327690642</v>
+        <v>18.41854336677335</v>
       </c>
       <c r="CH11" t="n">
-        <v>19.12037768750049</v>
+        <v>19.00346068033723</v>
       </c>
       <c r="CI11" t="n">
-        <v>18.91549312006941</v>
+        <v>20.77669091668657</v>
       </c>
       <c r="CJ11" t="n">
-        <v>17.39833890864234</v>
+        <v>17.78460836903193</v>
       </c>
       <c r="CK11" t="n">
-        <v>19.23914609376698</v>
+        <v>19.13906019988854</v>
       </c>
       <c r="CL11" t="n">
-        <v>19.8023187039856</v>
+        <v>18.98803913346927</v>
       </c>
       <c r="CM11" t="n">
-        <v>18.03725497801965</v>
+        <v>17.87198301751372</v>
       </c>
       <c r="CN11" t="n">
-        <v>18.53125518223474</v>
+        <v>18.40339884186332</v>
       </c>
       <c r="CO11" t="n">
-        <v>18.04021563712732</v>
+        <v>18.06243933594131</v>
       </c>
       <c r="CP11" t="n">
-        <v>18.34140871897575</v>
+        <v>17.69587547806351</v>
       </c>
       <c r="CQ11" t="n">
-        <v>19.49697769821995</v>
+        <v>16.56589584176086</v>
       </c>
       <c r="CR11" t="n">
-        <v>17.86766455737803</v>
+        <v>18.01750367482078</v>
       </c>
       <c r="CS11" t="n">
-        <v>18.65905218293495</v>
+        <v>19.60419498343408</v>
       </c>
       <c r="CT11" t="n">
-        <v>18.30708758995624</v>
+        <v>19.51773424467724</v>
       </c>
       <c r="CU11" t="n">
-        <v>19.01188675982757</v>
+        <v>18.78000403943425</v>
       </c>
       <c r="CV11" t="n">
-        <v>18.04746632910162</v>
+        <v>18.13527352767409</v>
       </c>
       <c r="CW11" t="n">
-        <v>19.41966077929519</v>
+        <v>19.19225006753242</v>
       </c>
       <c r="CX11" t="n">
-        <v>18.65700932610874</v>
+        <v>18.77255115333172</v>
       </c>
     </row>
     <row r="12">
@@ -4025,307 +4025,307 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>21.18492562320931</v>
+        <v>21.43658650956411</v>
       </c>
       <c r="C12" t="n">
-        <v>21.70744278758494</v>
+        <v>21.01005006539734</v>
       </c>
       <c r="D12" t="n">
-        <v>21.44373787668352</v>
+        <v>21.70525367722168</v>
       </c>
       <c r="E12" t="n">
-        <v>21.78370876897704</v>
+        <v>22.02595547536347</v>
       </c>
       <c r="F12" t="n">
-        <v>19.1002224096576</v>
+        <v>21.18857325066528</v>
       </c>
       <c r="G12" t="n">
-        <v>20.11956202432402</v>
+        <v>22.59637941484961</v>
       </c>
       <c r="H12" t="n">
-        <v>19.82836329237967</v>
+        <v>21.61725009477631</v>
       </c>
       <c r="I12" t="n">
-        <v>20.3508640455423</v>
+        <v>22.88591320532004</v>
       </c>
       <c r="J12" t="n">
-        <v>21.30233406403872</v>
+        <v>19.71834742032079</v>
       </c>
       <c r="K12" t="n">
-        <v>20.76106234958805</v>
+        <v>22.00443112398102</v>
       </c>
       <c r="L12" t="n">
-        <v>19.44146172036072</v>
+        <v>22.78779341480148</v>
       </c>
       <c r="M12" t="n">
-        <v>20.88348106162223</v>
+        <v>19.34186880640265</v>
       </c>
       <c r="N12" t="n">
-        <v>19.62285769954265</v>
+        <v>20.23962944442291</v>
       </c>
       <c r="O12" t="n">
-        <v>19.47847632527045</v>
+        <v>19.34167193614783</v>
       </c>
       <c r="P12" t="n">
-        <v>23.06491242969721</v>
+        <v>22.59951110680127</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.65456249334935</v>
+        <v>22.59839428662773</v>
       </c>
       <c r="R12" t="n">
-        <v>21.82101762621506</v>
+        <v>22.07267712636214</v>
       </c>
       <c r="S12" t="n">
-        <v>21.59745171261502</v>
+        <v>21.51947698641221</v>
       </c>
       <c r="T12" t="n">
-        <v>19.6090283501599</v>
+        <v>22.68012073066071</v>
       </c>
       <c r="U12" t="n">
-        <v>20.29780647863853</v>
+        <v>19.48903480477297</v>
       </c>
       <c r="V12" t="n">
-        <v>19.84005855874427</v>
+        <v>20.35210498950149</v>
       </c>
       <c r="W12" t="n">
-        <v>19.39005440332977</v>
+        <v>21.4569051415031</v>
       </c>
       <c r="X12" t="n">
-        <v>19.20298932957851</v>
+        <v>21.97687328761217</v>
       </c>
       <c r="Y12" t="n">
-        <v>20.23369778984879</v>
+        <v>18.69964653954327</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.52293494708319</v>
+        <v>20.42565512003727</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.29255259333753</v>
+        <v>22.32187748778694</v>
       </c>
       <c r="AB12" t="n">
-        <v>21.37395829176037</v>
+        <v>20.82924510998738</v>
       </c>
       <c r="AC12" t="n">
-        <v>23.77565239086476</v>
+        <v>20.69169759273598</v>
       </c>
       <c r="AD12" t="n">
-        <v>21.4754115461649</v>
+        <v>18.15229589073875</v>
       </c>
       <c r="AE12" t="n">
-        <v>21.10137665782331</v>
+        <v>21.02050421325233</v>
       </c>
       <c r="AF12" t="n">
-        <v>21.77983274473154</v>
+        <v>21.49789922355789</v>
       </c>
       <c r="AG12" t="n">
-        <v>20.8646854504786</v>
+        <v>18.87859208433063</v>
       </c>
       <c r="AH12" t="n">
-        <v>20.96157974061797</v>
+        <v>20.27187822762523</v>
       </c>
       <c r="AI12" t="n">
-        <v>22.81423249630596</v>
+        <v>22.39466050235449</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22.65557431993997</v>
+        <v>22.70808353805963</v>
       </c>
       <c r="AK12" t="n">
-        <v>20.30733967402205</v>
+        <v>19.71248699099644</v>
       </c>
       <c r="AL12" t="n">
-        <v>21.62490870499653</v>
+        <v>20.83480409255405</v>
       </c>
       <c r="AM12" t="n">
-        <v>19.83962174510862</v>
+        <v>22.76231823825743</v>
       </c>
       <c r="AN12" t="n">
-        <v>20.88278425681467</v>
+        <v>22.21251890736623</v>
       </c>
       <c r="AO12" t="n">
-        <v>20.2530952714014</v>
+        <v>20.59133861119844</v>
       </c>
       <c r="AP12" t="n">
-        <v>21.10761377561001</v>
+        <v>22.58487547937419</v>
       </c>
       <c r="AQ12" t="n">
-        <v>20.62055787528604</v>
+        <v>22.54982669427653</v>
       </c>
       <c r="AR12" t="n">
-        <v>20.66953735420606</v>
+        <v>21.7115537770657</v>
       </c>
       <c r="AS12" t="n">
-        <v>21.2203758001645</v>
+        <v>21.43942334669031</v>
       </c>
       <c r="AT12" t="n">
-        <v>21.25513094672158</v>
+        <v>20.98687544368702</v>
       </c>
       <c r="AU12" t="n">
-        <v>20.37078697355648</v>
+        <v>20.43686783053787</v>
       </c>
       <c r="AV12" t="n">
-        <v>20.02099922362093</v>
+        <v>22.09391276911882</v>
       </c>
       <c r="AW12" t="n">
-        <v>21.32707005246901</v>
+        <v>22.21766132380602</v>
       </c>
       <c r="AX12" t="n">
-        <v>21.43745725699172</v>
+        <v>19.77588817951593</v>
       </c>
       <c r="AY12" t="n">
-        <v>20.45342138150884</v>
+        <v>21.17422535840083</v>
       </c>
       <c r="AZ12" t="n">
-        <v>23.28371746727114</v>
+        <v>23.17948680665304</v>
       </c>
       <c r="BA12" t="n">
-        <v>22.27297282805813</v>
+        <v>21.30620162612603</v>
       </c>
       <c r="BB12" t="n">
-        <v>20.23769324123029</v>
+        <v>22.1992403820168</v>
       </c>
       <c r="BC12" t="n">
-        <v>20.03383031913785</v>
+        <v>20.9825299490821</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.56293131640699</v>
+        <v>21.5891980763603</v>
       </c>
       <c r="BE12" t="n">
-        <v>20.48182732840166</v>
+        <v>20.35919115893662</v>
       </c>
       <c r="BF12" t="n">
-        <v>22.22731557600706</v>
+        <v>21.43810688516322</v>
       </c>
       <c r="BG12" t="n">
-        <v>24.26482672963828</v>
+        <v>21.67207579956607</v>
       </c>
       <c r="BH12" t="n">
-        <v>22.40280016284457</v>
+        <v>19.74102656399241</v>
       </c>
       <c r="BI12" t="n">
-        <v>22.07565424680809</v>
+        <v>21.59811676839458</v>
       </c>
       <c r="BJ12" t="n">
-        <v>21.5239874880222</v>
+        <v>21.29685599401622</v>
       </c>
       <c r="BK12" t="n">
-        <v>19.29482945018683</v>
+        <v>20.26409661791049</v>
       </c>
       <c r="BL12" t="n">
-        <v>20.94742778117547</v>
+        <v>21.22955338063725</v>
       </c>
       <c r="BM12" t="n">
-        <v>20.79817837057587</v>
+        <v>20.24000594873901</v>
       </c>
       <c r="BN12" t="n">
-        <v>19.34773720798337</v>
+        <v>21.43671946316572</v>
       </c>
       <c r="BO12" t="n">
-        <v>20.85071642408315</v>
+        <v>20.84196621362242</v>
       </c>
       <c r="BP12" t="n">
-        <v>23.57372320404466</v>
+        <v>22.02369446874726</v>
       </c>
       <c r="BQ12" t="n">
-        <v>21.59921235647883</v>
+        <v>21.06685056053131</v>
       </c>
       <c r="BR12" t="n">
-        <v>22.75988018801808</v>
+        <v>21.04210073906372</v>
       </c>
       <c r="BS12" t="n">
-        <v>20.82839321573437</v>
+        <v>20.86997812218531</v>
       </c>
       <c r="BT12" t="n">
-        <v>21.05794300866984</v>
+        <v>22.71055258357905</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.09172873900307</v>
+        <v>20.05895530233315</v>
       </c>
       <c r="BV12" t="n">
-        <v>22.03978107930308</v>
+        <v>20.37378604521754</v>
       </c>
       <c r="BW12" t="n">
-        <v>21.15496157208556</v>
+        <v>20.978258051123</v>
       </c>
       <c r="BX12" t="n">
-        <v>19.49338638567046</v>
+        <v>20.26029793245575</v>
       </c>
       <c r="BY12" t="n">
-        <v>22.58177467611891</v>
+        <v>21.08808072350366</v>
       </c>
       <c r="BZ12" t="n">
-        <v>19.99301181059598</v>
+        <v>20.50814943393948</v>
       </c>
       <c r="CA12" t="n">
-        <v>20.90425527776171</v>
+        <v>22.69841808332362</v>
       </c>
       <c r="CB12" t="n">
-        <v>20.40505519956299</v>
+        <v>20.83892462028859</v>
       </c>
       <c r="CC12" t="n">
-        <v>22.52681376836664</v>
+        <v>22.3391754912547</v>
       </c>
       <c r="CD12" t="n">
-        <v>23.05486230415189</v>
+        <v>20.68891935016083</v>
       </c>
       <c r="CE12" t="n">
-        <v>21.76503781284938</v>
+        <v>21.60393554426026</v>
       </c>
       <c r="CF12" t="n">
-        <v>19.72641558934141</v>
+        <v>21.85576542854095</v>
       </c>
       <c r="CG12" t="n">
-        <v>19.91124567498768</v>
+        <v>20.701580366233</v>
       </c>
       <c r="CH12" t="n">
-        <v>21.69556005083103</v>
+        <v>21.5775291913881</v>
       </c>
       <c r="CI12" t="n">
-        <v>21.57050822116847</v>
+        <v>23.4854195314541</v>
       </c>
       <c r="CJ12" t="n">
-        <v>19.63797017374383</v>
+        <v>19.90395915243019</v>
       </c>
       <c r="CK12" t="n">
-        <v>21.50815268608897</v>
+        <v>21.50206115416711</v>
       </c>
       <c r="CL12" t="n">
-        <v>22.27399107888916</v>
+        <v>21.51583547386665</v>
       </c>
       <c r="CM12" t="n">
-        <v>20.39862777473492</v>
+        <v>20.1729010291731</v>
       </c>
       <c r="CN12" t="n">
-        <v>21.05932364575454</v>
+        <v>20.90221763112249</v>
       </c>
       <c r="CO12" t="n">
-        <v>20.34308306883069</v>
+        <v>20.57768771551532</v>
       </c>
       <c r="CP12" t="n">
-        <v>20.71159544060002</v>
+        <v>19.96399336275557</v>
       </c>
       <c r="CQ12" t="n">
-        <v>21.99104191088621</v>
+        <v>18.58169672823772</v>
       </c>
       <c r="CR12" t="n">
-        <v>20.2369986791718</v>
+        <v>20.31157039214789</v>
       </c>
       <c r="CS12" t="n">
-        <v>21.18493993514032</v>
+        <v>22.24638338573128</v>
       </c>
       <c r="CT12" t="n">
-        <v>20.66160923034981</v>
+        <v>22.06772777316054</v>
       </c>
       <c r="CU12" t="n">
-        <v>21.4327752412393</v>
+        <v>21.19738684106981</v>
       </c>
       <c r="CV12" t="n">
-        <v>20.44048685989928</v>
+        <v>20.42458138892427</v>
       </c>
       <c r="CW12" t="n">
-        <v>21.79738138837462</v>
+        <v>21.62267049577501</v>
       </c>
       <c r="CX12" t="n">
-        <v>21.07746543878823</v>
+        <v>21.18756830600387</v>
       </c>
     </row>
     <row r="13">
@@ -4333,307 +4333,307 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>23.52818629632697</v>
+        <v>23.88741355943234</v>
       </c>
       <c r="C13" t="n">
-        <v>24.13353553821709</v>
+        <v>23.25639102511286</v>
       </c>
       <c r="D13" t="n">
-        <v>24.12531062936432</v>
+        <v>24.13704271226051</v>
       </c>
       <c r="E13" t="n">
-        <v>24.29350293235637</v>
+        <v>24.46958488506383</v>
       </c>
       <c r="F13" t="n">
-        <v>21.51747844911314</v>
+        <v>23.63878785720952</v>
       </c>
       <c r="G13" t="n">
-        <v>22.44222688214232</v>
+        <v>25.21623734720172</v>
       </c>
       <c r="H13" t="n">
-        <v>22.09659841865422</v>
+        <v>24.02379870217651</v>
       </c>
       <c r="I13" t="n">
-        <v>22.73857294363749</v>
+        <v>25.48867695945527</v>
       </c>
       <c r="J13" t="n">
-        <v>23.72933394330746</v>
+        <v>22.12283778324189</v>
       </c>
       <c r="K13" t="n">
-        <v>23.2163535966441</v>
+        <v>24.55149200086811</v>
       </c>
       <c r="L13" t="n">
-        <v>21.61305123333352</v>
+        <v>25.27833093299521</v>
       </c>
       <c r="M13" t="n">
-        <v>23.34962361681802</v>
+        <v>21.72051844555072</v>
       </c>
       <c r="N13" t="n">
-        <v>21.77878756427734</v>
+        <v>22.64370910092081</v>
       </c>
       <c r="O13" t="n">
-        <v>21.70046328680885</v>
+        <v>21.66207125380695</v>
       </c>
       <c r="P13" t="n">
-        <v>25.61558031362429</v>
+        <v>25.23159729542968</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.09721804118684</v>
+        <v>25.1438626415754</v>
       </c>
       <c r="R13" t="n">
-        <v>24.38923171371261</v>
+        <v>24.6433263023602</v>
       </c>
       <c r="S13" t="n">
-        <v>24.07988248615161</v>
+        <v>23.94019686858068</v>
       </c>
       <c r="T13" t="n">
-        <v>21.7947012254842</v>
+        <v>25.25427054863829</v>
       </c>
       <c r="U13" t="n">
-        <v>22.74210808738419</v>
+        <v>21.7501290653466</v>
       </c>
       <c r="V13" t="n">
-        <v>22.14158303498376</v>
+        <v>22.78920856107503</v>
       </c>
       <c r="W13" t="n">
-        <v>21.65891129255683</v>
+        <v>23.79474840141304</v>
       </c>
       <c r="X13" t="n">
-        <v>21.40118451540006</v>
+        <v>24.43658220322686</v>
       </c>
       <c r="Y13" t="n">
-        <v>22.57912761160485</v>
+        <v>20.87693830619606</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.02663866883447</v>
+        <v>22.73986878876671</v>
       </c>
       <c r="AA13" t="n">
-        <v>23.56822999486971</v>
+        <v>24.86512852199893</v>
       </c>
       <c r="AB13" t="n">
-        <v>23.79099301519478</v>
+        <v>23.07862879860381</v>
       </c>
       <c r="AC13" t="n">
-        <v>26.37511271579933</v>
+        <v>23.16251762312094</v>
       </c>
       <c r="AD13" t="n">
-        <v>23.90553739073738</v>
+        <v>20.43838106909019</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.60457194285797</v>
+        <v>23.39569037685377</v>
       </c>
       <c r="AF13" t="n">
-        <v>24.38866239882078</v>
+        <v>23.87063772856797</v>
       </c>
       <c r="AG13" t="n">
-        <v>23.37056715610184</v>
+        <v>21.03760512089864</v>
       </c>
       <c r="AH13" t="n">
-        <v>23.2782908790522</v>
+        <v>22.7658230599817</v>
       </c>
       <c r="AI13" t="n">
-        <v>25.31007884105081</v>
+        <v>24.90800160325703</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25.10972613854021</v>
+        <v>25.21451866768964</v>
       </c>
       <c r="AK13" t="n">
-        <v>22.79820635952381</v>
+        <v>21.98244901234461</v>
       </c>
       <c r="AL13" t="n">
-        <v>24.28948541591971</v>
+        <v>23.30173163487163</v>
       </c>
       <c r="AM13" t="n">
-        <v>22.20942120240764</v>
+        <v>25.21046819255091</v>
       </c>
       <c r="AN13" t="n">
-        <v>23.35772654030233</v>
+        <v>24.80857002853814</v>
       </c>
       <c r="AO13" t="n">
-        <v>22.70682052676889</v>
+        <v>22.88692418053837</v>
       </c>
       <c r="AP13" t="n">
-        <v>23.64337973627108</v>
+        <v>25.19575707484268</v>
       </c>
       <c r="AQ13" t="n">
-        <v>22.92504900082167</v>
+        <v>25.01057688994841</v>
       </c>
       <c r="AR13" t="n">
-        <v>22.99863541607086</v>
+        <v>24.21682031534441</v>
       </c>
       <c r="AS13" t="n">
-        <v>23.58461361051381</v>
+        <v>23.77151753023097</v>
       </c>
       <c r="AT13" t="n">
-        <v>23.72516843939423</v>
+        <v>23.24126042951542</v>
       </c>
       <c r="AU13" t="n">
-        <v>22.75238887720767</v>
+        <v>23.0878883465578</v>
       </c>
       <c r="AV13" t="n">
-        <v>22.43916013782412</v>
+        <v>24.67174735674742</v>
       </c>
       <c r="AW13" t="n">
-        <v>23.77045025001986</v>
+        <v>24.72710702940461</v>
       </c>
       <c r="AX13" t="n">
-        <v>23.80381682333135</v>
+        <v>22.18732930570592</v>
       </c>
       <c r="AY13" t="n">
-        <v>22.83861094875133</v>
+        <v>23.63914895550761</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25.89131798513675</v>
+        <v>25.76568569625564</v>
       </c>
       <c r="BA13" t="n">
-        <v>24.86341902132288</v>
+        <v>23.78149561425264</v>
       </c>
       <c r="BB13" t="n">
-        <v>22.74314576964427</v>
+        <v>24.67523503701896</v>
       </c>
       <c r="BC13" t="n">
-        <v>22.28004942940753</v>
+        <v>23.53240398650568</v>
       </c>
       <c r="BD13" t="n">
-        <v>24.05550161268672</v>
+        <v>24.03713935194988</v>
       </c>
       <c r="BE13" t="n">
-        <v>22.87520554877202</v>
+        <v>22.84835180599953</v>
       </c>
       <c r="BF13" t="n">
-        <v>24.86138928250034</v>
+        <v>23.66473994853291</v>
       </c>
       <c r="BG13" t="n">
-        <v>26.91526130007554</v>
+        <v>24.15999790554484</v>
       </c>
       <c r="BH13" t="n">
-        <v>25.03337702256029</v>
+        <v>22.07835253660343</v>
       </c>
       <c r="BI13" t="n">
-        <v>24.79157346292944</v>
+        <v>23.93632282905449</v>
       </c>
       <c r="BJ13" t="n">
-        <v>23.89642072341647</v>
+        <v>23.79806764901998</v>
       </c>
       <c r="BK13" t="n">
-        <v>21.54271733149539</v>
+        <v>22.58028391838264</v>
       </c>
       <c r="BL13" t="n">
-        <v>23.26115229618838</v>
+        <v>23.56765306952195</v>
       </c>
       <c r="BM13" t="n">
-        <v>23.09320036119327</v>
+        <v>22.5341786448378</v>
       </c>
       <c r="BN13" t="n">
-        <v>21.58623593295711</v>
+        <v>23.77184056739974</v>
       </c>
       <c r="BO13" t="n">
-        <v>23.3569451674316</v>
+        <v>23.27165517009099</v>
       </c>
       <c r="BP13" t="n">
-        <v>26.08913237476342</v>
+        <v>24.75136357846775</v>
       </c>
       <c r="BQ13" t="n">
-        <v>24.01046900381478</v>
+        <v>23.34983190977875</v>
       </c>
       <c r="BR13" t="n">
-        <v>25.18343477089356</v>
+        <v>23.50034618091058</v>
       </c>
       <c r="BS13" t="n">
-        <v>23.19774570300929</v>
+        <v>23.3639859239822</v>
       </c>
       <c r="BT13" t="n">
-        <v>23.49691174894084</v>
+        <v>25.2444444227297</v>
       </c>
       <c r="BU13" t="n">
-        <v>24.53732396197629</v>
+        <v>22.35744566441783</v>
       </c>
       <c r="BV13" t="n">
-        <v>24.54071704681878</v>
+        <v>22.90806916940732</v>
       </c>
       <c r="BW13" t="n">
-        <v>23.63451975949309</v>
+        <v>23.34333077917731</v>
       </c>
       <c r="BX13" t="n">
-        <v>21.92234073021094</v>
+        <v>22.69324847718615</v>
       </c>
       <c r="BY13" t="n">
-        <v>25.03265854867345</v>
+        <v>23.75582746860794</v>
       </c>
       <c r="BZ13" t="n">
-        <v>22.40276158576799</v>
+        <v>22.89766744244755</v>
       </c>
       <c r="CA13" t="n">
-        <v>23.25761288297841</v>
+        <v>25.16890576568585</v>
       </c>
       <c r="CB13" t="n">
-        <v>22.78010287025636</v>
+        <v>23.20843610931775</v>
       </c>
       <c r="CC13" t="n">
-        <v>25.14230119530092</v>
+        <v>24.96279380920416</v>
       </c>
       <c r="CD13" t="n">
-        <v>25.57226354012267</v>
+        <v>23.15760218823646</v>
       </c>
       <c r="CE13" t="n">
-        <v>24.41839464201835</v>
+        <v>24.0110010854095</v>
       </c>
       <c r="CF13" t="n">
-        <v>22.06886509555819</v>
+        <v>24.33000704341694</v>
       </c>
       <c r="CG13" t="n">
-        <v>22.12659194691453</v>
+        <v>23.07284388511931</v>
       </c>
       <c r="CH13" t="n">
-        <v>24.28800783318481</v>
+        <v>24.23101540715839</v>
       </c>
       <c r="CI13" t="n">
-        <v>24.09415904742158</v>
+        <v>26.04100578177718</v>
       </c>
       <c r="CJ13" t="n">
-        <v>21.88645297828774</v>
+        <v>22.13224924721477</v>
       </c>
       <c r="CK13" t="n">
-        <v>23.84933390512639</v>
+        <v>23.91300562017658</v>
       </c>
       <c r="CL13" t="n">
-        <v>24.84805466484051</v>
+        <v>24.02946884034487</v>
       </c>
       <c r="CM13" t="n">
-        <v>22.81468996879817</v>
+        <v>22.48194775631164</v>
       </c>
       <c r="CN13" t="n">
-        <v>23.53337035523916</v>
+        <v>23.39520809693764</v>
       </c>
       <c r="CO13" t="n">
-        <v>22.61793101640202</v>
+        <v>23.1107308656328</v>
       </c>
       <c r="CP13" t="n">
-        <v>23.15574407615163</v>
+        <v>22.33385075642271</v>
       </c>
       <c r="CQ13" t="n">
-        <v>24.51954855007515</v>
+        <v>20.73501335928479</v>
       </c>
       <c r="CR13" t="n">
-        <v>22.59473003759557</v>
+        <v>22.61302005987396</v>
       </c>
       <c r="CS13" t="n">
-        <v>23.70952578735991</v>
+        <v>24.78200517041014</v>
       </c>
       <c r="CT13" t="n">
-        <v>23.1661810067799</v>
+        <v>24.53987877589501</v>
       </c>
       <c r="CU13" t="n">
-        <v>23.95296609339182</v>
+        <v>23.63126881787204</v>
       </c>
       <c r="CV13" t="n">
-        <v>22.79811199210474</v>
+        <v>22.69493828875132</v>
       </c>
       <c r="CW13" t="n">
-        <v>24.31414464712785</v>
+        <v>24.02378119525517</v>
       </c>
       <c r="CX13" t="n">
-        <v>23.50937907695194</v>
+        <v>23.6214279307441</v>
       </c>
     </row>
     <row r="14">
@@ -4641,307 +4641,307 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16.45840139559818</v>
+        <v>16.86516892189877</v>
       </c>
       <c r="C14" t="n">
-        <v>17.06524910402427</v>
+        <v>16.4467775027799</v>
       </c>
       <c r="D14" t="n">
-        <v>16.83060158523224</v>
+        <v>17.16782210416397</v>
       </c>
       <c r="E14" t="n">
-        <v>17.12254390004411</v>
+        <v>17.23609283951729</v>
       </c>
       <c r="F14" t="n">
-        <v>15.32971551245675</v>
+        <v>16.52358944316017</v>
       </c>
       <c r="G14" t="n">
-        <v>15.96900998250819</v>
+        <v>17.92173561868623</v>
       </c>
       <c r="H14" t="n">
-        <v>15.73175101482287</v>
+        <v>17.04307142338533</v>
       </c>
       <c r="I14" t="n">
-        <v>16.08676080215556</v>
+        <v>17.92300207322471</v>
       </c>
       <c r="J14" t="n">
-        <v>16.8184573661307</v>
+        <v>15.47517125231796</v>
       </c>
       <c r="K14" t="n">
-        <v>16.47496347936883</v>
+        <v>17.35009338293444</v>
       </c>
       <c r="L14" t="n">
-        <v>15.18688103896589</v>
+        <v>17.73904218840294</v>
       </c>
       <c r="M14" t="n">
-        <v>16.49880031362794</v>
+        <v>15.50572324087412</v>
       </c>
       <c r="N14" t="n">
-        <v>15.57327730040335</v>
+        <v>16.08395300372141</v>
       </c>
       <c r="O14" t="n">
-        <v>15.39233138103362</v>
+        <v>15.39160488773247</v>
       </c>
       <c r="P14" t="n">
-        <v>17.79905642556355</v>
+        <v>17.72304951830075</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.98844698112104</v>
+        <v>17.69391124643871</v>
       </c>
       <c r="R14" t="n">
-        <v>17.21753780790703</v>
+        <v>17.41635153549406</v>
       </c>
       <c r="S14" t="n">
-        <v>16.94644781433336</v>
+        <v>17.00259396553924</v>
       </c>
       <c r="T14" t="n">
-        <v>15.55689193121947</v>
+        <v>17.63660663294182</v>
       </c>
       <c r="U14" t="n">
-        <v>16.03411949025384</v>
+        <v>15.40959050567428</v>
       </c>
       <c r="V14" t="n">
-        <v>15.77992537467026</v>
+        <v>16.25337320504328</v>
       </c>
       <c r="W14" t="n">
-        <v>15.53663847608086</v>
+        <v>16.83426350416908</v>
       </c>
       <c r="X14" t="n">
-        <v>15.22246939324483</v>
+        <v>17.23968603611484</v>
       </c>
       <c r="Y14" t="n">
-        <v>15.92176828297984</v>
+        <v>14.82759083164268</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.27571778279194</v>
+        <v>15.98867438902426</v>
       </c>
       <c r="AA14" t="n">
-        <v>16.66088685959909</v>
+        <v>17.63554634542124</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.81026959027729</v>
+        <v>16.33235480784994</v>
       </c>
       <c r="AC14" t="n">
-        <v>18.39159025246171</v>
+        <v>16.47476712982798</v>
       </c>
       <c r="AD14" t="n">
-        <v>16.67758638804833</v>
+        <v>14.59276659826389</v>
       </c>
       <c r="AE14" t="n">
-        <v>16.78794464748271</v>
+        <v>16.56805279668551</v>
       </c>
       <c r="AF14" t="n">
-        <v>17.14916889778328</v>
+        <v>16.85149317637861</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.58620531173704</v>
+        <v>14.90416715257393</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.47247965767708</v>
+        <v>15.99528155107384</v>
       </c>
       <c r="AI14" t="n">
-        <v>17.66994678497804</v>
+        <v>17.42937932752941</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17.64665972943331</v>
+        <v>17.74916400723372</v>
       </c>
       <c r="AK14" t="n">
-        <v>16.26469275607325</v>
+        <v>15.62212906616667</v>
       </c>
       <c r="AL14" t="n">
-        <v>17.10805330392943</v>
+        <v>16.46230875146109</v>
       </c>
       <c r="AM14" t="n">
-        <v>15.75484172082675</v>
+        <v>17.76467562096082</v>
       </c>
       <c r="AN14" t="n">
-        <v>16.46931843006941</v>
+        <v>17.58748979529836</v>
       </c>
       <c r="AO14" t="n">
-        <v>16.16126563543085</v>
+        <v>16.11929592107429</v>
       </c>
       <c r="AP14" t="n">
-        <v>16.77537827686835</v>
+        <v>17.70256044371312</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16.22771032005427</v>
+        <v>17.57246905542338</v>
       </c>
       <c r="AR14" t="n">
-        <v>16.38067642985297</v>
+        <v>17.00354626081235</v>
       </c>
       <c r="AS14" t="n">
-        <v>16.68559744931498</v>
+        <v>16.62617226077692</v>
       </c>
       <c r="AT14" t="n">
-        <v>16.71622797768748</v>
+        <v>16.46774763374261</v>
       </c>
       <c r="AU14" t="n">
-        <v>16.10864395848322</v>
+        <v>16.2374492572804</v>
       </c>
       <c r="AV14" t="n">
-        <v>15.93195882414992</v>
+        <v>17.39886660888142</v>
       </c>
       <c r="AW14" t="n">
-        <v>16.67054725700888</v>
+        <v>17.33387491086028</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.6007842651451</v>
+        <v>15.64192109988428</v>
       </c>
       <c r="AY14" t="n">
-        <v>16.23348299655524</v>
+        <v>16.58580279517829</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.0089049973463</v>
+        <v>18.03970242282852</v>
       </c>
       <c r="BA14" t="n">
-        <v>17.48547639135007</v>
+        <v>16.86572851809019</v>
       </c>
       <c r="BB14" t="n">
-        <v>16.05546268534417</v>
+        <v>17.17591170524697</v>
       </c>
       <c r="BC14" t="n">
-        <v>15.85158313960323</v>
+        <v>16.56238811243201</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.997685227018</v>
+        <v>17.02340701686927</v>
       </c>
       <c r="BE14" t="n">
-        <v>16.26967021693378</v>
+        <v>16.33335619050827</v>
       </c>
       <c r="BF14" t="n">
-        <v>17.43292343674174</v>
+        <v>16.65106938255662</v>
       </c>
       <c r="BG14" t="n">
-        <v>18.87451194818071</v>
+        <v>17.06654501099387</v>
       </c>
       <c r="BH14" t="n">
-        <v>17.69784805473274</v>
+        <v>15.69249092413004</v>
       </c>
       <c r="BI14" t="n">
-        <v>17.41985637479821</v>
+        <v>17.05022836414929</v>
       </c>
       <c r="BJ14" t="n">
-        <v>16.85788435393325</v>
+        <v>16.90245569970606</v>
       </c>
       <c r="BK14" t="n">
-        <v>15.32240149206012</v>
+        <v>16.01619277717429</v>
       </c>
       <c r="BL14" t="n">
-        <v>16.55368001029534</v>
+        <v>16.66827941981207</v>
       </c>
       <c r="BM14" t="n">
-        <v>16.27572760026898</v>
+        <v>16.19326079311225</v>
       </c>
       <c r="BN14" t="n">
-        <v>15.31005110594069</v>
+        <v>16.76798571665537</v>
       </c>
       <c r="BO14" t="n">
-        <v>16.53141397236302</v>
+        <v>16.51153358135202</v>
       </c>
       <c r="BP14" t="n">
-        <v>18.43026129453199</v>
+        <v>17.39600972306206</v>
       </c>
       <c r="BQ14" t="n">
-        <v>16.95539153591904</v>
+        <v>16.49354796341022</v>
       </c>
       <c r="BR14" t="n">
-        <v>17.67499296817788</v>
+        <v>16.66189805973447</v>
       </c>
       <c r="BS14" t="n">
-        <v>16.44366536255744</v>
+        <v>16.64468802247902</v>
       </c>
       <c r="BT14" t="n">
-        <v>16.61404767662948</v>
+        <v>17.65992314091769</v>
       </c>
       <c r="BU14" t="n">
-        <v>17.20006269877144</v>
+        <v>15.87666679344674</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.26713570192558</v>
+        <v>16.29559817380294</v>
       </c>
       <c r="BW14" t="n">
-        <v>16.63352555108173</v>
+        <v>16.59285174369479</v>
       </c>
       <c r="BX14" t="n">
-        <v>15.49866447488059</v>
+        <v>16.16660634294195</v>
       </c>
       <c r="BY14" t="n">
-        <v>17.74077988183945</v>
+        <v>16.87171717908609</v>
       </c>
       <c r="BZ14" t="n">
-        <v>15.81866513907984</v>
+        <v>16.04411368188307</v>
       </c>
       <c r="CA14" t="n">
-        <v>16.37706359830134</v>
+        <v>17.78240598449952</v>
       </c>
       <c r="CB14" t="n">
-        <v>16.3059457946057</v>
+        <v>16.21481997269751</v>
       </c>
       <c r="CC14" t="n">
-        <v>17.56352533383769</v>
+        <v>17.54314425149753</v>
       </c>
       <c r="CD14" t="n">
-        <v>17.87566219892592</v>
+        <v>16.45213784524509</v>
       </c>
       <c r="CE14" t="n">
-        <v>17.01078174139266</v>
+        <v>16.88229060186083</v>
       </c>
       <c r="CF14" t="n">
-        <v>15.52041018652965</v>
+        <v>17.1040477732961</v>
       </c>
       <c r="CG14" t="n">
-        <v>15.71396174642191</v>
+        <v>16.40867587437808</v>
       </c>
       <c r="CH14" t="n">
-        <v>17.09324854854938</v>
+        <v>17.13053532635668</v>
       </c>
       <c r="CI14" t="n">
-        <v>16.96837024056919</v>
+        <v>18.31294244387449</v>
       </c>
       <c r="CJ14" t="n">
-        <v>15.6089147420675</v>
+        <v>15.62307154396274</v>
       </c>
       <c r="CK14" t="n">
-        <v>16.79163601885068</v>
+        <v>17.0090342304791</v>
       </c>
       <c r="CL14" t="n">
-        <v>17.50032041663828</v>
+        <v>17.06182280453644</v>
       </c>
       <c r="CM14" t="n">
-        <v>16.28936407588097</v>
+        <v>15.97705049620598</v>
       </c>
       <c r="CN14" t="n">
-        <v>16.6864810222488</v>
+        <v>16.53694121193793</v>
       </c>
       <c r="CO14" t="n">
-        <v>16.01554482368949</v>
+        <v>16.4359586430791</v>
       </c>
       <c r="CP14" t="n">
-        <v>16.4118469194628</v>
+        <v>15.84431820659181</v>
       </c>
       <c r="CQ14" t="n">
-        <v>17.31851055928882</v>
+        <v>14.8632871781691</v>
       </c>
       <c r="CR14" t="n">
-        <v>15.98030989858407</v>
+        <v>16.0262262387117</v>
       </c>
       <c r="CS14" t="n">
-        <v>16.72536804881402</v>
+        <v>17.57207635634168</v>
       </c>
       <c r="CT14" t="n">
-        <v>16.39650220284543</v>
+        <v>17.35101622577643</v>
       </c>
       <c r="CU14" t="n">
-        <v>17.08501168531075</v>
+        <v>16.82122589465668</v>
       </c>
       <c r="CV14" t="n">
-        <v>16.12271240308507</v>
+        <v>16.21303319187578</v>
       </c>
       <c r="CW14" t="n">
-        <v>17.13971466739139</v>
+        <v>16.94656562405787</v>
       </c>
       <c r="CX14" t="n">
-        <v>16.60483161823063</v>
+        <v>16.696946060077</v>
       </c>
     </row>
     <row r="15">
@@ -4949,307 +4949,307 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>17.18266612945218</v>
+        <v>17.72101730055297</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91267408737603</v>
+        <v>17.10577564925557</v>
       </c>
       <c r="D15" t="n">
-        <v>17.79565957850685</v>
+        <v>17.91576659264441</v>
       </c>
       <c r="E15" t="n">
-        <v>18.05386904220081</v>
+        <v>17.9398292288755</v>
       </c>
       <c r="F15" t="n">
-        <v>16.01522084694709</v>
+        <v>17.31166777779022</v>
       </c>
       <c r="G15" t="n">
-        <v>16.61588354483641</v>
+        <v>18.8789003604187</v>
       </c>
       <c r="H15" t="n">
-        <v>16.44014088829919</v>
+        <v>17.66980934029945</v>
       </c>
       <c r="I15" t="n">
-        <v>16.86595432006217</v>
+        <v>18.86173941054846</v>
       </c>
       <c r="J15" t="n">
-        <v>17.65606487244</v>
+        <v>16.24793432276175</v>
       </c>
       <c r="K15" t="n">
-        <v>17.31585002301031</v>
+        <v>18.15716853564166</v>
       </c>
       <c r="L15" t="n">
-        <v>15.61766211411235</v>
+        <v>18.59998583764218</v>
       </c>
       <c r="M15" t="n">
-        <v>17.32822004408382</v>
+        <v>16.31704936114073</v>
       </c>
       <c r="N15" t="n">
-        <v>16.16699904202365</v>
+        <v>16.86113393883431</v>
       </c>
       <c r="O15" t="n">
-        <v>16.05293959374425</v>
+        <v>16.12896613596113</v>
       </c>
       <c r="P15" t="n">
-        <v>18.76076665916668</v>
+        <v>18.73154003001125</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.73559625396103</v>
+        <v>18.50982212848415</v>
       </c>
       <c r="R15" t="n">
-        <v>18.18259580118165</v>
+        <v>18.28928232420215</v>
       </c>
       <c r="S15" t="n">
-        <v>17.73144346117207</v>
+        <v>17.77204854621971</v>
       </c>
       <c r="T15" t="n">
-        <v>16.1808809545617</v>
+        <v>18.39525217139855</v>
       </c>
       <c r="U15" t="n">
-        <v>16.87266947435921</v>
+        <v>16.0302023169139</v>
       </c>
       <c r="V15" t="n">
-        <v>16.46704077539556</v>
+        <v>16.98849606850625</v>
       </c>
       <c r="W15" t="n">
-        <v>16.17197650288418</v>
+        <v>17.5171770247202</v>
       </c>
       <c r="X15" t="n">
-        <v>15.8623725468729</v>
+        <v>18.02422026153255</v>
       </c>
       <c r="Y15" t="n">
-        <v>16.59718125107052</v>
+        <v>15.46555994229339</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.14934561237005</v>
+        <v>16.59746595790475</v>
       </c>
       <c r="AA15" t="n">
-        <v>17.26549618325949</v>
+        <v>18.52959452724768</v>
       </c>
       <c r="AB15" t="n">
-        <v>17.59654150913151</v>
+        <v>16.98882004524865</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.30583298456451</v>
+        <v>17.24423152798551</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.3940069577454</v>
+        <v>15.20347257516766</v>
       </c>
       <c r="AE15" t="n">
-        <v>17.57163456987477</v>
+        <v>17.35547336035371</v>
       </c>
       <c r="AF15" t="n">
-        <v>18.00833558367784</v>
+        <v>17.56766830914961</v>
       </c>
       <c r="AG15" t="n">
-        <v>17.45479677559236</v>
+        <v>15.49987202455681</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.14268936293526</v>
+        <v>16.86054489021177</v>
       </c>
       <c r="AI15" t="n">
-        <v>18.51528064571976</v>
+        <v>18.32105167991157</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18.47635434924638</v>
+        <v>18.58918661289546</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.16995249668219</v>
+        <v>16.32261587062381</v>
       </c>
       <c r="AL15" t="n">
-        <v>18.0598086158115</v>
+        <v>17.26343451308057</v>
       </c>
       <c r="AM15" t="n">
-        <v>16.47496347936883</v>
+        <v>18.4956162392037</v>
       </c>
       <c r="AN15" t="n">
-        <v>17.30113362492365</v>
+        <v>18.55115370683294</v>
       </c>
       <c r="AO15" t="n">
-        <v>16.90798293928097</v>
+        <v>16.74832131013931</v>
       </c>
       <c r="AP15" t="n">
-        <v>17.67359888643784</v>
+        <v>18.60816379601855</v>
       </c>
       <c r="AQ15" t="n">
-        <v>16.7969570914077</v>
+        <v>18.38138007633754</v>
       </c>
       <c r="AR15" t="n">
-        <v>17.0983143667033</v>
+        <v>17.90141344120832</v>
       </c>
       <c r="AS15" t="n">
-        <v>17.42563886877623</v>
+        <v>17.26743022623685</v>
       </c>
       <c r="AT15" t="n">
-        <v>17.53894237132335</v>
+        <v>16.94910835061187</v>
       </c>
       <c r="AU15" t="n">
-        <v>16.80334826896235</v>
+        <v>17.13885072941165</v>
       </c>
       <c r="AV15" t="n">
-        <v>16.71028840407679</v>
+        <v>18.26073310096265</v>
       </c>
       <c r="AW15" t="n">
-        <v>17.44684461918796</v>
+        <v>18.2008464910036</v>
       </c>
       <c r="AX15" t="n">
-        <v>17.31047986306807</v>
+        <v>16.39612913871781</v>
       </c>
       <c r="AY15" t="n">
-        <v>16.89919629732796</v>
+        <v>17.36056863093875</v>
       </c>
       <c r="AZ15" t="n">
-        <v>18.91130785213588</v>
+        <v>19.00914882834112</v>
       </c>
       <c r="BA15" t="n">
-        <v>18.41912827556583</v>
+        <v>17.69400942120914</v>
       </c>
       <c r="BB15" t="n">
-        <v>16.93597256632905</v>
+        <v>18.01283198816329</v>
       </c>
       <c r="BC15" t="n">
-        <v>16.47719204665747</v>
+        <v>17.38085153850849</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.90129563148381</v>
+        <v>17.82057633524064</v>
       </c>
       <c r="BE15" t="n">
-        <v>17.04474039448255</v>
+        <v>17.23294142938666</v>
       </c>
       <c r="BF15" t="n">
-        <v>18.34089280101441</v>
+        <v>17.19843299758239</v>
       </c>
       <c r="BG15" t="n">
-        <v>19.87496194619343</v>
+        <v>17.89535605787312</v>
       </c>
       <c r="BH15" t="n">
-        <v>18.68321840800822</v>
+        <v>16.35911725026771</v>
       </c>
       <c r="BI15" t="n">
-        <v>18.47632489681525</v>
+        <v>17.78394732839519</v>
       </c>
       <c r="BJ15" t="n">
-        <v>17.56276938810542</v>
+        <v>17.69728845854132</v>
       </c>
       <c r="BK15" t="n">
-        <v>15.92942591507296</v>
+        <v>16.68747258743009</v>
       </c>
       <c r="BL15" t="n">
-        <v>17.26819598944617</v>
+        <v>17.32220193065679</v>
       </c>
       <c r="BM15" t="n">
-        <v>16.91770224155302</v>
+        <v>16.85778617916283</v>
       </c>
       <c r="BN15" t="n">
-        <v>15.95030768874229</v>
+        <v>17.47966444494093</v>
       </c>
       <c r="BO15" t="n">
-        <v>17.37215325384886</v>
+        <v>17.24697060408035</v>
       </c>
       <c r="BP15" t="n">
-        <v>19.2325946058277</v>
+        <v>18.38987219397928</v>
       </c>
       <c r="BQ15" t="n">
-        <v>17.7130258742404</v>
+        <v>17.14368092811655</v>
       </c>
       <c r="BR15" t="n">
-        <v>18.37679531455871</v>
+        <v>17.41283687871285</v>
       </c>
       <c r="BS15" t="n">
-        <v>17.14572296334138</v>
+        <v>17.55102768556263</v>
       </c>
       <c r="BT15" t="n">
-        <v>17.4462064831802</v>
+        <v>18.51114748788488</v>
       </c>
       <c r="BU15" t="n">
-        <v>17.98692366624821</v>
+        <v>16.54388216820696</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.16717254474793</v>
+        <v>17.1855131977945</v>
       </c>
       <c r="BW15" t="n">
-        <v>17.46619486643867</v>
+        <v>17.34686343298746</v>
       </c>
       <c r="BX15" t="n">
-        <v>16.32160467048843</v>
+        <v>16.93357710193068</v>
       </c>
       <c r="BY15" t="n">
-        <v>18.55762342420393</v>
+        <v>17.84162500601969</v>
       </c>
       <c r="BZ15" t="n">
-        <v>16.59722052097869</v>
+        <v>16.78076807176467</v>
       </c>
       <c r="CA15" t="n">
-        <v>17.11792968583415</v>
+        <v>18.63574108903085</v>
       </c>
       <c r="CB15" t="n">
-        <v>17.10413613058948</v>
+        <v>16.92535987364614</v>
       </c>
       <c r="CC15" t="n">
-        <v>18.5151726534723</v>
+        <v>18.53836153424661</v>
       </c>
       <c r="CD15" t="n">
-        <v>18.61952261695669</v>
+        <v>17.23051651255717</v>
       </c>
       <c r="CE15" t="n">
-        <v>17.92233448478582</v>
+        <v>17.58266941407051</v>
       </c>
       <c r="CF15" t="n">
-        <v>16.26709803794865</v>
+        <v>17.92797953408524</v>
       </c>
       <c r="CG15" t="n">
-        <v>16.27272345229399</v>
+        <v>17.1617941732599</v>
       </c>
       <c r="CH15" t="n">
-        <v>17.98043431392314</v>
+        <v>18.08869163327044</v>
       </c>
       <c r="CI15" t="n">
-        <v>17.78998507677631</v>
+        <v>19.14821339064768</v>
       </c>
       <c r="CJ15" t="n">
-        <v>16.23276632073114</v>
+        <v>16.15933159245348</v>
       </c>
       <c r="CK15" t="n">
-        <v>17.41642025783335</v>
+        <v>17.79896806827016</v>
       </c>
       <c r="CL15" t="n">
-        <v>18.31884274757702</v>
+        <v>17.98005143231849</v>
       </c>
       <c r="CM15" t="n">
-        <v>17.0027019577867</v>
+        <v>16.59459925460835</v>
       </c>
       <c r="CN15" t="n">
-        <v>17.51087420445894</v>
+        <v>17.39148386614548</v>
       </c>
       <c r="CO15" t="n">
-        <v>16.66439169890325</v>
+        <v>17.37437200366046</v>
       </c>
       <c r="CP15" t="n">
-        <v>17.22143534629289</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="CQ15" t="n">
-        <v>18.25994770279925</v>
+        <v>15.36473445306724</v>
       </c>
       <c r="CR15" t="n">
-        <v>16.64451130789225</v>
+        <v>16.68156246625053</v>
       </c>
       <c r="CS15" t="n">
-        <v>17.67522858762689</v>
+        <v>18.43759494988271</v>
       </c>
       <c r="CT15" t="n">
-        <v>17.26071507193981</v>
+        <v>18.17691148197406</v>
       </c>
       <c r="CU15" t="n">
-        <v>17.83113012306129</v>
+        <v>17.57965544861847</v>
       </c>
       <c r="CV15" t="n">
-        <v>16.86379447511282</v>
+        <v>16.85488020595826</v>
       </c>
       <c r="CW15" t="n">
-        <v>17.89678940952131</v>
+        <v>17.6468658964512</v>
       </c>
       <c r="CX15" t="n">
-        <v>17.38545652429003</v>
+        <v>17.47168980651411</v>
       </c>
     </row>
     <row r="16">
@@ -5257,307 +5257,307 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>19.63143942815501</v>
+        <v>20.14583595527216</v>
       </c>
       <c r="C16" t="n">
-        <v>20.53488293551109</v>
+        <v>19.42237625453565</v>
       </c>
       <c r="D16" t="n">
-        <v>20.46120277030737</v>
+        <v>20.38931920340242</v>
       </c>
       <c r="E16" t="n">
-        <v>20.71580921992673</v>
+        <v>20.37989442544165</v>
       </c>
       <c r="F16" t="n">
-        <v>18.31388492167057</v>
+        <v>19.83280569977307</v>
       </c>
       <c r="G16" t="n">
-        <v>18.97825322808847</v>
+        <v>21.58640344909872</v>
       </c>
       <c r="H16" t="n">
-        <v>18.7745503969343</v>
+        <v>20.12750672563388</v>
       </c>
       <c r="I16" t="n">
-        <v>19.33798522187859</v>
+        <v>21.55250370087108</v>
       </c>
       <c r="J16" t="n">
-        <v>20.13181659805552</v>
+        <v>18.74467581429407</v>
       </c>
       <c r="K16" t="n">
-        <v>19.86927762698584</v>
+        <v>20.69882498464327</v>
       </c>
       <c r="L16" t="n">
-        <v>17.7504304617722</v>
+        <v>21.19740555624501</v>
       </c>
       <c r="M16" t="n">
-        <v>19.88561390878451</v>
+        <v>18.75626043720419</v>
       </c>
       <c r="N16" t="n">
-        <v>18.28144797752226</v>
+        <v>19.23212336692966</v>
       </c>
       <c r="O16" t="n">
-        <v>18.39534052869193</v>
+        <v>18.52866186692865</v>
       </c>
       <c r="P16" t="n">
-        <v>21.40054879120776</v>
+        <v>21.46143678382514</v>
       </c>
       <c r="Q16" t="n">
-        <v>20.14615011453752</v>
+        <v>21.04381112791559</v>
       </c>
       <c r="R16" t="n">
-        <v>20.87044430082265</v>
+        <v>20.96190391695028</v>
       </c>
       <c r="S16" t="n">
-        <v>20.2778908389704</v>
+        <v>20.2256225911963</v>
       </c>
       <c r="T16" t="n">
-        <v>18.4234676004186</v>
+        <v>20.94791401216477</v>
       </c>
       <c r="U16" t="n">
-        <v>19.42689229397518</v>
+        <v>18.39930678941709</v>
       </c>
       <c r="V16" t="n">
-        <v>18.84962464387806</v>
+        <v>19.3964286627124</v>
       </c>
       <c r="W16" t="n">
-        <v>18.35846608492042</v>
+        <v>19.87107422528461</v>
       </c>
       <c r="X16" t="n">
-        <v>18.13151546812968</v>
+        <v>20.4672896060737</v>
       </c>
       <c r="Y16" t="n">
-        <v>18.9720878525058</v>
+        <v>17.68651868622573</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.78993277752861</v>
+        <v>18.91581407409837</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.55312541378724</v>
+        <v>21.1609238115552</v>
       </c>
       <c r="AB16" t="n">
-        <v>20.07809536367913</v>
+        <v>19.32399531709308</v>
       </c>
       <c r="AC16" t="n">
-        <v>21.95778878813825</v>
+        <v>19.6781117140149</v>
       </c>
       <c r="AD16" t="n">
-        <v>19.89975107572566</v>
+        <v>17.40810485477838</v>
       </c>
       <c r="AE16" t="n">
-        <v>20.1337310060788</v>
+        <v>19.81022550257539</v>
       </c>
       <c r="AF16" t="n">
-        <v>20.59661523115413</v>
+        <v>19.93471111147389</v>
       </c>
       <c r="AG16" t="n">
-        <v>20.05126419892207</v>
+        <v>17.64665972943331</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.54689131586527</v>
+        <v>19.43067202263653</v>
       </c>
       <c r="AI16" t="n">
-        <v>21.05253886500635</v>
+        <v>21.00412888570994</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21.00550333249588</v>
+        <v>21.2041992503584</v>
       </c>
       <c r="AK16" t="n">
-        <v>19.70361751937123</v>
+        <v>18.6893150612516</v>
       </c>
       <c r="AL16" t="n">
-        <v>20.77547002791381</v>
+        <v>19.72949638885518</v>
       </c>
       <c r="AM16" t="n">
-        <v>18.77496273097009</v>
+        <v>20.86326772510461</v>
       </c>
       <c r="AN16" t="n">
-        <v>19.84224029521088</v>
+        <v>21.28429022807085</v>
       </c>
       <c r="AO16" t="n">
-        <v>19.36470839438819</v>
+        <v>19.06025861382421</v>
       </c>
       <c r="AP16" t="n">
-        <v>20.2702626593084</v>
+        <v>21.20222593747286</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19.09723123236614</v>
+        <v>20.85420619379441</v>
       </c>
       <c r="AR16" t="n">
-        <v>19.47325042056972</v>
+        <v>20.56631849700107</v>
       </c>
       <c r="AS16" t="n">
-        <v>19.84010008521562</v>
+        <v>19.50680655710087</v>
       </c>
       <c r="AT16" t="n">
-        <v>20.06487122210293</v>
+        <v>19.23051330069469</v>
       </c>
       <c r="AU16" t="n">
-        <v>19.15767743851662</v>
+        <v>19.65619910525611</v>
       </c>
       <c r="AV16" t="n">
-        <v>19.26773135616269</v>
+        <v>21.02607094689985</v>
       </c>
       <c r="AW16" t="n">
-        <v>19.98289528879832</v>
+        <v>20.80409779096965</v>
       </c>
       <c r="AX16" t="n">
-        <v>19.8196600980132</v>
+        <v>18.8631825796737</v>
       </c>
       <c r="AY16" t="n">
-        <v>19.24124380310211</v>
+        <v>19.78576034978556</v>
       </c>
       <c r="AZ16" t="n">
-        <v>21.72201225948633</v>
+        <v>21.68194713567602</v>
       </c>
       <c r="BA16" t="n">
-        <v>21.13261020776472</v>
+        <v>20.13150243879016</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.51872497423043</v>
+        <v>20.58752424741281</v>
       </c>
       <c r="BC16" t="n">
-        <v>18.78333703888731</v>
+        <v>19.85200868486814</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.52965022024745</v>
+        <v>20.4483124229506</v>
       </c>
       <c r="BE16" t="n">
-        <v>19.47664726762641</v>
+        <v>19.82476518607529</v>
       </c>
       <c r="BF16" t="n">
-        <v>20.92976149711324</v>
+        <v>19.45767990198036</v>
       </c>
       <c r="BG16" t="n">
-        <v>22.66642409854064</v>
+        <v>20.45331933624227</v>
       </c>
       <c r="BH16" t="n">
-        <v>21.40580114142548</v>
+        <v>18.6849462839677</v>
       </c>
       <c r="BI16" t="n">
-        <v>21.23715652078996</v>
+        <v>20.26232032038105</v>
       </c>
       <c r="BJ16" t="n">
-        <v>20.02558167897897</v>
+        <v>20.19518841236465</v>
       </c>
       <c r="BK16" t="n">
-        <v>18.2184394098637</v>
+        <v>19.06151525088564</v>
       </c>
       <c r="BL16" t="n">
-        <v>19.6433676627616</v>
+        <v>19.66039116795324</v>
       </c>
       <c r="BM16" t="n">
-        <v>19.23081764248301</v>
+        <v>19.17859848209412</v>
       </c>
       <c r="BN16" t="n">
-        <v>18.34409329853024</v>
+        <v>19.85520918238398</v>
       </c>
       <c r="BO16" t="n">
-        <v>19.92395115663534</v>
+        <v>19.70460908455252</v>
       </c>
       <c r="BP16" t="n">
-        <v>21.81280428717508</v>
+        <v>21.14064090398546</v>
       </c>
       <c r="BQ16" t="n">
-        <v>20.15001820049226</v>
+        <v>19.5317331313117</v>
       </c>
       <c r="BR16" t="n">
-        <v>20.82737502903734</v>
+        <v>19.83959939388646</v>
       </c>
       <c r="BS16" t="n">
-        <v>19.55447040814205</v>
+        <v>20.21298749824264</v>
       </c>
       <c r="BT16" t="n">
-        <v>19.91665677119279</v>
+        <v>21.12820216057265</v>
       </c>
       <c r="BU16" t="n">
-        <v>20.45879748843196</v>
+        <v>18.85079292364611</v>
       </c>
       <c r="BV16" t="n">
-        <v>20.85042646513306</v>
+        <v>19.63938176708236</v>
       </c>
       <c r="BW16" t="n">
-        <v>19.91216036670734</v>
+        <v>19.75078067908325</v>
       </c>
       <c r="BX16" t="n">
-        <v>18.87260735763448</v>
+        <v>19.39398411092883</v>
       </c>
       <c r="BY16" t="n">
-        <v>21.16291675939481</v>
+        <v>20.56012366898727</v>
       </c>
       <c r="BZ16" t="n">
-        <v>19.11213416251661</v>
+        <v>19.19971587521247</v>
       </c>
       <c r="CA16" t="n">
-        <v>19.60657175880643</v>
+        <v>21.24790665815146</v>
       </c>
       <c r="CB16" t="n">
-        <v>19.60960535921255</v>
+        <v>19.2610063843886</v>
       </c>
       <c r="CC16" t="n">
-        <v>21.22949888869683</v>
+        <v>21.27874335354186</v>
       </c>
       <c r="CD16" t="n">
-        <v>21.10140044824671</v>
+        <v>19.67518610585624</v>
       </c>
       <c r="CE16" t="n">
-        <v>20.48509850942873</v>
+        <v>20.07652456735234</v>
       </c>
       <c r="CF16" t="n">
-        <v>18.56609590689158</v>
+        <v>20.4242006993343</v>
       </c>
       <c r="CG16" t="n">
-        <v>18.50856549142271</v>
+        <v>19.58970533324747</v>
       </c>
       <c r="CH16" t="n">
-        <v>20.68425584871224</v>
+        <v>20.7395675143695</v>
       </c>
       <c r="CI16" t="n">
-        <v>20.43787644485446</v>
+        <v>21.84039139766441</v>
       </c>
       <c r="CJ16" t="n">
-        <v>18.45359743746194</v>
+        <v>18.43286292594824</v>
       </c>
       <c r="CK16" t="n">
-        <v>19.78681081982911</v>
+        <v>20.25207087434871</v>
       </c>
       <c r="CL16" t="n">
-        <v>20.92437170221693</v>
+        <v>20.58943865543608</v>
       </c>
       <c r="CM16" t="n">
-        <v>19.36530726048778</v>
+        <v>18.75294212996383</v>
       </c>
       <c r="CN16" t="n">
-        <v>19.97005402882677</v>
+        <v>19.95135173506087</v>
       </c>
       <c r="CO16" t="n">
-        <v>19.02660430252263</v>
+        <v>19.85341258408521</v>
       </c>
       <c r="CP16" t="n">
-        <v>19.70003414025073</v>
+        <v>18.86029624142322</v>
       </c>
       <c r="CQ16" t="n">
-        <v>20.99024697317189</v>
+        <v>17.48713554497025</v>
       </c>
       <c r="CR16" t="n">
-        <v>18.95590865033982</v>
+        <v>19.04477645252824</v>
       </c>
       <c r="CS16" t="n">
-        <v>20.23562660030258</v>
+        <v>21.05921474939523</v>
       </c>
       <c r="CT16" t="n">
-        <v>19.80161557520915</v>
+        <v>20.77964245565686</v>
       </c>
       <c r="CU16" t="n">
-        <v>20.33405662513036</v>
+        <v>20.07403092818355</v>
       </c>
       <c r="CV16" t="n">
-        <v>19.3474198173164</v>
+        <v>19.20186590268477</v>
       </c>
       <c r="CW16" t="n">
-        <v>20.38542166501655</v>
+        <v>19.96662772933895</v>
       </c>
       <c r="CX16" t="n">
-        <v>19.8718497077962</v>
+        <v>19.94422139965969</v>
       </c>
     </row>
     <row r="17">
@@ -5565,307 +5565,307 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>17.90910052573257</v>
+        <v>18.46378797863202</v>
       </c>
       <c r="C17" t="n">
-        <v>18.86213210963016</v>
+        <v>17.64570743416019</v>
       </c>
       <c r="D17" t="n">
-        <v>18.71490922390131</v>
+        <v>18.6819421359927</v>
       </c>
       <c r="E17" t="n">
-        <v>19.09644583420275</v>
+        <v>18.36666367825088</v>
       </c>
       <c r="F17" t="n">
-        <v>16.78106259607594</v>
+        <v>18.09641798770286</v>
       </c>
       <c r="G17" t="n">
-        <v>17.26187353423082</v>
+        <v>19.61192228379458</v>
       </c>
       <c r="H17" t="n">
-        <v>17.21697821171561</v>
+        <v>18.12254229411287</v>
       </c>
       <c r="I17" t="n">
-        <v>17.74412764151094</v>
+        <v>19.51707563808729</v>
       </c>
       <c r="J17" t="n">
-        <v>18.44602816266219</v>
+        <v>17.21050849434463</v>
       </c>
       <c r="K17" t="n">
-        <v>18.17034358983265</v>
+        <v>18.77147752662001</v>
       </c>
       <c r="L17" t="n">
-        <v>16.01506376731441</v>
+        <v>19.22716554102321</v>
       </c>
       <c r="M17" t="n">
-        <v>18.2314082970368</v>
+        <v>17.29966100336728</v>
       </c>
       <c r="N17" t="n">
-        <v>16.70481025188709</v>
+        <v>17.61820868096424</v>
       </c>
       <c r="O17" t="n">
-        <v>16.88025838411304</v>
+        <v>17.06245112306717</v>
       </c>
       <c r="P17" t="n">
-        <v>19.49331734364452</v>
+        <v>19.58670118527248</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.30415580192149</v>
+        <v>19.27204122858433</v>
       </c>
       <c r="R17" t="n">
-        <v>19.17195205013637</v>
+        <v>19.0483500141717</v>
       </c>
       <c r="S17" t="n">
-        <v>18.45819201671781</v>
+        <v>18.35589390593529</v>
       </c>
       <c r="T17" t="n">
-        <v>16.88717970542798</v>
+        <v>18.84942829433721</v>
       </c>
       <c r="U17" t="n">
-        <v>17.840309464096</v>
+        <v>16.86403991203888</v>
       </c>
       <c r="V17" t="n">
-        <v>17.34090422442269</v>
+        <v>17.77214672099014</v>
       </c>
       <c r="W17" t="n">
-        <v>16.85695169361422</v>
+        <v>18.02755820372699</v>
       </c>
       <c r="X17" t="n">
-        <v>16.58333860844063</v>
+        <v>18.60574869666611</v>
       </c>
       <c r="Y17" t="n">
-        <v>17.32268298703186</v>
+        <v>16.19233795027026</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.2608607281642</v>
+        <v>17.12570512765179</v>
       </c>
       <c r="AA17" t="n">
-        <v>17.70329675449131</v>
+        <v>19.26346075364921</v>
       </c>
       <c r="AB17" t="n">
-        <v>18.3751754308467</v>
+        <v>17.65803818532553</v>
       </c>
       <c r="AC17" t="n">
-        <v>19.8717418137235</v>
+        <v>18.05674556297425</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.12756884235861</v>
+        <v>15.94971864011974</v>
       </c>
       <c r="AE17" t="n">
-        <v>18.35616879529248</v>
+        <v>18.19904989270482</v>
       </c>
       <c r="AF17" t="n">
-        <v>18.74309520049024</v>
+        <v>18.188918256397</v>
       </c>
       <c r="AG17" t="n">
-        <v>18.41859813180554</v>
+        <v>16.0878799945384</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.82261837046547</v>
+        <v>17.80737182861852</v>
       </c>
       <c r="AI17" t="n">
-        <v>19.11894749158409</v>
+        <v>19.19715351370439</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19.08526372785138</v>
+        <v>19.24067438943365</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.12663618203958</v>
+        <v>17.18546411040929</v>
       </c>
       <c r="AL17" t="n">
-        <v>19.01049382269594</v>
+        <v>18.00960203821632</v>
       </c>
       <c r="AM17" t="n">
-        <v>17.17076734727671</v>
+        <v>18.93807029455365</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.1356093560564</v>
+        <v>19.48753484966651</v>
       </c>
       <c r="AO17" t="n">
-        <v>17.72099766559888</v>
+        <v>17.29577328245846</v>
       </c>
       <c r="AP17" t="n">
-        <v>18.42158264482645</v>
+        <v>19.21847707384063</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17.23517981415235</v>
+        <v>18.97154789126847</v>
       </c>
       <c r="AR17" t="n">
-        <v>17.80657661297808</v>
+        <v>18.95289468488778</v>
       </c>
       <c r="AS17" t="n">
-        <v>18.07633142967397</v>
+        <v>17.62147790081938</v>
       </c>
       <c r="AT17" t="n">
-        <v>18.35281121814396</v>
+        <v>17.22940713765138</v>
       </c>
       <c r="AU17" t="n">
-        <v>17.54333078356134</v>
+        <v>18.05611724444353</v>
       </c>
       <c r="AV17" t="n">
-        <v>17.74540391352646</v>
+        <v>19.16262544694602</v>
       </c>
       <c r="AW17" t="n">
-        <v>18.19259981028792</v>
+        <v>18.88826623351721</v>
       </c>
       <c r="AX17" t="n">
-        <v>17.99585757035686</v>
+        <v>17.28650558413037</v>
       </c>
       <c r="AY17" t="n">
-        <v>17.54144582796918</v>
+        <v>17.97770505530534</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19.72035631772864</v>
+        <v>19.71026395132898</v>
       </c>
       <c r="BA17" t="n">
-        <v>19.35602974468265</v>
+        <v>18.48517044363052</v>
       </c>
       <c r="BB17" t="n">
-        <v>17.86394994881426</v>
+        <v>18.76251417008024</v>
       </c>
       <c r="BC17" t="n">
-        <v>17.14631201196392</v>
+        <v>18.09655543238146</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.83700918587849</v>
+        <v>18.70742830639495</v>
       </c>
       <c r="BE17" t="n">
-        <v>17.88667740816758</v>
+        <v>18.14714489158129</v>
       </c>
       <c r="BF17" t="n">
-        <v>19.20428100203722</v>
+        <v>17.54496048475039</v>
       </c>
       <c r="BG17" t="n">
-        <v>20.65640366634276</v>
+        <v>18.64254460062128</v>
       </c>
       <c r="BH17" t="n">
-        <v>19.44644870824378</v>
+        <v>17.06213696380181</v>
       </c>
       <c r="BI17" t="n">
-        <v>19.53150732933972</v>
+        <v>18.5358875300319</v>
       </c>
       <c r="BJ17" t="n">
-        <v>18.15041411143644</v>
+        <v>18.49065841329725</v>
       </c>
       <c r="BK17" t="n">
-        <v>16.53838438106317</v>
+        <v>17.39453710150569</v>
       </c>
       <c r="BL17" t="n">
-        <v>17.92893182935835</v>
+        <v>17.82416953183818</v>
       </c>
       <c r="BM17" t="n">
-        <v>17.51497790986269</v>
+        <v>17.65583907046802</v>
       </c>
       <c r="BN17" t="n">
-        <v>16.71772023419794</v>
+        <v>18.07076492019089</v>
       </c>
       <c r="BO17" t="n">
-        <v>18.30231993371455</v>
+        <v>17.89385398388562</v>
       </c>
       <c r="BP17" t="n">
-        <v>19.80705445749067</v>
+        <v>19.20662737905037</v>
       </c>
       <c r="BQ17" t="n">
-        <v>18.41057725306184</v>
+        <v>17.7212332850479</v>
       </c>
       <c r="BR17" t="n">
-        <v>18.86268188834454</v>
+        <v>18.11872329554335</v>
       </c>
       <c r="BS17" t="n">
-        <v>17.74356804531952</v>
+        <v>18.60110503002502</v>
       </c>
       <c r="BT17" t="n">
-        <v>18.12528137020772</v>
+        <v>19.25606819343623</v>
       </c>
       <c r="BU17" t="n">
-        <v>18.59340812802373</v>
+        <v>17.23624010167293</v>
       </c>
       <c r="BV17" t="n">
-        <v>19.14424712992253</v>
+        <v>18.12593914116956</v>
       </c>
       <c r="BW17" t="n">
-        <v>18.19715511963563</v>
+        <v>18.08428358607837</v>
       </c>
       <c r="BX17" t="n">
-        <v>17.33254955145955</v>
+        <v>17.86052364932644</v>
       </c>
       <c r="BY17" t="n">
-        <v>19.21736769893483</v>
+        <v>18.92369750816348</v>
       </c>
       <c r="BZ17" t="n">
-        <v>17.49696283948976</v>
+        <v>17.57288138945917</v>
       </c>
       <c r="CA17" t="n">
-        <v>17.82483712027707</v>
+        <v>19.37219912937159</v>
       </c>
       <c r="CB17" t="n">
-        <v>17.88558766821586</v>
+        <v>17.53963941219337</v>
       </c>
       <c r="CC17" t="n">
-        <v>19.35228928592947</v>
+        <v>19.50917256906811</v>
       </c>
       <c r="CD17" t="n">
-        <v>19.04530659628853</v>
+        <v>17.94634803363169</v>
       </c>
       <c r="CE17" t="n">
-        <v>18.71204252060491</v>
+        <v>18.20642281796372</v>
       </c>
       <c r="CF17" t="n">
-        <v>16.95922035196561</v>
+        <v>18.58472947831818</v>
       </c>
       <c r="CG17" t="n">
-        <v>16.92295459177073</v>
+        <v>17.95375041132171</v>
       </c>
       <c r="CH17" t="n">
-        <v>18.80506311558229</v>
+        <v>18.98610720972245</v>
       </c>
       <c r="CI17" t="n">
-        <v>18.57875063479932</v>
+        <v>19.68944108252191</v>
       </c>
       <c r="CJ17" t="n">
-        <v>16.78612841422986</v>
+        <v>16.80122769392117</v>
       </c>
       <c r="CK17" t="n">
-        <v>17.91392090696042</v>
+        <v>18.53145003040871</v>
       </c>
       <c r="CL17" t="n">
-        <v>18.99037781223592</v>
+        <v>18.89571769859245</v>
       </c>
       <c r="CM17" t="n">
-        <v>17.70255062623609</v>
+        <v>17.14322932417259</v>
       </c>
       <c r="CN17" t="n">
-        <v>18.25594217216593</v>
+        <v>18.29268898873589</v>
       </c>
       <c r="CO17" t="n">
-        <v>17.41261107674087</v>
+        <v>18.33252831057422</v>
       </c>
       <c r="CP17" t="n">
-        <v>18.02324833130535</v>
+        <v>17.30697502376392</v>
       </c>
       <c r="CQ17" t="n">
-        <v>19.30673619245241</v>
+        <v>15.93864452601584</v>
       </c>
       <c r="CR17" t="n">
-        <v>17.36937490784584</v>
+        <v>17.29778586525217</v>
       </c>
       <c r="CS17" t="n">
-        <v>18.69721813027078</v>
+        <v>19.26871310386694</v>
       </c>
       <c r="CT17" t="n">
-        <v>18.20812124149206</v>
+        <v>18.91294737080198</v>
       </c>
       <c r="CU17" t="n">
-        <v>18.51579115452597</v>
+        <v>18.32268138110063</v>
       </c>
       <c r="CV17" t="n">
-        <v>17.70742991232619</v>
+        <v>17.5586264127935</v>
       </c>
       <c r="CW17" t="n">
-        <v>18.60899828156716</v>
+        <v>18.21967641197105</v>
       </c>
       <c r="CX17" t="n">
-        <v>18.14569563562029</v>
+        <v>18.1966841752619</v>
       </c>
     </row>
     <row r="18">
@@ -5873,307 +5873,307 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20.23196468136574</v>
+        <v>20.82696269500156</v>
       </c>
       <c r="C18" t="n">
-        <v>21.39449140787255</v>
+        <v>19.80900813542213</v>
       </c>
       <c r="D18" t="n">
-        <v>21.2558686320329</v>
+        <v>21.08768543281838</v>
       </c>
       <c r="E18" t="n">
-        <v>21.66408914493577</v>
+        <v>20.6894002066825</v>
       </c>
       <c r="F18" t="n">
-        <v>19.04170358221395</v>
+        <v>20.49480799422373</v>
       </c>
       <c r="G18" t="n">
-        <v>19.53266579163073</v>
+        <v>22.2317651199624</v>
       </c>
       <c r="H18" t="n">
-        <v>19.4703346298881</v>
+        <v>20.46170346163653</v>
       </c>
       <c r="I18" t="n">
-        <v>20.1148421802491</v>
+        <v>22.05976292217836</v>
       </c>
       <c r="J18" t="n">
-        <v>20.85758340589702</v>
+        <v>19.65634636741175</v>
       </c>
       <c r="K18" t="n">
-        <v>20.6911575350731</v>
+        <v>21.2266714553086</v>
       </c>
       <c r="L18" t="n">
-        <v>18.14939309382402</v>
+        <v>21.77723556785022</v>
       </c>
       <c r="M18" t="n">
-        <v>20.59647778647553</v>
+        <v>19.71319937696468</v>
       </c>
       <c r="N18" t="n">
-        <v>18.74417512296491</v>
+        <v>19.90410021805547</v>
       </c>
       <c r="O18" t="n">
-        <v>19.05921796125771</v>
+        <v>19.3397916376544</v>
       </c>
       <c r="P18" t="n">
-        <v>21.99042208182741</v>
+        <v>22.10949826087551</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.65901511523606</v>
+        <v>21.66203729223389</v>
       </c>
       <c r="R18" t="n">
-        <v>21.74389541581399</v>
+        <v>21.54566091937248</v>
       </c>
       <c r="S18" t="n">
-        <v>20.90227256139433</v>
+        <v>20.73372611552924</v>
       </c>
       <c r="T18" t="n">
-        <v>19.16322431304562</v>
+        <v>21.38668651362379</v>
       </c>
       <c r="U18" t="n">
-        <v>20.23218066586067</v>
+        <v>19.11547210471105</v>
       </c>
       <c r="V18" t="n">
-        <v>19.63332438374716</v>
+        <v>20.19155594585894</v>
       </c>
       <c r="W18" t="n">
-        <v>18.97894045148145</v>
+        <v>20.2967992997542</v>
       </c>
       <c r="X18" t="n">
-        <v>18.74161276145682</v>
+        <v>20.98697775331675</v>
       </c>
       <c r="Y18" t="n">
-        <v>19.56699750884825</v>
+        <v>18.35012122943433</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.73983258624965</v>
+        <v>19.32647913878482</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.92293995649997</v>
+        <v>21.70195515388857</v>
       </c>
       <c r="AB18" t="n">
-        <v>20.84171836299639</v>
+        <v>19.86634220135014</v>
       </c>
       <c r="AC18" t="n">
-        <v>22.38157981963046</v>
+        <v>20.30535032225819</v>
       </c>
       <c r="AD18" t="n">
-        <v>20.48746452139597</v>
+        <v>18.02519219175976</v>
       </c>
       <c r="AE18" t="n">
-        <v>20.97339036508997</v>
+        <v>20.52872737740546</v>
       </c>
       <c r="AF18" t="n">
-        <v>21.13899156784232</v>
+        <v>20.44340368442937</v>
       </c>
       <c r="AG18" t="n">
-        <v>20.94074725392376</v>
+        <v>18.21733985243494</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.13850229992144</v>
+        <v>20.24584659390379</v>
       </c>
       <c r="AI18" t="n">
-        <v>21.57692958375274</v>
+        <v>21.83163420814253</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21.51658155237269</v>
+        <v>21.75603963491553</v>
       </c>
       <c r="AK18" t="n">
-        <v>20.5498644054779</v>
+        <v>19.46804715773721</v>
       </c>
       <c r="AL18" t="n">
-        <v>21.62186417617612</v>
+        <v>20.35045181179128</v>
       </c>
       <c r="AM18" t="n">
-        <v>19.32983671593334</v>
+        <v>21.18641979943449</v>
       </c>
       <c r="AN18" t="n">
-        <v>20.61285333818238</v>
+        <v>22.07700241186494</v>
       </c>
       <c r="AO18" t="n">
-        <v>20.05550534900442</v>
+        <v>19.57491039534447</v>
       </c>
       <c r="AP18" t="n">
-        <v>20.93168572261357</v>
+        <v>21.77722575037317</v>
       </c>
       <c r="AQ18" t="n">
-        <v>19.55672842786182</v>
+        <v>21.3108857733789</v>
       </c>
       <c r="AR18" t="n">
-        <v>20.06862149833315</v>
+        <v>21.46760215940781</v>
       </c>
       <c r="AS18" t="n">
-        <v>20.41181104330671</v>
+        <v>19.80906704028438</v>
       </c>
       <c r="AT18" t="n">
-        <v>20.81783244135207</v>
+        <v>19.52859153865811</v>
       </c>
       <c r="AU18" t="n">
-        <v>19.80563092331952</v>
+        <v>20.41951776278505</v>
       </c>
       <c r="AV18" t="n">
-        <v>20.23271080962096</v>
+        <v>21.80431216953334</v>
       </c>
       <c r="AW18" t="n">
-        <v>20.60312421843329</v>
+        <v>21.41661018364923</v>
       </c>
       <c r="AX18" t="n">
-        <v>20.35915009645091</v>
+        <v>19.54875663650334</v>
       </c>
       <c r="AY18" t="n">
-        <v>19.83937359191448</v>
+        <v>20.38663903216982</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22.44467674458241</v>
+        <v>22.18539717589083</v>
       </c>
       <c r="BA18" t="n">
-        <v>21.98596494725013</v>
+        <v>20.73341195626388</v>
       </c>
       <c r="BB18" t="n">
-        <v>20.37652703081608</v>
+        <v>21.28687222453302</v>
       </c>
       <c r="BC18" t="n">
-        <v>19.32932620712714</v>
+        <v>20.5013660688881</v>
       </c>
       <c r="BD18" t="n">
-        <v>21.32574943362119</v>
+        <v>21.08373880704731</v>
       </c>
       <c r="BE18" t="n">
-        <v>20.18905248921311</v>
+        <v>20.70709130031302</v>
       </c>
       <c r="BF18" t="n">
-        <v>21.66091809985105</v>
+        <v>19.72722855165836</v>
       </c>
       <c r="BG18" t="n">
-        <v>23.17968179832087</v>
+        <v>21.09976092958062</v>
       </c>
       <c r="BH18" t="n">
-        <v>22.08172461832237</v>
+        <v>19.33610026628644</v>
       </c>
       <c r="BI18" t="n">
-        <v>22.13272641155799</v>
+        <v>21.02826024428032</v>
       </c>
       <c r="BJ18" t="n">
-        <v>20.43981048783183</v>
+        <v>20.8392247238276</v>
       </c>
       <c r="BK18" t="n">
-        <v>18.77929223834581</v>
+        <v>19.72299721905306</v>
       </c>
       <c r="BL18" t="n">
-        <v>20.16423390724975</v>
+        <v>20.09961527335622</v>
       </c>
       <c r="BM18" t="n">
-        <v>19.71815720287113</v>
+        <v>19.90432602002745</v>
       </c>
       <c r="BN18" t="n">
-        <v>19.05533024034889</v>
+        <v>20.41049550138302</v>
       </c>
       <c r="BO18" t="n">
-        <v>20.71273634961244</v>
+        <v>20.23853257350715</v>
       </c>
       <c r="BP18" t="n">
-        <v>22.37733866954812</v>
+        <v>21.83640550198517</v>
       </c>
       <c r="BQ18" t="n">
-        <v>20.79783424061656</v>
+        <v>20.05699760551487</v>
       </c>
       <c r="BR18" t="n">
-        <v>21.335184029059</v>
+        <v>20.42249245832891</v>
       </c>
       <c r="BS18" t="n">
-        <v>20.0669230748048</v>
+        <v>21.10752655392121</v>
       </c>
       <c r="BT18" t="n">
-        <v>20.52843285309419</v>
+        <v>21.64617224933327</v>
       </c>
       <c r="BU18" t="n">
-        <v>20.92479385372975</v>
+        <v>19.48208614990794</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.6770187622007</v>
+        <v>20.48158385264753</v>
       </c>
       <c r="BW18" t="n">
-        <v>20.51999964031471</v>
+        <v>20.43836731870658</v>
       </c>
       <c r="BX18" t="n">
-        <v>19.81494770903282</v>
+        <v>20.21593274135538</v>
       </c>
       <c r="BY18" t="n">
-        <v>21.73999787742813</v>
+        <v>21.49368719590965</v>
       </c>
       <c r="BZ18" t="n">
-        <v>19.98036237972136</v>
+        <v>19.86852168125357</v>
       </c>
       <c r="CA18" t="n">
-        <v>20.19706355047976</v>
+        <v>21.88969476737169</v>
       </c>
       <c r="CB18" t="n">
-        <v>20.35294545096007</v>
+        <v>19.76039198910782</v>
       </c>
       <c r="CC18" t="n">
-        <v>21.98204777391019</v>
+        <v>22.06373900038056</v>
       </c>
       <c r="CD18" t="n">
-        <v>21.53726697650117</v>
+        <v>20.30288613552053</v>
       </c>
       <c r="CE18" t="n">
-        <v>21.08883407763235</v>
+        <v>20.45630384926318</v>
       </c>
       <c r="CF18" t="n">
-        <v>19.17544707196349</v>
+        <v>20.97687556944005</v>
       </c>
       <c r="CG18" t="n">
-        <v>19.19841015076582</v>
+        <v>20.40539041332093</v>
       </c>
       <c r="CH18" t="n">
-        <v>21.42031137249424</v>
+        <v>21.44281302987558</v>
       </c>
       <c r="CI18" t="n">
-        <v>21.22275428196866</v>
+        <v>22.17481393563904</v>
       </c>
       <c r="CJ18" t="n">
-        <v>18.97734020272352</v>
+        <v>18.88861966269074</v>
       </c>
       <c r="CK18" t="n">
-        <v>20.22342347633879</v>
+        <v>20.93714423984918</v>
       </c>
       <c r="CL18" t="n">
-        <v>21.50305306900817</v>
+        <v>21.42771375018426</v>
       </c>
       <c r="CM18" t="n">
-        <v>19.95172479918848</v>
+        <v>19.18988858069296</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.56696645048588</v>
+        <v>20.78355962899681</v>
       </c>
       <c r="CO18" t="n">
-        <v>19.67755211782348</v>
+        <v>20.68355880784223</v>
       </c>
       <c r="CP18" t="n">
-        <v>20.40140451764169</v>
+        <v>19.55298796910864</v>
       </c>
       <c r="CQ18" t="n">
-        <v>21.96717429619084</v>
+        <v>18.04115540943081</v>
       </c>
       <c r="CR18" t="n">
-        <v>19.5058640793048</v>
+        <v>19.61199100613388</v>
       </c>
       <c r="CS18" t="n">
-        <v>21.12214477723744</v>
+        <v>21.86251017344109</v>
       </c>
       <c r="CT18" t="n">
-        <v>20.53204568464582</v>
+        <v>21.41759193135348</v>
       </c>
       <c r="CU18" t="n">
-        <v>20.8907762957776</v>
+        <v>20.64879512163485</v>
       </c>
       <c r="CV18" t="n">
-        <v>20.1337310060788</v>
+        <v>19.87763229994898</v>
       </c>
       <c r="CW18" t="n">
-        <v>21.01598839797724</v>
+        <v>20.42661579868675</v>
       </c>
       <c r="CX18" t="n">
-        <v>20.5385413201562</v>
+        <v>20.56808191222743</v>
       </c>
     </row>
     <row r="19">
@@ -6181,307 +6181,307 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.19473520248946</v>
+        <v>21.75168067510867</v>
       </c>
       <c r="C19" t="n">
-        <v>22.44142715968135</v>
+        <v>20.63209559318561</v>
       </c>
       <c r="D19" t="n">
-        <v>22.25902825370934</v>
+        <v>22.06520180445989</v>
       </c>
       <c r="E19" t="n">
-        <v>22.72066565920028</v>
+        <v>21.50673462289909</v>
       </c>
       <c r="F19" t="n">
-        <v>19.96466423393046</v>
+        <v>21.42002666566001</v>
       </c>
       <c r="G19" t="n">
-        <v>20.40595000951236</v>
+        <v>23.25724968443341</v>
       </c>
       <c r="H19" t="n">
-        <v>20.42011662888464</v>
+        <v>21.33815872460287</v>
       </c>
       <c r="I19" t="n">
-        <v>21.0643885597966</v>
+        <v>23.06223532046183</v>
       </c>
       <c r="J19" t="n">
-        <v>21.79746938803475</v>
+        <v>20.7000816217047</v>
       </c>
       <c r="K19" t="n">
-        <v>21.70402664154453</v>
+        <v>22.14252425364637</v>
       </c>
       <c r="L19" t="n">
-        <v>18.95817648753663</v>
+        <v>22.74649544129901</v>
       </c>
       <c r="M19" t="n">
-        <v>21.52871595399718</v>
+        <v>20.73349049608022</v>
       </c>
       <c r="N19" t="n">
-        <v>19.55775926295128</v>
+        <v>20.8064441679828</v>
       </c>
       <c r="O19" t="n">
-        <v>19.95789999224819</v>
+        <v>20.30462382895704</v>
       </c>
       <c r="P19" t="n">
-        <v>22.94381691237557</v>
+        <v>23.10367489105808</v>
       </c>
       <c r="Q19" t="n">
-        <v>21.54942101307974</v>
+        <v>22.58521392844534</v>
       </c>
       <c r="R19" t="n">
-        <v>22.81944911320159</v>
+        <v>22.4907697992968</v>
       </c>
       <c r="S19" t="n">
-        <v>21.82480124412097</v>
+        <v>21.66583665584933</v>
       </c>
       <c r="T19" t="n">
-        <v>20.11952511679835</v>
+        <v>22.35054677469923</v>
       </c>
       <c r="U19" t="n">
-        <v>21.25086171874124</v>
+        <v>20.01743317303372</v>
       </c>
       <c r="V19" t="n">
-        <v>20.61129235933262</v>
+        <v>21.21738412202643</v>
       </c>
       <c r="W19" t="n">
-        <v>19.85013354675302</v>
+        <v>21.19561877542328</v>
       </c>
       <c r="X19" t="n">
-        <v>19.61674266502243</v>
+        <v>21.871502982412</v>
       </c>
       <c r="Y19" t="n">
-        <v>20.42769572116142</v>
+        <v>19.25816913352332</v>
       </c>
       <c r="Z19" t="n">
-        <v>21.80907364589894</v>
+        <v>20.12779143246811</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.75694444873468</v>
+        <v>22.60828499949514</v>
       </c>
       <c r="AB19" t="n">
-        <v>21.84650768586187</v>
+        <v>20.68807484728176</v>
       </c>
       <c r="AC19" t="n">
-        <v>23.27338961669123</v>
+        <v>21.18863854924608</v>
       </c>
       <c r="AD19" t="n">
-        <v>21.43864060213253</v>
+        <v>18.90361095013459</v>
       </c>
       <c r="AE19" t="n">
-        <v>22.06278670510744</v>
+        <v>21.4680832157829</v>
       </c>
       <c r="AF19" t="n">
-        <v>22.0443985706069</v>
+        <v>21.34237042225409</v>
       </c>
       <c r="AG19" t="n">
-        <v>22.01505413172696</v>
+        <v>19.05746063286711</v>
       </c>
       <c r="AH19" t="n">
-        <v>21.06282758094685</v>
+        <v>21.25275649181044</v>
       </c>
       <c r="AI19" t="n">
-        <v>22.54818240504115</v>
+        <v>22.88038619320419</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22.44632608072554</v>
+        <v>22.73458684164649</v>
       </c>
       <c r="AK19" t="n">
-        <v>21.54579836405107</v>
+        <v>20.42945304955202</v>
       </c>
       <c r="AL19" t="n">
-        <v>22.68032564603277</v>
+        <v>21.26726672287921</v>
       </c>
       <c r="AM19" t="n">
-        <v>20.15989458239698</v>
+        <v>21.97934796772351</v>
       </c>
       <c r="AN19" t="n">
-        <v>21.57823530819939</v>
+        <v>23.10914322577074</v>
       </c>
       <c r="AO19" t="n">
-        <v>21.0286234909309</v>
+        <v>20.40723609900492</v>
       </c>
       <c r="AP19" t="n">
-        <v>21.92424246908413</v>
+        <v>22.76238993663076</v>
       </c>
       <c r="AQ19" t="n">
-        <v>20.45943562443972</v>
+        <v>22.19002120757783</v>
       </c>
       <c r="AR19" t="n">
-        <v>20.97253624458727</v>
+        <v>22.50528003036557</v>
       </c>
       <c r="AS19" t="n">
-        <v>21.3525904158553</v>
+        <v>20.63931143881182</v>
       </c>
       <c r="AT19" t="n">
-        <v>21.81496413212442</v>
+        <v>20.39597545283721</v>
       </c>
       <c r="AU19" t="n">
-        <v>20.71503363924038</v>
+        <v>21.36000261102236</v>
       </c>
       <c r="AV19" t="n">
-        <v>21.31334996011655</v>
+        <v>22.83509817160728</v>
       </c>
       <c r="AW19" t="n">
-        <v>21.52800909565012</v>
+        <v>22.35028170281908</v>
       </c>
       <c r="AX19" t="n">
-        <v>21.29956622234893</v>
+        <v>20.43898581976026</v>
       </c>
       <c r="AY19" t="n">
-        <v>20.74649865316149</v>
+        <v>21.31595159153281</v>
       </c>
       <c r="AZ19" t="n">
-        <v>23.52450104448348</v>
+        <v>23.11778260556811</v>
       </c>
       <c r="BA19" t="n">
-        <v>23.03922315427428</v>
+        <v>21.57259025889997</v>
       </c>
       <c r="BB19" t="n">
-        <v>21.40045061643733</v>
+        <v>22.25756544963001</v>
       </c>
       <c r="BC19" t="n">
-        <v>20.15037162966578</v>
+        <v>21.45842281837311</v>
       </c>
       <c r="BD19" t="n">
-        <v>22.29692371509326</v>
+        <v>22.00249757858965</v>
       </c>
       <c r="BE19" t="n">
-        <v>21.13620340436226</v>
+        <v>21.76480664191445</v>
       </c>
       <c r="BF19" t="n">
-        <v>22.65105974696917</v>
+        <v>20.51061413226211</v>
       </c>
       <c r="BG19" t="n">
-        <v>24.09481792083453</v>
+        <v>22.05085847050085</v>
       </c>
       <c r="BH19" t="n">
-        <v>23.0923749749822</v>
+        <v>20.26009175309241</v>
       </c>
       <c r="BI19" t="n">
-        <v>23.18226379478304</v>
+        <v>22.03775213864915</v>
       </c>
       <c r="BJ19" t="n">
-        <v>21.32948989237437</v>
+        <v>21.77433941212269</v>
       </c>
       <c r="BK19" t="n">
-        <v>19.67140637719489</v>
+        <v>20.68356862531927</v>
       </c>
       <c r="BL19" t="n">
-        <v>21.05054591716673</v>
+        <v>20.9612363285114</v>
       </c>
       <c r="BM19" t="n">
-        <v>20.55884739697176</v>
+        <v>20.81265863095068</v>
       </c>
       <c r="BN19" t="n">
-        <v>20.02229282416975</v>
+        <v>21.31618721098183</v>
       </c>
       <c r="BO19" t="n">
-        <v>21.6829583358114</v>
+        <v>21.17946902568842</v>
       </c>
       <c r="BP19" t="n">
-        <v>23.38557392685551</v>
+        <v>22.85798271059327</v>
       </c>
       <c r="BQ19" t="n">
-        <v>21.77861001463616</v>
+        <v>20.98409141506626</v>
       </c>
       <c r="BR19" t="n">
-        <v>22.27278253904583</v>
+        <v>21.35236461388332</v>
       </c>
       <c r="BS19" t="n">
-        <v>20.96627269423418</v>
+        <v>22.14426194708288</v>
       </c>
       <c r="BT19" t="n">
-        <v>21.44711308482018</v>
+        <v>22.5973188776387</v>
       </c>
       <c r="BU19" t="n">
-        <v>21.81534701372908</v>
+        <v>20.33965258704457</v>
       </c>
       <c r="BV19" t="n">
-        <v>22.70620451551672</v>
+        <v>21.48279961386956</v>
       </c>
       <c r="BW19" t="n">
-        <v>21.41450924356215</v>
+        <v>21.38256317326595</v>
       </c>
       <c r="BX19" t="n">
-        <v>20.87406694985132</v>
+        <v>21.18938467750131</v>
       </c>
       <c r="BY19" t="n">
-        <v>22.70110924493168</v>
+        <v>22.5714498256318</v>
       </c>
       <c r="BZ19" t="n">
-        <v>21.01046115840233</v>
+        <v>20.77177865654584</v>
       </c>
       <c r="CA19" t="n">
-        <v>21.14257494696282</v>
+        <v>22.85048215813283</v>
       </c>
       <c r="CB19" t="n">
-        <v>21.38039351083957</v>
+        <v>20.60900488718173</v>
       </c>
       <c r="CC19" t="n">
-        <v>23.02565540100159</v>
+        <v>23.11343346323829</v>
       </c>
       <c r="CD19" t="n">
-        <v>22.46870992838237</v>
+        <v>21.23203179777379</v>
       </c>
       <c r="CE19" t="n">
-        <v>21.99894365190027</v>
+        <v>21.2931554098402</v>
       </c>
       <c r="CF19" t="n">
-        <v>20.04349857458148</v>
+        <v>21.9030367186724</v>
       </c>
       <c r="CG19" t="n">
-        <v>20.12997091237153</v>
+        <v>21.40783335917327</v>
       </c>
       <c r="CH19" t="n">
-        <v>22.46381100733818</v>
+        <v>22.41738415840435</v>
       </c>
       <c r="CI19" t="n">
-        <v>22.27287089633922</v>
+        <v>23.06756621049588</v>
       </c>
       <c r="CJ19" t="n">
-        <v>19.85145890615376</v>
+        <v>19.66086240685128</v>
       </c>
       <c r="CK19" t="n">
-        <v>21.1280058110318</v>
+        <v>21.87841448624989</v>
       </c>
       <c r="CL19" t="n">
-        <v>22.50325763009482</v>
+        <v>22.45185332030045</v>
       </c>
       <c r="CM19" t="n">
-        <v>20.83207760054068</v>
+        <v>19.96791381883151</v>
       </c>
       <c r="CN19" t="n">
-        <v>21.44616078954706</v>
+        <v>21.80205414981357</v>
       </c>
       <c r="CO19" t="n">
-        <v>20.57536039335719</v>
+        <v>21.65612717105433</v>
       </c>
       <c r="CP19" t="n">
-        <v>21.41618803213641</v>
+        <v>20.45413418683679</v>
       </c>
       <c r="CQ19" t="n">
-        <v>23.11546568098609</v>
+        <v>18.96363500477224</v>
       </c>
       <c r="CR19" t="n">
-        <v>20.2900743279801</v>
+        <v>20.51572903780124</v>
       </c>
       <c r="CS19" t="n">
-        <v>22.11656684434608</v>
+        <v>22.9081991056655</v>
       </c>
       <c r="CT19" t="n">
-        <v>21.45598808406658</v>
+        <v>22.41779649244013</v>
       </c>
       <c r="CU19" t="n">
-        <v>21.78909508011752</v>
+        <v>21.53697245218989</v>
       </c>
       <c r="CV19" t="n">
-        <v>21.14734624080546</v>
+        <v>20.82834695926454</v>
       </c>
       <c r="CW19" t="n">
-        <v>22.00654237913114</v>
+        <v>21.30388591224762</v>
       </c>
       <c r="CX19" t="n">
-        <v>21.49267795926968</v>
+        <v>21.50134924586744</v>
       </c>
     </row>
     <row r="20">
@@ -6489,307 +6489,307 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>23.71262353957125</v>
+        <v>24.21707496244439</v>
       </c>
       <c r="C20" t="n">
-        <v>25.16210530255237</v>
+        <v>23.0313691726403</v>
       </c>
       <c r="D20" t="n">
-        <v>24.87399180378706</v>
+        <v>24.62159428650224</v>
       </c>
       <c r="E20" t="n">
-        <v>25.33817193583199</v>
+        <v>23.95495814288753</v>
       </c>
       <c r="F20" t="n">
-        <v>22.41592135432502</v>
+        <v>24.01999892829388</v>
       </c>
       <c r="G20" t="n">
-        <v>22.8312889905148</v>
+        <v>25.93738164711903</v>
       </c>
       <c r="H20" t="n">
-        <v>22.92796168695198</v>
+        <v>23.89630853503583</v>
       </c>
       <c r="I20" t="n">
-        <v>23.4983374681653</v>
+        <v>25.7553263528435</v>
       </c>
       <c r="J20" t="n">
-        <v>24.29283643278112</v>
+        <v>23.36214942663218</v>
       </c>
       <c r="K20" t="n">
-        <v>24.38097774166839</v>
+        <v>24.74862262195474</v>
       </c>
       <c r="L20" t="n">
-        <v>21.37950012042871</v>
+        <v>25.4207271002821</v>
       </c>
       <c r="M20" t="n">
-        <v>24.11928307362436</v>
+        <v>23.36060808273651</v>
       </c>
       <c r="N20" t="n">
-        <v>21.86219601417573</v>
+        <v>23.28479752501457</v>
       </c>
       <c r="O20" t="n">
-        <v>22.47635774299845</v>
+        <v>22.82102972700542</v>
       </c>
       <c r="P20" t="n">
-        <v>25.58165518396224</v>
+        <v>25.7694046149224</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.03721878302638</v>
+        <v>25.14149841824023</v>
       </c>
       <c r="R20" t="n">
-        <v>25.58505203101894</v>
+        <v>25.09031991041784</v>
       </c>
       <c r="S20" t="n">
-        <v>24.33571917250261</v>
+        <v>24.1915102522258</v>
       </c>
       <c r="T20" t="n">
-        <v>22.55882455015519</v>
+        <v>25.03734480429668</v>
       </c>
       <c r="U20" t="n">
-        <v>23.80272834386702</v>
+        <v>22.42923385319461</v>
       </c>
       <c r="V20" t="n">
-        <v>23.17771830291237</v>
+        <v>23.76903476265727</v>
       </c>
       <c r="W20" t="n">
-        <v>22.1744801414196</v>
+        <v>23.66519530797909</v>
       </c>
       <c r="X20" t="n">
-        <v>22.02509741074141</v>
+        <v>24.42597123895403</v>
       </c>
       <c r="Y20" t="n">
-        <v>22.86814379933223</v>
+        <v>21.69895100591357</v>
       </c>
       <c r="Z20" t="n">
-        <v>24.48772316955115</v>
+        <v>22.51499933263761</v>
       </c>
       <c r="AA20" t="n">
-        <v>23.20987054022646</v>
+        <v>25.16874191703308</v>
       </c>
       <c r="AB20" t="n">
-        <v>24.4151229268221</v>
+        <v>23.1701195756815</v>
       </c>
       <c r="AC20" t="n">
-        <v>25.92689658163768</v>
+        <v>23.57857570803339</v>
       </c>
       <c r="AD20" t="n">
-        <v>24.05866015288712</v>
+        <v>21.20004645756943</v>
       </c>
       <c r="AE20" t="n">
-        <v>24.81830707400218</v>
+        <v>24.05291692881728</v>
       </c>
       <c r="AF20" t="n">
-        <v>24.59931843109288</v>
+        <v>23.87921630750489</v>
       </c>
       <c r="AG20" t="n">
-        <v>24.67077984648501</v>
+        <v>21.4639696929021</v>
       </c>
       <c r="AH20" t="n">
-        <v>23.51250408753758</v>
+        <v>23.80333702744366</v>
       </c>
       <c r="AI20" t="n">
-        <v>25.19885211912233</v>
+        <v>25.62260388070638</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25.04698556675238</v>
+        <v>25.32478089714606</v>
       </c>
       <c r="AK20" t="n">
-        <v>24.29748991689924</v>
+        <v>22.89436628051266</v>
       </c>
       <c r="AL20" t="n">
-        <v>25.50162311111204</v>
+        <v>23.79241999297243</v>
       </c>
       <c r="AM20" t="n">
-        <v>22.56718904059537</v>
+        <v>24.37715874309887</v>
       </c>
       <c r="AN20" t="n">
-        <v>24.14570190434565</v>
+        <v>25.72090627833261</v>
       </c>
       <c r="AO20" t="n">
-        <v>23.57739761078829</v>
+        <v>22.8157773767877</v>
       </c>
       <c r="AP20" t="n">
-        <v>24.62184954090535</v>
+        <v>25.38799563182252</v>
       </c>
       <c r="AQ20" t="n">
-        <v>23.01037940672351</v>
+        <v>24.77611155767365</v>
       </c>
       <c r="AR20" t="n">
-        <v>23.41076557294648</v>
+        <v>25.14326556410787</v>
       </c>
       <c r="AS20" t="n">
-        <v>23.97113734505352</v>
+        <v>23.02296541229195</v>
       </c>
       <c r="AT20" t="n">
-        <v>24.48715375588269</v>
+        <v>22.90030585412335</v>
       </c>
       <c r="AU20" t="n">
-        <v>23.19198309705508</v>
+        <v>23.93793463769589</v>
       </c>
       <c r="AV20" t="n">
-        <v>23.95755977430379</v>
+        <v>25.4879277306378</v>
       </c>
       <c r="AW20" t="n">
-        <v>24.14271739132473</v>
+        <v>24.85749844235571</v>
       </c>
       <c r="AX20" t="n">
-        <v>23.96837863400459</v>
+        <v>22.92678358970689</v>
       </c>
       <c r="AY20" t="n">
-        <v>23.22286887983069</v>
+        <v>23.84728005468574</v>
       </c>
       <c r="AZ20" t="n">
-        <v>26.34068360402362</v>
+        <v>25.64415324281459</v>
       </c>
       <c r="BA20" t="n">
-        <v>25.7909245245995</v>
+        <v>24.03802381614386</v>
       </c>
       <c r="BB20" t="n">
-        <v>24.01441278385672</v>
+        <v>24.96688477156289</v>
       </c>
       <c r="BC20" t="n">
-        <v>22.54665087862253</v>
+        <v>24.03564798669958</v>
       </c>
       <c r="BD20" t="n">
-        <v>24.85477900121495</v>
+        <v>24.59573505197238</v>
       </c>
       <c r="BE20" t="n">
-        <v>23.57377496175963</v>
+        <v>24.48617200817844</v>
       </c>
       <c r="BF20" t="n">
-        <v>25.30390894095378</v>
+        <v>22.9006396483428</v>
       </c>
       <c r="BG20" t="n">
-        <v>26.69502580291742</v>
+        <v>24.68086239540762</v>
       </c>
       <c r="BH20" t="n">
-        <v>25.83786188233953</v>
+        <v>22.83395934427035</v>
       </c>
       <c r="BI20" t="n">
-        <v>25.93554577891209</v>
+        <v>24.75412040909852</v>
       </c>
       <c r="BJ20" t="n">
-        <v>23.95024575390715</v>
+        <v>24.31908836639267</v>
       </c>
       <c r="BK20" t="n">
-        <v>22.18207886865047</v>
+        <v>23.2272867444998</v>
       </c>
       <c r="BL20" t="n">
-        <v>23.42215384631575</v>
+        <v>23.35351004683481</v>
       </c>
       <c r="BM20" t="n">
-        <v>23.05754256643553</v>
+        <v>23.27011057935905</v>
       </c>
       <c r="BN20" t="n">
-        <v>22.51339908387969</v>
+        <v>23.77470926438782</v>
       </c>
       <c r="BO20" t="n">
-        <v>24.18532524168904</v>
+        <v>23.71387035915564</v>
       </c>
       <c r="BP20" t="n">
-        <v>26.11120989563297</v>
+        <v>25.53782014896762</v>
       </c>
       <c r="BQ20" t="n">
-        <v>24.38458075574298</v>
+        <v>23.48433774590274</v>
       </c>
       <c r="BR20" t="n">
-        <v>24.90727305096102</v>
+        <v>23.78279886547082</v>
       </c>
       <c r="BS20" t="n">
-        <v>23.40921441157377</v>
+        <v>24.8423304403251</v>
       </c>
       <c r="BT20" t="n">
-        <v>24.06507096539585</v>
+        <v>25.22053892590914</v>
       </c>
       <c r="BU20" t="n">
-        <v>24.34858006742825</v>
+        <v>22.78995741216601</v>
       </c>
       <c r="BV20" t="n">
-        <v>25.30853297264078</v>
+        <v>24.00057014122684</v>
       </c>
       <c r="BW20" t="n">
-        <v>23.96462835777436</v>
+        <v>23.89240117917292</v>
       </c>
       <c r="BX20" t="n">
-        <v>23.51933705155914</v>
+        <v>23.76828863440204</v>
       </c>
       <c r="BY20" t="n">
-        <v>25.35387989909994</v>
+        <v>25.27966959013592</v>
       </c>
       <c r="BZ20" t="n">
-        <v>23.70859837398384</v>
+        <v>23.2513984681161</v>
       </c>
       <c r="CA20" t="n">
-        <v>23.6909269153074</v>
+        <v>25.4498751896212</v>
       </c>
       <c r="CB20" t="n">
-        <v>23.95839425985239</v>
+        <v>23.0535370358022</v>
       </c>
       <c r="CC20" t="n">
-        <v>25.69472306706035</v>
+        <v>25.83779316000024</v>
       </c>
       <c r="CD20" t="n">
-        <v>25.15480109963277</v>
+        <v>23.75892276130353</v>
       </c>
       <c r="CE20" t="n">
-        <v>24.61830543169302</v>
+        <v>23.70827439724144</v>
       </c>
       <c r="CF20" t="n">
-        <v>22.46147444780207</v>
+        <v>24.41602613471</v>
       </c>
       <c r="CG20" t="n">
-        <v>22.58854205316274</v>
+        <v>24.04332525374679</v>
       </c>
       <c r="CH20" t="n">
-        <v>25.14213655424799</v>
+        <v>24.97030125357367</v>
       </c>
       <c r="CI20" t="n">
-        <v>25.05266006848293</v>
+        <v>25.69512558361909</v>
       </c>
       <c r="CJ20" t="n">
-        <v>22.30327562273974</v>
+        <v>21.97195540751053</v>
       </c>
       <c r="CK20" t="n">
-        <v>23.61276998057231</v>
+        <v>24.53310936591848</v>
       </c>
       <c r="CL20" t="n">
-        <v>25.24159741416523</v>
+        <v>25.07526971811174</v>
       </c>
       <c r="CM20" t="n">
-        <v>23.29407504081971</v>
+        <v>22.18272682213527</v>
       </c>
       <c r="CN20" t="n">
-        <v>23.91602202893711</v>
+        <v>24.51048989881263</v>
       </c>
       <c r="CO20" t="n">
-        <v>23.01853773014579</v>
+        <v>24.25995770216589</v>
       </c>
       <c r="CP20" t="n">
-        <v>23.97632097293194</v>
+        <v>22.94655598847042</v>
       </c>
       <c r="CQ20" t="n">
-        <v>25.82666995851112</v>
+        <v>21.33870850331725</v>
       </c>
       <c r="CR20" t="n">
-        <v>22.62533795711791</v>
+        <v>23.07684372630101</v>
       </c>
       <c r="CS20" t="n">
-        <v>24.71087442272645</v>
+        <v>25.68229414112458</v>
       </c>
       <c r="CT20" t="n">
-        <v>24.07421103652239</v>
+        <v>25.09799717746505</v>
       </c>
       <c r="CU20" t="n">
-        <v>24.34403457555759</v>
+        <v>24.0356774391307</v>
       </c>
       <c r="CV20" t="n">
-        <v>23.67744751932809</v>
+        <v>23.41403479280163</v>
       </c>
       <c r="CW20" t="n">
-        <v>24.6251678481457</v>
+        <v>23.7040823345443</v>
       </c>
       <c r="CX20" t="n">
-        <v>24.06330931731536</v>
+        <v>24.04526184926819</v>
       </c>
     </row>
     <row r="21">
@@ -6797,307 +6797,307 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17.82318778413393</v>
+        <v>18.26448337719287</v>
       </c>
       <c r="C21" t="n">
-        <v>19.01395939209193</v>
+        <v>17.35305826100126</v>
       </c>
       <c r="D21" t="n">
-        <v>18.48020280024702</v>
+        <v>18.76573430255017</v>
       </c>
       <c r="E21" t="n">
-        <v>19.05367108672872</v>
+        <v>17.83546944791406</v>
       </c>
       <c r="F21" t="n">
-        <v>17.00135696343188</v>
+        <v>18.05291674692769</v>
       </c>
       <c r="G21" t="n">
-        <v>17.16311953266063</v>
+        <v>19.39398411092883</v>
       </c>
       <c r="H21" t="n">
-        <v>17.39882733897325</v>
+        <v>17.95325953746959</v>
       </c>
       <c r="I21" t="n">
-        <v>17.66631431847233</v>
+        <v>19.17890282388244</v>
       </c>
       <c r="J21" t="n">
-        <v>18.38132117147529</v>
+        <v>17.52275335168032</v>
       </c>
       <c r="K21" t="n">
-        <v>18.27731481968738</v>
+        <v>18.5272874201427</v>
       </c>
       <c r="L21" t="n">
-        <v>16.05077974879491</v>
+        <v>18.99237076007554</v>
       </c>
       <c r="M21" t="n">
-        <v>18.22432989608918</v>
+        <v>17.68380906256201</v>
       </c>
       <c r="N21" t="n">
-        <v>16.65095157283211</v>
+        <v>17.58340572484869</v>
       </c>
       <c r="O21" t="n">
-        <v>17.06094904907967</v>
+        <v>17.36002866970142</v>
       </c>
       <c r="P21" t="n">
-        <v>19.01324271626783</v>
+        <v>19.22422029791047</v>
       </c>
       <c r="Q21" t="n">
-        <v>18.07754879682724</v>
+        <v>19.12657567124608</v>
       </c>
       <c r="R21" t="n">
-        <v>19.24401233162808</v>
+        <v>18.71540009775343</v>
       </c>
       <c r="S21" t="n">
-        <v>18.27169922281909</v>
+        <v>18.16369715787489</v>
       </c>
       <c r="T21" t="n">
-        <v>17.1630900802295</v>
+        <v>18.61507529985645</v>
       </c>
       <c r="U21" t="n">
-        <v>17.80722456646288</v>
+        <v>16.96579806158407</v>
       </c>
       <c r="V21" t="n">
-        <v>17.60716401929147</v>
+        <v>18.05249459541486</v>
       </c>
       <c r="W21" t="n">
-        <v>16.97000975923529</v>
+        <v>17.84260675372393</v>
       </c>
       <c r="X21" t="n">
-        <v>16.62891133687177</v>
+        <v>18.42591215220218</v>
       </c>
       <c r="Y21" t="n">
-        <v>17.23779126304564</v>
+        <v>16.40151893361412</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.50700451257297</v>
+        <v>16.84140080997895</v>
       </c>
       <c r="AA21" t="n">
-        <v>17.50803695359366</v>
+        <v>18.93258232488692</v>
       </c>
       <c r="AB21" t="n">
-        <v>18.38314722220519</v>
+        <v>17.68465336558766</v>
       </c>
       <c r="AC21" t="n">
-        <v>19.26529662185616</v>
+        <v>17.94712361431805</v>
       </c>
       <c r="AD21" t="n">
-        <v>18.12600786350886</v>
+        <v>15.9834122213295</v>
       </c>
       <c r="AE21" t="n">
-        <v>18.69609893788794</v>
+        <v>18.29151089149079</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.41683098593789</v>
+        <v>18.21347176648021</v>
       </c>
       <c r="AG21" t="n">
-        <v>18.57545196251305</v>
+        <v>16.08900900439828</v>
       </c>
       <c r="AH21" t="n">
-        <v>17.77997125019299</v>
+        <v>17.72903817929667</v>
       </c>
       <c r="AI21" t="n">
-        <v>18.83970899206517</v>
+        <v>19.16349920240281</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18.79706187179269</v>
+        <v>18.92752632421004</v>
       </c>
       <c r="AK21" t="n">
-        <v>18.35305665507002</v>
+        <v>17.35956724828042</v>
       </c>
       <c r="AL21" t="n">
-        <v>19.10673455014325</v>
+        <v>17.95990596942735</v>
       </c>
       <c r="AM21" t="n">
-        <v>17.08769185654335</v>
+        <v>18.47332074884025</v>
       </c>
       <c r="AN21" t="n">
-        <v>18.06605253121051</v>
+        <v>19.33313538821961</v>
       </c>
       <c r="AO21" t="n">
-        <v>17.88870962591536</v>
+        <v>17.09150103763583</v>
       </c>
       <c r="AP21" t="n">
-        <v>18.34729379604609</v>
+        <v>18.94612062572848</v>
       </c>
       <c r="AQ21" t="n">
-        <v>17.28662339385488</v>
+        <v>18.66182612553268</v>
       </c>
       <c r="AR21" t="n">
-        <v>17.83005020058662</v>
+        <v>19.01710098474552</v>
       </c>
       <c r="AS21" t="n">
-        <v>18.13558972110231</v>
+        <v>17.25126084154791</v>
       </c>
       <c r="AT21" t="n">
-        <v>18.44131577368181</v>
+        <v>17.21053794677575</v>
       </c>
       <c r="AU21" t="n">
-        <v>17.58973799754108</v>
+        <v>17.93694289062501</v>
       </c>
       <c r="AV21" t="n">
-        <v>18.05457590054786</v>
+        <v>19.00368049362847</v>
       </c>
       <c r="AW21" t="n">
-        <v>18.1215310939775</v>
+        <v>18.37964238290103</v>
       </c>
       <c r="AX21" t="n">
-        <v>17.94943072142303</v>
+        <v>17.23584740259124</v>
       </c>
       <c r="AY21" t="n">
-        <v>17.65613359477929</v>
+        <v>17.92318860528851</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19.61283530915953</v>
+        <v>19.07193159402771</v>
       </c>
       <c r="BA21" t="n">
-        <v>19.42806057374323</v>
+        <v>18.31561279763005</v>
       </c>
       <c r="BB21" t="n">
-        <v>17.87539712704578</v>
+        <v>18.68867692524384</v>
       </c>
       <c r="BC21" t="n">
-        <v>17.11431685428252</v>
+        <v>17.99602446746658</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.74416530548786</v>
+        <v>18.59661844301661</v>
       </c>
       <c r="BE21" t="n">
-        <v>17.87160758090738</v>
+        <v>18.34145239720582</v>
       </c>
       <c r="BF21" t="n">
-        <v>19.16833921858474</v>
+        <v>17.20309629917756</v>
       </c>
       <c r="BG21" t="n">
-        <v>19.93067612840943</v>
+        <v>18.51650783035007</v>
       </c>
       <c r="BH21" t="n">
-        <v>19.2265863098777</v>
+        <v>17.32153434221789</v>
       </c>
       <c r="BI21" t="n">
-        <v>19.42640142012306</v>
+        <v>18.87407997919085</v>
       </c>
       <c r="BJ21" t="n">
-        <v>18.04017366172656</v>
+        <v>18.5159580516357</v>
       </c>
       <c r="BK21" t="n">
-        <v>16.62647660256524</v>
+        <v>17.47921284099698</v>
       </c>
       <c r="BL21" t="n">
-        <v>17.73953306225506</v>
+        <v>17.45439425903362</v>
       </c>
       <c r="BM21" t="n">
-        <v>17.49199519610627</v>
+        <v>17.90784388867113</v>
       </c>
       <c r="BN21" t="n">
-        <v>16.81981217796256</v>
+        <v>17.93686435080867</v>
       </c>
       <c r="BO21" t="n">
-        <v>18.25303619896136</v>
+        <v>17.82615266220076</v>
       </c>
       <c r="BP21" t="n">
-        <v>19.78881358514577</v>
+        <v>18.9249050578397</v>
       </c>
       <c r="BQ21" t="n">
-        <v>18.44058928038067</v>
+        <v>17.64223204728716</v>
       </c>
       <c r="BR21" t="n">
-        <v>18.8030308978345</v>
+        <v>17.91601202957047</v>
       </c>
       <c r="BS21" t="n">
-        <v>17.66252477233394</v>
+        <v>18.69986884907225</v>
       </c>
       <c r="BT21" t="n">
-        <v>18.04739932482982</v>
+        <v>19.0577355222243</v>
       </c>
       <c r="BU21" t="n">
-        <v>18.24364087343172</v>
+        <v>17.25762256667143</v>
       </c>
       <c r="BV21" t="n">
-        <v>19.18047362020923</v>
+        <v>18.19262926271905</v>
       </c>
       <c r="BW21" t="n">
-        <v>18.03714987879748</v>
+        <v>18.17680348972659</v>
       </c>
       <c r="BX21" t="n">
-        <v>17.61198440051932</v>
+        <v>18.17133515501394</v>
       </c>
       <c r="BY21" t="n">
-        <v>19.06292896757976</v>
+        <v>18.99683771212987</v>
       </c>
       <c r="BZ21" t="n">
-        <v>17.77694746726391</v>
+        <v>17.45058507794114</v>
       </c>
       <c r="CA21" t="n">
-        <v>17.77719290418997</v>
+        <v>19.25769789462529</v>
       </c>
       <c r="CB21" t="n">
-        <v>17.90444704161444</v>
+        <v>17.28714372013813</v>
       </c>
       <c r="CC21" t="n">
-        <v>19.11132912939913</v>
+        <v>19.33902587444509</v>
       </c>
       <c r="CD21" t="n">
-        <v>18.91263321153662</v>
+        <v>17.89932231859827</v>
       </c>
       <c r="CE21" t="n">
-        <v>18.45062274191807</v>
+        <v>17.77675111772306</v>
       </c>
       <c r="CF21" t="n">
-        <v>16.83530415673558</v>
+        <v>18.23418664303982</v>
       </c>
       <c r="CG21" t="n">
-        <v>17.23364828773372</v>
+        <v>18.25484261473717</v>
       </c>
       <c r="CH21" t="n">
-        <v>18.63634977260748</v>
+        <v>18.65200864849022</v>
       </c>
       <c r="CI21" t="n">
-        <v>18.68673306478943</v>
+        <v>19.09457069608763</v>
       </c>
       <c r="CJ21" t="n">
-        <v>16.88890758138746</v>
+        <v>16.7288532531641</v>
       </c>
       <c r="CK21" t="n">
-        <v>17.74220341601061</v>
+        <v>18.69156326349432</v>
       </c>
       <c r="CL21" t="n">
-        <v>18.9462188004989</v>
+        <v>18.88264081917188</v>
       </c>
       <c r="CM21" t="n">
-        <v>17.77950001129495</v>
+        <v>16.90701100905377</v>
       </c>
       <c r="CN21" t="n">
-        <v>18.01346030669401</v>
+        <v>18.46083291804224</v>
       </c>
       <c r="CO21" t="n">
-        <v>17.45823289255722</v>
+        <v>18.40887882953349</v>
       </c>
       <c r="CP21" t="n">
-        <v>18.01644481971492</v>
+        <v>17.40134061309612</v>
       </c>
       <c r="CQ21" t="n">
-        <v>19.37545853174969</v>
+        <v>16.27428443114374</v>
       </c>
       <c r="CR21" t="n">
-        <v>17.19628297011009</v>
+        <v>17.37733688172728</v>
       </c>
       <c r="CS21" t="n">
-        <v>18.64180828984309</v>
+        <v>19.48139892651497</v>
       </c>
       <c r="CT21" t="n">
-        <v>18.25048365493031</v>
+        <v>18.81168991258596</v>
       </c>
       <c r="CU21" t="n">
-        <v>18.42564708032203</v>
+        <v>18.19759690610254</v>
       </c>
       <c r="CV21" t="n">
-        <v>17.82977531122943</v>
+        <v>17.82962804907379</v>
       </c>
       <c r="CW21" t="n">
-        <v>18.60305870795647</v>
+        <v>18.05225897596584</v>
       </c>
       <c r="CX21" t="n">
-        <v>18.11816762634275</v>
+        <v>18.1142096122983</v>
       </c>
     </row>
   </sheetData>

--- a/output/100_model_iteration.xlsx
+++ b/output/100_model_iteration.xlsx
@@ -1253,307 +1253,307 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.07275613491221</v>
+        <v>11.95215824692253</v>
       </c>
       <c r="C3" t="n">
-        <v>12.00020497956837</v>
+        <v>11.94214442033921</v>
       </c>
       <c r="D3" t="n">
-        <v>12.01649217398183</v>
+        <v>11.93495802714413</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99154596481691</v>
+        <v>11.9468568093196</v>
       </c>
       <c r="F3" t="n">
-        <v>11.96977080073672</v>
+        <v>11.94798581917948</v>
       </c>
       <c r="G3" t="n">
-        <v>12.01495083008616</v>
+        <v>11.95009657674361</v>
       </c>
       <c r="H3" t="n">
-        <v>12.08292704112821</v>
+        <v>11.96630523134073</v>
       </c>
       <c r="I3" t="n">
-        <v>12.00323857997449</v>
+        <v>11.89518742764509</v>
       </c>
       <c r="J3" t="n">
-        <v>11.91164151916827</v>
+        <v>11.97876360970762</v>
       </c>
       <c r="K3" t="n">
-        <v>12.00241391190293</v>
+        <v>11.95956062461255</v>
       </c>
       <c r="L3" t="n">
-        <v>12.05210016321486</v>
+        <v>12.0405057228277</v>
       </c>
       <c r="M3" t="n">
-        <v>11.89247780398137</v>
+        <v>12.07004651124849</v>
       </c>
       <c r="N3" t="n">
-        <v>11.93077578192404</v>
+        <v>11.97858689512086</v>
       </c>
       <c r="O3" t="n">
-        <v>11.90579030285095</v>
+        <v>11.89198693012925</v>
       </c>
       <c r="P3" t="n">
-        <v>12.03954361007754</v>
+        <v>12.0460525973567</v>
       </c>
       <c r="Q3" t="n">
-        <v>12.11332195005169</v>
+        <v>11.93122738586799</v>
       </c>
       <c r="R3" t="n">
-        <v>11.99431449334289</v>
+        <v>11.95626195232628</v>
       </c>
       <c r="S3" t="n">
-        <v>12.02485666442201</v>
+        <v>12.07437601862422</v>
       </c>
       <c r="T3" t="n">
-        <v>12.03404582293376</v>
+        <v>11.99128089293677</v>
       </c>
       <c r="U3" t="n">
-        <v>11.89694475603569</v>
+        <v>12.02539662565935</v>
       </c>
       <c r="V3" t="n">
-        <v>11.95415119476215</v>
+        <v>12.03568534159985</v>
       </c>
       <c r="W3" t="n">
-        <v>12.08615699107518</v>
+        <v>11.93604776709584</v>
       </c>
       <c r="X3" t="n">
-        <v>12.07590754504284</v>
+        <v>12.03866985462076</v>
       </c>
       <c r="Y3" t="n">
-        <v>11.95550600659401</v>
+        <v>12.00575185409737</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.949262091195</v>
+        <v>11.912505457148</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.06715035552096</v>
+        <v>12.02817497166236</v>
       </c>
       <c r="AB3" t="n">
-        <v>12.00663542703119</v>
+        <v>11.94934063101134</v>
       </c>
       <c r="AC3" t="n">
-        <v>11.92440423932347</v>
+        <v>12.0521787030312</v>
       </c>
       <c r="AD3" t="n">
-        <v>11.90041032543168</v>
+        <v>12.01819059751017</v>
       </c>
       <c r="AE3" t="n">
-        <v>11.93377011242199</v>
+        <v>11.90046923029394</v>
       </c>
       <c r="AF3" t="n">
-        <v>11.97389414109456</v>
+        <v>12.01349784348387</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.98520387464748</v>
+        <v>12.03552826196717</v>
       </c>
       <c r="AH3" t="n">
-        <v>11.92802688835214</v>
+        <v>11.98395705506308</v>
       </c>
       <c r="AI3" t="n">
-        <v>11.97435556251555</v>
+        <v>11.90929514215512</v>
       </c>
       <c r="AJ3" t="n">
-        <v>12.01286952495315</v>
+        <v>11.91562741484751</v>
       </c>
       <c r="AK3" t="n">
-        <v>11.91828795112602</v>
+        <v>11.98037367594259</v>
       </c>
       <c r="AL3" t="n">
-        <v>11.8852030534929</v>
+        <v>12.04941017450522</v>
       </c>
       <c r="AM3" t="n">
-        <v>12.067160172998</v>
+        <v>11.95611469017065</v>
       </c>
       <c r="AN3" t="n">
-        <v>12.0564100356365</v>
+        <v>11.96423374368477</v>
       </c>
       <c r="AO3" t="n">
-        <v>12.01322295412668</v>
+        <v>11.94174190378047</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.00792151652375</v>
+        <v>12.0450119447902</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.96358579019996</v>
+        <v>11.97975517488891</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.92270581579513</v>
+        <v>11.91663861498288</v>
       </c>
       <c r="AS3" t="n">
-        <v>12.07873497843107</v>
+        <v>11.91624591590118</v>
       </c>
       <c r="AT3" t="n">
-        <v>12.01555951366279</v>
+        <v>11.99040713747999</v>
       </c>
       <c r="AU3" t="n">
-        <v>11.8822676278572</v>
+        <v>11.92381519070093</v>
       </c>
       <c r="AV3" t="n">
-        <v>12.01662961866042</v>
+        <v>12.07037048799089</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.99457956522304</v>
+        <v>11.9005772225414</v>
       </c>
       <c r="AX3" t="n">
-        <v>11.91235819499237</v>
+        <v>11.94348941469403</v>
       </c>
       <c r="AY3" t="n">
-        <v>11.87467871810337</v>
+        <v>12.02587768203442</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.99005370830646</v>
+        <v>11.9558496182905</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.9389733752545</v>
+        <v>12.01935887727823</v>
       </c>
       <c r="BB3" t="n">
-        <v>12.08706019896309</v>
+        <v>11.93440824842975</v>
       </c>
       <c r="BC3" t="n">
-        <v>11.91565686727863</v>
+        <v>12.03128711188482</v>
       </c>
       <c r="BD3" t="n">
-        <v>11.95407265494581</v>
+        <v>11.91986856492985</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.00601692597751</v>
+        <v>12.03254374894626</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.0040730655231</v>
+        <v>11.94436317015081</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.989484294638</v>
+        <v>11.91695277424824</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.92785017376538</v>
+        <v>11.98920940528081</v>
       </c>
       <c r="BI3" t="n">
-        <v>12.01442068632586</v>
+        <v>12.0902999663871</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.99786842003226</v>
+        <v>11.91967221538901</v>
       </c>
       <c r="BK3" t="n">
-        <v>11.99505080412107</v>
+        <v>11.99372544472034</v>
       </c>
       <c r="BL3" t="n">
-        <v>12.06967344712088</v>
+        <v>11.89253670884362</v>
       </c>
       <c r="BM3" t="n">
-        <v>12.07280522229742</v>
+        <v>11.8777123185095</v>
       </c>
       <c r="BN3" t="n">
-        <v>12.05277756913079</v>
+        <v>11.94145719694624</v>
       </c>
       <c r="BO3" t="n">
-        <v>11.97479734898246</v>
+        <v>11.89653242199991</v>
       </c>
       <c r="BP3" t="n">
-        <v>11.96312436877897</v>
+        <v>12.0648236134619</v>
       </c>
       <c r="BQ3" t="n">
-        <v>12.03507665802322</v>
+        <v>11.92325559450951</v>
       </c>
       <c r="BR3" t="n">
-        <v>12.01102383926917</v>
+        <v>11.94622849078888</v>
       </c>
       <c r="BS3" t="n">
-        <v>11.96300655905446</v>
+        <v>11.98488971538212</v>
       </c>
       <c r="BT3" t="n">
-        <v>11.95594779306093</v>
+        <v>12.04066280246038</v>
       </c>
       <c r="BU3" t="n">
-        <v>11.93191460926096</v>
+        <v>11.95060708554982</v>
       </c>
       <c r="BV3" t="n">
-        <v>11.96208371621247</v>
+        <v>12.03421272004348</v>
       </c>
       <c r="BW3" t="n">
-        <v>12.09357900371928</v>
+        <v>11.93938570929028</v>
       </c>
       <c r="BX3" t="n">
-        <v>11.8823363501965</v>
+        <v>12.00692995134246</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.94191861836724</v>
+        <v>11.91938750855477</v>
       </c>
       <c r="BZ3" t="n">
-        <v>12.03808080599821</v>
+        <v>11.96767967812668</v>
       </c>
       <c r="CA3" t="n">
-        <v>12.03536136485745</v>
+        <v>11.95911883814564</v>
       </c>
       <c r="CB3" t="n">
-        <v>12.13395828679496</v>
+        <v>11.98399632497125</v>
       </c>
       <c r="CC3" t="n">
-        <v>11.98942538977574</v>
+        <v>11.94283164373219</v>
       </c>
       <c r="CD3" t="n">
-        <v>11.9755925646229</v>
+        <v>11.94215423781626</v>
       </c>
       <c r="CE3" t="n">
-        <v>12.05667510751665</v>
+        <v>11.99788805498635</v>
       </c>
       <c r="CF3" t="n">
-        <v>12.0832019304854</v>
+        <v>11.95190299251943</v>
       </c>
       <c r="CG3" t="n">
-        <v>11.98003988172314</v>
+        <v>12.03715796315622</v>
       </c>
       <c r="CH3" t="n">
-        <v>11.95206988962915</v>
+        <v>12.06504941543387</v>
       </c>
       <c r="CI3" t="n">
-        <v>12.04798664033406</v>
+        <v>11.90232473345496</v>
       </c>
       <c r="CJ3" t="n">
-        <v>11.99239026784257</v>
+        <v>12.03272046353302</v>
       </c>
       <c r="CK3" t="n">
-        <v>12.07089081427414</v>
+        <v>12.01326222403485</v>
       </c>
       <c r="CL3" t="n">
-        <v>12.09722128770204</v>
+        <v>12.03226885958907</v>
       </c>
       <c r="CM3" t="n">
-        <v>11.99079983656169</v>
+        <v>11.93949370153775</v>
       </c>
       <c r="CN3" t="n">
-        <v>11.92620083762225</v>
+        <v>12.00747973005684</v>
       </c>
       <c r="CO3" t="n">
-        <v>11.94482459157181</v>
+        <v>11.92829196023229</v>
       </c>
       <c r="CP3" t="n">
-        <v>11.92685860858409</v>
+        <v>11.98191501983825</v>
       </c>
       <c r="CQ3" t="n">
-        <v>11.92816433303074</v>
+        <v>11.99023042289322</v>
       </c>
       <c r="CR3" t="n">
-        <v>11.97135141454056</v>
+        <v>11.88610626138081</v>
       </c>
       <c r="CS3" t="n">
-        <v>11.98455592116268</v>
+        <v>11.97689828906955</v>
       </c>
       <c r="CT3" t="n">
-        <v>11.98667649620385</v>
+        <v>12.02447378281735</v>
       </c>
       <c r="CU3" t="n">
-        <v>11.95268839068282</v>
+        <v>11.95124522155758</v>
       </c>
       <c r="CV3" t="n">
-        <v>11.98134560616979</v>
+        <v>11.96863197339979</v>
       </c>
       <c r="CW3" t="n">
-        <v>12.02231393786801</v>
+        <v>11.99917414447891</v>
       </c>
       <c r="CX3" t="n">
-        <v>11.99086443556062</v>
+        <v>11.97467178345109</v>
       </c>
     </row>
     <row r="4">
@@ -1561,307 +1561,307 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.0598954173151</v>
+        <v>12.76671981372923</v>
       </c>
       <c r="C4" t="n">
-        <v>12.96716973945932</v>
+        <v>12.72692088072515</v>
       </c>
       <c r="D4" t="n">
-        <v>13.01820287898862</v>
+        <v>12.75074593141273</v>
       </c>
       <c r="E4" t="n">
-        <v>13.00782353142669</v>
+        <v>12.94033786702187</v>
       </c>
       <c r="F4" t="n">
-        <v>12.80196496748134</v>
+        <v>12.7826581352313</v>
       </c>
       <c r="G4" t="n">
-        <v>12.96625046888413</v>
+        <v>12.87094440123942</v>
       </c>
       <c r="H4" t="n">
-        <v>13.13661777186416</v>
+        <v>12.80585646984717</v>
       </c>
       <c r="I4" t="n">
-        <v>12.91597810882386</v>
+        <v>12.64563442955815</v>
       </c>
       <c r="J4" t="n">
-        <v>12.64791371527181</v>
+        <v>13.00094559977275</v>
       </c>
       <c r="K4" t="n">
-        <v>12.96168918042905</v>
+        <v>12.84979704060568</v>
       </c>
       <c r="L4" t="n">
-        <v>13.02849212125256</v>
+        <v>12.99915047386048</v>
       </c>
       <c r="M4" t="n">
-        <v>12.65504253863694</v>
+        <v>13.08440278358064</v>
       </c>
       <c r="N4" t="n">
-        <v>12.72008070349772</v>
+        <v>12.95579521558859</v>
       </c>
       <c r="O4" t="n">
-        <v>12.69380700384971</v>
+        <v>12.64575574272383</v>
       </c>
       <c r="P4" t="n">
-        <v>12.92854422554993</v>
+        <v>12.93136457934971</v>
       </c>
       <c r="Q4" t="n">
-        <v>13.19798329164159</v>
+        <v>12.83229397253982</v>
       </c>
       <c r="R4" t="n">
-        <v>13.02289034103031</v>
+        <v>12.92874297441759</v>
       </c>
       <c r="S4" t="n">
-        <v>12.96496341211036</v>
+        <v>12.97984194993154</v>
       </c>
       <c r="T4" t="n">
-        <v>13.04482840491653</v>
+        <v>12.8485843427412</v>
       </c>
       <c r="U4" t="n">
-        <v>12.73042605531134</v>
+        <v>13.04025305580944</v>
       </c>
       <c r="V4" t="n">
-        <v>12.86840706493838</v>
+        <v>13.01438262475906</v>
       </c>
       <c r="W4" t="n">
-        <v>13.03580841073596</v>
+        <v>12.77008517045165</v>
       </c>
       <c r="X4" t="n">
-        <v>13.07202639586967</v>
+        <v>13.00286347726316</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.7659013079954</v>
+        <v>12.96198988564572</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.7888024820929</v>
+        <v>12.77663952929299</v>
       </c>
       <c r="AA4" t="n">
-        <v>13.03960878241585</v>
+        <v>12.94180037205457</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.90313314824121</v>
+        <v>12.83416895773837</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.7869348690969</v>
+        <v>12.97078490580607</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.677722045778</v>
+        <v>12.94601312097167</v>
       </c>
       <c r="AE4" t="n">
-        <v>12.9145714688922</v>
+        <v>12.71062034688588</v>
       </c>
       <c r="AF4" t="n">
-        <v>12.92834085099798</v>
+        <v>13.00546305448308</v>
       </c>
       <c r="AG4" t="n">
-        <v>12.77818002258695</v>
+        <v>13.00139427353413</v>
       </c>
       <c r="AH4" t="n">
-        <v>12.69523567354788</v>
+        <v>12.85673101590583</v>
       </c>
       <c r="AI4" t="n">
-        <v>13.02229360294584</v>
+        <v>12.79822185539429</v>
       </c>
       <c r="AJ4" t="n">
-        <v>13.03272687249457</v>
+        <v>12.83341058458251</v>
       </c>
       <c r="AK4" t="n">
-        <v>12.79571838078321</v>
+        <v>12.9467808229745</v>
       </c>
       <c r="AL4" t="n">
-        <v>12.82196724829008</v>
+        <v>12.96109806616564</v>
       </c>
       <c r="AM4" t="n">
-        <v>13.11768716666757</v>
+        <v>12.77985127835849</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.98618392727585</v>
+        <v>12.91322265935671</v>
       </c>
       <c r="AO4" t="n">
-        <v>12.90111339036216</v>
+        <v>12.79483862660397</v>
       </c>
       <c r="AP4" t="n">
-        <v>12.92453384723579</v>
+        <v>13.04267626580504</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.95110901040358</v>
+        <v>12.80992586753182</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.86450461199473</v>
+        <v>12.75383882731462</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.07642155480993</v>
+        <v>12.72766586296559</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.98947795674407</v>
+        <v>12.88790429076242</v>
       </c>
       <c r="AU4" t="n">
-        <v>12.65863709738206</v>
+        <v>12.84701847255318</v>
       </c>
       <c r="AV4" t="n">
-        <v>12.98112211853797</v>
+        <v>13.03394059961619</v>
       </c>
       <c r="AW4" t="n">
-        <v>12.93269689053537</v>
+        <v>12.79618935860917</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.73882276879558</v>
+        <v>12.77921711174741</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.71977883959509</v>
+        <v>12.97170690748779</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.8978105103756</v>
+        <v>12.81714816302593</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.73687926662299</v>
+        <v>12.94659108011701</v>
       </c>
       <c r="BB4" t="n">
-        <v>13.02798290097868</v>
+        <v>12.83805335550365</v>
       </c>
       <c r="BC4" t="n">
-        <v>12.76353956826169</v>
+        <v>13.04596041662425</v>
       </c>
       <c r="BD4" t="n">
-        <v>12.91036704756793</v>
+        <v>12.7841418470257</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.94712593663913</v>
+        <v>12.93110438527078</v>
       </c>
       <c r="BF4" t="n">
-        <v>12.98891123661283</v>
+        <v>12.90308326520506</v>
       </c>
       <c r="BG4" t="n">
-        <v>12.97528084245459</v>
+        <v>12.69588591678122</v>
       </c>
       <c r="BH4" t="n">
-        <v>12.71468428872405</v>
+        <v>12.97433866433001</v>
       </c>
       <c r="BI4" t="n">
-        <v>13.032077229765</v>
+        <v>13.08814088339861</v>
       </c>
       <c r="BJ4" t="n">
-        <v>13.0434049948444</v>
+        <v>12.90738085103209</v>
       </c>
       <c r="BK4" t="n">
-        <v>12.85781847953028</v>
+        <v>12.8730173785246</v>
       </c>
       <c r="BL4" t="n">
-        <v>13.06040927498924</v>
+        <v>12.86774793175553</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.05630216739519</v>
+        <v>12.61835116102484</v>
       </c>
       <c r="BN4" t="n">
-        <v>13.08425465436702</v>
+        <v>12.76226454878829</v>
       </c>
       <c r="BO4" t="n">
-        <v>12.86056000422809</v>
+        <v>12.74735183703469</v>
       </c>
       <c r="BP4" t="n">
-        <v>12.84081015941285</v>
+        <v>13.05249184050714</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12.95233683210329</v>
+        <v>12.71292216540381</v>
       </c>
       <c r="BR4" t="n">
-        <v>13.00621187713636</v>
+        <v>12.7810107183233</v>
       </c>
       <c r="BS4" t="n">
-        <v>12.86174114904296</v>
+        <v>12.89494943707492</v>
       </c>
       <c r="BT4" t="n">
-        <v>13.00129447273219</v>
+        <v>13.04877764944422</v>
       </c>
       <c r="BU4" t="n">
-        <v>12.70767016792176</v>
+        <v>12.80914282579172</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.73690311816876</v>
+        <v>13.0204808802561</v>
       </c>
       <c r="BW4" t="n">
-        <v>13.06473245909722</v>
+        <v>12.79014844657844</v>
       </c>
       <c r="BX4" t="n">
-        <v>12.72711392448931</v>
+        <v>12.94969712101675</v>
       </c>
       <c r="BY4" t="n">
-        <v>12.83964539878626</v>
+        <v>12.78355332440247</v>
       </c>
       <c r="BZ4" t="n">
-        <v>12.85361883207127</v>
+        <v>12.85461837852178</v>
       </c>
       <c r="CA4" t="n">
-        <v>13.08717956951612</v>
+        <v>12.82002111497146</v>
       </c>
       <c r="CB4" t="n">
-        <v>13.06185142158692</v>
+        <v>12.89613832593422</v>
       </c>
       <c r="CC4" t="n">
-        <v>12.9708630420005</v>
+        <v>12.85183770792546</v>
       </c>
       <c r="CD4" t="n">
-        <v>12.86309204587184</v>
+        <v>12.83796635282824</v>
       </c>
       <c r="CE4" t="n">
-        <v>12.97408850741948</v>
+        <v>12.96980334805973</v>
       </c>
       <c r="CF4" t="n">
-        <v>13.00067486878251</v>
+        <v>12.75166008265865</v>
       </c>
       <c r="CG4" t="n">
-        <v>12.88476418452671</v>
+        <v>12.9873436908312</v>
       </c>
       <c r="CH4" t="n">
-        <v>12.81169377253786</v>
+        <v>12.99179995206576</v>
       </c>
       <c r="CI4" t="n">
-        <v>13.24233106146069</v>
+        <v>12.65994049994158</v>
       </c>
       <c r="CJ4" t="n">
-        <v>12.84571643018527</v>
+        <v>12.86058525538527</v>
       </c>
       <c r="CK4" t="n">
-        <v>13.02398511262629</v>
+        <v>12.98320709062486</v>
       </c>
       <c r="CL4" t="n">
-        <v>13.05043425980864</v>
+        <v>12.91694788249538</v>
       </c>
       <c r="CM4" t="n">
-        <v>12.84698461837034</v>
+        <v>12.7931524765727</v>
       </c>
       <c r="CN4" t="n">
-        <v>12.80849208471616</v>
+        <v>12.92753847644721</v>
       </c>
       <c r="CO4" t="n">
-        <v>12.73869892561823</v>
+        <v>12.81453736483815</v>
       </c>
       <c r="CP4" t="n">
-        <v>12.68585144249201</v>
+        <v>12.83947411800831</v>
       </c>
       <c r="CQ4" t="n">
-        <v>12.74961452865543</v>
+        <v>12.92155879470194</v>
       </c>
       <c r="CR4" t="n">
-        <v>12.84595535760828</v>
+        <v>12.68368709510668</v>
       </c>
       <c r="CS4" t="n">
-        <v>12.90395242748183</v>
+        <v>12.9865748478723</v>
       </c>
       <c r="CT4" t="n">
-        <v>13.00362695977267</v>
+        <v>12.90940672629606</v>
       </c>
       <c r="CU4" t="n">
-        <v>12.91921410577512</v>
+        <v>12.86596568609903</v>
       </c>
       <c r="CV4" t="n">
-        <v>12.93178847559217</v>
+        <v>12.87740370364535</v>
       </c>
       <c r="CW4" t="n">
-        <v>12.9748032920085</v>
+        <v>12.89156647202547</v>
       </c>
       <c r="CX4" t="n">
-        <v>12.91015174974516</v>
+        <v>12.87393661390406</v>
       </c>
     </row>
     <row r="5">
@@ -1869,307 +1869,307 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.24784879061232</v>
+        <v>13.78578821272037</v>
       </c>
       <c r="C5" t="n">
-        <v>14.19263507487201</v>
+        <v>13.76789711591398</v>
       </c>
       <c r="D5" t="n">
-        <v>14.34803694451572</v>
+        <v>13.74642460237573</v>
       </c>
       <c r="E5" t="n">
-        <v>14.31316279208769</v>
+        <v>14.09256335732234</v>
       </c>
       <c r="F5" t="n">
-        <v>13.96123583054294</v>
+        <v>13.84644513146259</v>
       </c>
       <c r="G5" t="n">
-        <v>14.34141026950796</v>
+        <v>13.89739856585876</v>
       </c>
       <c r="H5" t="n">
-        <v>14.474923287141</v>
+        <v>13.87836609762894</v>
       </c>
       <c r="I5" t="n">
-        <v>14.17011677414972</v>
+        <v>13.7032213777695</v>
       </c>
       <c r="J5" t="n">
-        <v>13.5655356879224</v>
+        <v>14.10215221063437</v>
       </c>
       <c r="K5" t="n">
-        <v>14.15286858151551</v>
+        <v>14.00347144706348</v>
       </c>
       <c r="L5" t="n">
-        <v>14.36221163247428</v>
+        <v>14.2980879128047</v>
       </c>
       <c r="M5" t="n">
-        <v>13.73045624656507</v>
+        <v>14.29822391702174</v>
       </c>
       <c r="N5" t="n">
-        <v>13.67013914967443</v>
+        <v>14.1499529162455</v>
       </c>
       <c r="O5" t="n">
-        <v>13.61165535224007</v>
+        <v>13.72644384463075</v>
       </c>
       <c r="P5" t="n">
-        <v>14.12454816516104</v>
+        <v>14.00261261307835</v>
       </c>
       <c r="Q5" t="n">
-        <v>14.59436179981944</v>
+        <v>13.87784864677321</v>
       </c>
       <c r="R5" t="n">
-        <v>14.29445708565912</v>
+        <v>14.14827008672846</v>
       </c>
       <c r="S5" t="n">
-        <v>14.22267596891255</v>
+        <v>14.16758356503831</v>
       </c>
       <c r="T5" t="n">
-        <v>14.39280597233462</v>
+        <v>13.88126195331348</v>
       </c>
       <c r="U5" t="n">
-        <v>13.68431801332736</v>
+        <v>14.44572975217192</v>
       </c>
       <c r="V5" t="n">
-        <v>13.98674528038131</v>
+        <v>14.36067099758407</v>
       </c>
       <c r="W5" t="n">
-        <v>14.3442891257696</v>
+        <v>13.81181189782659</v>
       </c>
       <c r="X5" t="n">
-        <v>14.31805346343197</v>
+        <v>14.25623368213911</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.75931687940621</v>
+        <v>14.21116973723828</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.82127326567696</v>
+        <v>13.82873079857845</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.31703657558805</v>
+        <v>14.19301331881062</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.031908550514</v>
+        <v>14.05466419901432</v>
       </c>
       <c r="AC5" t="n">
-        <v>13.87606102270822</v>
+        <v>14.09378751076567</v>
       </c>
       <c r="AD5" t="n">
-        <v>13.61922332226429</v>
+        <v>14.17408328966827</v>
       </c>
       <c r="AE5" t="n">
-        <v>13.99797359980913</v>
+        <v>13.74718070240696</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.07151363992609</v>
+        <v>14.3113595735792</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.71779224345444</v>
+        <v>14.21805958724055</v>
       </c>
       <c r="AH5" t="n">
-        <v>13.71408871389769</v>
+        <v>14.0291418574523</v>
       </c>
       <c r="AI5" t="n">
-        <v>14.32298463714005</v>
+        <v>13.92810907805632</v>
       </c>
       <c r="AJ5" t="n">
-        <v>14.40058590003955</v>
+        <v>13.85849820791529</v>
       </c>
       <c r="AK5" t="n">
-        <v>13.85672721718964</v>
+        <v>14.08122998107844</v>
       </c>
       <c r="AL5" t="n">
-        <v>13.9058347657497</v>
+        <v>14.14581665613435</v>
       </c>
       <c r="AM5" t="n">
-        <v>14.47430087328964</v>
+        <v>13.78322316432599</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.26373205109</v>
+        <v>14.14921210119606</v>
       </c>
       <c r="AO5" t="n">
-        <v>14.05437457409498</v>
+        <v>13.9387808858808</v>
       </c>
       <c r="AP5" t="n">
-        <v>14.15695389400622</v>
+        <v>14.2543775173323</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14.1750037418005</v>
+        <v>13.8316803874701</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.97568883253383</v>
+        <v>13.77867589373141</v>
       </c>
       <c r="AS5" t="n">
-        <v>14.264489734425</v>
+        <v>13.74249373798824</v>
       </c>
       <c r="AT5" t="n">
-        <v>14.26887751206668</v>
+        <v>14.14969086433702</v>
       </c>
       <c r="AU5" t="n">
-        <v>13.56054436479255</v>
+        <v>13.92950890471714</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.31873997859577</v>
+        <v>14.33958049251806</v>
       </c>
       <c r="AW5" t="n">
-        <v>14.17569292250098</v>
+        <v>13.81537948828964</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.67352649347123</v>
+        <v>13.71705144325796</v>
       </c>
       <c r="AY5" t="n">
-        <v>13.74433668325593</v>
+        <v>14.26850373084564</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.10458687815754</v>
+        <v>14.03563161777291</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.87381899922315</v>
+        <v>14.05035132440706</v>
       </c>
       <c r="BB5" t="n">
-        <v>14.20991634306389</v>
+        <v>13.97937910314508</v>
       </c>
       <c r="BC5" t="n">
-        <v>13.9189661838846</v>
+        <v>14.33509124835243</v>
       </c>
       <c r="BD5" t="n">
-        <v>14.1061404610368</v>
+        <v>13.91199286581892</v>
       </c>
       <c r="BE5" t="n">
-        <v>14.11045138923385</v>
+        <v>14.15338812244696</v>
       </c>
       <c r="BF5" t="n">
-        <v>14.19218961324712</v>
+        <v>14.04409675299519</v>
       </c>
       <c r="BG5" t="n">
-        <v>14.22578274969583</v>
+        <v>13.72135781432416</v>
       </c>
       <c r="BH5" t="n">
-        <v>13.77477493424514</v>
+        <v>14.06527839662087</v>
       </c>
       <c r="BI5" t="n">
-        <v>14.30419667577398</v>
+        <v>14.4468484365479</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14.19203954358107</v>
+        <v>14.08298182858465</v>
       </c>
       <c r="BK5" t="n">
-        <v>13.92853577021456</v>
+        <v>14.089769961163</v>
       </c>
       <c r="BL5" t="n">
-        <v>14.34107899443992</v>
+        <v>13.97181770769922</v>
       </c>
       <c r="BM5" t="n">
-        <v>14.21361978999082</v>
+        <v>13.61417698823961</v>
       </c>
       <c r="BN5" t="n">
-        <v>14.36155999653551</v>
+        <v>13.96517361385324</v>
       </c>
       <c r="BO5" t="n">
-        <v>14.02725437040189</v>
+        <v>13.80152707570422</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.03168391645993</v>
+        <v>14.34814454750968</v>
       </c>
       <c r="BQ5" t="n">
-        <v>14.11785740017961</v>
+        <v>13.74368161023923</v>
       </c>
       <c r="BR5" t="n">
-        <v>14.22100185215237</v>
+        <v>13.87870984769755</v>
       </c>
       <c r="BS5" t="n">
-        <v>13.95608207426726</v>
+        <v>14.1128146937625</v>
       </c>
       <c r="BT5" t="n">
-        <v>14.14741136580681</v>
+        <v>14.18216793903104</v>
       </c>
       <c r="BU5" t="n">
-        <v>13.77572109065107</v>
+        <v>13.80221884289394</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.84738886087526</v>
+        <v>14.22871823633506</v>
       </c>
       <c r="BW5" t="n">
-        <v>14.26174590509363</v>
+        <v>13.89334501570543</v>
       </c>
       <c r="BX5" t="n">
-        <v>13.75168980073618</v>
+        <v>14.136237372157</v>
       </c>
       <c r="BY5" t="n">
-        <v>13.93319539937027</v>
+        <v>13.83604627067639</v>
       </c>
       <c r="BZ5" t="n">
-        <v>13.92873906763741</v>
+        <v>14.02892089701448</v>
       </c>
       <c r="CA5" t="n">
-        <v>14.45848775956584</v>
+        <v>13.87460708641103</v>
       </c>
       <c r="CB5" t="n">
-        <v>14.20256531804922</v>
+        <v>13.94113613139779</v>
       </c>
       <c r="CC5" t="n">
-        <v>14.22452205770877</v>
+        <v>14.08749933235694</v>
       </c>
       <c r="CD5" t="n">
-        <v>13.97434365202142</v>
+        <v>13.91385682631114</v>
       </c>
       <c r="CE5" t="n">
-        <v>14.17671532061473</v>
+        <v>14.18717626048733</v>
       </c>
       <c r="CF5" t="n">
-        <v>14.28899705352086</v>
+        <v>13.84822761601729</v>
       </c>
       <c r="CG5" t="n">
-        <v>13.98757312898885</v>
+        <v>14.12352335581556</v>
       </c>
       <c r="CH5" t="n">
-        <v>13.92868232225343</v>
+        <v>14.15330598563973</v>
       </c>
       <c r="CI5" t="n">
-        <v>14.67310868978149</v>
+        <v>13.72592062226044</v>
       </c>
       <c r="CJ5" t="n">
-        <v>13.91491849193581</v>
+        <v>13.90332957595057</v>
       </c>
       <c r="CK5" t="n">
-        <v>14.21911250128582</v>
+        <v>14.13488007756562</v>
       </c>
       <c r="CL5" t="n">
-        <v>14.22233240971886</v>
+        <v>14.12151957161872</v>
       </c>
       <c r="CM5" t="n">
-        <v>13.91667630374014</v>
+        <v>13.90649639716654</v>
       </c>
       <c r="CN5" t="n">
-        <v>13.9398639207951</v>
+        <v>14.18605942990443</v>
       </c>
       <c r="CO5" t="n">
-        <v>13.70920898642766</v>
+        <v>13.83084984496859</v>
       </c>
       <c r="CP5" t="n">
-        <v>13.7040788461013</v>
+        <v>14.04329424768488</v>
       </c>
       <c r="CQ5" t="n">
-        <v>13.77688897923332</v>
+        <v>13.99136050052902</v>
       </c>
       <c r="CR5" t="n">
-        <v>13.99550849924859</v>
+        <v>13.68396136357542</v>
       </c>
       <c r="CS5" t="n">
-        <v>14.10269152095434</v>
+        <v>14.17563735713113</v>
       </c>
       <c r="CT5" t="n">
-        <v>14.27753724328618</v>
+        <v>14.05891400036713</v>
       </c>
       <c r="CU5" t="n">
-        <v>14.19277013748023</v>
+        <v>14.06255306109441</v>
       </c>
       <c r="CV5" t="n">
-        <v>14.09928270348933</v>
+        <v>14.04543263189624</v>
       </c>
       <c r="CW5" t="n">
-        <v>14.18140384143527</v>
+        <v>13.94641339005546</v>
       </c>
       <c r="CX5" t="n">
-        <v>14.07647772391497</v>
+        <v>14.01227285810839</v>
       </c>
     </row>
     <row r="6">
@@ -2177,307 +2177,307 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.60658945935367</v>
+        <v>14.93877268475315</v>
       </c>
       <c r="C6" t="n">
-        <v>15.56111195269313</v>
+        <v>15.04350025257969</v>
       </c>
       <c r="D6" t="n">
-        <v>15.86165375300003</v>
+        <v>14.89799215705186</v>
       </c>
       <c r="E6" t="n">
-        <v>15.92227290771522</v>
+        <v>15.56457015404795</v>
       </c>
       <c r="F6" t="n">
-        <v>15.25087558441776</v>
+        <v>15.23575259232437</v>
       </c>
       <c r="G6" t="n">
-        <v>15.9675267956803</v>
+        <v>15.12290455916427</v>
       </c>
       <c r="H6" t="n">
-        <v>16.01827829273913</v>
+        <v>15.09079469603254</v>
       </c>
       <c r="I6" t="n">
-        <v>15.66233652052307</v>
+        <v>14.89093549091002</v>
       </c>
       <c r="J6" t="n">
-        <v>14.62161989919663</v>
+        <v>15.53936146150848</v>
       </c>
       <c r="K6" t="n">
-        <v>15.63957632596985</v>
+        <v>15.3370431143503</v>
       </c>
       <c r="L6" t="n">
-        <v>15.96833767084097</v>
+        <v>15.76703670098648</v>
       </c>
       <c r="M6" t="n">
-        <v>14.86280723370989</v>
+        <v>15.82767260569998</v>
       </c>
       <c r="N6" t="n">
-        <v>14.93070289613144</v>
+        <v>15.53670984496515</v>
       </c>
       <c r="O6" t="n">
-        <v>14.75971086829307</v>
+        <v>14.86186602094897</v>
       </c>
       <c r="P6" t="n">
-        <v>15.52260448792753</v>
+        <v>15.38683475439337</v>
       </c>
       <c r="Q6" t="n">
-        <v>16.14819145781469</v>
+        <v>15.15638128696609</v>
       </c>
       <c r="R6" t="n">
-        <v>15.81554703132375</v>
+        <v>15.63632708281576</v>
       </c>
       <c r="S6" t="n">
-        <v>15.70600844928407</v>
+        <v>15.64361801889956</v>
       </c>
       <c r="T6" t="n">
-        <v>15.93591329461495</v>
+        <v>15.11245170111511</v>
       </c>
       <c r="U6" t="n">
-        <v>14.83475357263752</v>
+        <v>16.09328172852891</v>
       </c>
       <c r="V6" t="n">
-        <v>15.25512091011173</v>
+        <v>15.91324170689005</v>
       </c>
       <c r="W6" t="n">
-        <v>15.84952768616812</v>
+        <v>15.12946894918428</v>
       </c>
       <c r="X6" t="n">
-        <v>15.73807895651393</v>
+        <v>15.75690343430106</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.84509977991646</v>
+        <v>15.67456467514132</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.12351531322054</v>
+        <v>15.06456780879418</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.91088095814466</v>
+        <v>15.76367982316925</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.32524274193967</v>
+        <v>15.35038677653325</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.17630472955119</v>
+        <v>15.53910825147097</v>
       </c>
       <c r="AD6" t="n">
-        <v>14.70461741616213</v>
+        <v>15.71752501066723</v>
       </c>
       <c r="AE6" t="n">
-        <v>15.37105025593739</v>
+        <v>15.05284958967441</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.37245821855763</v>
+        <v>15.84127033128481</v>
       </c>
       <c r="AG6" t="n">
-        <v>14.8058256971197</v>
+        <v>15.54839300592808</v>
       </c>
       <c r="AH6" t="n">
-        <v>14.87326773158964</v>
+        <v>15.32689400224608</v>
       </c>
       <c r="AI6" t="n">
-        <v>15.81691259677618</v>
+        <v>15.25240895426677</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15.95936760772475</v>
+        <v>15.0998445309834</v>
       </c>
       <c r="AK6" t="n">
-        <v>15.05375810922772</v>
+        <v>15.40023894152754</v>
       </c>
       <c r="AL6" t="n">
-        <v>15.24271422431108</v>
+        <v>15.52733001956049</v>
       </c>
       <c r="AM6" t="n">
-        <v>16.08741705415042</v>
+        <v>14.91820226267163</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.86362574571965</v>
+        <v>15.63957639998981</v>
       </c>
       <c r="AO6" t="n">
-        <v>15.34268629726694</v>
+        <v>15.29024295616673</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.62369373086518</v>
+        <v>15.69753909137868</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.71972159831436</v>
+        <v>15.10820295483853</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.26612903115984</v>
+        <v>14.96554249902598</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.69537979810593</v>
+        <v>15.02212602689903</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.77851026710328</v>
+        <v>15.59726952817056</v>
       </c>
       <c r="AU6" t="n">
-        <v>14.69628960141293</v>
+        <v>15.34660677715647</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.90965046920312</v>
+        <v>15.94415307674333</v>
       </c>
       <c r="AW6" t="n">
-        <v>15.65468866326682</v>
+        <v>15.03042141279805</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.91857368097628</v>
+        <v>14.97666570650835</v>
       </c>
       <c r="AY6" t="n">
-        <v>15.06134308056354</v>
+        <v>15.71185092565976</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.56903602591515</v>
+        <v>15.36270474441428</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.26408053675224</v>
+        <v>15.33605613654255</v>
       </c>
       <c r="BB6" t="n">
-        <v>15.64210074334892</v>
+        <v>15.33536843744054</v>
       </c>
       <c r="BC6" t="n">
-        <v>15.27285601679453</v>
+        <v>15.82350611420505</v>
       </c>
       <c r="BD6" t="n">
-        <v>15.45684736967473</v>
+        <v>15.19992363460188</v>
       </c>
       <c r="BE6" t="n">
-        <v>15.4738365159095</v>
+        <v>15.52216745432171</v>
       </c>
       <c r="BF6" t="n">
-        <v>15.72990512262538</v>
+        <v>15.42430254148963</v>
       </c>
       <c r="BG6" t="n">
-        <v>15.71375024193945</v>
+        <v>14.91565549179245</v>
       </c>
       <c r="BH6" t="n">
-        <v>14.96117246756597</v>
+        <v>15.4594455119497</v>
       </c>
       <c r="BI6" t="n">
-        <v>15.84963325003953</v>
+        <v>15.96393071396959</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15.70293350118126</v>
+        <v>15.41260322629046</v>
       </c>
       <c r="BK6" t="n">
-        <v>15.21177438591566</v>
+        <v>15.44144217634143</v>
       </c>
       <c r="BL6" t="n">
-        <v>15.84018462473185</v>
+        <v>15.18533029534668</v>
       </c>
       <c r="BM6" t="n">
-        <v>15.60094975283983</v>
+        <v>14.7754668283658</v>
       </c>
       <c r="BN6" t="n">
-        <v>15.7563537753199</v>
+        <v>15.27459556897338</v>
       </c>
       <c r="BO6" t="n">
-        <v>15.3979543864292</v>
+        <v>15.08420447464414</v>
       </c>
       <c r="BP6" t="n">
-        <v>15.42854821560325</v>
+        <v>15.89911837712873</v>
       </c>
       <c r="BQ6" t="n">
-        <v>15.46190350923645</v>
+        <v>14.92821195457004</v>
       </c>
       <c r="BR6" t="n">
-        <v>15.62436764788496</v>
+        <v>15.08005447841571</v>
       </c>
       <c r="BS6" t="n">
-        <v>15.22276420089976</v>
+        <v>15.59870491978094</v>
       </c>
       <c r="BT6" t="n">
-        <v>15.57756051074058</v>
+        <v>15.48569091438209</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.98780039391213</v>
+        <v>14.96090335884902</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.13133101678349</v>
+        <v>15.64307999432036</v>
       </c>
       <c r="BW6" t="n">
-        <v>15.72630324339516</v>
+        <v>15.2110146691519</v>
       </c>
       <c r="BX6" t="n">
-        <v>15.07006618544012</v>
+        <v>15.49037578682639</v>
       </c>
       <c r="BY6" t="n">
-        <v>15.22632985945991</v>
+        <v>15.10841984639862</v>
       </c>
       <c r="BZ6" t="n">
-        <v>15.18119054809242</v>
+        <v>15.50012298975959</v>
       </c>
       <c r="CA6" t="n">
-        <v>16.0626757682289</v>
+        <v>15.12892102597241</v>
       </c>
       <c r="CB6" t="n">
-        <v>15.47252856823409</v>
+        <v>15.17895427177719</v>
       </c>
       <c r="CC6" t="n">
-        <v>15.66878490828919</v>
+        <v>15.47774389183262</v>
       </c>
       <c r="CD6" t="n">
-        <v>15.34387323074777</v>
+        <v>15.25173849276285</v>
       </c>
       <c r="CE6" t="n">
-        <v>15.55141559229608</v>
+        <v>15.62744633013694</v>
       </c>
       <c r="CF6" t="n">
-        <v>15.78277751793589</v>
+        <v>15.18273739968271</v>
       </c>
       <c r="CG6" t="n">
-        <v>15.32270651298269</v>
+        <v>15.42065527361242</v>
       </c>
       <c r="CH6" t="n">
-        <v>15.2812132326813</v>
+        <v>15.69841662965994</v>
       </c>
       <c r="CI6" t="n">
-        <v>16.34055813279553</v>
+        <v>15.00175730300161</v>
       </c>
       <c r="CJ6" t="n">
-        <v>15.2713303820274</v>
+        <v>15.2233130441679</v>
       </c>
       <c r="CK6" t="n">
-        <v>15.60928894368737</v>
+        <v>15.51449805949855</v>
       </c>
       <c r="CL6" t="n">
-        <v>15.71448656155091</v>
+        <v>15.57581885809687</v>
       </c>
       <c r="CM6" t="n">
-        <v>15.18668209188114</v>
+        <v>15.19475257454453</v>
       </c>
       <c r="CN6" t="n">
-        <v>15.30071045839592</v>
+        <v>15.56190591041922</v>
       </c>
       <c r="CO6" t="n">
-        <v>14.91150959942677</v>
+        <v>15.20756211778478</v>
       </c>
       <c r="CP6" t="n">
-        <v>14.93853580062546</v>
+        <v>15.33057453104361</v>
       </c>
       <c r="CQ6" t="n">
-        <v>14.95688424315016</v>
+        <v>15.18450719385833</v>
       </c>
       <c r="CR6" t="n">
-        <v>15.30964147604281</v>
+        <v>14.97351441857786</v>
       </c>
       <c r="CS6" t="n">
-        <v>15.50521466060867</v>
+        <v>15.75670771403733</v>
       </c>
       <c r="CT6" t="n">
-        <v>15.84522151815689</v>
+        <v>15.27486009102417</v>
       </c>
       <c r="CU6" t="n">
-        <v>15.66965254458394</v>
+        <v>15.46190991235683</v>
       </c>
       <c r="CV6" t="n">
-        <v>15.466600041653</v>
+        <v>15.46198089817643</v>
       </c>
       <c r="CW6" t="n">
-        <v>15.66199611850671</v>
+        <v>15.08664541622784</v>
       </c>
       <c r="CX6" t="n">
-        <v>15.45893692357867</v>
+        <v>15.36090204336198</v>
       </c>
     </row>
     <row r="7">
@@ -2485,307 +2485,307 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.1251871765696</v>
+        <v>16.32550034036187</v>
       </c>
       <c r="C7" t="n">
-        <v>17.11370979507502</v>
+        <v>16.45704194048604</v>
       </c>
       <c r="D7" t="n">
-        <v>17.54047610812333</v>
+        <v>16.14648351572465</v>
       </c>
       <c r="E7" t="n">
-        <v>17.66321940448429</v>
+        <v>17.22857108424953</v>
       </c>
       <c r="F7" t="n">
-        <v>16.77480931811331</v>
+        <v>16.80763395969876</v>
       </c>
       <c r="G7" t="n">
-        <v>17.82416837852911</v>
+        <v>16.53795507678272</v>
       </c>
       <c r="H7" t="n">
-        <v>17.82617386206327</v>
+        <v>16.51641644514479</v>
       </c>
       <c r="I7" t="n">
-        <v>17.49974247434916</v>
+        <v>16.29186705574667</v>
       </c>
       <c r="J7" t="n">
-        <v>15.94069708914556</v>
+        <v>17.08351802822913</v>
       </c>
       <c r="K7" t="n">
-        <v>17.3731429617902</v>
+        <v>16.91206882589447</v>
       </c>
       <c r="L7" t="n">
-        <v>17.79831685536199</v>
+        <v>17.44985483422631</v>
       </c>
       <c r="M7" t="n">
-        <v>16.15750300131166</v>
+        <v>17.58423722728883</v>
       </c>
       <c r="N7" t="n">
-        <v>16.41195736243278</v>
+        <v>17.29957440324499</v>
       </c>
       <c r="O7" t="n">
-        <v>15.99697957218819</v>
+        <v>16.1977310520497</v>
       </c>
       <c r="P7" t="n">
-        <v>17.28834568435269</v>
+        <v>16.9559216193743</v>
       </c>
       <c r="Q7" t="n">
-        <v>17.95155186305254</v>
+        <v>16.6013873207207</v>
       </c>
       <c r="R7" t="n">
-        <v>17.59418256788272</v>
+        <v>17.29249689356832</v>
       </c>
       <c r="S7" t="n">
-        <v>17.32731498090916</v>
+        <v>17.26681628142602</v>
       </c>
       <c r="T7" t="n">
-        <v>17.72762830296926</v>
+        <v>16.51848595699727</v>
       </c>
       <c r="U7" t="n">
-        <v>16.16051030346092</v>
+        <v>17.9560990768451</v>
       </c>
       <c r="V7" t="n">
-        <v>16.75751138088362</v>
+        <v>17.64193855766574</v>
       </c>
       <c r="W7" t="n">
-        <v>17.50658481263041</v>
+        <v>16.61165518165706</v>
       </c>
       <c r="X7" t="n">
-        <v>17.52307504980654</v>
+        <v>17.5089001098805</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.0792738527446</v>
+        <v>17.36374713008448</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.53752937751188</v>
+        <v>16.52986500254458</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.60916342073468</v>
+        <v>17.55153847262796</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.87215136071606</v>
+        <v>16.85572434502104</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.62585582186976</v>
+        <v>17.13699777863708</v>
       </c>
       <c r="AD7" t="n">
-        <v>15.94003548133652</v>
+        <v>17.45223099817974</v>
       </c>
       <c r="AE7" t="n">
-        <v>16.85119718035559</v>
+        <v>16.59913590378865</v>
       </c>
       <c r="AF7" t="n">
-        <v>16.93641969603582</v>
+        <v>17.61259664043386</v>
       </c>
       <c r="AG7" t="n">
-        <v>16.13118893248097</v>
+        <v>17.21209444597232</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.28496701272989</v>
+        <v>16.75112696171224</v>
       </c>
       <c r="AI7" t="n">
-        <v>17.47407305871601</v>
+        <v>16.87575407205998</v>
       </c>
       <c r="AJ7" t="n">
-        <v>17.78044564580084</v>
+        <v>16.56347469593447</v>
       </c>
       <c r="AK7" t="n">
-        <v>16.39372148713688</v>
+        <v>16.97395640793128</v>
       </c>
       <c r="AL7" t="n">
-        <v>16.73491841282009</v>
+        <v>17.12332534748323</v>
       </c>
       <c r="AM7" t="n">
-        <v>17.82004135616929</v>
+        <v>16.37694175978301</v>
       </c>
       <c r="AN7" t="n">
-        <v>17.54360921665488</v>
+        <v>17.41965868660078</v>
       </c>
       <c r="AO7" t="n">
-        <v>16.9019342508561</v>
+        <v>16.73918952532193</v>
       </c>
       <c r="AP7" t="n">
-        <v>17.29625614965244</v>
+        <v>17.32803951252657</v>
       </c>
       <c r="AQ7" t="n">
-        <v>17.53532142413348</v>
+        <v>16.55352593576953</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.76161056257239</v>
+        <v>16.3767829825337</v>
       </c>
       <c r="AS7" t="n">
-        <v>17.32487492941736</v>
+        <v>16.46835660643161</v>
       </c>
       <c r="AT7" t="n">
-        <v>17.46673373219263</v>
+        <v>17.28639030199607</v>
       </c>
       <c r="AU7" t="n">
-        <v>16.04446670836784</v>
+        <v>16.96826488091808</v>
       </c>
       <c r="AV7" t="n">
-        <v>17.61949422662877</v>
+        <v>17.71841585783754</v>
       </c>
       <c r="AW7" t="n">
-        <v>17.40007474170743</v>
+        <v>16.405562240457</v>
       </c>
       <c r="AX7" t="n">
-        <v>16.27189597888427</v>
+        <v>16.32060061355209</v>
       </c>
       <c r="AY7" t="n">
-        <v>16.60179840254566</v>
+        <v>17.33001502292652</v>
       </c>
       <c r="AZ7" t="n">
-        <v>17.31606310546199</v>
+        <v>16.9378477504331</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.8001086652152</v>
+        <v>16.77014106532429</v>
       </c>
       <c r="BB7" t="n">
-        <v>17.28489442301936</v>
+        <v>16.88119346957389</v>
       </c>
       <c r="BC7" t="n">
-        <v>16.74706867290747</v>
+        <v>17.60790943552689</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.19270785191814</v>
+        <v>16.72424973752763</v>
       </c>
       <c r="BE7" t="n">
-        <v>17.00606427381769</v>
+        <v>17.18784457071861</v>
       </c>
       <c r="BF7" t="n">
-        <v>17.50028785931022</v>
+        <v>16.97601256511388</v>
       </c>
       <c r="BG7" t="n">
-        <v>17.40651115445818</v>
+        <v>16.34839431615858</v>
       </c>
       <c r="BH7" t="n">
-        <v>16.38542535131114</v>
+        <v>17.00652782088109</v>
       </c>
       <c r="BI7" t="n">
-        <v>17.560240506909</v>
+        <v>17.79622319990631</v>
       </c>
       <c r="BJ7" t="n">
-        <v>17.26847698925102</v>
+        <v>16.87334369265445</v>
       </c>
       <c r="BK7" t="n">
-        <v>16.70404926970794</v>
+        <v>16.94982930256336</v>
       </c>
       <c r="BL7" t="n">
-        <v>17.50197758778557</v>
+        <v>16.62039438494722</v>
       </c>
       <c r="BM7" t="n">
-        <v>17.15922691018504</v>
+        <v>16.1289322643124</v>
       </c>
       <c r="BN7" t="n">
-        <v>17.35041387615583</v>
+        <v>16.82032994316122</v>
       </c>
       <c r="BO7" t="n">
-        <v>16.97239081571336</v>
+        <v>16.54417470263897</v>
       </c>
       <c r="BP7" t="n">
-        <v>17.06969094383681</v>
+        <v>17.72546958777716</v>
       </c>
       <c r="BQ7" t="n">
-        <v>17.02720610524625</v>
+        <v>16.30609956482839</v>
       </c>
       <c r="BR7" t="n">
-        <v>17.190200614759</v>
+        <v>16.45561482166999</v>
       </c>
       <c r="BS7" t="n">
-        <v>16.66851663599623</v>
+        <v>17.17833657762179</v>
       </c>
       <c r="BT7" t="n">
-        <v>17.25591620874281</v>
+        <v>17.05577959509884</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.38178255408648</v>
+        <v>16.36655973011452</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.52981406127466</v>
+        <v>17.33013899014099</v>
       </c>
       <c r="BW7" t="n">
-        <v>17.27179054502723</v>
+        <v>16.62208634329572</v>
       </c>
       <c r="BX7" t="n">
-        <v>16.46731454724643</v>
+        <v>16.98121014607672</v>
       </c>
       <c r="BY7" t="n">
-        <v>16.7470966675883</v>
+        <v>16.69072483156247</v>
       </c>
       <c r="BZ7" t="n">
-        <v>16.62187554653198</v>
+        <v>17.11891162996782</v>
       </c>
       <c r="CA7" t="n">
-        <v>17.82360015266286</v>
+        <v>16.50141715237275</v>
       </c>
       <c r="CB7" t="n">
-        <v>17.02765776587749</v>
+        <v>16.62694737634551</v>
       </c>
       <c r="CC7" t="n">
-        <v>17.29376911300615</v>
+        <v>17.08016134642977</v>
       </c>
       <c r="CD7" t="n">
-        <v>16.90422029310957</v>
+        <v>16.741956233891</v>
       </c>
       <c r="CE7" t="n">
-        <v>17.24062793449872</v>
+        <v>17.25664468282162</v>
       </c>
       <c r="CF7" t="n">
-        <v>17.50391978360722</v>
+        <v>16.66279833713715</v>
       </c>
       <c r="CG7" t="n">
-        <v>16.82896489881962</v>
+        <v>16.88773109388559</v>
       </c>
       <c r="CH7" t="n">
-        <v>16.85440068335157</v>
+        <v>17.29684030067618</v>
       </c>
       <c r="CI7" t="n">
-        <v>18.27308705993811</v>
+        <v>16.39872950036634</v>
       </c>
       <c r="CJ7" t="n">
-        <v>16.75469977532517</v>
+        <v>16.66582040561686</v>
       </c>
       <c r="CK7" t="n">
-        <v>17.31720711152299</v>
+        <v>17.16874677793543</v>
       </c>
       <c r="CL7" t="n">
-        <v>17.31884890908792</v>
+        <v>17.2725622119449</v>
       </c>
       <c r="CM7" t="n">
-        <v>16.66116483678963</v>
+        <v>16.65705485115829</v>
       </c>
       <c r="CN7" t="n">
-        <v>16.87847531069296</v>
+        <v>17.12493708312708</v>
       </c>
       <c r="CO7" t="n">
-        <v>16.39596030321665</v>
+        <v>16.6067706660671</v>
       </c>
       <c r="CP7" t="n">
-        <v>16.35284322207123</v>
+        <v>16.68738626627005</v>
       </c>
       <c r="CQ7" t="n">
-        <v>16.25409762458104</v>
+        <v>16.57212562895512</v>
       </c>
       <c r="CR7" t="n">
-        <v>16.78239313944121</v>
+        <v>16.39732188581349</v>
       </c>
       <c r="CS7" t="n">
-        <v>17.17877064788816</v>
+        <v>17.45379074410183</v>
       </c>
       <c r="CT7" t="n">
-        <v>17.61912737880871</v>
+        <v>16.75491486097342</v>
       </c>
       <c r="CU7" t="n">
-        <v>17.36004611972881</v>
+        <v>17.04184118993841</v>
       </c>
       <c r="CV7" t="n">
-        <v>17.02621189707829</v>
+        <v>17.09358423991609</v>
       </c>
       <c r="CW7" t="n">
-        <v>17.33203429676088</v>
+        <v>16.42304109321034</v>
       </c>
       <c r="CX7" t="n">
-        <v>17.04091080727586</v>
+        <v>16.90462870884879</v>
       </c>
     </row>
     <row r="8">
@@ -2793,307 +2793,307 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.3464523864813</v>
+        <v>11.39314373563334</v>
       </c>
       <c r="C8" t="n">
-        <v>12.32576494343418</v>
+        <v>11.54660843078557</v>
       </c>
       <c r="D8" t="n">
-        <v>12.66995615522553</v>
+        <v>11.27508371358679</v>
       </c>
       <c r="E8" t="n">
-        <v>12.69058541462346</v>
+        <v>12.43381824804819</v>
       </c>
       <c r="F8" t="n">
-        <v>12.03600975679925</v>
+        <v>12.09214918757793</v>
       </c>
       <c r="G8" t="n">
-        <v>12.80478229055452</v>
+        <v>11.56784362755141</v>
       </c>
       <c r="H8" t="n">
-        <v>12.72852570820175</v>
+        <v>11.70460301389568</v>
       </c>
       <c r="I8" t="n">
-        <v>12.63537761027703</v>
+        <v>11.48353208155272</v>
       </c>
       <c r="J8" t="n">
-        <v>11.07283745604422</v>
+        <v>12.32696970692446</v>
       </c>
       <c r="K8" t="n">
-        <v>12.39744860352455</v>
+        <v>11.99147848719198</v>
       </c>
       <c r="L8" t="n">
-        <v>12.99884033469219</v>
+        <v>12.43847617936476</v>
       </c>
       <c r="M8" t="n">
-        <v>11.2480416440493</v>
+        <v>12.82976805487748</v>
       </c>
       <c r="N8" t="n">
-        <v>11.56456595411646</v>
+        <v>12.45499134825943</v>
       </c>
       <c r="O8" t="n">
-        <v>11.15996690704012</v>
+        <v>11.2880370047684</v>
       </c>
       <c r="P8" t="n">
-        <v>12.47775875958495</v>
+        <v>12.1134155430815</v>
       </c>
       <c r="Q8" t="n">
-        <v>13.08072891139706</v>
+        <v>11.87527799234671</v>
       </c>
       <c r="R8" t="n">
-        <v>12.61407673931074</v>
+        <v>12.45251570688528</v>
       </c>
       <c r="S8" t="n">
-        <v>12.35025724407251</v>
+        <v>12.4182114757276</v>
       </c>
       <c r="T8" t="n">
-        <v>12.76671627375829</v>
+        <v>11.79036815733231</v>
       </c>
       <c r="U8" t="n">
-        <v>11.26954984032954</v>
+        <v>13.03679818877306</v>
       </c>
       <c r="V8" t="n">
-        <v>11.88346433910772</v>
+        <v>12.75106349145459</v>
       </c>
       <c r="W8" t="n">
-        <v>12.55053298013694</v>
+        <v>11.71399905132094</v>
       </c>
       <c r="X8" t="n">
-        <v>12.69391965616249</v>
+        <v>12.58583294037493</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.13322089158586</v>
+        <v>12.3351278142363</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.7164423783008</v>
+        <v>11.54101509025963</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.69532342636543</v>
+        <v>12.66865804702538</v>
       </c>
       <c r="AB8" t="n">
-        <v>12.02172555822257</v>
+        <v>11.9468650197602</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.82230648154583</v>
+        <v>12.31060346976124</v>
       </c>
       <c r="AD8" t="n">
-        <v>10.90472752752505</v>
+        <v>12.59730962597576</v>
       </c>
       <c r="AE8" t="n">
-        <v>12.02037117114526</v>
+        <v>11.86130414619682</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.22115845610291</v>
+        <v>12.59121662799715</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.22863452422502</v>
+        <v>12.35595043366381</v>
       </c>
       <c r="AH8" t="n">
-        <v>11.45507079826103</v>
+        <v>11.78267175396731</v>
       </c>
       <c r="AI8" t="n">
-        <v>12.65182707616596</v>
+        <v>12.0733924161892</v>
       </c>
       <c r="AJ8" t="n">
-        <v>12.83072803436326</v>
+        <v>11.70298709392187</v>
       </c>
       <c r="AK8" t="n">
-        <v>11.60455046005277</v>
+        <v>12.03022934006019</v>
       </c>
       <c r="AL8" t="n">
-        <v>11.88049933713786</v>
+        <v>12.16779459072271</v>
       </c>
       <c r="AM8" t="n">
-        <v>12.99007270899478</v>
+        <v>11.39753145173312</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.7086501222421</v>
+        <v>12.62482011017735</v>
       </c>
       <c r="AO8" t="n">
-        <v>11.96728635977372</v>
+        <v>11.872265216321</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.52054389426345</v>
+        <v>12.42857538348728</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.72815471666262</v>
+        <v>11.75765537365135</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.12831441267399</v>
+        <v>11.48090816700241</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.43816718256617</v>
+        <v>11.6643565098796</v>
       </c>
       <c r="AT8" t="n">
-        <v>12.4645871594578</v>
+        <v>12.42083769602789</v>
       </c>
       <c r="AU8" t="n">
-        <v>11.32858588468558</v>
+        <v>12.16960510544549</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.53396954494029</v>
+        <v>12.83860301748823</v>
       </c>
       <c r="AW8" t="n">
-        <v>12.46397089477504</v>
+        <v>11.41722769674223</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.38761647186286</v>
+        <v>11.61325302541916</v>
       </c>
       <c r="AY8" t="n">
-        <v>11.82968179520379</v>
+        <v>12.2805860971796</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.48933632551974</v>
+        <v>12.0727089977013</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.00217106974471</v>
+        <v>11.8242958670911</v>
       </c>
       <c r="BB8" t="n">
-        <v>12.49971977661183</v>
+        <v>12.03239449703791</v>
       </c>
       <c r="BC8" t="n">
-        <v>11.81011448909116</v>
+        <v>12.5819604494736</v>
       </c>
       <c r="BD8" t="n">
-        <v>12.38875909185302</v>
+        <v>11.92922695139741</v>
       </c>
       <c r="BE8" t="n">
-        <v>11.97346087748419</v>
+        <v>12.29603822047059</v>
       </c>
       <c r="BF8" t="n">
-        <v>12.62084816261441</v>
+        <v>12.06191309590737</v>
       </c>
       <c r="BG8" t="n">
-        <v>12.46897008867619</v>
+        <v>11.62572733548905</v>
       </c>
       <c r="BH8" t="n">
-        <v>11.49704544489196</v>
+        <v>12.08166348546796</v>
       </c>
       <c r="BI8" t="n">
-        <v>12.55932571184203</v>
+        <v>12.83723967664008</v>
       </c>
       <c r="BJ8" t="n">
-        <v>12.37360469186732</v>
+        <v>11.99341351247765</v>
       </c>
       <c r="BK8" t="n">
-        <v>11.78010395012527</v>
+        <v>12.03946117285585</v>
       </c>
       <c r="BL8" t="n">
-        <v>12.52040085343166</v>
+        <v>11.81462032842093</v>
       </c>
       <c r="BM8" t="n">
-        <v>12.21308300406579</v>
+        <v>11.36021360409715</v>
       </c>
       <c r="BN8" t="n">
-        <v>12.39999279998119</v>
+        <v>12.04631143777437</v>
       </c>
       <c r="BO8" t="n">
-        <v>11.97523729115361</v>
+        <v>11.77100914674235</v>
       </c>
       <c r="BP8" t="n">
-        <v>12.16779442317222</v>
+        <v>12.88906795328298</v>
       </c>
       <c r="BQ8" t="n">
-        <v>12.14408111046973</v>
+        <v>11.3295744685752</v>
       </c>
       <c r="BR8" t="n">
-        <v>12.28243568265255</v>
+        <v>11.51448358866364</v>
       </c>
       <c r="BS8" t="n">
-        <v>11.82232222160727</v>
+        <v>12.17951535525006</v>
       </c>
       <c r="BT8" t="n">
-        <v>12.59970292468783</v>
+        <v>12.31105606670506</v>
       </c>
       <c r="BU8" t="n">
-        <v>11.55256404597541</v>
+        <v>11.3560220702307</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.80253456737764</v>
+        <v>12.34925084951385</v>
       </c>
       <c r="BW8" t="n">
-        <v>12.28505987220295</v>
+        <v>11.62903755208954</v>
       </c>
       <c r="BX8" t="n">
-        <v>11.62710418541893</v>
+        <v>12.17271580912693</v>
       </c>
       <c r="BY8" t="n">
-        <v>12.02122766676188</v>
+        <v>11.96863696173458</v>
       </c>
       <c r="BZ8" t="n">
-        <v>11.7520541020339</v>
+        <v>12.1380078084252</v>
       </c>
       <c r="CA8" t="n">
-        <v>12.96017132902091</v>
+        <v>11.53373538067712</v>
       </c>
       <c r="CB8" t="n">
-        <v>12.1318108180056</v>
+        <v>11.73425403156823</v>
       </c>
       <c r="CC8" t="n">
-        <v>12.4576779775842</v>
+        <v>12.27849873797169</v>
       </c>
       <c r="CD8" t="n">
-        <v>11.94658196292316</v>
+        <v>11.78072020588715</v>
       </c>
       <c r="CE8" t="n">
-        <v>12.36722742267023</v>
+        <v>12.19827112751591</v>
       </c>
       <c r="CF8" t="n">
-        <v>12.59367726207039</v>
+        <v>11.93951271971934</v>
       </c>
       <c r="CG8" t="n">
-        <v>12.04754999473029</v>
+        <v>11.97851193113704</v>
       </c>
       <c r="CH8" t="n">
-        <v>11.99187397859076</v>
+        <v>12.47746233269036</v>
       </c>
       <c r="CI8" t="n">
-        <v>13.21157183824926</v>
+        <v>11.59178179034206</v>
       </c>
       <c r="CJ8" t="n">
-        <v>11.87346871253857</v>
+        <v>11.8962796693287</v>
       </c>
       <c r="CK8" t="n">
-        <v>12.4875000457698</v>
+        <v>12.19797147615376</v>
       </c>
       <c r="CL8" t="n">
-        <v>12.38549958433735</v>
+        <v>12.53284228640814</v>
       </c>
       <c r="CM8" t="n">
-        <v>11.7606800345097</v>
+        <v>11.8030417977796</v>
       </c>
       <c r="CN8" t="n">
-        <v>12.0023891981319</v>
+        <v>12.06400823992269</v>
       </c>
       <c r="CO8" t="n">
-        <v>11.58603849840859</v>
+        <v>11.66219323832051</v>
       </c>
       <c r="CP8" t="n">
-        <v>11.48466145276828</v>
+        <v>11.59225867066281</v>
       </c>
       <c r="CQ8" t="n">
-        <v>11.22685105895166</v>
+        <v>11.5972555876864</v>
       </c>
       <c r="CR8" t="n">
-        <v>11.79294374928671</v>
+        <v>11.56121993423017</v>
       </c>
       <c r="CS8" t="n">
-        <v>12.46229042376149</v>
+        <v>12.59477222944919</v>
       </c>
       <c r="CT8" t="n">
-        <v>12.63897877830554</v>
+        <v>12.02470920884559</v>
       </c>
       <c r="CU8" t="n">
-        <v>12.43491979142257</v>
+        <v>12.15392177914224</v>
       </c>
       <c r="CV8" t="n">
-        <v>11.9842097147066</v>
+        <v>12.1834596647409</v>
       </c>
       <c r="CW8" t="n">
-        <v>12.56090606421266</v>
+        <v>11.45478240155126</v>
       </c>
       <c r="CX8" t="n">
-        <v>12.16060881300296</v>
+        <v>12.0253236639198</v>
       </c>
     </row>
     <row r="9">
@@ -3101,307 +3101,307 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.35266260537566</v>
+        <v>13.15948427324323</v>
       </c>
       <c r="C9" t="n">
-        <v>14.31649803606611</v>
+        <v>13.42399314840468</v>
       </c>
       <c r="D9" t="n">
-        <v>14.79317248829323</v>
+        <v>12.95867090666482</v>
       </c>
       <c r="E9" t="n">
-        <v>14.79876755907192</v>
+        <v>14.55425996457225</v>
       </c>
       <c r="F9" t="n">
-        <v>14.08976158036006</v>
+        <v>14.29344104268854</v>
       </c>
       <c r="G9" t="n">
-        <v>14.98106079263704</v>
+        <v>13.45026284379102</v>
       </c>
       <c r="H9" t="n">
-        <v>14.75678905410541</v>
+        <v>13.54881794931329</v>
       </c>
       <c r="I9" t="n">
-        <v>14.93380536009378</v>
+        <v>13.35121587549224</v>
       </c>
       <c r="J9" t="n">
-        <v>12.91457020224563</v>
+        <v>14.29575527712166</v>
       </c>
       <c r="K9" t="n">
-        <v>14.58214569465878</v>
+        <v>14.06265298098262</v>
       </c>
       <c r="L9" t="n">
-        <v>15.28716320125054</v>
+        <v>14.47282460322228</v>
       </c>
       <c r="M9" t="n">
-        <v>13.03246091604858</v>
+        <v>15.02177120712996</v>
       </c>
       <c r="N9" t="n">
-        <v>13.50391085707053</v>
+        <v>14.6023325237639</v>
       </c>
       <c r="O9" t="n">
-        <v>12.93267138337416</v>
+        <v>13.05548084750785</v>
       </c>
       <c r="P9" t="n">
-        <v>14.71657544701841</v>
+        <v>14.11443446805032</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.33588012769989</v>
+        <v>13.98870464162028</v>
       </c>
       <c r="R9" t="n">
-        <v>14.72578616028443</v>
+        <v>14.62761942938671</v>
       </c>
       <c r="S9" t="n">
-        <v>14.39724309401422</v>
+        <v>14.57607027336066</v>
       </c>
       <c r="T9" t="n">
-        <v>15.1035863256428</v>
+        <v>13.89316401364993</v>
       </c>
       <c r="U9" t="n">
-        <v>13.02868170943536</v>
+        <v>15.24279302771742</v>
       </c>
       <c r="V9" t="n">
-        <v>13.83604356223687</v>
+        <v>14.89523187558947</v>
       </c>
       <c r="W9" t="n">
-        <v>14.61116841891138</v>
+        <v>13.78857178106163</v>
       </c>
       <c r="X9" t="n">
-        <v>14.83277397941703</v>
+        <v>14.81047058650623</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.81108392282449</v>
+        <v>14.50526463595235</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.68970967944229</v>
+        <v>13.53859981430078</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.87792003440779</v>
+        <v>14.90817888781526</v>
       </c>
       <c r="AB9" t="n">
-        <v>14.0571794598148</v>
+        <v>13.89483909946892</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.81100459104926</v>
+        <v>14.39609716926574</v>
       </c>
       <c r="AD9" t="n">
-        <v>12.40708472027844</v>
+        <v>14.84201095657655</v>
       </c>
       <c r="AE9" t="n">
-        <v>14.09195385891351</v>
+        <v>13.8932678973771</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.31322743375118</v>
+        <v>14.8006178896153</v>
       </c>
       <c r="AG9" t="n">
-        <v>12.93642419594474</v>
+        <v>14.40209870809687</v>
       </c>
       <c r="AH9" t="n">
-        <v>13.36078183823551</v>
+        <v>13.72600383823923</v>
       </c>
       <c r="AI9" t="n">
-        <v>14.89248936824549</v>
+        <v>14.1583721067401</v>
       </c>
       <c r="AJ9" t="n">
-        <v>15.11010242091962</v>
+        <v>13.59838157686974</v>
       </c>
       <c r="AK9" t="n">
-        <v>13.48542112070038</v>
+        <v>14.01143236903662</v>
       </c>
       <c r="AL9" t="n">
-        <v>13.92607100853347</v>
+        <v>14.16288663253381</v>
       </c>
       <c r="AM9" t="n">
-        <v>15.35385147793904</v>
+        <v>13.27360108891492</v>
       </c>
       <c r="AN9" t="n">
-        <v>14.84180734193199</v>
+        <v>14.83230878626572</v>
       </c>
       <c r="AO9" t="n">
-        <v>13.90981816425785</v>
+        <v>13.85588450456671</v>
       </c>
       <c r="AP9" t="n">
-        <v>14.73738058118207</v>
+        <v>14.48447391090476</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.95895812971555</v>
+        <v>13.67388623763624</v>
       </c>
       <c r="AR9" t="n">
-        <v>14.24132590776575</v>
+        <v>13.22899146718139</v>
       </c>
       <c r="AS9" t="n">
-        <v>14.5286825930221</v>
+        <v>13.54286752821091</v>
       </c>
       <c r="AT9" t="n">
-        <v>14.47181556586998</v>
+        <v>14.591396476499</v>
       </c>
       <c r="AU9" t="n">
-        <v>13.35311247701245</v>
+        <v>14.2798385590963</v>
       </c>
       <c r="AV9" t="n">
-        <v>14.72931850493181</v>
+        <v>15.06177160182332</v>
       </c>
       <c r="AW9" t="n">
-        <v>14.73433890545539</v>
+        <v>13.16432539394648</v>
       </c>
       <c r="AX9" t="n">
-        <v>13.1751231785641</v>
+        <v>13.59495207171442</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.94202865441597</v>
+        <v>14.27640352949226</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.8485461016331</v>
+        <v>14.06672061924416</v>
       </c>
       <c r="BA9" t="n">
-        <v>14.04513014658832</v>
+        <v>13.69671239002546</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.75897138495477</v>
+        <v>14.01035634707787</v>
       </c>
       <c r="BC9" t="n">
-        <v>13.80432880829429</v>
+        <v>14.71818493602703</v>
       </c>
       <c r="BD9" t="n">
-        <v>14.5869031286549</v>
+        <v>13.95296428780148</v>
       </c>
       <c r="BE9" t="n">
-        <v>13.84704039853704</v>
+        <v>14.31838826790546</v>
       </c>
       <c r="BF9" t="n">
-        <v>14.68001113302778</v>
+        <v>14.10004557623502</v>
       </c>
       <c r="BG9" t="n">
-        <v>14.60288192810112</v>
+        <v>13.67063519206997</v>
       </c>
       <c r="BH9" t="n">
-        <v>13.32270108975768</v>
+        <v>13.92701164851305</v>
       </c>
       <c r="BI9" t="n">
-        <v>14.69330630610564</v>
+        <v>15.0570210863032</v>
       </c>
       <c r="BJ9" t="n">
-        <v>14.35439925226173</v>
+        <v>13.83891274375009</v>
       </c>
       <c r="BK9" t="n">
-        <v>13.71907854386249</v>
+        <v>14.03961574893923</v>
       </c>
       <c r="BL9" t="n">
-        <v>14.55889215981428</v>
+        <v>13.88199683953498</v>
       </c>
       <c r="BM9" t="n">
-        <v>14.08051335746534</v>
+        <v>13.2213585254184</v>
       </c>
       <c r="BN9" t="n">
-        <v>14.44138535617109</v>
+        <v>14.0283845659155</v>
       </c>
       <c r="BO9" t="n">
-        <v>13.89735213504288</v>
+        <v>13.76279560873725</v>
       </c>
       <c r="BP9" t="n">
-        <v>14.30772048196099</v>
+        <v>15.18979148985099</v>
       </c>
       <c r="BQ9" t="n">
-        <v>14.22461496270739</v>
+        <v>13.02489210153947</v>
       </c>
       <c r="BR9" t="n">
-        <v>14.25023913876768</v>
+        <v>13.312524542723</v>
       </c>
       <c r="BS9" t="n">
-        <v>13.89188338639288</v>
+        <v>14.14843705271386</v>
       </c>
       <c r="BT9" t="n">
-        <v>14.97930411117633</v>
+        <v>14.34327600563041</v>
       </c>
       <c r="BU9" t="n">
-        <v>13.43206005570349</v>
+        <v>13.12120318217831</v>
       </c>
       <c r="BV9" t="n">
-        <v>13.74408241473418</v>
+        <v>14.43832342693322</v>
       </c>
       <c r="BW9" t="n">
-        <v>14.2114879368105</v>
+        <v>13.43103213459058</v>
       </c>
       <c r="BX9" t="n">
-        <v>13.53674068670669</v>
+        <v>14.14531767758074</v>
       </c>
       <c r="BY9" t="n">
-        <v>14.01608919658159</v>
+        <v>14.04080209030382</v>
       </c>
       <c r="BZ9" t="n">
-        <v>13.72845269369951</v>
+        <v>14.12805875771243</v>
       </c>
       <c r="CA9" t="n">
-        <v>15.13081491749135</v>
+        <v>13.25738857031256</v>
       </c>
       <c r="CB9" t="n">
-        <v>14.10349521329312</v>
+        <v>13.73790633028275</v>
       </c>
       <c r="CC9" t="n">
-        <v>14.66267825048494</v>
+        <v>14.34370728678502</v>
       </c>
       <c r="CD9" t="n">
-        <v>13.98464318008625</v>
+        <v>13.6925509902762</v>
       </c>
       <c r="CE9" t="n">
-        <v>14.43562156573144</v>
+        <v>14.19309965421123</v>
       </c>
       <c r="CF9" t="n">
-        <v>14.67829797762048</v>
+        <v>14.03993864934659</v>
       </c>
       <c r="CG9" t="n">
-        <v>13.98185090285089</v>
+        <v>13.9323617170318</v>
       </c>
       <c r="CH9" t="n">
-        <v>14.1263972765019</v>
+        <v>14.54771847420597</v>
       </c>
       <c r="CI9" t="n">
-        <v>15.55174348622528</v>
+        <v>13.48108231412985</v>
       </c>
       <c r="CJ9" t="n">
-        <v>13.74195766436777</v>
+        <v>13.90832310209306</v>
       </c>
       <c r="CK9" t="n">
-        <v>14.66624359112332</v>
+        <v>14.20413367621072</v>
       </c>
       <c r="CL9" t="n">
-        <v>14.36966479572066</v>
+        <v>14.75386736369813</v>
       </c>
       <c r="CM9" t="n">
-        <v>13.60197384900398</v>
+        <v>13.83596798504671</v>
       </c>
       <c r="CN9" t="n">
-        <v>13.97490994991947</v>
+        <v>14.06234903192361</v>
       </c>
       <c r="CO9" t="n">
-        <v>13.55316613753095</v>
+        <v>13.54029273083878</v>
       </c>
       <c r="CP9" t="n">
-        <v>13.3277969373099</v>
+        <v>13.2598113172176</v>
       </c>
       <c r="CQ9" t="n">
-        <v>12.90668277003185</v>
+        <v>13.34529240522143</v>
       </c>
       <c r="CR9" t="n">
-        <v>13.73240150842119</v>
+        <v>13.47749349126929</v>
       </c>
       <c r="CS9" t="n">
-        <v>14.73407727787267</v>
+        <v>14.75771202472437</v>
       </c>
       <c r="CT9" t="n">
-        <v>14.76674176744188</v>
+        <v>14.23111098949983</v>
       </c>
       <c r="CU9" t="n">
-        <v>14.3992079654694</v>
+        <v>14.16177195884766</v>
       </c>
       <c r="CV9" t="n">
-        <v>13.92127181190416</v>
+        <v>14.28215149780635</v>
       </c>
       <c r="CW9" t="n">
-        <v>14.68462076080824</v>
+        <v>13.28507613494897</v>
       </c>
       <c r="CX9" t="n">
-        <v>14.20211569543162</v>
+        <v>14.02832646820165</v>
       </c>
     </row>
     <row r="10">
@@ -3409,307 +3409,307 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16.54638814960526</v>
+        <v>15.17082187996641</v>
       </c>
       <c r="C10" t="n">
-        <v>16.4770383853013</v>
+        <v>15.54821259866379</v>
       </c>
       <c r="D10" t="n">
-        <v>16.9686946088239</v>
+        <v>14.94819484509037</v>
       </c>
       <c r="E10" t="n">
-        <v>17.173055425793</v>
+        <v>16.84519772623807</v>
       </c>
       <c r="F10" t="n">
-        <v>16.36939513044033</v>
+        <v>16.69308468929327</v>
       </c>
       <c r="G10" t="n">
-        <v>17.3885533571835</v>
+        <v>15.43955277104618</v>
       </c>
       <c r="H10" t="n">
-        <v>16.92881268159161</v>
+        <v>15.59713707989472</v>
       </c>
       <c r="I10" t="n">
-        <v>17.43018482154963</v>
+        <v>15.42460275040458</v>
       </c>
       <c r="J10" t="n">
-        <v>15.02542634168089</v>
+        <v>16.48839257914298</v>
       </c>
       <c r="K10" t="n">
-        <v>16.96650211151913</v>
+        <v>16.31826059875823</v>
       </c>
       <c r="L10" t="n">
-        <v>17.70845690287893</v>
+        <v>16.61969083347012</v>
       </c>
       <c r="M10" t="n">
-        <v>14.97546380339087</v>
+        <v>17.35285839206314</v>
       </c>
       <c r="N10" t="n">
-        <v>15.60273786151087</v>
+        <v>16.92701045394896</v>
       </c>
       <c r="O10" t="n">
-        <v>15.00572195436386</v>
+        <v>15.07537723541303</v>
       </c>
       <c r="P10" t="n">
-        <v>17.19952061170209</v>
+        <v>16.30966115369083</v>
       </c>
       <c r="Q10" t="n">
-        <v>17.69840084982416</v>
+        <v>16.17522071480007</v>
       </c>
       <c r="R10" t="n">
-        <v>17.05510825027532</v>
+        <v>16.89714078442641</v>
       </c>
       <c r="S10" t="n">
-        <v>16.69886035870831</v>
+        <v>16.96658467196474</v>
       </c>
       <c r="T10" t="n">
-        <v>17.58182762238041</v>
+        <v>16.15766838891113</v>
       </c>
       <c r="U10" t="n">
-        <v>15.05899165504491</v>
+        <v>17.56442957743953</v>
       </c>
       <c r="V10" t="n">
-        <v>15.88488951693985</v>
+        <v>17.2248866805208</v>
       </c>
       <c r="W10" t="n">
-        <v>16.83167766234221</v>
+        <v>15.98657893732242</v>
       </c>
       <c r="X10" t="n">
-        <v>17.12578914160122</v>
+        <v>17.17596368000505</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.68775851027494</v>
+        <v>16.97856247787539</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.88988878194443</v>
+        <v>15.84036937365684</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.20409680760021</v>
+        <v>17.31959917710661</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.2586175293822</v>
+        <v>16.01855234936711</v>
       </c>
       <c r="AC10" t="n">
-        <v>15.95583486987152</v>
+        <v>16.63304845412918</v>
       </c>
       <c r="AD10" t="n">
-        <v>14.15633211176235</v>
+        <v>17.17737452610774</v>
       </c>
       <c r="AE10" t="n">
-        <v>16.26183141208283</v>
+        <v>16.1511491694969</v>
       </c>
       <c r="AF10" t="n">
-        <v>16.64858748315902</v>
+        <v>17.16561870802175</v>
       </c>
       <c r="AG10" t="n">
-        <v>14.79863542648817</v>
+        <v>16.68927285174651</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.4667362063345</v>
+        <v>15.95095478093021</v>
       </c>
       <c r="AI10" t="n">
-        <v>17.3242661335234</v>
+        <v>16.36190915662754</v>
       </c>
       <c r="AJ10" t="n">
-        <v>17.63248413105696</v>
+        <v>15.65258083438518</v>
       </c>
       <c r="AK10" t="n">
-        <v>15.48367942956276</v>
+        <v>16.19625022450765</v>
       </c>
       <c r="AL10" t="n">
-        <v>16.11848000452729</v>
+        <v>16.37338171175347</v>
       </c>
       <c r="AM10" t="n">
-        <v>17.78112408848345</v>
+        <v>15.42945463086355</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.17430943107707</v>
+        <v>17.209024978409</v>
       </c>
       <c r="AO10" t="n">
-        <v>16.03471265315219</v>
+        <v>16.04189287299039</v>
       </c>
       <c r="AP10" t="n">
-        <v>17.20232161586798</v>
+        <v>16.8466729446357</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17.42016371749058</v>
+        <v>15.97974586473346</v>
       </c>
       <c r="AR10" t="n">
-        <v>16.64477411082207</v>
+        <v>15.06629477084724</v>
       </c>
       <c r="AS10" t="n">
-        <v>16.78124054753675</v>
+        <v>15.682254421939</v>
       </c>
       <c r="AT10" t="n">
-        <v>16.59713481063527</v>
+        <v>16.90771743097217</v>
       </c>
       <c r="AU10" t="n">
-        <v>15.54112556372191</v>
+        <v>16.69884634946983</v>
       </c>
       <c r="AV10" t="n">
-        <v>17.12281026791613</v>
+        <v>17.49667956933639</v>
       </c>
       <c r="AW10" t="n">
-        <v>17.14523990504136</v>
+        <v>15.14952916793046</v>
       </c>
       <c r="AX10" t="n">
-        <v>15.25522464693188</v>
+        <v>15.83258061754338</v>
       </c>
       <c r="AY10" t="n">
-        <v>16.25252932740671</v>
+        <v>16.39947640064932</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17.49088212640508</v>
+        <v>16.3092327446649</v>
       </c>
       <c r="BA10" t="n">
-        <v>16.38383079735338</v>
+        <v>15.69806827843304</v>
       </c>
       <c r="BB10" t="n">
-        <v>17.19702326814243</v>
+        <v>16.20453240217947</v>
       </c>
       <c r="BC10" t="n">
-        <v>16.03835466476334</v>
+        <v>17.02283463323858</v>
       </c>
       <c r="BD10" t="n">
-        <v>16.84795050821043</v>
+        <v>16.27190822220788</v>
       </c>
       <c r="BE10" t="n">
-        <v>15.85396589288896</v>
+        <v>16.57770517838298</v>
       </c>
       <c r="BF10" t="n">
-        <v>16.8502235287385</v>
+        <v>16.26503198427742</v>
       </c>
       <c r="BG10" t="n">
-        <v>16.88023726706736</v>
+        <v>15.90793340256015</v>
       </c>
       <c r="BH10" t="n">
-        <v>15.30986373977897</v>
+        <v>15.85970676775382</v>
       </c>
       <c r="BI10" t="n">
-        <v>16.92496243101238</v>
+        <v>17.44276931830925</v>
       </c>
       <c r="BJ10" t="n">
-        <v>16.52671616132903</v>
+        <v>15.83392400638834</v>
       </c>
       <c r="BK10" t="n">
-        <v>15.7684906631988</v>
+        <v>16.34699528057283</v>
       </c>
       <c r="BL10" t="n">
-        <v>16.68887786009424</v>
+        <v>16.26593059823283</v>
       </c>
       <c r="BM10" t="n">
-        <v>16.01027534315542</v>
+        <v>15.36505434471842</v>
       </c>
       <c r="BN10" t="n">
-        <v>16.62158510088837</v>
+        <v>16.24823096276785</v>
       </c>
       <c r="BO10" t="n">
-        <v>16.11203775290263</v>
+        <v>15.85435769397706</v>
       </c>
       <c r="BP10" t="n">
-        <v>16.74127700776206</v>
+        <v>17.63917419897907</v>
       </c>
       <c r="BQ10" t="n">
-        <v>16.47412846486066</v>
+        <v>14.89354790265652</v>
       </c>
       <c r="BR10" t="n">
-        <v>16.3625832794697</v>
+        <v>15.29291341554331</v>
       </c>
       <c r="BS10" t="n">
-        <v>16.098072844563</v>
+        <v>16.22893988947319</v>
       </c>
       <c r="BT10" t="n">
-        <v>17.50746665688097</v>
+        <v>16.50287222640061</v>
       </c>
       <c r="BU10" t="n">
-        <v>15.52270418674964</v>
+        <v>15.0911387121539</v>
       </c>
       <c r="BV10" t="n">
-        <v>15.80711640366937</v>
+        <v>16.75853654305489</v>
       </c>
       <c r="BW10" t="n">
-        <v>16.38340254890979</v>
+        <v>15.4042583373545</v>
       </c>
       <c r="BX10" t="n">
-        <v>15.66834062630243</v>
+        <v>16.25632711817913</v>
       </c>
       <c r="BY10" t="n">
-        <v>16.23125803758485</v>
+        <v>16.29860745027795</v>
       </c>
       <c r="BZ10" t="n">
-        <v>15.88406058001414</v>
+        <v>16.35671230354162</v>
       </c>
       <c r="CA10" t="n">
-        <v>17.54183026522051</v>
+        <v>15.27022219646649</v>
       </c>
       <c r="CB10" t="n">
-        <v>16.27599705657979</v>
+        <v>15.87659964619957</v>
       </c>
       <c r="CC10" t="n">
-        <v>17.104034531814</v>
+        <v>16.69643826679723</v>
       </c>
       <c r="CD10" t="n">
-        <v>16.13282427127411</v>
+        <v>15.7932632068024</v>
       </c>
       <c r="CE10" t="n">
-        <v>16.80158303153887</v>
+        <v>16.2489052079243</v>
       </c>
       <c r="CF10" t="n">
-        <v>16.92135454978803</v>
+        <v>16.30929686587801</v>
       </c>
       <c r="CG10" t="n">
-        <v>16.16232454842432</v>
+        <v>16.06645103491506</v>
       </c>
       <c r="CH10" t="n">
-        <v>16.48903313097479</v>
+        <v>16.81447180235786</v>
       </c>
       <c r="CI10" t="n">
-        <v>18.17650348067787</v>
+        <v>15.49369420247682</v>
       </c>
       <c r="CJ10" t="n">
-        <v>15.71123114573552</v>
+        <v>16.03300643917296</v>
       </c>
       <c r="CK10" t="n">
-        <v>16.86818257980487</v>
+        <v>16.30160882901866</v>
       </c>
       <c r="CL10" t="n">
-        <v>16.56094280805312</v>
+        <v>17.145196057764</v>
       </c>
       <c r="CM10" t="n">
-        <v>15.67404812219808</v>
+        <v>16.08297944211911</v>
       </c>
       <c r="CN10" t="n">
-        <v>16.12553323168006</v>
+        <v>16.34249042493629</v>
       </c>
       <c r="CO10" t="n">
-        <v>15.67619507657416</v>
+        <v>15.64000824750292</v>
       </c>
       <c r="CP10" t="n">
-        <v>15.39717522607598</v>
+        <v>15.14760864700648</v>
       </c>
       <c r="CQ10" t="n">
-        <v>14.69040280750722</v>
+        <v>15.28341364860711</v>
       </c>
       <c r="CR10" t="n">
-        <v>15.83089017040672</v>
+        <v>15.70292493141891</v>
       </c>
       <c r="CS10" t="n">
-        <v>17.09860015632487</v>
+        <v>17.0453438775487</v>
       </c>
       <c r="CT10" t="n">
-        <v>17.10116945252591</v>
+        <v>16.64763846203412</v>
       </c>
       <c r="CU10" t="n">
-        <v>16.5161047131729</v>
+        <v>16.3928237614355</v>
       </c>
       <c r="CV10" t="n">
-        <v>15.94144803409066</v>
+        <v>16.49601801621058</v>
       </c>
       <c r="CW10" t="n">
-        <v>16.90035247354344</v>
+        <v>15.30311056887368</v>
       </c>
       <c r="CX10" t="n">
-        <v>16.42424885334787</v>
+        <v>16.22486080538253</v>
       </c>
     </row>
     <row r="11">
@@ -3717,307 +3717,307 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>19.00786798477715</v>
+        <v>17.32473208093094</v>
       </c>
       <c r="C11" t="n">
-        <v>18.70224909110548</v>
+        <v>17.80268531705556</v>
       </c>
       <c r="D11" t="n">
-        <v>19.32367341136189</v>
+        <v>17.08653789239716</v>
       </c>
       <c r="E11" t="n">
-        <v>19.57178319139215</v>
+        <v>19.26164481753187</v>
       </c>
       <c r="F11" t="n">
-        <v>18.74516876845564</v>
+        <v>19.13101408841268</v>
       </c>
       <c r="G11" t="n">
-        <v>19.94425355855649</v>
+        <v>17.6249894309466</v>
       </c>
       <c r="H11" t="n">
-        <v>19.21355205342945</v>
+        <v>17.86070083781928</v>
       </c>
       <c r="I11" t="n">
-        <v>20.16369427818715</v>
+        <v>17.70024472152195</v>
       </c>
       <c r="J11" t="n">
-        <v>17.34942715306169</v>
+        <v>18.79036871871827</v>
       </c>
       <c r="K11" t="n">
-        <v>19.48888352481007</v>
+        <v>18.74663705392751</v>
       </c>
       <c r="L11" t="n">
-        <v>20.22052171369004</v>
+        <v>18.76229639836982</v>
       </c>
       <c r="M11" t="n">
-        <v>17.09547834274289</v>
+        <v>19.81421838506598</v>
       </c>
       <c r="N11" t="n">
-        <v>17.85393732595527</v>
+        <v>19.35337524587905</v>
       </c>
       <c r="O11" t="n">
-        <v>17.13095905958399</v>
+        <v>17.25437743964226</v>
       </c>
       <c r="P11" t="n">
-        <v>19.84990393022214</v>
+        <v>18.55459895144904</v>
       </c>
       <c r="Q11" t="n">
-        <v>20.16965746872936</v>
+        <v>18.59408466924196</v>
       </c>
       <c r="R11" t="n">
-        <v>19.58065750436666</v>
+        <v>19.42443736870399</v>
       </c>
       <c r="S11" t="n">
-        <v>19.12070309477961</v>
+        <v>19.47898759290825</v>
       </c>
       <c r="T11" t="n">
-        <v>20.16380085818956</v>
+        <v>18.44439479172244</v>
       </c>
       <c r="U11" t="n">
-        <v>17.26908128045326</v>
+        <v>19.95241066601364</v>
       </c>
       <c r="V11" t="n">
-        <v>18.07856221201568</v>
+        <v>19.71478506261647</v>
       </c>
       <c r="W11" t="n">
-        <v>19.16548618785664</v>
+        <v>18.3724622872764</v>
       </c>
       <c r="X11" t="n">
-        <v>19.44989917170599</v>
+        <v>19.68988045531655</v>
       </c>
       <c r="Y11" t="n">
-        <v>16.64082334030432</v>
+        <v>19.52241692504082</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.15544196288288</v>
+        <v>18.30716266217521</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.69074910903651</v>
+        <v>19.89809159836663</v>
       </c>
       <c r="AB11" t="n">
-        <v>18.4391796278289</v>
+        <v>18.29062798830561</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.26355817210123</v>
+        <v>18.94933122173496</v>
       </c>
       <c r="AD11" t="n">
-        <v>16.11156319782156</v>
+        <v>19.68893598011913</v>
       </c>
       <c r="AE11" t="n">
-        <v>18.52172688226571</v>
+        <v>18.50281714609429</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.06139091856464</v>
+        <v>19.60670968847019</v>
       </c>
       <c r="AG11" t="n">
-        <v>16.77247279743305</v>
+        <v>19.06768848186982</v>
       </c>
       <c r="AH11" t="n">
-        <v>17.83979810885371</v>
+        <v>18.37170623648682</v>
       </c>
       <c r="AI11" t="n">
-        <v>19.86644730434395</v>
+        <v>18.84422335810601</v>
       </c>
       <c r="AJ11" t="n">
-        <v>20.15450943122965</v>
+        <v>17.77197026206296</v>
       </c>
       <c r="AK11" t="n">
-        <v>17.56634272334789</v>
+        <v>18.47887952291174</v>
       </c>
       <c r="AL11" t="n">
-        <v>18.43748608083351</v>
+        <v>18.68195209285287</v>
       </c>
       <c r="AM11" t="n">
-        <v>20.28774489340372</v>
+        <v>17.68659042845275</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.66258211375055</v>
+        <v>19.65664081801448</v>
       </c>
       <c r="AO11" t="n">
-        <v>18.24717418283092</v>
+        <v>18.37863778963598</v>
       </c>
       <c r="AP11" t="n">
-        <v>19.8705325510277</v>
+        <v>19.3365865508589</v>
       </c>
       <c r="AQ11" t="n">
-        <v>20.04730954237592</v>
+        <v>18.33639416674427</v>
       </c>
       <c r="AR11" t="n">
-        <v>19.16390340117607</v>
+        <v>17.04045887812867</v>
       </c>
       <c r="AS11" t="n">
-        <v>19.11416436874821</v>
+        <v>17.93338620774593</v>
       </c>
       <c r="AT11" t="n">
-        <v>18.76486099571611</v>
+        <v>19.41258154623706</v>
       </c>
       <c r="AU11" t="n">
-        <v>18.00541611753792</v>
+        <v>19.28086392761012</v>
       </c>
       <c r="AV11" t="n">
-        <v>19.55431657728866</v>
+        <v>20.10347367822261</v>
       </c>
       <c r="AW11" t="n">
-        <v>19.64826928706321</v>
+        <v>17.21338820245911</v>
       </c>
       <c r="AX11" t="n">
-        <v>17.43575046572215</v>
+        <v>18.31766993636057</v>
       </c>
       <c r="AY11" t="n">
-        <v>18.70527557169969</v>
+        <v>18.7155551587162</v>
       </c>
       <c r="AZ11" t="n">
-        <v>20.3669365440369</v>
+        <v>18.71546680722419</v>
       </c>
       <c r="BA11" t="n">
-        <v>18.77762787920729</v>
+        <v>18.01081068278074</v>
       </c>
       <c r="BB11" t="n">
-        <v>19.71659646127132</v>
+        <v>18.48231510253457</v>
       </c>
       <c r="BC11" t="n">
-        <v>18.48984380934075</v>
+        <v>19.43173081711462</v>
       </c>
       <c r="BD11" t="n">
-        <v>19.22869568488262</v>
+        <v>18.68569384439455</v>
       </c>
       <c r="BE11" t="n">
-        <v>18.0355581096655</v>
+        <v>18.93133327346172</v>
       </c>
       <c r="BF11" t="n">
-        <v>19.09697773843462</v>
+        <v>18.56455051884539</v>
       </c>
       <c r="BG11" t="n">
-        <v>19.22902616272122</v>
+        <v>18.25062275612659</v>
       </c>
       <c r="BH11" t="n">
-        <v>17.446705040916</v>
+        <v>17.91108642912545</v>
       </c>
       <c r="BI11" t="n">
-        <v>19.22725721012782</v>
+        <v>19.99142669603853</v>
       </c>
       <c r="BJ11" t="n">
-        <v>18.91756564988682</v>
+        <v>18.11251292766253</v>
       </c>
       <c r="BK11" t="n">
-        <v>17.97640878770623</v>
+        <v>18.86572715605343</v>
       </c>
       <c r="BL11" t="n">
-        <v>18.95370430221589</v>
+        <v>18.76919076524149</v>
       </c>
       <c r="BM11" t="n">
-        <v>18.04988637283112</v>
+        <v>17.63338257838989</v>
       </c>
       <c r="BN11" t="n">
-        <v>19.01556588986907</v>
+        <v>18.55486127144223</v>
       </c>
       <c r="BO11" t="n">
-        <v>18.48388312204121</v>
+        <v>18.04498725507843</v>
       </c>
       <c r="BP11" t="n">
-        <v>19.32179038897917</v>
+        <v>20.1428129481793</v>
       </c>
       <c r="BQ11" t="n">
-        <v>18.76678474878347</v>
+        <v>16.85273324734626</v>
       </c>
       <c r="BR11" t="n">
-        <v>18.67517529353135</v>
+        <v>17.388924250801</v>
       </c>
       <c r="BS11" t="n">
-        <v>18.38224155598032</v>
+        <v>18.36843955064852</v>
       </c>
       <c r="BT11" t="n">
-        <v>20.15166533411526</v>
+        <v>18.76569304998928</v>
       </c>
       <c r="BU11" t="n">
-        <v>17.73033003203256</v>
+        <v>17.2767073618061</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.98407077589516</v>
+        <v>19.14441258649152</v>
       </c>
       <c r="BW11" t="n">
-        <v>18.69092254639153</v>
+        <v>17.55024018404357</v>
       </c>
       <c r="BX11" t="n">
-        <v>17.9792868554361</v>
+        <v>18.51032646833216</v>
       </c>
       <c r="BY11" t="n">
-        <v>18.5693060834173</v>
+        <v>18.68544908835423</v>
       </c>
       <c r="BZ11" t="n">
-        <v>18.16489168860955</v>
+        <v>18.74124157078975</v>
       </c>
       <c r="CA11" t="n">
-        <v>20.1179263256465</v>
+        <v>17.35223016208764</v>
       </c>
       <c r="CB11" t="n">
-        <v>18.49969834893368</v>
+        <v>18.18904308154492</v>
       </c>
       <c r="CC11" t="n">
-        <v>19.70201426516748</v>
+        <v>19.13418750199229</v>
       </c>
       <c r="CD11" t="n">
-        <v>18.33555069086971</v>
+        <v>17.98880621438951</v>
       </c>
       <c r="CE11" t="n">
-        <v>19.17532119649575</v>
+        <v>18.37072869572826</v>
       </c>
       <c r="CF11" t="n">
-        <v>19.35095382821319</v>
+        <v>18.8408914889207</v>
       </c>
       <c r="CG11" t="n">
-        <v>18.41854336677335</v>
+        <v>18.28274284243946</v>
       </c>
       <c r="CH11" t="n">
-        <v>19.00346068033723</v>
+        <v>19.17462979368913</v>
       </c>
       <c r="CI11" t="n">
-        <v>20.77669091668657</v>
+        <v>17.75999652642303</v>
       </c>
       <c r="CJ11" t="n">
-        <v>17.78460836903193</v>
+        <v>18.45869975223782</v>
       </c>
       <c r="CK11" t="n">
-        <v>19.13906019988854</v>
+        <v>18.54902222991554</v>
       </c>
       <c r="CL11" t="n">
-        <v>18.98803913346927</v>
+        <v>19.6832972454312</v>
       </c>
       <c r="CM11" t="n">
-        <v>17.87198301751372</v>
+        <v>18.52998780531762</v>
       </c>
       <c r="CN11" t="n">
-        <v>18.40339884186332</v>
+        <v>18.68366787171441</v>
       </c>
       <c r="CO11" t="n">
-        <v>18.06243933594131</v>
+        <v>17.79544249364985</v>
       </c>
       <c r="CP11" t="n">
-        <v>17.69587547806351</v>
+        <v>17.33364432498453</v>
       </c>
       <c r="CQ11" t="n">
-        <v>16.56589584176086</v>
+        <v>17.4559620062714</v>
       </c>
       <c r="CR11" t="n">
-        <v>18.01750367482078</v>
+        <v>18.07751373718585</v>
       </c>
       <c r="CS11" t="n">
-        <v>19.60419498343408</v>
+        <v>19.53333015144519</v>
       </c>
       <c r="CT11" t="n">
-        <v>19.51773424467724</v>
+        <v>19.29226465388023</v>
       </c>
       <c r="CU11" t="n">
-        <v>18.78000403943425</v>
+        <v>18.82067188647517</v>
       </c>
       <c r="CV11" t="n">
-        <v>18.13527352767409</v>
+        <v>18.95885628896854</v>
       </c>
       <c r="CW11" t="n">
-        <v>19.19225006753242</v>
+        <v>17.37215644139649</v>
       </c>
       <c r="CX11" t="n">
-        <v>18.77255115333172</v>
+        <v>18.56155057111637</v>
       </c>
     </row>
     <row r="12">
@@ -4025,307 +4025,307 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>21.43658650956411</v>
+        <v>19.53844521585308</v>
       </c>
       <c r="C12" t="n">
-        <v>21.01005006539734</v>
+        <v>20.33796237127201</v>
       </c>
       <c r="D12" t="n">
-        <v>21.70525367722168</v>
+        <v>19.50803187004042</v>
       </c>
       <c r="E12" t="n">
-        <v>22.02595547536347</v>
+        <v>21.64764905315334</v>
       </c>
       <c r="F12" t="n">
-        <v>21.18857325066528</v>
+        <v>21.58049045616213</v>
       </c>
       <c r="G12" t="n">
-        <v>22.59637941484961</v>
+        <v>19.98272903238281</v>
       </c>
       <c r="H12" t="n">
-        <v>21.61725009477631</v>
+        <v>20.10374298642253</v>
       </c>
       <c r="I12" t="n">
-        <v>22.88591320532004</v>
+        <v>20.10311637168496</v>
       </c>
       <c r="J12" t="n">
-        <v>19.71834742032079</v>
+        <v>21.16475728443968</v>
       </c>
       <c r="K12" t="n">
-        <v>22.00443112398102</v>
+        <v>21.21898873642796</v>
       </c>
       <c r="L12" t="n">
-        <v>22.78779341480148</v>
+        <v>20.95545700117064</v>
       </c>
       <c r="M12" t="n">
-        <v>19.34186880640265</v>
+        <v>22.27575372995368</v>
       </c>
       <c r="N12" t="n">
-        <v>20.23962944442291</v>
+        <v>21.80356071930398</v>
       </c>
       <c r="O12" t="n">
-        <v>19.34167193614783</v>
+        <v>19.62812240086195</v>
       </c>
       <c r="P12" t="n">
-        <v>22.59951110680127</v>
+        <v>21.09421695483485</v>
       </c>
       <c r="Q12" t="n">
-        <v>22.59839428662773</v>
+        <v>21.07793959901045</v>
       </c>
       <c r="R12" t="n">
-        <v>22.07267712636214</v>
+        <v>21.96087367256847</v>
       </c>
       <c r="S12" t="n">
-        <v>21.51947698641221</v>
+        <v>22.09651613011599</v>
       </c>
       <c r="T12" t="n">
-        <v>22.68012073066071</v>
+        <v>20.83846484733299</v>
       </c>
       <c r="U12" t="n">
-        <v>19.48903480477297</v>
+        <v>22.35776622800095</v>
       </c>
       <c r="V12" t="n">
-        <v>20.35210498950149</v>
+        <v>22.24951720871741</v>
       </c>
       <c r="W12" t="n">
-        <v>21.4569051415031</v>
+        <v>20.92513761813091</v>
       </c>
       <c r="X12" t="n">
-        <v>21.97687328761217</v>
+        <v>22.37232152631339</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.69964653954327</v>
+        <v>22.10366848361529</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.42565512003727</v>
+        <v>20.82743328784456</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.32187748778694</v>
+        <v>22.46721812098008</v>
       </c>
       <c r="AB12" t="n">
-        <v>20.82924510998738</v>
+        <v>20.67528014277087</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.69169759273598</v>
+        <v>21.50108441779683</v>
       </c>
       <c r="AD12" t="n">
-        <v>18.15229589073875</v>
+        <v>22.09177645423707</v>
       </c>
       <c r="AE12" t="n">
-        <v>21.02050421325233</v>
+        <v>20.99585469949577</v>
       </c>
       <c r="AF12" t="n">
-        <v>21.49789922355789</v>
+        <v>22.08161678710714</v>
       </c>
       <c r="AG12" t="n">
-        <v>18.87859208433063</v>
+        <v>21.51156926345998</v>
       </c>
       <c r="AH12" t="n">
-        <v>20.27187822762523</v>
+        <v>20.85098143460039</v>
       </c>
       <c r="AI12" t="n">
-        <v>22.39466050235449</v>
+        <v>21.25154442924273</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22.70808353805963</v>
+        <v>19.97240443350656</v>
       </c>
       <c r="AK12" t="n">
-        <v>19.71248699099644</v>
+        <v>20.86175821344812</v>
       </c>
       <c r="AL12" t="n">
-        <v>20.83480409255405</v>
+        <v>21.11781683067512</v>
       </c>
       <c r="AM12" t="n">
-        <v>22.76231823825743</v>
+        <v>20.06980032545974</v>
       </c>
       <c r="AN12" t="n">
-        <v>22.21251890736623</v>
+        <v>22.18029908599438</v>
       </c>
       <c r="AO12" t="n">
-        <v>20.59133861119844</v>
+        <v>20.8617659282612</v>
       </c>
       <c r="AP12" t="n">
-        <v>22.58487547937419</v>
+        <v>21.86300241611826</v>
       </c>
       <c r="AQ12" t="n">
-        <v>22.54982669427653</v>
+        <v>20.77745234865662</v>
       </c>
       <c r="AR12" t="n">
-        <v>21.7115537770657</v>
+        <v>19.11067943848652</v>
       </c>
       <c r="AS12" t="n">
-        <v>21.43942334669031</v>
+        <v>20.3060119731866</v>
       </c>
       <c r="AT12" t="n">
-        <v>20.98687544368702</v>
+        <v>21.91871545689737</v>
       </c>
       <c r="AU12" t="n">
-        <v>20.43686783053787</v>
+        <v>21.94169864722109</v>
       </c>
       <c r="AV12" t="n">
-        <v>22.09391276911882</v>
+        <v>22.73844477153779</v>
       </c>
       <c r="AW12" t="n">
-        <v>22.21766132380602</v>
+        <v>19.3747093644828</v>
       </c>
       <c r="AX12" t="n">
-        <v>19.77588817951593</v>
+        <v>20.77225248390826</v>
       </c>
       <c r="AY12" t="n">
-        <v>21.17422535840083</v>
+        <v>20.98316268464937</v>
       </c>
       <c r="AZ12" t="n">
-        <v>23.17948680665304</v>
+        <v>21.22817310625793</v>
       </c>
       <c r="BA12" t="n">
-        <v>21.30620162612603</v>
+        <v>20.48121267864479</v>
       </c>
       <c r="BB12" t="n">
-        <v>22.1992403820168</v>
+        <v>20.90324117110119</v>
       </c>
       <c r="BC12" t="n">
-        <v>20.9825299490821</v>
+        <v>21.90214964915866</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.5891980763603</v>
+        <v>21.23564507349455</v>
       </c>
       <c r="BE12" t="n">
-        <v>20.35919115893662</v>
+        <v>21.43309731564268</v>
       </c>
       <c r="BF12" t="n">
-        <v>21.43810688516322</v>
+        <v>20.93430986406197</v>
       </c>
       <c r="BG12" t="n">
-        <v>21.67207579956607</v>
+        <v>20.69702245934745</v>
       </c>
       <c r="BH12" t="n">
-        <v>19.74102656399241</v>
+        <v>20.11350854670408</v>
       </c>
       <c r="BI12" t="n">
-        <v>21.59811676839458</v>
+        <v>22.50992031098365</v>
       </c>
       <c r="BJ12" t="n">
-        <v>21.29685599401622</v>
+        <v>20.35750926683032</v>
       </c>
       <c r="BK12" t="n">
-        <v>20.26409661791049</v>
+        <v>21.51606887246858</v>
       </c>
       <c r="BL12" t="n">
-        <v>21.22955338063725</v>
+        <v>21.24371272146321</v>
       </c>
       <c r="BM12" t="n">
-        <v>20.24000594873901</v>
+        <v>20.10935281551083</v>
       </c>
       <c r="BN12" t="n">
-        <v>21.43671946316572</v>
+        <v>21.00741274147397</v>
       </c>
       <c r="BO12" t="n">
-        <v>20.84196621362242</v>
+        <v>20.27344679960861</v>
       </c>
       <c r="BP12" t="n">
-        <v>22.02369446874726</v>
+        <v>22.73452318711479</v>
       </c>
       <c r="BQ12" t="n">
-        <v>21.06685056053131</v>
+        <v>18.87752559991513</v>
       </c>
       <c r="BR12" t="n">
-        <v>21.04210073906372</v>
+        <v>19.6973167633841</v>
       </c>
       <c r="BS12" t="n">
-        <v>20.86997812218531</v>
+        <v>20.64626555684159</v>
       </c>
       <c r="BT12" t="n">
-        <v>22.71055258357905</v>
+        <v>21.25057062547378</v>
       </c>
       <c r="BU12" t="n">
-        <v>20.05895530233315</v>
+        <v>19.70133588012172</v>
       </c>
       <c r="BV12" t="n">
-        <v>20.37378604521754</v>
+        <v>21.6608992629692</v>
       </c>
       <c r="BW12" t="n">
-        <v>20.978258051123</v>
+        <v>19.93034048909908</v>
       </c>
       <c r="BX12" t="n">
-        <v>20.26029793245575</v>
+        <v>20.87985392699836</v>
       </c>
       <c r="BY12" t="n">
-        <v>21.08808072350366</v>
+        <v>21.14087197849853</v>
       </c>
       <c r="BZ12" t="n">
-        <v>20.50814943393948</v>
+        <v>21.25240450943745</v>
       </c>
       <c r="CA12" t="n">
-        <v>22.69841808332362</v>
+        <v>19.5703880151487</v>
       </c>
       <c r="CB12" t="n">
-        <v>20.83892462028859</v>
+        <v>20.6671849749537</v>
       </c>
       <c r="CC12" t="n">
-        <v>22.3391754912547</v>
+        <v>21.65802996729341</v>
       </c>
       <c r="CD12" t="n">
-        <v>20.68891935016083</v>
+        <v>20.27923998273823</v>
       </c>
       <c r="CE12" t="n">
-        <v>21.60393554426026</v>
+        <v>20.53786537507924</v>
       </c>
       <c r="CF12" t="n">
-        <v>21.85576542854095</v>
+        <v>21.47351846691444</v>
       </c>
       <c r="CG12" t="n">
-        <v>20.701580366233</v>
+        <v>20.59513437152045</v>
       </c>
       <c r="CH12" t="n">
-        <v>21.5775291913881</v>
+        <v>21.59210746443531</v>
       </c>
       <c r="CI12" t="n">
-        <v>23.4854195314541</v>
+        <v>20.11481116630987</v>
       </c>
       <c r="CJ12" t="n">
-        <v>19.90395915243019</v>
+        <v>20.92256150508963</v>
       </c>
       <c r="CK12" t="n">
-        <v>21.50206115416711</v>
+        <v>20.85446904371237</v>
       </c>
       <c r="CL12" t="n">
-        <v>21.51583547386665</v>
+        <v>22.28832860177966</v>
       </c>
       <c r="CM12" t="n">
-        <v>20.1729010291731</v>
+        <v>21.14576139701373</v>
       </c>
       <c r="CN12" t="n">
-        <v>20.90221763112249</v>
+        <v>21.05528335298046</v>
       </c>
       <c r="CO12" t="n">
-        <v>20.57768771551532</v>
+        <v>19.98924112418852</v>
       </c>
       <c r="CP12" t="n">
-        <v>19.96399336275557</v>
+        <v>19.55191472327736</v>
       </c>
       <c r="CQ12" t="n">
-        <v>18.58169672823772</v>
+        <v>19.82891776726756</v>
       </c>
       <c r="CR12" t="n">
-        <v>20.31157039214789</v>
+        <v>20.53514267713928</v>
       </c>
       <c r="CS12" t="n">
-        <v>22.24638338573128</v>
+        <v>22.01105487660168</v>
       </c>
       <c r="CT12" t="n">
-        <v>22.06772777316054</v>
+        <v>22.04068649222968</v>
       </c>
       <c r="CU12" t="n">
-        <v>21.19738684106981</v>
+        <v>21.23793933780056</v>
       </c>
       <c r="CV12" t="n">
-        <v>20.42458138892427</v>
+        <v>21.46000462841031</v>
       </c>
       <c r="CW12" t="n">
-        <v>21.62267049577501</v>
+        <v>19.66227542478277</v>
       </c>
       <c r="CX12" t="n">
-        <v>21.18756830600387</v>
+        <v>20.98819114847069</v>
       </c>
     </row>
     <row r="13">
@@ -4333,307 +4333,307 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>23.88741355943234</v>
+        <v>21.86359389987793</v>
       </c>
       <c r="C13" t="n">
-        <v>23.25639102511286</v>
+        <v>22.81328975350561</v>
       </c>
       <c r="D13" t="n">
-        <v>24.13704271226051</v>
+        <v>22.03512308360435</v>
       </c>
       <c r="E13" t="n">
-        <v>24.46958488506383</v>
+        <v>24.07714830633287</v>
       </c>
       <c r="F13" t="n">
-        <v>23.63878785720952</v>
+        <v>24.03836745854796</v>
       </c>
       <c r="G13" t="n">
-        <v>25.21623734720172</v>
+        <v>22.36557604711321</v>
       </c>
       <c r="H13" t="n">
-        <v>24.02379870217651</v>
+        <v>22.45073217434737</v>
       </c>
       <c r="I13" t="n">
-        <v>25.48867695945527</v>
+        <v>22.46327731936486</v>
       </c>
       <c r="J13" t="n">
-        <v>22.12283778324189</v>
+        <v>23.45784364655832</v>
       </c>
       <c r="K13" t="n">
-        <v>24.55149200086811</v>
+        <v>23.77436875506986</v>
       </c>
       <c r="L13" t="n">
-        <v>25.27833093299521</v>
+        <v>23.20128581340657</v>
       </c>
       <c r="M13" t="n">
-        <v>21.72051844555072</v>
+        <v>24.70497924234669</v>
       </c>
       <c r="N13" t="n">
-        <v>22.64370910092081</v>
+        <v>24.12361000706518</v>
       </c>
       <c r="O13" t="n">
-        <v>21.66207125380695</v>
+        <v>22.09671094885641</v>
       </c>
       <c r="P13" t="n">
-        <v>25.23159729542968</v>
+        <v>23.59086328160442</v>
       </c>
       <c r="Q13" t="n">
-        <v>25.1438626415754</v>
+        <v>23.5436339910372</v>
       </c>
       <c r="R13" t="n">
-        <v>24.6433263023602</v>
+        <v>24.44399942797292</v>
       </c>
       <c r="S13" t="n">
-        <v>23.94019686858068</v>
+        <v>24.64006992218229</v>
       </c>
       <c r="T13" t="n">
-        <v>25.25427054863829</v>
+        <v>23.21429097257963</v>
       </c>
       <c r="U13" t="n">
-        <v>21.7501290653466</v>
+        <v>24.68644492354665</v>
       </c>
       <c r="V13" t="n">
-        <v>22.78920856107503</v>
+        <v>24.87948848581139</v>
       </c>
       <c r="W13" t="n">
-        <v>23.79474840141304</v>
+        <v>23.46697149597749</v>
       </c>
       <c r="X13" t="n">
-        <v>24.43658220322686</v>
+        <v>24.93653349485014</v>
       </c>
       <c r="Y13" t="n">
-        <v>20.87693830619606</v>
+        <v>24.79032986480594</v>
       </c>
       <c r="Z13" t="n">
-        <v>22.73986878876671</v>
+        <v>23.4654087059162</v>
       </c>
       <c r="AA13" t="n">
-        <v>24.86512852199893</v>
+        <v>24.95357406008925</v>
       </c>
       <c r="AB13" t="n">
-        <v>23.07862879860381</v>
+        <v>23.1238009032282</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.16251762312094</v>
+        <v>23.89713112796566</v>
       </c>
       <c r="AD13" t="n">
-        <v>20.43838106909019</v>
+        <v>24.40610672293868</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.39569037685377</v>
+        <v>23.43568080141143</v>
       </c>
       <c r="AF13" t="n">
-        <v>23.87063772856797</v>
+        <v>24.63589989287057</v>
       </c>
       <c r="AG13" t="n">
-        <v>21.03760512089864</v>
+        <v>23.89913246712147</v>
       </c>
       <c r="AH13" t="n">
-        <v>22.7658230599817</v>
+        <v>23.38718743743956</v>
       </c>
       <c r="AI13" t="n">
-        <v>24.90800160325703</v>
+        <v>23.77252328610845</v>
       </c>
       <c r="AJ13" t="n">
-        <v>25.21451866768964</v>
+        <v>22.24189938181852</v>
       </c>
       <c r="AK13" t="n">
-        <v>21.98244901234461</v>
+        <v>23.42570783520671</v>
       </c>
       <c r="AL13" t="n">
-        <v>23.30173163487163</v>
+        <v>23.59502613916558</v>
       </c>
       <c r="AM13" t="n">
-        <v>25.21046819255091</v>
+        <v>22.60383070599087</v>
       </c>
       <c r="AN13" t="n">
-        <v>24.80857002853814</v>
+        <v>24.71710739663229</v>
       </c>
       <c r="AO13" t="n">
-        <v>22.88692418053837</v>
+        <v>23.32003999236245</v>
       </c>
       <c r="AP13" t="n">
-        <v>25.19575707484268</v>
+        <v>24.48548144788646</v>
       </c>
       <c r="AQ13" t="n">
-        <v>25.01057688994841</v>
+        <v>23.23384500411574</v>
       </c>
       <c r="AR13" t="n">
-        <v>24.21682031534441</v>
+        <v>21.23608219430443</v>
       </c>
       <c r="AS13" t="n">
-        <v>23.77151753023097</v>
+        <v>22.79452628131305</v>
       </c>
       <c r="AT13" t="n">
-        <v>23.24126042951542</v>
+        <v>24.42154416391282</v>
       </c>
       <c r="AU13" t="n">
-        <v>23.0878883465578</v>
+        <v>24.56431047337731</v>
       </c>
       <c r="AV13" t="n">
-        <v>24.67174735674742</v>
+        <v>25.35977221929273</v>
       </c>
       <c r="AW13" t="n">
-        <v>24.72710702940461</v>
+        <v>21.62654767219792</v>
       </c>
       <c r="AX13" t="n">
-        <v>22.18732930570592</v>
+        <v>23.23645918805875</v>
       </c>
       <c r="AY13" t="n">
-        <v>23.63914895550761</v>
+        <v>23.33232779164595</v>
       </c>
       <c r="AZ13" t="n">
-        <v>25.76568569625564</v>
+        <v>23.72046520750181</v>
       </c>
       <c r="BA13" t="n">
-        <v>23.78149561425264</v>
+        <v>22.97986095278248</v>
       </c>
       <c r="BB13" t="n">
-        <v>24.67523503701896</v>
+        <v>23.30555389572602</v>
       </c>
       <c r="BC13" t="n">
-        <v>23.53240398650568</v>
+        <v>24.40869572280449</v>
       </c>
       <c r="BD13" t="n">
-        <v>24.03713935194988</v>
+        <v>23.75337760691218</v>
       </c>
       <c r="BE13" t="n">
-        <v>22.84835180599953</v>
+        <v>23.92706463244251</v>
       </c>
       <c r="BF13" t="n">
-        <v>23.66473994853291</v>
+        <v>23.27242239352892</v>
       </c>
       <c r="BG13" t="n">
-        <v>24.15999790554484</v>
+        <v>23.26655093322408</v>
       </c>
       <c r="BH13" t="n">
-        <v>22.07835253660343</v>
+        <v>22.40174269019615</v>
       </c>
       <c r="BI13" t="n">
-        <v>23.93632282905449</v>
+        <v>25.07329672057138</v>
       </c>
       <c r="BJ13" t="n">
-        <v>23.79806764901998</v>
+        <v>22.65837035374219</v>
       </c>
       <c r="BK13" t="n">
-        <v>22.58028391838264</v>
+        <v>24.25511983288344</v>
       </c>
       <c r="BL13" t="n">
-        <v>23.56765306952195</v>
+        <v>23.71764178808159</v>
       </c>
       <c r="BM13" t="n">
-        <v>22.5341786448378</v>
+        <v>22.57179380423122</v>
       </c>
       <c r="BN13" t="n">
-        <v>23.77184056739974</v>
+        <v>23.33383350214894</v>
       </c>
       <c r="BO13" t="n">
-        <v>23.27165517009099</v>
+        <v>22.46836105895947</v>
       </c>
       <c r="BP13" t="n">
-        <v>24.75136357846775</v>
+        <v>25.27867153052715</v>
       </c>
       <c r="BQ13" t="n">
-        <v>23.34983190977875</v>
+        <v>20.92006959531266</v>
       </c>
       <c r="BR13" t="n">
-        <v>23.50034618091058</v>
+        <v>22.17063834649706</v>
       </c>
       <c r="BS13" t="n">
-        <v>23.3639859239822</v>
+        <v>23.06194505258051</v>
       </c>
       <c r="BT13" t="n">
-        <v>25.2444444227297</v>
+        <v>23.62213125851835</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.35744566441783</v>
+        <v>22.15533500280426</v>
       </c>
       <c r="BV13" t="n">
-        <v>22.90806916940732</v>
+        <v>24.14587368800943</v>
       </c>
       <c r="BW13" t="n">
-        <v>23.34333077917731</v>
+        <v>22.32307983493873</v>
       </c>
       <c r="BX13" t="n">
-        <v>22.69324847718615</v>
+        <v>23.33400846960346</v>
       </c>
       <c r="BY13" t="n">
-        <v>23.75582746860794</v>
+        <v>23.70494264169785</v>
       </c>
       <c r="BZ13" t="n">
-        <v>22.89766744244755</v>
+        <v>23.72042539591665</v>
       </c>
       <c r="CA13" t="n">
-        <v>25.16890576568585</v>
+        <v>21.84517982410076</v>
       </c>
       <c r="CB13" t="n">
-        <v>23.20843610931775</v>
+        <v>23.03914999867167</v>
       </c>
       <c r="CC13" t="n">
-        <v>24.96279380920416</v>
+        <v>24.04524442626935</v>
       </c>
       <c r="CD13" t="n">
-        <v>23.15760218823646</v>
+        <v>22.61545688853791</v>
       </c>
       <c r="CE13" t="n">
-        <v>24.0110010854095</v>
+        <v>22.75895446173647</v>
       </c>
       <c r="CF13" t="n">
-        <v>24.33000704341694</v>
+        <v>24.19725861252435</v>
       </c>
       <c r="CG13" t="n">
-        <v>23.07284388511931</v>
+        <v>23.01387186420447</v>
       </c>
       <c r="CH13" t="n">
-        <v>24.23101540715839</v>
+        <v>24.01321650148659</v>
       </c>
       <c r="CI13" t="n">
-        <v>26.04100578177718</v>
+        <v>22.46046380103137</v>
       </c>
       <c r="CJ13" t="n">
-        <v>22.13224924721477</v>
+        <v>23.32091094192941</v>
       </c>
       <c r="CK13" t="n">
-        <v>23.91300562017658</v>
+        <v>23.0868876393041</v>
       </c>
       <c r="CL13" t="n">
-        <v>24.02946884034487</v>
+        <v>24.75523171060037</v>
       </c>
       <c r="CM13" t="n">
-        <v>22.48194775631164</v>
+        <v>23.68143070217752</v>
       </c>
       <c r="CN13" t="n">
-        <v>23.39520809693764</v>
+        <v>23.40201247537385</v>
       </c>
       <c r="CO13" t="n">
-        <v>23.1107308656328</v>
+        <v>22.21634125521604</v>
       </c>
       <c r="CP13" t="n">
-        <v>22.33385075642271</v>
+        <v>21.81912001086939</v>
       </c>
       <c r="CQ13" t="n">
-        <v>20.73501335928479</v>
+        <v>22.06599228682633</v>
       </c>
       <c r="CR13" t="n">
-        <v>22.61302005987396</v>
+        <v>22.99422019238985</v>
       </c>
       <c r="CS13" t="n">
-        <v>24.78200517041014</v>
+        <v>24.41766922941993</v>
       </c>
       <c r="CT13" t="n">
-        <v>24.53987877589501</v>
+        <v>24.88172083410633</v>
       </c>
       <c r="CU13" t="n">
-        <v>23.63126881787204</v>
+        <v>23.72245800371309</v>
       </c>
       <c r="CV13" t="n">
-        <v>22.69493828875132</v>
+        <v>23.97793780510482</v>
       </c>
       <c r="CW13" t="n">
-        <v>24.02378119525517</v>
+        <v>22.05417436815121</v>
       </c>
       <c r="CX13" t="n">
-        <v>23.6214279307441</v>
+        <v>23.42765661354625</v>
       </c>
     </row>
     <row r="14">
@@ -4641,307 +4641,307 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16.86516892189877</v>
+        <v>15.57067566898709</v>
       </c>
       <c r="C14" t="n">
-        <v>16.4467775027799</v>
+        <v>16.08700623908162</v>
       </c>
       <c r="D14" t="n">
-        <v>17.16782210416397</v>
+        <v>15.70830687964545</v>
       </c>
       <c r="E14" t="n">
-        <v>17.23609283951729</v>
+        <v>16.89767458838638</v>
       </c>
       <c r="F14" t="n">
-        <v>16.52358944316017</v>
+        <v>16.97022574373022</v>
       </c>
       <c r="G14" t="n">
-        <v>17.92173561868623</v>
+        <v>15.87726565954633</v>
       </c>
       <c r="H14" t="n">
-        <v>17.04307142338533</v>
+        <v>15.90240821825209</v>
       </c>
       <c r="I14" t="n">
-        <v>17.92300207322471</v>
+        <v>15.82485014961659</v>
       </c>
       <c r="J14" t="n">
-        <v>15.47517125231796</v>
+        <v>16.60081371757623</v>
       </c>
       <c r="K14" t="n">
-        <v>17.35009338293444</v>
+        <v>16.8395158543868</v>
       </c>
       <c r="L14" t="n">
-        <v>17.73904218840294</v>
+        <v>16.44100482627893</v>
       </c>
       <c r="M14" t="n">
-        <v>15.50572324087412</v>
+        <v>17.30896797160354</v>
       </c>
       <c r="N14" t="n">
-        <v>16.08395300372141</v>
+        <v>16.97245431101886</v>
       </c>
       <c r="O14" t="n">
-        <v>15.39160488773247</v>
+        <v>15.78088748742042</v>
       </c>
       <c r="P14" t="n">
-        <v>17.72304951830075</v>
+        <v>16.87497658146419</v>
       </c>
       <c r="Q14" t="n">
-        <v>17.69391124643871</v>
+        <v>16.61811211212506</v>
       </c>
       <c r="R14" t="n">
-        <v>17.41635153549406</v>
+        <v>17.43118574330522</v>
       </c>
       <c r="S14" t="n">
-        <v>17.00259396553924</v>
+        <v>17.2648285948206</v>
       </c>
       <c r="T14" t="n">
-        <v>17.63660663294182</v>
+        <v>16.25832121347268</v>
       </c>
       <c r="U14" t="n">
-        <v>15.40959050567428</v>
+        <v>17.42643408441667</v>
       </c>
       <c r="V14" t="n">
-        <v>16.25337320504328</v>
+        <v>17.58006778265425</v>
       </c>
       <c r="W14" t="n">
-        <v>16.83426350416908</v>
+        <v>16.45126408978831</v>
       </c>
       <c r="X14" t="n">
-        <v>17.23968603611484</v>
+        <v>17.61682441670125</v>
       </c>
       <c r="Y14" t="n">
-        <v>14.82759083164268</v>
+        <v>17.32301678125131</v>
       </c>
       <c r="Z14" t="n">
-        <v>15.98867438902426</v>
+        <v>16.45410134065358</v>
       </c>
       <c r="AA14" t="n">
-        <v>17.63554634542124</v>
+        <v>17.36868768445287</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.33235480784994</v>
+        <v>16.36425179076092</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.47476712982798</v>
+        <v>16.93754336265584</v>
       </c>
       <c r="AD14" t="n">
-        <v>14.59276659826389</v>
+        <v>17.19070664314997</v>
       </c>
       <c r="AE14" t="n">
-        <v>16.56805279668551</v>
+        <v>16.471998601302</v>
       </c>
       <c r="AF14" t="n">
-        <v>16.85149317637861</v>
+        <v>17.41475128673613</v>
       </c>
       <c r="AG14" t="n">
-        <v>14.90416715257393</v>
+        <v>16.93170196381557</v>
       </c>
       <c r="AH14" t="n">
-        <v>15.99528155107384</v>
+        <v>16.50476933966976</v>
       </c>
       <c r="AI14" t="n">
-        <v>17.42937932752941</v>
+        <v>16.70883541747451</v>
       </c>
       <c r="AJ14" t="n">
-        <v>17.74916400723372</v>
+        <v>15.75147432620119</v>
       </c>
       <c r="AK14" t="n">
-        <v>15.62212906616667</v>
+        <v>16.52833128457168</v>
       </c>
       <c r="AL14" t="n">
-        <v>16.46230875146109</v>
+        <v>16.69799692281962</v>
       </c>
       <c r="AM14" t="n">
-        <v>17.76467562096082</v>
+        <v>15.99380892951747</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.58748979529836</v>
+        <v>17.33507264305946</v>
       </c>
       <c r="AO14" t="n">
-        <v>16.11929592107429</v>
+        <v>16.47881193036948</v>
       </c>
       <c r="AP14" t="n">
-        <v>17.70256044371312</v>
+        <v>17.3614816563037</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17.57246905542338</v>
+        <v>16.38963978639274</v>
       </c>
       <c r="AR14" t="n">
-        <v>17.00354626081235</v>
+        <v>15.18171704604155</v>
       </c>
       <c r="AS14" t="n">
-        <v>16.62617226077692</v>
+        <v>16.20148783887383</v>
       </c>
       <c r="AT14" t="n">
-        <v>16.46774763374261</v>
+        <v>17.215682304746</v>
       </c>
       <c r="AU14" t="n">
-        <v>16.2374492572804</v>
+        <v>17.2031748389939</v>
       </c>
       <c r="AV14" t="n">
-        <v>17.39886660888142</v>
+        <v>17.91075967935275</v>
       </c>
       <c r="AW14" t="n">
-        <v>17.33387491086028</v>
+        <v>15.29736692560182</v>
       </c>
       <c r="AX14" t="n">
-        <v>15.64192109988428</v>
+        <v>16.28347358965549</v>
       </c>
       <c r="AY14" t="n">
-        <v>16.58580279517829</v>
+        <v>16.50402321141453</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.03970242282852</v>
+        <v>16.67400300892783</v>
       </c>
       <c r="BA14" t="n">
-        <v>16.86572851809019</v>
+        <v>16.38095131921015</v>
       </c>
       <c r="BB14" t="n">
-        <v>17.17591170524697</v>
+        <v>16.48668554695753</v>
       </c>
       <c r="BC14" t="n">
-        <v>16.56238811243201</v>
+        <v>17.21941294602214</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.02340701686927</v>
+        <v>16.84868537794446</v>
       </c>
       <c r="BE14" t="n">
-        <v>16.33335619050827</v>
+        <v>16.89398321701841</v>
       </c>
       <c r="BF14" t="n">
-        <v>16.65106938255662</v>
+        <v>16.41383004982538</v>
       </c>
       <c r="BG14" t="n">
-        <v>17.06654501099387</v>
+        <v>16.45777307706746</v>
       </c>
       <c r="BH14" t="n">
-        <v>15.69249092413004</v>
+        <v>16.02592189692338</v>
       </c>
       <c r="BI14" t="n">
-        <v>17.05022836414929</v>
+        <v>17.54158327264778</v>
       </c>
       <c r="BJ14" t="n">
-        <v>16.90245569970606</v>
+        <v>16.12199572726097</v>
       </c>
       <c r="BK14" t="n">
-        <v>16.01619277717429</v>
+        <v>17.21002743796954</v>
       </c>
       <c r="BL14" t="n">
-        <v>16.66827941981207</v>
+        <v>16.52751643397716</v>
       </c>
       <c r="BM14" t="n">
-        <v>16.19326079311225</v>
+        <v>16.00796573141271</v>
       </c>
       <c r="BN14" t="n">
-        <v>16.76798571665537</v>
+        <v>16.40548519433928</v>
       </c>
       <c r="BO14" t="n">
-        <v>16.51153358135202</v>
+        <v>15.97376164139675</v>
       </c>
       <c r="BP14" t="n">
-        <v>17.39600972306206</v>
+        <v>17.83052143948466</v>
       </c>
       <c r="BQ14" t="n">
-        <v>16.49354796341022</v>
+        <v>14.91094121173323</v>
       </c>
       <c r="BR14" t="n">
-        <v>16.66189805973447</v>
+        <v>15.76174340718761</v>
       </c>
       <c r="BS14" t="n">
-        <v>16.64468802247902</v>
+        <v>16.48019619463246</v>
       </c>
       <c r="BT14" t="n">
-        <v>17.65992314091769</v>
+        <v>16.76308679561118</v>
       </c>
       <c r="BU14" t="n">
-        <v>15.87666679344674</v>
+        <v>15.65647060086122</v>
       </c>
       <c r="BV14" t="n">
-        <v>16.29559817380294</v>
+        <v>17.01101736084167</v>
       </c>
       <c r="BW14" t="n">
-        <v>16.59285174369479</v>
+        <v>15.81670164367134</v>
       </c>
       <c r="BX14" t="n">
-        <v>16.16660634294195</v>
+        <v>16.49406828969347</v>
       </c>
       <c r="BY14" t="n">
-        <v>16.87171717908609</v>
+        <v>16.69811473254413</v>
       </c>
       <c r="BZ14" t="n">
-        <v>16.04411368188307</v>
+        <v>16.86403991203888</v>
       </c>
       <c r="CA14" t="n">
-        <v>17.78240598449952</v>
+        <v>15.44675947375706</v>
       </c>
       <c r="CB14" t="n">
-        <v>16.21481997269751</v>
+        <v>16.30022220548994</v>
       </c>
       <c r="CC14" t="n">
-        <v>17.54314425149753</v>
+        <v>16.8683203320294</v>
       </c>
       <c r="CD14" t="n">
-        <v>16.45213784524509</v>
+        <v>15.93183119694837</v>
       </c>
       <c r="CE14" t="n">
-        <v>16.88229060186083</v>
+        <v>16.18506319978179</v>
       </c>
       <c r="CF14" t="n">
-        <v>17.1040477732961</v>
+        <v>17.07621522588071</v>
       </c>
       <c r="CG14" t="n">
-        <v>16.40867587437808</v>
+        <v>16.41870933591549</v>
       </c>
       <c r="CH14" t="n">
-        <v>17.13053532635668</v>
+        <v>16.9785215118311</v>
       </c>
       <c r="CI14" t="n">
-        <v>18.31294244387449</v>
+        <v>16.07986893327174</v>
       </c>
       <c r="CJ14" t="n">
-        <v>15.62307154396274</v>
+        <v>16.45002708768096</v>
       </c>
       <c r="CK14" t="n">
-        <v>17.0090342304791</v>
+        <v>16.37537499225003</v>
       </c>
       <c r="CL14" t="n">
-        <v>17.06182280453644</v>
+        <v>17.30729900050632</v>
       </c>
       <c r="CM14" t="n">
-        <v>15.97705049620598</v>
+        <v>16.84623100868384</v>
       </c>
       <c r="CN14" t="n">
-        <v>16.53694121193793</v>
+        <v>16.5078520274611</v>
       </c>
       <c r="CO14" t="n">
-        <v>16.4359586430791</v>
+        <v>15.71947916851978</v>
       </c>
       <c r="CP14" t="n">
-        <v>15.84431820659181</v>
+        <v>15.53318272416191</v>
       </c>
       <c r="CQ14" t="n">
-        <v>14.8632871781691</v>
+        <v>15.76099727893238</v>
       </c>
       <c r="CR14" t="n">
-        <v>16.0262262387117</v>
+        <v>16.19344732517606</v>
       </c>
       <c r="CS14" t="n">
-        <v>17.57207635634168</v>
+        <v>17.08087852747587</v>
       </c>
       <c r="CT14" t="n">
-        <v>17.35101622577643</v>
+        <v>17.5724494204693</v>
       </c>
       <c r="CU14" t="n">
-        <v>16.82122589465668</v>
+        <v>16.74236210157454</v>
       </c>
       <c r="CV14" t="n">
-        <v>16.21303319187578</v>
+        <v>16.90036457709601</v>
       </c>
       <c r="CW14" t="n">
-        <v>16.94656562405787</v>
+        <v>15.69890173663877</v>
       </c>
       <c r="CX14" t="n">
-        <v>16.696946060077</v>
+        <v>16.5575958091885</v>
       </c>
     </row>
     <row r="15">
@@ -4949,307 +4949,307 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>17.72101730055297</v>
+        <v>16.25925387379172</v>
       </c>
       <c r="C15" t="n">
-        <v>17.10577564925557</v>
+        <v>16.91287204284812</v>
       </c>
       <c r="D15" t="n">
-        <v>17.91576659264441</v>
+        <v>16.56430252045529</v>
       </c>
       <c r="E15" t="n">
-        <v>17.9398292288755</v>
+        <v>17.65530892670773</v>
       </c>
       <c r="F15" t="n">
-        <v>17.31166777779022</v>
+        <v>17.73317133713154</v>
       </c>
       <c r="G15" t="n">
-        <v>18.8789003604187</v>
+        <v>16.59366659428931</v>
       </c>
       <c r="H15" t="n">
-        <v>17.66980934029945</v>
+        <v>16.57630929487823</v>
       </c>
       <c r="I15" t="n">
-        <v>18.86173941054846</v>
+        <v>16.56487193412375</v>
       </c>
       <c r="J15" t="n">
-        <v>16.24793432276175</v>
+        <v>17.32037587992689</v>
       </c>
       <c r="K15" t="n">
-        <v>18.15716853564166</v>
+        <v>17.64830906557645</v>
       </c>
       <c r="L15" t="n">
-        <v>18.59998583764218</v>
+        <v>16.88986969413762</v>
       </c>
       <c r="M15" t="n">
-        <v>16.31704936114073</v>
+        <v>18.02556525588737</v>
       </c>
       <c r="N15" t="n">
-        <v>16.86113393883431</v>
+        <v>17.66142521490519</v>
       </c>
       <c r="O15" t="n">
-        <v>16.12896613596113</v>
+        <v>16.71690538360341</v>
       </c>
       <c r="P15" t="n">
-        <v>18.73154003001125</v>
+        <v>17.80310122610504</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.50982212848415</v>
+        <v>17.47779912430286</v>
       </c>
       <c r="R15" t="n">
-        <v>18.28928232420215</v>
+        <v>18.24206025962788</v>
       </c>
       <c r="S15" t="n">
-        <v>17.77204854621971</v>
+        <v>18.17023559758518</v>
       </c>
       <c r="T15" t="n">
-        <v>18.39525217139855</v>
+        <v>16.99406257798933</v>
       </c>
       <c r="U15" t="n">
-        <v>16.0302023169139</v>
+        <v>18.09870545985376</v>
       </c>
       <c r="V15" t="n">
-        <v>16.98849606850625</v>
+        <v>18.42675645522783</v>
       </c>
       <c r="W15" t="n">
-        <v>17.5171770247202</v>
+        <v>17.30664122954447</v>
       </c>
       <c r="X15" t="n">
-        <v>18.02422026153255</v>
+        <v>18.55328409935116</v>
       </c>
       <c r="Y15" t="n">
-        <v>15.46555994229339</v>
+        <v>18.25052292483849</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.59746595790475</v>
+        <v>17.36785319890426</v>
       </c>
       <c r="AA15" t="n">
-        <v>18.52959452724768</v>
+        <v>18.14734124112214</v>
       </c>
       <c r="AB15" t="n">
-        <v>16.98882004524865</v>
+        <v>17.1275115434276</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.24423152798551</v>
+        <v>17.77538648841416</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.20347257516766</v>
+        <v>17.91012154334499</v>
       </c>
       <c r="AE15" t="n">
-        <v>17.35547336035371</v>
+        <v>17.21324757043947</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.56766830914961</v>
+        <v>18.27613672244228</v>
       </c>
       <c r="AG15" t="n">
-        <v>15.49987202455681</v>
+        <v>17.7096290271837</v>
       </c>
       <c r="AH15" t="n">
-        <v>16.86054489021177</v>
+        <v>17.3659191559269</v>
       </c>
       <c r="AI15" t="n">
-        <v>18.32105167991157</v>
+        <v>17.54173053480341</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18.58918661289546</v>
+        <v>16.34651160974518</v>
       </c>
       <c r="AK15" t="n">
-        <v>16.32261587062381</v>
+        <v>17.3433585936833</v>
       </c>
       <c r="AL15" t="n">
-        <v>17.26343451308057</v>
+        <v>17.48294348227311</v>
       </c>
       <c r="AM15" t="n">
-        <v>18.4956162392037</v>
+        <v>16.87302290353274</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.55115370683294</v>
+        <v>18.20772854241036</v>
       </c>
       <c r="AO15" t="n">
-        <v>16.74832131013931</v>
+        <v>17.2843162867499</v>
       </c>
       <c r="AP15" t="n">
-        <v>18.60816379601855</v>
+        <v>18.23497204120322</v>
       </c>
       <c r="AQ15" t="n">
-        <v>18.38138007633754</v>
+        <v>17.2543337118622</v>
       </c>
       <c r="AR15" t="n">
-        <v>17.90141344120832</v>
+        <v>15.72605687813823</v>
       </c>
       <c r="AS15" t="n">
-        <v>17.26743022623685</v>
+        <v>17.10861290012085</v>
       </c>
       <c r="AT15" t="n">
-        <v>16.94910835061187</v>
+        <v>18.06709318377701</v>
       </c>
       <c r="AU15" t="n">
-        <v>17.13885072941165</v>
+        <v>18.15228924955155</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.26073310096265</v>
+        <v>18.78532016924989</v>
       </c>
       <c r="AW15" t="n">
-        <v>18.2008464910036</v>
+        <v>15.88966513305097</v>
       </c>
       <c r="AX15" t="n">
-        <v>16.39612913871781</v>
+        <v>17.15920235932069</v>
       </c>
       <c r="AY15" t="n">
-        <v>17.36056863093875</v>
+        <v>17.06986331823423</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19.00914882834112</v>
+        <v>17.58008741760834</v>
       </c>
       <c r="BA15" t="n">
-        <v>17.69400942120914</v>
+        <v>17.27129831219159</v>
       </c>
       <c r="BB15" t="n">
-        <v>18.01283198816329</v>
+        <v>17.2507503327417</v>
       </c>
       <c r="BC15" t="n">
-        <v>17.38085153850849</v>
+        <v>18.0549784171066</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.82057633524064</v>
+        <v>17.7555846372195</v>
       </c>
       <c r="BE15" t="n">
-        <v>17.23294142938666</v>
+        <v>17.75578098676035</v>
       </c>
       <c r="BF15" t="n">
-        <v>17.19843299758239</v>
+        <v>17.13350020442351</v>
       </c>
       <c r="BG15" t="n">
-        <v>17.89535605787312</v>
+        <v>17.32834767128537</v>
       </c>
       <c r="BH15" t="n">
-        <v>16.35911725026771</v>
+        <v>16.71874125181035</v>
       </c>
       <c r="BI15" t="n">
-        <v>17.78394732839519</v>
+        <v>18.43795819653328</v>
       </c>
       <c r="BJ15" t="n">
-        <v>17.69728845854132</v>
+        <v>16.73590220168059</v>
       </c>
       <c r="BK15" t="n">
-        <v>16.68747258743009</v>
+        <v>18.29401434813662</v>
       </c>
       <c r="BL15" t="n">
-        <v>17.32220193065679</v>
+        <v>17.41038250945223</v>
       </c>
       <c r="BM15" t="n">
-        <v>16.85778617916283</v>
+        <v>16.80864970656528</v>
       </c>
       <c r="BN15" t="n">
-        <v>17.47966444494093</v>
+        <v>17.06850850640237</v>
       </c>
       <c r="BO15" t="n">
-        <v>17.24697060408035</v>
+        <v>16.57870475927659</v>
       </c>
       <c r="BP15" t="n">
-        <v>18.38987219397928</v>
+        <v>18.71936635847859</v>
       </c>
       <c r="BQ15" t="n">
-        <v>17.14368092811655</v>
+        <v>15.36254515568677</v>
       </c>
       <c r="BR15" t="n">
-        <v>17.41283687871285</v>
+        <v>16.48983695708817</v>
       </c>
       <c r="BS15" t="n">
-        <v>17.55102768556263</v>
+        <v>17.29424175603983</v>
       </c>
       <c r="BT15" t="n">
-        <v>18.51114748788488</v>
+        <v>17.54222140865554</v>
       </c>
       <c r="BU15" t="n">
-        <v>16.54388216820696</v>
+        <v>16.48481040884242</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.1855131977945</v>
+        <v>17.87189228774162</v>
       </c>
       <c r="BW15" t="n">
-        <v>17.34686343298746</v>
+        <v>16.58474250765771</v>
       </c>
       <c r="BX15" t="n">
-        <v>16.93357710193068</v>
+        <v>17.29084490898314</v>
       </c>
       <c r="BY15" t="n">
-        <v>17.84162500601969</v>
+        <v>17.56662765658312</v>
       </c>
       <c r="BZ15" t="n">
-        <v>16.78076807176467</v>
+        <v>17.68758879122336</v>
       </c>
       <c r="CA15" t="n">
-        <v>18.63574108903085</v>
+        <v>16.00014120220986</v>
       </c>
       <c r="CB15" t="n">
-        <v>16.92535987364614</v>
+        <v>17.07972988266191</v>
       </c>
       <c r="CC15" t="n">
-        <v>18.53836153424661</v>
+        <v>17.64272292113928</v>
       </c>
       <c r="CD15" t="n">
-        <v>17.23051651255717</v>
+        <v>16.58251394036906</v>
       </c>
       <c r="CE15" t="n">
-        <v>17.58266941407051</v>
+        <v>16.66251656078814</v>
       </c>
       <c r="CF15" t="n">
-        <v>17.92797953408524</v>
+        <v>18.12901201148386</v>
       </c>
       <c r="CG15" t="n">
-        <v>17.1617941732599</v>
+        <v>17.10573637934741</v>
       </c>
       <c r="CH15" t="n">
-        <v>18.08869163327044</v>
+        <v>17.75807827638828</v>
       </c>
       <c r="CI15" t="n">
-        <v>19.14821339064768</v>
+        <v>16.8221094675905</v>
       </c>
       <c r="CJ15" t="n">
-        <v>16.15933159245348</v>
+        <v>17.19564483410233</v>
       </c>
       <c r="CK15" t="n">
-        <v>17.79896806827016</v>
+        <v>16.99383677601735</v>
       </c>
       <c r="CL15" t="n">
-        <v>17.98005143231849</v>
+        <v>18.11141909262375</v>
       </c>
       <c r="CM15" t="n">
-        <v>16.59459925460835</v>
+        <v>17.78948438544714</v>
       </c>
       <c r="CN15" t="n">
-        <v>17.39148386614548</v>
+        <v>17.16851914503399</v>
       </c>
       <c r="CO15" t="n">
-        <v>17.37437200366046</v>
+        <v>16.28525055300017</v>
       </c>
       <c r="CP15" t="n">
-        <v>16.52575910558656</v>
+        <v>16.17128927949121</v>
       </c>
       <c r="CQ15" t="n">
-        <v>15.36473445306724</v>
+        <v>16.44412678397844</v>
       </c>
       <c r="CR15" t="n">
-        <v>16.68156246625053</v>
+        <v>17.03177150730945</v>
       </c>
       <c r="CS15" t="n">
-        <v>18.43759494988271</v>
+        <v>17.82015418372781</v>
       </c>
       <c r="CT15" t="n">
-        <v>18.17691148197406</v>
+        <v>18.71730468829967</v>
       </c>
       <c r="CU15" t="n">
-        <v>17.57965544861847</v>
+        <v>17.58498633865253</v>
       </c>
       <c r="CV15" t="n">
-        <v>16.85488020595826</v>
+        <v>17.66580380966613</v>
       </c>
       <c r="CW15" t="n">
-        <v>17.6468658964512</v>
+        <v>16.41975980595903</v>
       </c>
       <c r="CX15" t="n">
-        <v>17.47168980651411</v>
+        <v>17.34125362843062</v>
       </c>
     </row>
     <row r="16">
@@ -5257,307 +5257,307 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>20.14583595527216</v>
+        <v>18.55750561447942</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42237625453565</v>
+        <v>19.47429107313622</v>
       </c>
       <c r="D16" t="n">
-        <v>20.38931920340242</v>
+        <v>19.04036840533617</v>
       </c>
       <c r="E16" t="n">
-        <v>20.37989442544165</v>
+        <v>20.14312633160844</v>
       </c>
       <c r="F16" t="n">
-        <v>19.83280569977307</v>
+        <v>20.17109632370244</v>
       </c>
       <c r="G16" t="n">
-        <v>21.58640344909872</v>
+        <v>18.94385278853166</v>
       </c>
       <c r="H16" t="n">
-        <v>20.12750672563388</v>
+        <v>18.86280951554609</v>
       </c>
       <c r="I16" t="n">
-        <v>21.55250370087108</v>
+        <v>18.96620718375736</v>
       </c>
       <c r="J16" t="n">
-        <v>18.74467581429407</v>
+        <v>19.76756856482587</v>
       </c>
       <c r="K16" t="n">
-        <v>20.69882498464327</v>
+        <v>20.15369975438318</v>
       </c>
       <c r="L16" t="n">
-        <v>21.19740555624501</v>
+        <v>19.04418740390569</v>
       </c>
       <c r="M16" t="n">
-        <v>18.75626043720419</v>
+        <v>20.48810265740373</v>
       </c>
       <c r="N16" t="n">
-        <v>19.23212336692966</v>
+        <v>20.09976253551186</v>
       </c>
       <c r="O16" t="n">
-        <v>18.52866186692865</v>
+        <v>19.3929140059312</v>
       </c>
       <c r="P16" t="n">
-        <v>21.46143678382514</v>
+        <v>20.40057984957012</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.04381112791559</v>
+        <v>20.03052968740838</v>
       </c>
       <c r="R16" t="n">
-        <v>20.96190391695028</v>
+        <v>20.73046671315114</v>
       </c>
       <c r="S16" t="n">
-        <v>20.2256225911963</v>
+        <v>20.77031585246652</v>
       </c>
       <c r="T16" t="n">
-        <v>20.94791401216477</v>
+        <v>19.42247442930607</v>
       </c>
       <c r="U16" t="n">
-        <v>18.39930678941709</v>
+        <v>20.53979167403232</v>
       </c>
       <c r="V16" t="n">
-        <v>19.3964286627124</v>
+        <v>21.12756402456489</v>
       </c>
       <c r="W16" t="n">
-        <v>19.87107422528461</v>
+        <v>19.83143125298712</v>
       </c>
       <c r="X16" t="n">
-        <v>20.4672896060737</v>
+        <v>21.24788702319738</v>
       </c>
       <c r="Y16" t="n">
-        <v>17.68651868622573</v>
+        <v>20.95949863507488</v>
       </c>
       <c r="Z16" t="n">
-        <v>18.91581407409837</v>
+        <v>20.09936983643016</v>
       </c>
       <c r="AA16" t="n">
-        <v>21.1609238115552</v>
+        <v>20.63977286023282</v>
       </c>
       <c r="AB16" t="n">
-        <v>19.32399531709308</v>
+        <v>19.6084370794445</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.6781117140149</v>
+        <v>20.24644546000338</v>
       </c>
       <c r="AD16" t="n">
-        <v>17.40810485477838</v>
+        <v>20.40431049084626</v>
       </c>
       <c r="AE16" t="n">
-        <v>19.81022550257539</v>
+        <v>19.57892574345484</v>
       </c>
       <c r="AF16" t="n">
-        <v>19.93471111147389</v>
+        <v>20.96813801487225</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.64665972943331</v>
+        <v>20.26971288059402</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.43067202263653</v>
+        <v>19.9549645666125</v>
       </c>
       <c r="AI16" t="n">
-        <v>21.00412888570994</v>
+        <v>20.0595697845</v>
       </c>
       <c r="AJ16" t="n">
-        <v>21.2041992503584</v>
+        <v>18.55482544324683</v>
       </c>
       <c r="AK16" t="n">
-        <v>18.6893150612516</v>
+        <v>19.91718691495308</v>
       </c>
       <c r="AL16" t="n">
-        <v>19.72949638885518</v>
+        <v>19.96744257993348</v>
       </c>
       <c r="AM16" t="n">
-        <v>20.86326772510461</v>
+        <v>19.48778028659257</v>
       </c>
       <c r="AN16" t="n">
-        <v>21.28429022807085</v>
+        <v>20.84631294225226</v>
       </c>
       <c r="AO16" t="n">
-        <v>19.06025861382421</v>
+        <v>19.79688355127468</v>
       </c>
       <c r="AP16" t="n">
-        <v>21.20222593747286</v>
+        <v>20.82722776688171</v>
       </c>
       <c r="AQ16" t="n">
-        <v>20.85420619379441</v>
+        <v>19.75125191798129</v>
       </c>
       <c r="AR16" t="n">
-        <v>20.56631849700107</v>
+        <v>17.88222027359029</v>
       </c>
       <c r="AS16" t="n">
-        <v>19.50680655710087</v>
+        <v>19.72125952561655</v>
       </c>
       <c r="AT16" t="n">
-        <v>19.23051330069469</v>
+        <v>20.69494708121149</v>
       </c>
       <c r="AU16" t="n">
-        <v>19.65619910525611</v>
+        <v>20.83541554273512</v>
       </c>
       <c r="AV16" t="n">
-        <v>21.02607094689985</v>
+        <v>21.42372785450502</v>
       </c>
       <c r="AW16" t="n">
-        <v>20.80409779096965</v>
+        <v>18.16020213604778</v>
       </c>
       <c r="AX16" t="n">
-        <v>18.8631825796737</v>
+        <v>19.5327737838782</v>
       </c>
       <c r="AY16" t="n">
-        <v>19.78576034978556</v>
+        <v>19.37812888550524</v>
       </c>
       <c r="AZ16" t="n">
-        <v>21.68194713567602</v>
+        <v>20.18039347446165</v>
       </c>
       <c r="BA16" t="n">
-        <v>20.13150243879016</v>
+        <v>19.78341397277241</v>
       </c>
       <c r="BB16" t="n">
-        <v>20.58752424741281</v>
+        <v>19.64156124698579</v>
       </c>
       <c r="BC16" t="n">
-        <v>19.85200868486814</v>
+        <v>20.71368864488556</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.4483124229506</v>
+        <v>20.30899260624094</v>
       </c>
       <c r="BE16" t="n">
-        <v>19.82476518607529</v>
+        <v>20.37374868481306</v>
       </c>
       <c r="BF16" t="n">
-        <v>19.45767990198036</v>
+        <v>19.45979065954449</v>
       </c>
       <c r="BG16" t="n">
-        <v>20.45331933624227</v>
+        <v>19.82448047924106</v>
       </c>
       <c r="BH16" t="n">
-        <v>18.6849462839677</v>
+        <v>19.11001358747544</v>
       </c>
       <c r="BI16" t="n">
-        <v>20.26232032038105</v>
+        <v>21.18327820678089</v>
       </c>
       <c r="BJ16" t="n">
-        <v>20.19518841236465</v>
+        <v>19.00686135619023</v>
       </c>
       <c r="BK16" t="n">
-        <v>19.06151525088564</v>
+        <v>21.04507758245407</v>
       </c>
       <c r="BL16" t="n">
-        <v>19.66039116795324</v>
+        <v>20.02531660709882</v>
       </c>
       <c r="BM16" t="n">
-        <v>19.17859848209412</v>
+        <v>19.20381958061622</v>
       </c>
       <c r="BN16" t="n">
-        <v>19.85520918238398</v>
+        <v>19.34606500548454</v>
       </c>
       <c r="BO16" t="n">
-        <v>19.70460908455252</v>
+        <v>18.77276361611257</v>
       </c>
       <c r="BP16" t="n">
-        <v>21.14064090398546</v>
+        <v>21.37196029806009</v>
       </c>
       <c r="BQ16" t="n">
-        <v>19.5317331313117</v>
+        <v>17.4724682342688</v>
       </c>
       <c r="BR16" t="n">
-        <v>19.83959939388646</v>
+        <v>18.90749867104341</v>
       </c>
       <c r="BS16" t="n">
-        <v>20.21298749824264</v>
+        <v>19.81835437356656</v>
       </c>
       <c r="BT16" t="n">
-        <v>21.12820216057265</v>
+        <v>19.96169935586363</v>
       </c>
       <c r="BU16" t="n">
-        <v>18.85079292364611</v>
+        <v>19.03651013685848</v>
       </c>
       <c r="BV16" t="n">
-        <v>19.63938176708236</v>
+        <v>20.58709227842294</v>
       </c>
       <c r="BW16" t="n">
-        <v>19.75078067908325</v>
+        <v>19.0258581742674</v>
       </c>
       <c r="BX16" t="n">
-        <v>19.39398411092883</v>
+        <v>19.8113839648664</v>
       </c>
       <c r="BY16" t="n">
-        <v>20.56012366898727</v>
+        <v>20.01618635344933</v>
       </c>
       <c r="BZ16" t="n">
-        <v>19.19971587521247</v>
+        <v>20.32424896556493</v>
       </c>
       <c r="CA16" t="n">
-        <v>21.24790665815146</v>
+        <v>18.19173587230818</v>
       </c>
       <c r="CB16" t="n">
-        <v>19.2610063843886</v>
+        <v>19.49563426822655</v>
       </c>
       <c r="CC16" t="n">
-        <v>21.27874335354186</v>
+        <v>20.14909535765026</v>
       </c>
       <c r="CD16" t="n">
-        <v>19.67518610585624</v>
+        <v>18.97784089405269</v>
       </c>
       <c r="CE16" t="n">
-        <v>20.07652456735234</v>
+        <v>18.91878876964224</v>
       </c>
       <c r="CF16" t="n">
-        <v>20.4242006993343</v>
+        <v>20.83091913824967</v>
       </c>
       <c r="CG16" t="n">
-        <v>19.58970533324747</v>
+        <v>19.39502476349533</v>
       </c>
       <c r="CH16" t="n">
-        <v>20.7395675143695</v>
+        <v>20.27643785236812</v>
       </c>
       <c r="CI16" t="n">
-        <v>21.84039139766441</v>
+        <v>19.19915627902105</v>
       </c>
       <c r="CJ16" t="n">
-        <v>18.43286292594824</v>
+        <v>19.48812389828905</v>
       </c>
       <c r="CK16" t="n">
-        <v>20.25207087434871</v>
+        <v>19.35563704560095</v>
       </c>
       <c r="CL16" t="n">
-        <v>20.58943865543608</v>
+        <v>20.65223123859971</v>
       </c>
       <c r="CM16" t="n">
-        <v>18.75294212996383</v>
+        <v>20.37634049875227</v>
       </c>
       <c r="CN16" t="n">
-        <v>19.95135173506087</v>
+        <v>19.52211200381008</v>
       </c>
       <c r="CO16" t="n">
-        <v>19.85341258408521</v>
+        <v>18.48696704192929</v>
       </c>
       <c r="CP16" t="n">
-        <v>18.86029624142322</v>
+        <v>18.52596206074197</v>
       </c>
       <c r="CQ16" t="n">
-        <v>17.48713554497025</v>
+        <v>18.74247669943656</v>
       </c>
       <c r="CR16" t="n">
-        <v>19.04477645252824</v>
+        <v>19.53128152736775</v>
       </c>
       <c r="CS16" t="n">
-        <v>21.05921474939523</v>
+        <v>20.30745126234527</v>
       </c>
       <c r="CT16" t="n">
-        <v>20.77964245565686</v>
+        <v>21.47094010160225</v>
       </c>
       <c r="CU16" t="n">
-        <v>20.07403092818355</v>
+        <v>20.1658636084388</v>
       </c>
       <c r="CV16" t="n">
-        <v>19.20186590268477</v>
+        <v>20.10262923880826</v>
       </c>
       <c r="CW16" t="n">
-        <v>19.96662772933895</v>
+        <v>18.76986746038505</v>
       </c>
       <c r="CX16" t="n">
-        <v>19.94422139965969</v>
+        <v>19.82018307501525</v>
       </c>
     </row>
     <row r="17">
@@ -5565,307 +5565,307 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>18.46378797863202</v>
+        <v>16.97798155059377</v>
       </c>
       <c r="C17" t="n">
-        <v>17.64570743416019</v>
+        <v>17.77885205781015</v>
       </c>
       <c r="D17" t="n">
-        <v>18.6819421359927</v>
+        <v>17.54462669053094</v>
       </c>
       <c r="E17" t="n">
-        <v>18.36666367825088</v>
+        <v>18.36668331320497</v>
       </c>
       <c r="F17" t="n">
-        <v>18.09641798770286</v>
+        <v>18.39370101002584</v>
       </c>
       <c r="G17" t="n">
-        <v>19.61192228379458</v>
+        <v>17.29810002451752</v>
       </c>
       <c r="H17" t="n">
-        <v>18.12254229411287</v>
+        <v>17.23335376342245</v>
       </c>
       <c r="I17" t="n">
-        <v>19.51707563808729</v>
+        <v>17.31461302090296</v>
       </c>
       <c r="J17" t="n">
-        <v>17.21050849434463</v>
+        <v>18.10334912649484</v>
       </c>
       <c r="K17" t="n">
-        <v>18.77147752662001</v>
+        <v>18.36499470715366</v>
       </c>
       <c r="L17" t="n">
-        <v>19.22716554102321</v>
+        <v>17.15378311199325</v>
       </c>
       <c r="M17" t="n">
-        <v>17.29966100336728</v>
+        <v>18.69781699637037</v>
       </c>
       <c r="N17" t="n">
-        <v>17.61820868096424</v>
+        <v>18.25029712286651</v>
       </c>
       <c r="O17" t="n">
-        <v>17.06245112306717</v>
+        <v>17.96479507299449</v>
       </c>
       <c r="P17" t="n">
-        <v>19.58670118527248</v>
+        <v>18.92201871958922</v>
       </c>
       <c r="Q17" t="n">
-        <v>19.27204122858433</v>
+        <v>18.36641824132482</v>
       </c>
       <c r="R17" t="n">
-        <v>19.0483500141717</v>
+        <v>19.04704428972505</v>
       </c>
       <c r="S17" t="n">
-        <v>18.35589390593529</v>
+        <v>18.94187947564613</v>
       </c>
       <c r="T17" t="n">
-        <v>18.84942829433721</v>
+        <v>17.75640930529106</v>
       </c>
       <c r="U17" t="n">
-        <v>16.86403991203888</v>
+        <v>18.57100464541281</v>
       </c>
       <c r="V17" t="n">
-        <v>17.77214672099014</v>
+        <v>19.22970826757721</v>
       </c>
       <c r="W17" t="n">
-        <v>18.02755820372699</v>
+        <v>18.0792963077408</v>
       </c>
       <c r="X17" t="n">
-        <v>18.60574869666611</v>
+        <v>19.42349544691849</v>
       </c>
       <c r="Y17" t="n">
-        <v>16.19233795027026</v>
+        <v>19.01255549287486</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.12570512765179</v>
+        <v>18.3716607740655</v>
       </c>
       <c r="AA17" t="n">
-        <v>19.26346075364921</v>
+        <v>18.64969172390819</v>
       </c>
       <c r="AB17" t="n">
-        <v>17.65803818532553</v>
+        <v>17.89893943699362</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.05674556297425</v>
+        <v>18.55125188160337</v>
       </c>
       <c r="AD17" t="n">
-        <v>15.94971864011974</v>
+        <v>18.62942845129254</v>
       </c>
       <c r="AE17" t="n">
-        <v>18.19904989270482</v>
+        <v>17.75791137927856</v>
       </c>
       <c r="AF17" t="n">
-        <v>18.188918256397</v>
+        <v>19.06775916628466</v>
       </c>
       <c r="AG17" t="n">
-        <v>16.0878799945384</v>
+        <v>18.56519269900367</v>
       </c>
       <c r="AH17" t="n">
-        <v>17.80737182861852</v>
+        <v>18.26435574999132</v>
       </c>
       <c r="AI17" t="n">
-        <v>19.19715351370439</v>
+        <v>18.29681232909372</v>
       </c>
       <c r="AJ17" t="n">
-        <v>19.24067438943365</v>
+        <v>16.88225133195266</v>
       </c>
       <c r="AK17" t="n">
-        <v>17.18546411040929</v>
+        <v>18.11116383822065</v>
       </c>
       <c r="AL17" t="n">
-        <v>18.00960203821632</v>
+        <v>18.1561377005522</v>
       </c>
       <c r="AM17" t="n">
-        <v>18.93807029455365</v>
+        <v>17.85696972263706</v>
       </c>
       <c r="AN17" t="n">
-        <v>19.48753484966651</v>
+        <v>18.92498359765604</v>
       </c>
       <c r="AO17" t="n">
-        <v>17.29577328245846</v>
+        <v>18.11899818490054</v>
       </c>
       <c r="AP17" t="n">
-        <v>19.21847707384063</v>
+        <v>19.12664439358538</v>
       </c>
       <c r="AQ17" t="n">
-        <v>18.97154789126847</v>
+        <v>18.15911239609606</v>
       </c>
       <c r="AR17" t="n">
-        <v>18.95289468488778</v>
+        <v>16.34504880566585</v>
       </c>
       <c r="AS17" t="n">
-        <v>17.62147790081938</v>
+        <v>18.26131233210815</v>
       </c>
       <c r="AT17" t="n">
-        <v>17.22940713765138</v>
+        <v>18.92875350884035</v>
       </c>
       <c r="AU17" t="n">
-        <v>18.05611724444353</v>
+        <v>19.04138942294859</v>
       </c>
       <c r="AV17" t="n">
-        <v>19.16262544694602</v>
+        <v>19.53416786561823</v>
       </c>
       <c r="AW17" t="n">
-        <v>18.88826623351721</v>
+        <v>16.51179865323217</v>
       </c>
       <c r="AX17" t="n">
-        <v>17.28650558413037</v>
+        <v>17.91729811906303</v>
       </c>
       <c r="AY17" t="n">
-        <v>17.97770505530534</v>
+        <v>17.50709447579759</v>
       </c>
       <c r="AZ17" t="n">
-        <v>19.71026395132898</v>
+        <v>18.48510172129122</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.48517044363052</v>
+        <v>18.08957520620426</v>
       </c>
       <c r="BB17" t="n">
-        <v>18.76251417008024</v>
+        <v>17.91760246085135</v>
       </c>
       <c r="BC17" t="n">
-        <v>18.09655543238146</v>
+        <v>18.82875268768577</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.70742830639495</v>
+        <v>18.66765770689591</v>
       </c>
       <c r="BE17" t="n">
-        <v>18.14714489158129</v>
+        <v>18.65458082747534</v>
       </c>
       <c r="BF17" t="n">
-        <v>17.54496048475039</v>
+        <v>17.72686851687028</v>
       </c>
       <c r="BG17" t="n">
-        <v>18.64254460062128</v>
+        <v>18.19946222674061</v>
       </c>
       <c r="BH17" t="n">
-        <v>17.06213696380181</v>
+        <v>17.53024408666373</v>
       </c>
       <c r="BI17" t="n">
-        <v>18.5358875300319</v>
+        <v>19.1761441128335</v>
       </c>
       <c r="BJ17" t="n">
-        <v>18.49065841329725</v>
+        <v>17.27006131008424</v>
       </c>
       <c r="BK17" t="n">
-        <v>17.39453710150569</v>
+        <v>19.41642686344791</v>
       </c>
       <c r="BL17" t="n">
-        <v>17.82416953183818</v>
+        <v>18.35506923786373</v>
       </c>
       <c r="BM17" t="n">
-        <v>17.65583907046802</v>
+        <v>17.65332579634515</v>
       </c>
       <c r="BN17" t="n">
-        <v>18.07076492019089</v>
+        <v>17.53807843334362</v>
       </c>
       <c r="BO17" t="n">
-        <v>17.89385398388562</v>
+        <v>17.19008814209629</v>
       </c>
       <c r="BP17" t="n">
-        <v>19.20662737905037</v>
+        <v>19.45936850803167</v>
       </c>
       <c r="BQ17" t="n">
-        <v>17.7212332850479</v>
+        <v>15.83780921931265</v>
       </c>
       <c r="BR17" t="n">
-        <v>18.11872329554335</v>
+        <v>17.23787962033903</v>
       </c>
       <c r="BS17" t="n">
-        <v>18.60110503002502</v>
+        <v>18.11790844494882</v>
       </c>
       <c r="BT17" t="n">
-        <v>19.25606819343623</v>
+        <v>18.30168179770678</v>
       </c>
       <c r="BU17" t="n">
-        <v>17.23624010167293</v>
+        <v>17.43569196526771</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.12593914116956</v>
+        <v>18.82974425286706</v>
       </c>
       <c r="BW17" t="n">
-        <v>18.08428358607837</v>
+        <v>17.36993450403726</v>
       </c>
       <c r="BX17" t="n">
-        <v>17.86052364932644</v>
+        <v>18.18697439594259</v>
       </c>
       <c r="BY17" t="n">
-        <v>18.92369750816348</v>
+        <v>18.29451503946579</v>
       </c>
       <c r="BZ17" t="n">
-        <v>17.57288138945917</v>
+        <v>18.45230153049233</v>
       </c>
       <c r="CA17" t="n">
-        <v>19.37219912937159</v>
+        <v>16.50077362651348</v>
       </c>
       <c r="CB17" t="n">
-        <v>17.53963941219337</v>
+        <v>17.89338274498758</v>
       </c>
       <c r="CC17" t="n">
-        <v>19.50917256906811</v>
+        <v>18.41632047713168</v>
       </c>
       <c r="CD17" t="n">
-        <v>17.94634803363169</v>
+        <v>17.19237561424719</v>
       </c>
       <c r="CE17" t="n">
-        <v>18.20642281796372</v>
+        <v>17.04210931063517</v>
       </c>
       <c r="CF17" t="n">
-        <v>18.58472947831818</v>
+        <v>19.20551800414457</v>
       </c>
       <c r="CG17" t="n">
-        <v>17.95375041132171</v>
+        <v>17.66189645380322</v>
       </c>
       <c r="CH17" t="n">
-        <v>18.98610720972245</v>
+        <v>18.50974358866781</v>
       </c>
       <c r="CI17" t="n">
-        <v>19.68944108252191</v>
+        <v>17.72829205104144</v>
       </c>
       <c r="CJ17" t="n">
-        <v>16.80122769392117</v>
+        <v>17.82480766784594</v>
       </c>
       <c r="CK17" t="n">
-        <v>18.53145003040871</v>
+        <v>17.58478998911168</v>
       </c>
       <c r="CL17" t="n">
-        <v>18.89571769859245</v>
+        <v>18.69909326838589</v>
       </c>
       <c r="CM17" t="n">
-        <v>17.14322932417259</v>
+        <v>18.70464996039193</v>
       </c>
       <c r="CN17" t="n">
-        <v>18.29268898873589</v>
+        <v>17.65001730658184</v>
       </c>
       <c r="CO17" t="n">
-        <v>18.33252831057422</v>
+        <v>16.79556300966767</v>
       </c>
       <c r="CP17" t="n">
-        <v>17.30697502376392</v>
+        <v>16.92291532186256</v>
       </c>
       <c r="CQ17" t="n">
-        <v>15.93864452601584</v>
+        <v>17.26420027628988</v>
       </c>
       <c r="CR17" t="n">
-        <v>17.29778586525217</v>
+        <v>17.81200567778256</v>
       </c>
       <c r="CS17" t="n">
-        <v>19.26871310386694</v>
+        <v>18.37754144281394</v>
       </c>
       <c r="CT17" t="n">
-        <v>18.91294737080198</v>
+        <v>19.80899831794508</v>
       </c>
       <c r="CU17" t="n">
-        <v>18.32268138110063</v>
+        <v>18.32417363761108</v>
       </c>
       <c r="CV17" t="n">
-        <v>17.5586264127935</v>
+        <v>18.23671955211677</v>
       </c>
       <c r="CW17" t="n">
-        <v>18.21967641197105</v>
+        <v>17.22004126455286</v>
       </c>
       <c r="CX17" t="n">
-        <v>18.1966841752619</v>
+        <v>18.09827682880608</v>
       </c>
     </row>
     <row r="18">
@@ -5873,307 +5873,307 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>20.82696269500156</v>
+        <v>19.19855741292146</v>
       </c>
       <c r="C18" t="n">
-        <v>19.80900813542213</v>
+        <v>20.2355382430092</v>
       </c>
       <c r="D18" t="n">
-        <v>21.08768543281838</v>
+        <v>19.91217018418438</v>
       </c>
       <c r="E18" t="n">
-        <v>20.6894002066825</v>
+        <v>20.77469444722746</v>
       </c>
       <c r="F18" t="n">
-        <v>20.49480799422373</v>
+        <v>20.65388057474285</v>
       </c>
       <c r="G18" t="n">
-        <v>22.2317651199624</v>
+        <v>19.52385951472364</v>
       </c>
       <c r="H18" t="n">
-        <v>20.46170346163653</v>
+        <v>19.34699766580358</v>
       </c>
       <c r="I18" t="n">
-        <v>22.05976292217836</v>
+        <v>19.69072717201447</v>
       </c>
       <c r="J18" t="n">
-        <v>19.65634636741175</v>
+        <v>20.48490215988788</v>
       </c>
       <c r="K18" t="n">
-        <v>21.2266714553086</v>
+        <v>20.81066568311106</v>
       </c>
       <c r="L18" t="n">
-        <v>21.77723556785022</v>
+        <v>19.20653902175698</v>
       </c>
       <c r="M18" t="n">
-        <v>19.71319937696468</v>
+        <v>21.04907329561036</v>
       </c>
       <c r="N18" t="n">
-        <v>19.90410021805547</v>
+        <v>20.5736521523518</v>
       </c>
       <c r="O18" t="n">
-        <v>19.3397916376544</v>
+        <v>20.53945787981288</v>
       </c>
       <c r="P18" t="n">
-        <v>22.10949826087551</v>
+        <v>21.41179961989842</v>
       </c>
       <c r="Q18" t="n">
-        <v>21.66203729223389</v>
+        <v>20.80495191147235</v>
       </c>
       <c r="R18" t="n">
-        <v>21.54566091937248</v>
+        <v>21.36295767161215</v>
       </c>
       <c r="S18" t="n">
-        <v>20.73372611552924</v>
+        <v>21.41916272768028</v>
       </c>
       <c r="T18" t="n">
-        <v>21.38668651362379</v>
+        <v>20.02437412930275</v>
       </c>
       <c r="U18" t="n">
-        <v>19.11547210471105</v>
+        <v>20.84723578509426</v>
       </c>
       <c r="V18" t="n">
-        <v>20.19155594585894</v>
+        <v>21.81634839638741</v>
       </c>
       <c r="W18" t="n">
-        <v>20.2967992997542</v>
+        <v>20.57297474643587</v>
       </c>
       <c r="X18" t="n">
-        <v>20.98697775331675</v>
+        <v>21.96740991563987</v>
       </c>
       <c r="Y18" t="n">
-        <v>18.35012122943433</v>
+        <v>21.62973779276417</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.32647913878482</v>
+        <v>21.01736284476318</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.70195515388857</v>
+        <v>21.01598839797724</v>
       </c>
       <c r="AB18" t="n">
-        <v>19.86634220135014</v>
+        <v>20.25510447475483</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.30535032225819</v>
+        <v>20.95366705371165</v>
       </c>
       <c r="AD18" t="n">
-        <v>18.02519219175976</v>
+        <v>21.0555331955043</v>
       </c>
       <c r="AE18" t="n">
-        <v>20.52872737740546</v>
+        <v>20.05111693676643</v>
       </c>
       <c r="AF18" t="n">
-        <v>20.44340368442937</v>
+        <v>21.66004434439428</v>
       </c>
       <c r="AG18" t="n">
-        <v>18.21733985243494</v>
+        <v>20.96449573088949</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.24584659390379</v>
+        <v>20.75301745791769</v>
       </c>
       <c r="AI18" t="n">
-        <v>21.83163420814253</v>
+        <v>20.71794942992199</v>
       </c>
       <c r="AJ18" t="n">
-        <v>21.75603963491553</v>
+        <v>19.01188790443597</v>
       </c>
       <c r="AK18" t="n">
-        <v>19.46804715773721</v>
+        <v>20.61604401822117</v>
       </c>
       <c r="AL18" t="n">
-        <v>20.35045181179128</v>
+        <v>20.53171189042637</v>
       </c>
       <c r="AM18" t="n">
-        <v>21.18641979943449</v>
+        <v>20.35247421206203</v>
       </c>
       <c r="AN18" t="n">
-        <v>22.07700241186494</v>
+        <v>21.4942762445322</v>
       </c>
       <c r="AO18" t="n">
-        <v>19.57491039534447</v>
+        <v>20.55823871339512</v>
       </c>
       <c r="AP18" t="n">
-        <v>21.77722575037317</v>
+        <v>21.54575909414291</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21.3108857733789</v>
+        <v>20.49723291105322</v>
       </c>
       <c r="AR18" t="n">
-        <v>21.46760215940781</v>
+        <v>18.44290620496269</v>
       </c>
       <c r="AS18" t="n">
-        <v>19.80906704028438</v>
+        <v>20.8167328839233</v>
       </c>
       <c r="AT18" t="n">
-        <v>19.52859153865811</v>
+        <v>21.44338244354405</v>
       </c>
       <c r="AU18" t="n">
-        <v>20.41951776278505</v>
+        <v>21.51706260874777</v>
       </c>
       <c r="AV18" t="n">
-        <v>21.80431216953334</v>
+        <v>22.04433966574464</v>
       </c>
       <c r="AW18" t="n">
-        <v>21.41661018364923</v>
+        <v>18.74929984598108</v>
       </c>
       <c r="AX18" t="n">
-        <v>19.54875663650334</v>
+        <v>20.26627676362916</v>
       </c>
       <c r="AY18" t="n">
-        <v>20.38663903216982</v>
+        <v>19.72501961932381</v>
       </c>
       <c r="AZ18" t="n">
-        <v>22.18539717589083</v>
+        <v>20.90264562552195</v>
       </c>
       <c r="BA18" t="n">
-        <v>20.73341195626388</v>
+        <v>20.56479678805949</v>
       </c>
       <c r="BB18" t="n">
-        <v>21.28687222453302</v>
+        <v>20.22794933325537</v>
       </c>
       <c r="BC18" t="n">
-        <v>20.5013660688881</v>
+        <v>21.41810244015969</v>
       </c>
       <c r="BD18" t="n">
-        <v>21.08373880704731</v>
+        <v>21.0883137513491</v>
       </c>
       <c r="BE18" t="n">
-        <v>20.70709130031302</v>
+        <v>21.19844620881151</v>
       </c>
       <c r="BF18" t="n">
-        <v>19.72722855165836</v>
+        <v>19.96256329384337</v>
       </c>
       <c r="BG18" t="n">
-        <v>21.09976092958062</v>
+        <v>20.64293408784049</v>
       </c>
       <c r="BH18" t="n">
-        <v>19.33610026628644</v>
+        <v>19.79247550408261</v>
       </c>
       <c r="BI18" t="n">
-        <v>21.02826024428032</v>
+        <v>21.74560365681938</v>
       </c>
       <c r="BJ18" t="n">
-        <v>20.8392247238276</v>
+        <v>19.455284437582</v>
       </c>
       <c r="BK18" t="n">
-        <v>19.72299721905306</v>
+        <v>22.09788418553427</v>
       </c>
       <c r="BL18" t="n">
-        <v>20.09961527335622</v>
+        <v>20.84294554762669</v>
       </c>
       <c r="BM18" t="n">
-        <v>19.90432602002745</v>
+        <v>19.98634122324023</v>
       </c>
       <c r="BN18" t="n">
-        <v>20.41049550138302</v>
+        <v>19.74433059666634</v>
       </c>
       <c r="BO18" t="n">
-        <v>20.23853257350715</v>
+        <v>19.37169843804243</v>
       </c>
       <c r="BP18" t="n">
-        <v>21.83640550198517</v>
+        <v>22.00699398307509</v>
       </c>
       <c r="BQ18" t="n">
-        <v>20.05699760551487</v>
+        <v>17.91276244466941</v>
       </c>
       <c r="BR18" t="n">
-        <v>20.42249245832891</v>
+        <v>19.53352972961047</v>
       </c>
       <c r="BS18" t="n">
-        <v>21.10752655392121</v>
+        <v>20.56536620172795</v>
       </c>
       <c r="BT18" t="n">
-        <v>21.64617224933327</v>
+        <v>20.57392704170899</v>
       </c>
       <c r="BU18" t="n">
-        <v>19.48208614990794</v>
+        <v>19.83485755247495</v>
       </c>
       <c r="BV18" t="n">
-        <v>20.48158385264753</v>
+        <v>21.43679491644855</v>
       </c>
       <c r="BW18" t="n">
-        <v>20.43836731870658</v>
+        <v>19.73125371724578</v>
       </c>
       <c r="BX18" t="n">
-        <v>20.21593274135538</v>
+        <v>20.58282167590946</v>
       </c>
       <c r="BY18" t="n">
-        <v>21.49368719590965</v>
+        <v>20.61036951649062</v>
       </c>
       <c r="BZ18" t="n">
-        <v>19.86852168125357</v>
+        <v>21.03838206311111</v>
       </c>
       <c r="CA18" t="n">
-        <v>21.88969476737169</v>
+        <v>18.58382627043028</v>
       </c>
       <c r="CB18" t="n">
-        <v>19.76039198910782</v>
+        <v>20.32494600643495</v>
       </c>
       <c r="CC18" t="n">
-        <v>22.06373900038056</v>
+        <v>20.86235469973965</v>
       </c>
       <c r="CD18" t="n">
-        <v>20.30288613552053</v>
+        <v>19.58739822614249</v>
       </c>
       <c r="CE18" t="n">
-        <v>20.45630384926318</v>
+        <v>19.26268517296286</v>
       </c>
       <c r="CF18" t="n">
-        <v>20.97687556944005</v>
+        <v>21.78496192228264</v>
       </c>
       <c r="CG18" t="n">
-        <v>20.40539041332093</v>
+        <v>19.89614806165107</v>
       </c>
       <c r="CH18" t="n">
-        <v>21.44281302987558</v>
+        <v>20.92411644781383</v>
       </c>
       <c r="CI18" t="n">
-        <v>22.17481393563904</v>
+        <v>20.02214556201411</v>
       </c>
       <c r="CJ18" t="n">
-        <v>18.88861966269074</v>
+        <v>20.05202996213138</v>
       </c>
       <c r="CK18" t="n">
-        <v>20.93714423984918</v>
+        <v>19.96704006337474</v>
       </c>
       <c r="CL18" t="n">
-        <v>21.42771375018426</v>
+        <v>21.12117284701024</v>
       </c>
       <c r="CM18" t="n">
-        <v>19.18988858069296</v>
+        <v>21.18071584527281</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.78355962899681</v>
+        <v>20.02629835480307</v>
       </c>
       <c r="CO18" t="n">
-        <v>20.68355880784223</v>
+        <v>18.94292012821263</v>
       </c>
       <c r="CP18" t="n">
-        <v>19.55298796910864</v>
+        <v>19.22601689620924</v>
       </c>
       <c r="CQ18" t="n">
-        <v>18.04115540943081</v>
+        <v>19.43027932355484</v>
       </c>
       <c r="CR18" t="n">
-        <v>19.61199100613388</v>
+        <v>20.23855220846123</v>
       </c>
       <c r="CS18" t="n">
-        <v>21.86251017344109</v>
+        <v>20.80182995377284</v>
       </c>
       <c r="CT18" t="n">
-        <v>21.41759193135348</v>
+        <v>22.41612752134291</v>
       </c>
       <c r="CU18" t="n">
-        <v>20.64879512163485</v>
+        <v>20.84311244473642</v>
       </c>
       <c r="CV18" t="n">
-        <v>19.87763229994898</v>
+        <v>20.53585486573829</v>
       </c>
       <c r="CW18" t="n">
-        <v>20.42661579868675</v>
+        <v>19.47350567497282</v>
       </c>
       <c r="CX18" t="n">
-        <v>20.56808191222743</v>
+        <v>20.48288005414144</v>
       </c>
     </row>
     <row r="19">
@@ -6181,307 +6181,307 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>21.75168067510867</v>
+        <v>20.11989818092596</v>
       </c>
       <c r="C19" t="n">
-        <v>20.63209559318561</v>
+        <v>21.27897897299088</v>
       </c>
       <c r="D19" t="n">
-        <v>22.06520180445989</v>
+        <v>20.84797209587244</v>
       </c>
       <c r="E19" t="n">
-        <v>21.50673462289909</v>
+        <v>21.73390122418476</v>
       </c>
       <c r="F19" t="n">
-        <v>21.42002666566001</v>
+        <v>21.49014308669732</v>
       </c>
       <c r="G19" t="n">
-        <v>23.25724968443341</v>
+        <v>20.37163792724893</v>
       </c>
       <c r="H19" t="n">
-        <v>21.33815872460287</v>
+        <v>20.13036361145323</v>
       </c>
       <c r="I19" t="n">
-        <v>23.06223532046183</v>
+        <v>20.62914053259582</v>
       </c>
       <c r="J19" t="n">
-        <v>20.7000816217047</v>
+        <v>21.4546529071888</v>
       </c>
       <c r="K19" t="n">
-        <v>22.14252425364637</v>
+        <v>21.81169491226928</v>
       </c>
       <c r="L19" t="n">
-        <v>22.74649544129901</v>
+        <v>19.93505472317037</v>
       </c>
       <c r="M19" t="n">
-        <v>20.73349049608022</v>
+        <v>21.9703060713674</v>
       </c>
       <c r="N19" t="n">
-        <v>20.8064441679828</v>
+        <v>21.44783957812133</v>
       </c>
       <c r="O19" t="n">
-        <v>20.30462382895704</v>
+        <v>21.62035228471157</v>
       </c>
       <c r="P19" t="n">
-        <v>23.10367489105808</v>
+        <v>22.50847071040437</v>
       </c>
       <c r="Q19" t="n">
-        <v>22.58521392844534</v>
+        <v>21.82065826880905</v>
       </c>
       <c r="R19" t="n">
-        <v>22.4907697992968</v>
+        <v>22.26901262786153</v>
       </c>
       <c r="S19" t="n">
-        <v>21.66583665584933</v>
+        <v>22.36969085493204</v>
       </c>
       <c r="T19" t="n">
-        <v>22.35054677469923</v>
+        <v>20.90312668189703</v>
       </c>
       <c r="U19" t="n">
-        <v>20.01743317303372</v>
+        <v>21.7094066189638</v>
       </c>
       <c r="V19" t="n">
-        <v>21.21738412202643</v>
+        <v>22.81146750436606</v>
       </c>
       <c r="W19" t="n">
-        <v>21.19561877542328</v>
+        <v>21.53888686021318</v>
       </c>
       <c r="X19" t="n">
-        <v>21.871502982412</v>
+        <v>22.98383294880067</v>
       </c>
       <c r="Y19" t="n">
-        <v>19.25816913352332</v>
+        <v>22.65197277233413</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.12779143246811</v>
+        <v>22.10398083877764</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.60828499949514</v>
+        <v>21.88965549746352</v>
       </c>
       <c r="AB19" t="n">
-        <v>20.68807484728176</v>
+        <v>21.22746667094904</v>
       </c>
       <c r="AC19" t="n">
-        <v>21.18863854924608</v>
+        <v>21.91828326051935</v>
       </c>
       <c r="AD19" t="n">
-        <v>18.90361095013459</v>
+        <v>22.00937962999642</v>
       </c>
       <c r="AE19" t="n">
-        <v>21.4680832157829</v>
+        <v>20.91966913071358</v>
       </c>
       <c r="AF19" t="n">
-        <v>21.34237042225409</v>
+        <v>22.69710371429835</v>
       </c>
       <c r="AG19" t="n">
-        <v>19.05746063286711</v>
+        <v>21.94537949715657</v>
       </c>
       <c r="AH19" t="n">
-        <v>21.25275649181044</v>
+        <v>21.79314969813606</v>
       </c>
       <c r="AI19" t="n">
-        <v>22.88038619320419</v>
+        <v>21.70109121590884</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22.73458684164649</v>
+        <v>19.83456302816367</v>
       </c>
       <c r="AK19" t="n">
-        <v>20.42945304955202</v>
+        <v>21.6491862147853</v>
       </c>
       <c r="AL19" t="n">
-        <v>21.26726672287921</v>
+        <v>21.43134621668998</v>
       </c>
       <c r="AM19" t="n">
-        <v>21.97934796772351</v>
+        <v>21.37896015919137</v>
       </c>
       <c r="AN19" t="n">
-        <v>23.10914322577074</v>
+        <v>22.45957967473288</v>
       </c>
       <c r="AO19" t="n">
-        <v>20.40723609900492</v>
+        <v>21.55898323571911</v>
       </c>
       <c r="AP19" t="n">
-        <v>22.76238993663076</v>
+        <v>22.49372485988658</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22.19002120757783</v>
+        <v>21.37394342842267</v>
       </c>
       <c r="AR19" t="n">
-        <v>22.50528003036557</v>
+        <v>19.29463124325905</v>
       </c>
       <c r="AS19" t="n">
-        <v>20.63931143881182</v>
+        <v>21.93194918856247</v>
       </c>
       <c r="AT19" t="n">
-        <v>20.39597545283721</v>
+        <v>22.4289785987915</v>
       </c>
       <c r="AU19" t="n">
-        <v>21.36000261102236</v>
+        <v>22.4795582405143</v>
       </c>
       <c r="AV19" t="n">
-        <v>22.83509817160728</v>
+        <v>23.06863631549351</v>
       </c>
       <c r="AW19" t="n">
-        <v>22.35028170281908</v>
+        <v>19.64511517367516</v>
       </c>
       <c r="AX19" t="n">
-        <v>20.43898581976026</v>
+        <v>21.20481775141207</v>
       </c>
       <c r="AY19" t="n">
-        <v>21.31595159153281</v>
+        <v>20.58237007196551</v>
       </c>
       <c r="AZ19" t="n">
-        <v>23.11778260556811</v>
+        <v>21.83563973877586</v>
       </c>
       <c r="BA19" t="n">
-        <v>21.57259025889997</v>
+        <v>21.57905015879392</v>
       </c>
       <c r="BB19" t="n">
-        <v>22.25756544963001</v>
+        <v>21.1582436403226</v>
       </c>
       <c r="BC19" t="n">
-        <v>21.45842281837311</v>
+        <v>22.46149408275616</v>
       </c>
       <c r="BD19" t="n">
-        <v>22.00249757858965</v>
+        <v>22.0296723550432</v>
       </c>
       <c r="BE19" t="n">
-        <v>21.76480664191445</v>
+        <v>22.25362864133598</v>
       </c>
       <c r="BF19" t="n">
-        <v>20.51061413226211</v>
+        <v>20.793082581728</v>
       </c>
       <c r="BG19" t="n">
-        <v>22.05085847050085</v>
+        <v>21.60612676047704</v>
       </c>
       <c r="BH19" t="n">
-        <v>20.26009175309241</v>
+        <v>20.68585609747016</v>
       </c>
       <c r="BI19" t="n">
-        <v>22.03775213864915</v>
+        <v>22.70130559447253</v>
       </c>
       <c r="BJ19" t="n">
-        <v>21.77433941212269</v>
+        <v>20.26160364455695</v>
       </c>
       <c r="BK19" t="n">
-        <v>20.68356862531927</v>
+        <v>23.20582573968496</v>
       </c>
       <c r="BL19" t="n">
-        <v>20.9612363285114</v>
+        <v>21.85687494161872</v>
       </c>
       <c r="BM19" t="n">
-        <v>20.81265863095068</v>
+        <v>20.96416193667005</v>
       </c>
       <c r="BN19" t="n">
-        <v>21.31618721098183</v>
+        <v>20.55418409537658</v>
       </c>
       <c r="BO19" t="n">
-        <v>21.17946902568842</v>
+        <v>20.21989900208055</v>
       </c>
       <c r="BP19" t="n">
-        <v>22.85798271059327</v>
+        <v>23.05192696956723</v>
       </c>
       <c r="BQ19" t="n">
-        <v>20.98409141506626</v>
+        <v>18.74714981850877</v>
       </c>
       <c r="BR19" t="n">
-        <v>21.35236461388332</v>
+        <v>20.43173070422588</v>
       </c>
       <c r="BS19" t="n">
-        <v>22.14426194708288</v>
+        <v>21.55642087421102</v>
       </c>
       <c r="BT19" t="n">
-        <v>22.5973188776387</v>
+        <v>21.46041576621273</v>
       </c>
       <c r="BU19" t="n">
-        <v>20.33965258704457</v>
+        <v>20.81882400653335</v>
       </c>
       <c r="BV19" t="n">
-        <v>21.48279961386956</v>
+        <v>22.55901108221899</v>
       </c>
       <c r="BW19" t="n">
-        <v>21.38256317326595</v>
+        <v>20.68109462110457</v>
       </c>
       <c r="BX19" t="n">
-        <v>21.18938467750131</v>
+        <v>21.5774989974212</v>
       </c>
       <c r="BY19" t="n">
-        <v>22.5714498256318</v>
+        <v>21.49699568567296</v>
       </c>
       <c r="BZ19" t="n">
-        <v>20.77177865654584</v>
+        <v>22.14402632763387</v>
       </c>
       <c r="CA19" t="n">
-        <v>22.85048215813283</v>
+        <v>19.40369359572383</v>
       </c>
       <c r="CB19" t="n">
-        <v>20.60900488718173</v>
+        <v>21.36522550880896</v>
       </c>
       <c r="CC19" t="n">
-        <v>23.11343346323829</v>
+        <v>21.85412604804682</v>
       </c>
       <c r="CD19" t="n">
-        <v>21.23203179777379</v>
+        <v>20.57309255616038</v>
       </c>
       <c r="CE19" t="n">
-        <v>21.2931554098402</v>
+        <v>20.14086831188867</v>
       </c>
       <c r="CF19" t="n">
-        <v>21.9030367186724</v>
+        <v>22.82600718786595</v>
       </c>
       <c r="CG19" t="n">
-        <v>21.40783335917327</v>
+        <v>20.76713498990476</v>
       </c>
       <c r="CH19" t="n">
-        <v>22.41738415840435</v>
+        <v>21.87721675405071</v>
       </c>
       <c r="CI19" t="n">
-        <v>23.06756621049588</v>
+        <v>20.97978154264462</v>
       </c>
       <c r="CJ19" t="n">
-        <v>19.66086240685128</v>
+        <v>20.93591705521887</v>
       </c>
       <c r="CK19" t="n">
-        <v>21.87841448624989</v>
+        <v>20.91540834567715</v>
       </c>
       <c r="CL19" t="n">
-        <v>22.45185332030045</v>
+        <v>22.04305357625208</v>
       </c>
       <c r="CM19" t="n">
-        <v>19.96791381883151</v>
+        <v>22.19355549931312</v>
       </c>
       <c r="CN19" t="n">
-        <v>21.80205414981357</v>
+        <v>20.97261478440361</v>
       </c>
       <c r="CO19" t="n">
-        <v>21.65612717105433</v>
+        <v>19.78886267253098</v>
       </c>
       <c r="CP19" t="n">
-        <v>20.45413418683679</v>
+        <v>20.15343468250303</v>
       </c>
       <c r="CQ19" t="n">
-        <v>18.96363500477224</v>
+        <v>20.27912784107775</v>
       </c>
       <c r="CR19" t="n">
-        <v>20.51572903780124</v>
+        <v>21.23660674207558</v>
       </c>
       <c r="CS19" t="n">
-        <v>22.9081991056655</v>
+        <v>21.70781618768292</v>
       </c>
       <c r="CT19" t="n">
-        <v>22.41779649244013</v>
+        <v>23.49595182124398</v>
       </c>
       <c r="CU19" t="n">
-        <v>21.53697245218989</v>
+        <v>21.89134410351482</v>
       </c>
       <c r="CV19" t="n">
-        <v>20.82834695926454</v>
+        <v>21.40309151776176</v>
       </c>
       <c r="CW19" t="n">
-        <v>21.30388591224762</v>
+        <v>20.36995913867467</v>
       </c>
       <c r="CX19" t="n">
-        <v>21.50134924586744</v>
+        <v>21.43295598840063</v>
       </c>
     </row>
     <row r="20">
@@ -6489,307 +6489,307 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>24.21707496244439</v>
+        <v>22.59633712993446</v>
       </c>
       <c r="C20" t="n">
-        <v>23.0313691726403</v>
+        <v>23.93791500274181</v>
       </c>
       <c r="D20" t="n">
-        <v>24.62159428650224</v>
+        <v>23.35460960426357</v>
       </c>
       <c r="E20" t="n">
-        <v>23.95495814288753</v>
+        <v>24.29973811914197</v>
       </c>
       <c r="F20" t="n">
-        <v>24.01999892829388</v>
+        <v>23.969399651617</v>
       </c>
       <c r="G20" t="n">
-        <v>25.93738164711903</v>
+        <v>22.82600718786596</v>
       </c>
       <c r="H20" t="n">
-        <v>23.89630853503583</v>
+        <v>22.5045240846333</v>
       </c>
       <c r="I20" t="n">
-        <v>25.7553263528435</v>
+        <v>23.15933016841183</v>
       </c>
       <c r="J20" t="n">
-        <v>23.36214942663218</v>
+        <v>23.99569085513674</v>
       </c>
       <c r="K20" t="n">
-        <v>24.74862262195474</v>
+        <v>24.38526797913595</v>
       </c>
       <c r="L20" t="n">
-        <v>25.4207271002821</v>
+        <v>22.21029429767053</v>
       </c>
       <c r="M20" t="n">
-        <v>23.36060808273651</v>
+        <v>24.59752183279411</v>
       </c>
       <c r="N20" t="n">
-        <v>23.28479752501457</v>
+        <v>23.98227036401968</v>
       </c>
       <c r="O20" t="n">
-        <v>22.82102972700542</v>
+        <v>24.24707717228617</v>
       </c>
       <c r="P20" t="n">
-        <v>25.7694046149224</v>
+        <v>25.0837912881846</v>
       </c>
       <c r="Q20" t="n">
-        <v>25.14149841824023</v>
+        <v>24.4165562784703</v>
       </c>
       <c r="R20" t="n">
-        <v>25.09031991041784</v>
+        <v>24.70181289141625</v>
       </c>
       <c r="S20" t="n">
-        <v>24.1915102522258</v>
+        <v>24.94846718463122</v>
       </c>
       <c r="T20" t="n">
-        <v>25.03734480429668</v>
+        <v>23.30734826978112</v>
       </c>
       <c r="U20" t="n">
-        <v>22.42923385319461</v>
+        <v>24.168900602597</v>
       </c>
       <c r="V20" t="n">
-        <v>23.76903476265727</v>
+        <v>25.39764621175527</v>
       </c>
       <c r="W20" t="n">
-        <v>23.66519530797909</v>
+        <v>24.26713427788393</v>
       </c>
       <c r="X20" t="n">
-        <v>24.42597123895403</v>
+        <v>25.57812089222695</v>
       </c>
       <c r="Y20" t="n">
-        <v>21.69895100591357</v>
+        <v>25.34655606122626</v>
       </c>
       <c r="Z20" t="n">
-        <v>22.51499933263761</v>
+        <v>24.89123129347363</v>
       </c>
       <c r="AA20" t="n">
-        <v>25.16874191703308</v>
+        <v>24.47942740145027</v>
       </c>
       <c r="AB20" t="n">
-        <v>23.1701195756815</v>
+        <v>23.82589758968724</v>
       </c>
       <c r="AC20" t="n">
-        <v>23.57857570803339</v>
+        <v>24.40933061536704</v>
       </c>
       <c r="AD20" t="n">
-        <v>21.20004645756943</v>
+        <v>24.5887351908411</v>
       </c>
       <c r="AE20" t="n">
-        <v>24.05291692881728</v>
+        <v>23.44037508370657</v>
       </c>
       <c r="AF20" t="n">
-        <v>23.87921630750489</v>
+        <v>25.45162270053475</v>
       </c>
       <c r="AG20" t="n">
-        <v>21.4639696929021</v>
+        <v>24.5351710360974</v>
       </c>
       <c r="AH20" t="n">
-        <v>23.80333702744366</v>
+        <v>24.48131235704242</v>
       </c>
       <c r="AI20" t="n">
-        <v>25.62260388070638</v>
+        <v>24.29450540387833</v>
       </c>
       <c r="AJ20" t="n">
-        <v>25.32478089714606</v>
+        <v>22.17601166783823</v>
       </c>
       <c r="AK20" t="n">
-        <v>22.89436628051266</v>
+        <v>24.43176355040908</v>
       </c>
       <c r="AL20" t="n">
-        <v>23.79241999297243</v>
+        <v>24.06028003659913</v>
       </c>
       <c r="AM20" t="n">
-        <v>24.37715874309887</v>
+        <v>23.97908950145792</v>
       </c>
       <c r="AN20" t="n">
-        <v>25.72090627833261</v>
+        <v>25.05881562658856</v>
       </c>
       <c r="AO20" t="n">
-        <v>22.8157773767877</v>
+        <v>24.24180518711437</v>
       </c>
       <c r="AP20" t="n">
-        <v>25.38799563182252</v>
+        <v>24.94804503311839</v>
       </c>
       <c r="AQ20" t="n">
-        <v>24.77611155767365</v>
+        <v>23.974946526146</v>
       </c>
       <c r="AR20" t="n">
-        <v>25.14326556410787</v>
+        <v>21.57785242659473</v>
       </c>
       <c r="AS20" t="n">
-        <v>23.02296541229195</v>
+        <v>24.73266922176073</v>
       </c>
       <c r="AT20" t="n">
-        <v>22.90030585412335</v>
+        <v>25.03436029127577</v>
       </c>
       <c r="AU20" t="n">
-        <v>23.93793463769589</v>
+        <v>25.15579266481406</v>
       </c>
       <c r="AV20" t="n">
-        <v>25.4879277306378</v>
+        <v>25.74509654176525</v>
       </c>
       <c r="AW20" t="n">
-        <v>24.85749844235571</v>
+        <v>22.1849063020387</v>
       </c>
       <c r="AX20" t="n">
-        <v>22.92678358970689</v>
+        <v>23.61805178322115</v>
       </c>
       <c r="AY20" t="n">
-        <v>23.84728005468574</v>
+        <v>22.98461834696407</v>
       </c>
       <c r="AZ20" t="n">
-        <v>25.64415324281459</v>
+        <v>24.43402157012885</v>
       </c>
       <c r="BA20" t="n">
-        <v>24.03802381614386</v>
+        <v>24.27851273377616</v>
       </c>
       <c r="BB20" t="n">
-        <v>24.96688477156289</v>
+        <v>23.57357861221877</v>
       </c>
       <c r="BC20" t="n">
-        <v>24.03564798669958</v>
+        <v>25.13947601796948</v>
       </c>
       <c r="BD20" t="n">
-        <v>24.59573505197238</v>
+        <v>24.57924169054104</v>
       </c>
       <c r="BE20" t="n">
-        <v>24.48617200817844</v>
+        <v>24.98180733666744</v>
       </c>
       <c r="BF20" t="n">
-        <v>22.9006396483428</v>
+        <v>23.21183403563495</v>
       </c>
       <c r="BG20" t="n">
-        <v>24.68086239540762</v>
+        <v>24.13981141812016</v>
       </c>
       <c r="BH20" t="n">
-        <v>22.83395934427035</v>
+        <v>23.14018608817902</v>
       </c>
       <c r="BI20" t="n">
-        <v>24.75412040909852</v>
+        <v>25.3740744493763</v>
       </c>
       <c r="BJ20" t="n">
-        <v>24.31908836639267</v>
+        <v>22.72774406014789</v>
       </c>
       <c r="BK20" t="n">
-        <v>23.2272867444998</v>
+        <v>25.9649982100395</v>
       </c>
       <c r="BL20" t="n">
-        <v>23.35351004683481</v>
+        <v>24.50145781993356</v>
       </c>
       <c r="BM20" t="n">
-        <v>23.27011057935905</v>
+        <v>23.53875602114914</v>
       </c>
       <c r="BN20" t="n">
-        <v>23.77470926438782</v>
+        <v>22.99556483386642</v>
       </c>
       <c r="BO20" t="n">
-        <v>23.71387035915564</v>
+        <v>22.6085991587605</v>
       </c>
       <c r="BP20" t="n">
-        <v>25.53782014896762</v>
+        <v>25.74988747056198</v>
       </c>
       <c r="BQ20" t="n">
-        <v>23.48433774590274</v>
+        <v>21.05846862114</v>
       </c>
       <c r="BR20" t="n">
-        <v>23.78279886547082</v>
+        <v>22.9361003754202</v>
       </c>
       <c r="BS20" t="n">
-        <v>24.8423304403251</v>
+        <v>24.18674877586021</v>
       </c>
       <c r="BT20" t="n">
-        <v>25.22053892590914</v>
+        <v>23.88016860277801</v>
       </c>
       <c r="BU20" t="n">
-        <v>22.78995741216601</v>
+        <v>23.42305705420366</v>
       </c>
       <c r="BV20" t="n">
-        <v>24.00057014122684</v>
+        <v>25.2715505366218</v>
       </c>
       <c r="BW20" t="n">
-        <v>23.89240117917292</v>
+        <v>23.15772010217687</v>
       </c>
       <c r="BX20" t="n">
-        <v>23.76828863440204</v>
+        <v>24.16463981756057</v>
       </c>
       <c r="BY20" t="n">
-        <v>25.27966959013592</v>
+        <v>24.00354483677071</v>
       </c>
       <c r="BZ20" t="n">
-        <v>23.2513984681161</v>
+        <v>25.0511972644036</v>
       </c>
       <c r="CA20" t="n">
-        <v>25.4498751896212</v>
+        <v>21.68591339640118</v>
       </c>
       <c r="CB20" t="n">
-        <v>23.0535370358022</v>
+        <v>24.0204407147608</v>
       </c>
       <c r="CC20" t="n">
-        <v>25.83779316000024</v>
+        <v>24.51132438436124</v>
       </c>
       <c r="CD20" t="n">
-        <v>23.75892276130353</v>
+        <v>23.13104601705248</v>
       </c>
       <c r="CE20" t="n">
-        <v>23.70827439724144</v>
+        <v>22.58100223079412</v>
       </c>
       <c r="CF20" t="n">
-        <v>24.41602613471</v>
+        <v>25.51691874034421</v>
       </c>
       <c r="CG20" t="n">
-        <v>24.04332525374679</v>
+        <v>23.31542805338708</v>
       </c>
       <c r="CH20" t="n">
-        <v>24.97030125357367</v>
+        <v>24.39956222570979</v>
       </c>
       <c r="CI20" t="n">
-        <v>25.69512558361909</v>
+        <v>23.52319532003683</v>
       </c>
       <c r="CJ20" t="n">
-        <v>21.97195540751053</v>
+        <v>23.36443689878308</v>
       </c>
       <c r="CK20" t="n">
-        <v>24.53310936591848</v>
+        <v>23.48392541186696</v>
       </c>
       <c r="CL20" t="n">
-        <v>25.07526971811174</v>
+        <v>24.71937635784523</v>
       </c>
       <c r="CM20" t="n">
-        <v>22.18272682213527</v>
+        <v>24.84959537333653</v>
       </c>
       <c r="CN20" t="n">
-        <v>24.51048989881263</v>
+        <v>23.55017374694953</v>
       </c>
       <c r="CO20" t="n">
-        <v>24.25995770216589</v>
+        <v>22.15336274830125</v>
       </c>
       <c r="CP20" t="n">
-        <v>22.94655598847042</v>
+        <v>22.60060773244793</v>
       </c>
       <c r="CQ20" t="n">
-        <v>21.33870850331725</v>
+        <v>22.61156403682732</v>
       </c>
       <c r="CR20" t="n">
-        <v>23.07684372630101</v>
+        <v>23.82142082015588</v>
       </c>
       <c r="CS20" t="n">
-        <v>25.68229414112458</v>
+        <v>24.31649655245346</v>
       </c>
       <c r="CT20" t="n">
-        <v>25.09799717746505</v>
+        <v>26.23051187665304</v>
       </c>
       <c r="CU20" t="n">
-        <v>24.0356774391307</v>
+        <v>24.56266978929335</v>
       </c>
       <c r="CV20" t="n">
-        <v>23.41403479280163</v>
+        <v>23.89417814251761</v>
       </c>
       <c r="CW20" t="n">
-        <v>23.7040823345443</v>
+        <v>22.88732714947321</v>
       </c>
       <c r="CX20" t="n">
-        <v>24.04526184926819</v>
+        <v>23.99387256021369</v>
       </c>
     </row>
     <row r="21">
@@ -6797,307 +6797,307 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.26448337719287</v>
+        <v>17.08945900241099</v>
       </c>
       <c r="C21" t="n">
-        <v>17.35305826100126</v>
+        <v>17.91807369974939</v>
       </c>
       <c r="D21" t="n">
-        <v>18.76573430255017</v>
+        <v>17.57716180944968</v>
       </c>
       <c r="E21" t="n">
-        <v>17.83546944791406</v>
+        <v>18.38550341669538</v>
       </c>
       <c r="F21" t="n">
-        <v>18.05291674692769</v>
+        <v>18.12239503195723</v>
       </c>
       <c r="G21" t="n">
-        <v>19.39398411092883</v>
+        <v>17.13057459626485</v>
       </c>
       <c r="H21" t="n">
-        <v>17.95325953746959</v>
+        <v>16.99014540464939</v>
       </c>
       <c r="I21" t="n">
-        <v>19.17890282388244</v>
+        <v>17.33369819627351</v>
       </c>
       <c r="J21" t="n">
-        <v>17.52275335168032</v>
+        <v>18.28030915018533</v>
       </c>
       <c r="K21" t="n">
-        <v>18.5272874201427</v>
+        <v>18.40629683307133</v>
       </c>
       <c r="L21" t="n">
-        <v>18.99237076007554</v>
+        <v>16.86364721295718</v>
       </c>
       <c r="M21" t="n">
-        <v>17.68380906256201</v>
+        <v>18.71313226055662</v>
       </c>
       <c r="N21" t="n">
-        <v>17.58340572484869</v>
+        <v>18.15564682670007</v>
       </c>
       <c r="O21" t="n">
-        <v>17.36002866970142</v>
+        <v>18.32788464393314</v>
       </c>
       <c r="P21" t="n">
-        <v>19.22422029791047</v>
+        <v>19.20290655525127</v>
       </c>
       <c r="Q21" t="n">
-        <v>19.12657567124608</v>
+        <v>18.4367604643341</v>
       </c>
       <c r="R21" t="n">
-        <v>18.71540009775343</v>
+        <v>18.89300807492872</v>
       </c>
       <c r="S21" t="n">
-        <v>18.16369715787489</v>
+        <v>18.55485489567795</v>
       </c>
       <c r="T21" t="n">
-        <v>18.61507529985645</v>
+        <v>17.48345399107933</v>
       </c>
       <c r="U21" t="n">
-        <v>16.96579806158407</v>
+        <v>18.15421347505188</v>
       </c>
       <c r="V21" t="n">
-        <v>18.05249459541486</v>
+        <v>19.09021173628078</v>
       </c>
       <c r="W21" t="n">
-        <v>17.84260675372393</v>
+        <v>18.18097591746964</v>
       </c>
       <c r="X21" t="n">
-        <v>18.42591215220218</v>
+        <v>19.14692730115512</v>
       </c>
       <c r="Y21" t="n">
-        <v>16.40151893361412</v>
+        <v>18.6877442649248</v>
       </c>
       <c r="Z21" t="n">
-        <v>16.84140080997895</v>
+        <v>18.56487853973831</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.93258232488692</v>
+        <v>18.19365028033146</v>
       </c>
       <c r="AB21" t="n">
-        <v>17.68465336558766</v>
+        <v>17.99580848297165</v>
       </c>
       <c r="AC21" t="n">
-        <v>17.94712361431805</v>
+        <v>18.45763242052639</v>
       </c>
       <c r="AD21" t="n">
-        <v>15.9834122213295</v>
+        <v>18.63715480572496</v>
       </c>
       <c r="AE21" t="n">
-        <v>18.29151089149079</v>
+        <v>17.55699671160445</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.21347176648021</v>
+        <v>18.98593049513568</v>
       </c>
       <c r="AG21" t="n">
-        <v>16.08900900439828</v>
+        <v>18.61628284953267</v>
       </c>
       <c r="AH21" t="n">
-        <v>17.72903817929667</v>
+        <v>18.382872332848</v>
       </c>
       <c r="AI21" t="n">
-        <v>19.16349920240281</v>
+        <v>18.16354007824222</v>
       </c>
       <c r="AJ21" t="n">
-        <v>18.92752632421004</v>
+        <v>16.77067570536501</v>
       </c>
       <c r="AK21" t="n">
-        <v>17.35956724828042</v>
+        <v>18.36015469097173</v>
       </c>
       <c r="AL21" t="n">
-        <v>17.95990596942735</v>
+        <v>18.07410286238533</v>
       </c>
       <c r="AM21" t="n">
-        <v>18.47332074884025</v>
+        <v>17.82644718651203</v>
       </c>
       <c r="AN21" t="n">
-        <v>19.33313538821961</v>
+        <v>18.55352953627722</v>
       </c>
       <c r="AO21" t="n">
-        <v>17.09150103763583</v>
+        <v>18.29349402185337</v>
       </c>
       <c r="AP21" t="n">
-        <v>18.94612062572848</v>
+        <v>18.96052286454978</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18.66182612553268</v>
+        <v>18.16887096827628</v>
       </c>
       <c r="AR21" t="n">
-        <v>19.01710098474552</v>
+        <v>16.41999542540805</v>
       </c>
       <c r="AS21" t="n">
-        <v>17.25126084154791</v>
+        <v>18.7338176846851</v>
       </c>
       <c r="AT21" t="n">
-        <v>17.21053794677575</v>
+        <v>18.80701679351375</v>
       </c>
       <c r="AU21" t="n">
-        <v>17.93694289062501</v>
+        <v>18.87526789391299</v>
       </c>
       <c r="AV21" t="n">
-        <v>19.00368049362847</v>
+        <v>19.46904854039554</v>
       </c>
       <c r="AW21" t="n">
-        <v>18.37964238290103</v>
+        <v>16.71448046677392</v>
       </c>
       <c r="AX21" t="n">
-        <v>17.23584740259124</v>
+        <v>17.72361893196922</v>
       </c>
       <c r="AY21" t="n">
-        <v>17.92318860528851</v>
+        <v>17.32123981790662</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19.07193159402771</v>
+        <v>18.25102361616765</v>
       </c>
       <c r="BA21" t="n">
-        <v>18.31561279763005</v>
+        <v>18.26503315590725</v>
       </c>
       <c r="BB21" t="n">
-        <v>18.68867692524384</v>
+        <v>17.75307136309662</v>
       </c>
       <c r="BC21" t="n">
-        <v>17.99602446746658</v>
+        <v>18.78334685636436</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.59661844301661</v>
+        <v>18.57699330640872</v>
       </c>
       <c r="BE21" t="n">
-        <v>18.34145239720582</v>
+        <v>18.79235930028934</v>
       </c>
       <c r="BF21" t="n">
-        <v>17.20309629917756</v>
+        <v>17.50869472455551</v>
       </c>
       <c r="BG21" t="n">
-        <v>18.51650783035007</v>
+        <v>18.23336197496825</v>
       </c>
       <c r="BH21" t="n">
-        <v>17.32153434221789</v>
+        <v>17.58339590737165</v>
       </c>
       <c r="BI21" t="n">
-        <v>18.87407997919085</v>
+        <v>18.77570885922531</v>
       </c>
       <c r="BJ21" t="n">
-        <v>18.5159580516357</v>
+        <v>17.24842359068264</v>
       </c>
       <c r="BK21" t="n">
-        <v>17.47921284099698</v>
+        <v>19.57694261309226</v>
       </c>
       <c r="BL21" t="n">
-        <v>17.45439425903362</v>
+        <v>18.28742682104112</v>
       </c>
       <c r="BM21" t="n">
-        <v>17.90784388867113</v>
+        <v>17.85984624341051</v>
       </c>
       <c r="BN21" t="n">
-        <v>17.93686435080867</v>
+        <v>17.30414759037568</v>
       </c>
       <c r="BO21" t="n">
-        <v>17.82615266220076</v>
+        <v>17.31038168829765</v>
       </c>
       <c r="BP21" t="n">
-        <v>18.9249050578397</v>
+        <v>19.30109114315299</v>
       </c>
       <c r="BQ21" t="n">
-        <v>17.64223204728716</v>
+        <v>15.97222029750108</v>
       </c>
       <c r="BR21" t="n">
-        <v>17.91601202957047</v>
+        <v>17.19576264382684</v>
       </c>
       <c r="BS21" t="n">
-        <v>18.69986884907225</v>
+        <v>18.21257837606935</v>
       </c>
       <c r="BT21" t="n">
-        <v>19.0577355222243</v>
+        <v>18.11213576844785</v>
       </c>
       <c r="BU21" t="n">
-        <v>17.25762256667143</v>
+        <v>17.48057747030588</v>
       </c>
       <c r="BV21" t="n">
-        <v>18.19262926271905</v>
+        <v>18.93493851937711</v>
       </c>
       <c r="BW21" t="n">
-        <v>18.17680348972659</v>
+        <v>17.2693348167831</v>
       </c>
       <c r="BX21" t="n">
-        <v>18.17133515501394</v>
+        <v>18.355825183596</v>
       </c>
       <c r="BY21" t="n">
-        <v>18.99683771212987</v>
+        <v>17.97968818566792</v>
       </c>
       <c r="BZ21" t="n">
-        <v>17.45058507794114</v>
+        <v>18.81786510564567</v>
       </c>
       <c r="CA21" t="n">
-        <v>19.25769789462529</v>
+        <v>16.31117850986934</v>
       </c>
       <c r="CB21" t="n">
-        <v>17.28714372013813</v>
+        <v>18.18923241566236</v>
       </c>
       <c r="CC21" t="n">
-        <v>19.33902587444509</v>
+        <v>18.51775464993447</v>
       </c>
       <c r="CD21" t="n">
-        <v>17.89932231859827</v>
+        <v>17.25556089649251</v>
       </c>
       <c r="CE21" t="n">
-        <v>17.77675111772306</v>
+        <v>17.01170458423465</v>
       </c>
       <c r="CF21" t="n">
-        <v>18.23418664303982</v>
+        <v>19.20533147208076</v>
       </c>
       <c r="CG21" t="n">
-        <v>18.25484261473717</v>
+        <v>17.81177005833354</v>
       </c>
       <c r="CH21" t="n">
-        <v>18.65200864849022</v>
+        <v>18.44250368840395</v>
       </c>
       <c r="CI21" t="n">
-        <v>19.09457069608763</v>
+        <v>18.04380612823228</v>
       </c>
       <c r="CJ21" t="n">
-        <v>16.7288532531641</v>
+        <v>17.81705186098239</v>
       </c>
       <c r="CK21" t="n">
-        <v>18.69156326349432</v>
+        <v>17.77023231296686</v>
       </c>
       <c r="CL21" t="n">
-        <v>18.88264081917188</v>
+        <v>18.43901848405387</v>
       </c>
       <c r="CM21" t="n">
-        <v>16.90701100905377</v>
+        <v>18.79872102541286</v>
       </c>
       <c r="CN21" t="n">
-        <v>18.46083291804224</v>
+        <v>17.70338511178469</v>
       </c>
       <c r="CO21" t="n">
-        <v>18.40887882953349</v>
+        <v>16.76191851584313</v>
       </c>
       <c r="CP21" t="n">
-        <v>17.40134061309612</v>
+        <v>17.06742858392769</v>
       </c>
       <c r="CQ21" t="n">
-        <v>16.27428443114374</v>
+        <v>17.25385265548712</v>
       </c>
       <c r="CR21" t="n">
-        <v>17.37733688172728</v>
+        <v>17.82133228097291</v>
       </c>
       <c r="CS21" t="n">
-        <v>19.48139892651497</v>
+        <v>18.18235036425559</v>
       </c>
       <c r="CT21" t="n">
-        <v>18.81168991258596</v>
+        <v>19.83178468216065</v>
       </c>
       <c r="CU21" t="n">
-        <v>18.19759690610254</v>
+        <v>18.24872632653971</v>
       </c>
       <c r="CV21" t="n">
-        <v>17.82962804907379</v>
+        <v>17.97309084109538</v>
       </c>
       <c r="CW21" t="n">
-        <v>18.05225897596584</v>
+        <v>17.3178135184188</v>
       </c>
       <c r="CX21" t="n">
-        <v>18.1142096122983</v>
+        <v>18.07269739237193</v>
       </c>
     </row>
   </sheetData>

--- a/output/100_model_iteration.xlsx
+++ b/output/100_model_iteration.xlsx
@@ -1253,307 +1253,307 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.95215824692253</v>
+        <v>18.53895489664365</v>
       </c>
       <c r="C3" t="n">
-        <v>11.94214442033921</v>
+        <v>18.61118207524509</v>
       </c>
       <c r="D3" t="n">
-        <v>11.93495802714413</v>
+        <v>18.51058238799092</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9468568093196</v>
+        <v>18.42654478450739</v>
       </c>
       <c r="F3" t="n">
-        <v>11.94798581917948</v>
+        <v>18.60576282791765</v>
       </c>
       <c r="G3" t="n">
-        <v>11.95009657674361</v>
+        <v>18.50466244933431</v>
       </c>
       <c r="H3" t="n">
-        <v>11.96630523134073</v>
+        <v>18.55704850683292</v>
       </c>
       <c r="I3" t="n">
-        <v>11.89518742764509</v>
+        <v>18.48044273347054</v>
       </c>
       <c r="J3" t="n">
-        <v>11.97876360970762</v>
+        <v>18.60497742975425</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95956062461255</v>
+        <v>18.61037704212761</v>
       </c>
       <c r="L3" t="n">
-        <v>12.0405057228277</v>
+        <v>18.45237456660612</v>
       </c>
       <c r="M3" t="n">
-        <v>12.07004651124849</v>
+        <v>18.47888175462079</v>
       </c>
       <c r="N3" t="n">
-        <v>11.97858689512086</v>
+        <v>18.54528716933605</v>
       </c>
       <c r="O3" t="n">
-        <v>11.89198693012925</v>
+        <v>18.56845641515627</v>
       </c>
       <c r="P3" t="n">
-        <v>12.0460525973567</v>
+        <v>18.52523006373828</v>
       </c>
       <c r="Q3" t="n">
-        <v>11.93122738586799</v>
+        <v>18.56116202971371</v>
       </c>
       <c r="R3" t="n">
-        <v>11.95626195232628</v>
+        <v>18.57422909165724</v>
       </c>
       <c r="S3" t="n">
-        <v>12.07437601862422</v>
+        <v>18.55779463508815</v>
       </c>
       <c r="T3" t="n">
-        <v>11.99128089293677</v>
+        <v>18.55124637790082</v>
       </c>
       <c r="U3" t="n">
-        <v>12.02539662565935</v>
+        <v>18.53827749072772</v>
       </c>
       <c r="V3" t="n">
-        <v>12.03568534159985</v>
+        <v>18.57227541372579</v>
       </c>
       <c r="W3" t="n">
-        <v>11.93604776709584</v>
+        <v>18.44992019734551</v>
       </c>
       <c r="X3" t="n">
-        <v>12.03866985462076</v>
+        <v>18.54720157735932</v>
       </c>
       <c r="Y3" t="n">
-        <v>12.00575185409737</v>
+        <v>18.51178993766715</v>
       </c>
       <c r="Z3" t="n">
-        <v>11.912505457148</v>
+        <v>18.66630720883855</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.02817497166236</v>
+        <v>18.5594930586165</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.94934063101134</v>
+        <v>18.58147438971458</v>
       </c>
       <c r="AC3" t="n">
-        <v>12.0521787030312</v>
+        <v>18.47422827050266</v>
       </c>
       <c r="AD3" t="n">
-        <v>12.01819059751017</v>
+        <v>18.44068195144855</v>
       </c>
       <c r="AE3" t="n">
-        <v>11.90046923029394</v>
+        <v>18.53689322646473</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.01349784348387</v>
+        <v>18.42646624469105</v>
       </c>
       <c r="AG3" t="n">
-        <v>12.03552826196717</v>
+        <v>18.50051947402239</v>
       </c>
       <c r="AH3" t="n">
-        <v>11.98395705506308</v>
+        <v>18.42835120028321</v>
       </c>
       <c r="AI3" t="n">
-        <v>11.90929514215512</v>
+        <v>18.48748186450999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>11.91562741484751</v>
+        <v>18.41279049917089</v>
       </c>
       <c r="AK3" t="n">
-        <v>11.98037367594259</v>
+        <v>18.3936955063233</v>
       </c>
       <c r="AL3" t="n">
-        <v>12.04941017450522</v>
+        <v>18.40425911162099</v>
       </c>
       <c r="AM3" t="n">
-        <v>11.95611469017065</v>
+        <v>18.4674640288204</v>
       </c>
       <c r="AN3" t="n">
-        <v>11.96423374368477</v>
+        <v>18.54094784448327</v>
       </c>
       <c r="AO3" t="n">
-        <v>11.94174190378047</v>
+        <v>18.49610160935328</v>
       </c>
       <c r="AP3" t="n">
-        <v>12.0450119447902</v>
+        <v>18.55735284862124</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11.97975517488891</v>
+        <v>18.48275965805257</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.91663861498288</v>
+        <v>18.43759926365721</v>
       </c>
       <c r="AS3" t="n">
-        <v>11.91624591590118</v>
+        <v>18.42967655968394</v>
       </c>
       <c r="AT3" t="n">
-        <v>11.99040713747999</v>
+        <v>18.54655362387452</v>
       </c>
       <c r="AU3" t="n">
-        <v>11.92381519070093</v>
+        <v>18.65965095940376</v>
       </c>
       <c r="AV3" t="n">
-        <v>12.07037048799089</v>
+        <v>18.43971983869838</v>
       </c>
       <c r="AW3" t="n">
-        <v>11.9005772225414</v>
+        <v>18.4603659929187</v>
       </c>
       <c r="AX3" t="n">
-        <v>11.94348941469403</v>
+        <v>18.4157750121918</v>
       </c>
       <c r="AY3" t="n">
-        <v>12.02587768203442</v>
+        <v>18.39992960424526</v>
       </c>
       <c r="AZ3" t="n">
-        <v>11.9558496182905</v>
+        <v>18.39110369238409</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.01935887727823</v>
+        <v>18.48269093571326</v>
       </c>
       <c r="BB3" t="n">
-        <v>11.93440824842975</v>
+        <v>18.63248600042725</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.03128711188482</v>
+        <v>18.55760810302434</v>
       </c>
       <c r="BD3" t="n">
-        <v>11.91986856492985</v>
+        <v>18.4969851822871</v>
       </c>
       <c r="BE3" t="n">
-        <v>12.03254374894626</v>
+        <v>18.49954754379518</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.94436317015081</v>
+        <v>18.51233971638152</v>
       </c>
       <c r="BG3" t="n">
-        <v>11.91695277424824</v>
+        <v>18.53324112500493</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.98920940528081</v>
+        <v>18.43011834615085</v>
       </c>
       <c r="BI3" t="n">
-        <v>12.0902999663871</v>
+        <v>18.45363120366756</v>
       </c>
       <c r="BJ3" t="n">
-        <v>11.91967221538901</v>
+        <v>18.4154510354494</v>
       </c>
       <c r="BK3" t="n">
-        <v>11.99372544472034</v>
+        <v>18.42799777110968</v>
       </c>
       <c r="BL3" t="n">
-        <v>11.89253670884362</v>
+        <v>18.43269052513597</v>
       </c>
       <c r="BM3" t="n">
-        <v>11.8777123185095</v>
+        <v>18.49697536481006</v>
       </c>
       <c r="BN3" t="n">
-        <v>11.94145719694624</v>
+        <v>18.60515414434101</v>
       </c>
       <c r="BO3" t="n">
-        <v>11.89653242199991</v>
+        <v>18.50734262056691</v>
       </c>
       <c r="BP3" t="n">
-        <v>12.0648236134619</v>
+        <v>18.53039405666262</v>
       </c>
       <c r="BQ3" t="n">
-        <v>11.92325559450951</v>
+        <v>18.5953955721608</v>
       </c>
       <c r="BR3" t="n">
-        <v>11.94622849078888</v>
+        <v>18.43483073513124</v>
       </c>
       <c r="BS3" t="n">
-        <v>11.98488971538212</v>
+        <v>18.42207783245307</v>
       </c>
       <c r="BT3" t="n">
-        <v>12.04066280246038</v>
+        <v>18.59537593720672</v>
       </c>
       <c r="BU3" t="n">
-        <v>11.95060708554982</v>
+        <v>18.60994507313774</v>
       </c>
       <c r="BV3" t="n">
-        <v>12.03421272004348</v>
+        <v>18.51499043518299</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.93938570929028</v>
+        <v>18.44977293518987</v>
       </c>
       <c r="BX3" t="n">
-        <v>12.00692995134246</v>
+        <v>18.56459814667858</v>
       </c>
       <c r="BY3" t="n">
-        <v>11.91938750855477</v>
+        <v>18.59145876386677</v>
       </c>
       <c r="BZ3" t="n">
-        <v>11.96767967812668</v>
+        <v>18.62990400396508</v>
       </c>
       <c r="CA3" t="n">
-        <v>11.95911883814564</v>
+        <v>18.5362845428881</v>
       </c>
       <c r="CB3" t="n">
-        <v>11.98399632497125</v>
+        <v>18.45622301760677</v>
       </c>
       <c r="CC3" t="n">
-        <v>11.94283164373219</v>
+        <v>18.425297964923</v>
       </c>
       <c r="CD3" t="n">
-        <v>11.94215423781626</v>
+        <v>18.68203480706059</v>
       </c>
       <c r="CE3" t="n">
-        <v>11.99788805498635</v>
+        <v>18.54681869575467</v>
       </c>
       <c r="CF3" t="n">
-        <v>11.95190299251943</v>
+        <v>18.5536222073451</v>
       </c>
       <c r="CG3" t="n">
-        <v>12.03715796315622</v>
+        <v>18.48522384479022</v>
       </c>
       <c r="CH3" t="n">
-        <v>12.06504941543387</v>
+        <v>18.45661571668847</v>
       </c>
       <c r="CI3" t="n">
-        <v>11.90232473345496</v>
+        <v>18.57796955041042</v>
       </c>
       <c r="CJ3" t="n">
-        <v>12.03272046353302</v>
+        <v>18.5146468234865</v>
       </c>
       <c r="CK3" t="n">
-        <v>12.01326222403485</v>
+        <v>18.45445587173913</v>
       </c>
       <c r="CL3" t="n">
-        <v>12.03226885958907</v>
+        <v>18.41652114044703</v>
       </c>
       <c r="CM3" t="n">
-        <v>11.93949370153775</v>
+        <v>18.45206040734077</v>
       </c>
       <c r="CN3" t="n">
-        <v>12.00747973005684</v>
+        <v>18.46572633538388</v>
       </c>
       <c r="CO3" t="n">
-        <v>11.92829196023229</v>
+        <v>18.49008349592625</v>
       </c>
       <c r="CP3" t="n">
-        <v>11.98191501983825</v>
+        <v>18.53074748583615</v>
       </c>
       <c r="CQ3" t="n">
-        <v>11.99023042289322</v>
+        <v>18.58626531851131</v>
       </c>
       <c r="CR3" t="n">
-        <v>11.88610626138081</v>
+        <v>18.62407242260185</v>
       </c>
       <c r="CS3" t="n">
-        <v>11.97689828906955</v>
+        <v>18.52447411800601</v>
       </c>
       <c r="CT3" t="n">
-        <v>12.02447378281735</v>
+        <v>18.52589765217717</v>
       </c>
       <c r="CU3" t="n">
-        <v>11.95124522155758</v>
+        <v>18.47508239100535</v>
       </c>
       <c r="CV3" t="n">
-        <v>11.96863197339979</v>
+        <v>18.57943235448975</v>
       </c>
       <c r="CW3" t="n">
-        <v>11.99917414447891</v>
+        <v>18.67929573096573</v>
       </c>
       <c r="CX3" t="n">
-        <v>11.97467178345109</v>
+        <v>18.51384159401948</v>
       </c>
     </row>
     <row r="4">
@@ -1561,307 +1561,307 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.76671981372923</v>
+        <v>11.4239624241901</v>
       </c>
       <c r="C4" t="n">
-        <v>12.72692088072515</v>
+        <v>11.62834298476581</v>
       </c>
       <c r="D4" t="n">
-        <v>12.75074593141273</v>
+        <v>11.36651991344913</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94033786702187</v>
+        <v>11.24812895913845</v>
       </c>
       <c r="F4" t="n">
-        <v>12.7826581352313</v>
+        <v>11.5046955168066</v>
       </c>
       <c r="G4" t="n">
-        <v>12.87094440123942</v>
+        <v>11.40532258704844</v>
       </c>
       <c r="H4" t="n">
-        <v>12.80585646984717</v>
+        <v>11.40568969187769</v>
       </c>
       <c r="I4" t="n">
-        <v>12.64563442955815</v>
+        <v>11.48498816772756</v>
       </c>
       <c r="J4" t="n">
-        <v>13.00094559977275</v>
+        <v>11.56682104134367</v>
       </c>
       <c r="K4" t="n">
-        <v>12.84979704060568</v>
+        <v>11.56984118204594</v>
       </c>
       <c r="L4" t="n">
-        <v>12.99915047386048</v>
+        <v>11.23565307586586</v>
       </c>
       <c r="M4" t="n">
-        <v>13.08440278358064</v>
+        <v>11.56731858689695</v>
       </c>
       <c r="N4" t="n">
-        <v>12.95579521558859</v>
+        <v>11.50943891767599</v>
       </c>
       <c r="O4" t="n">
-        <v>12.64575574272383</v>
+        <v>11.53853208658223</v>
       </c>
       <c r="P4" t="n">
-        <v>12.93136457934971</v>
+        <v>11.3905530096766</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.83229397253982</v>
+        <v>11.52115026091552</v>
       </c>
       <c r="R4" t="n">
-        <v>12.92874297441759</v>
+        <v>11.53684940020794</v>
       </c>
       <c r="S4" t="n">
-        <v>12.97984194993154</v>
+        <v>11.52773024500039</v>
       </c>
       <c r="T4" t="n">
-        <v>12.8485843427412</v>
+        <v>11.61901757009291</v>
       </c>
       <c r="U4" t="n">
-        <v>13.04025305580944</v>
+        <v>11.50884478851056</v>
       </c>
       <c r="V4" t="n">
-        <v>13.01438262475906</v>
+        <v>11.68149160855807</v>
       </c>
       <c r="W4" t="n">
-        <v>12.77008517045165</v>
+        <v>11.34194856259294</v>
       </c>
       <c r="X4" t="n">
-        <v>13.00286347726316</v>
+        <v>11.38892809343978</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.96198988564572</v>
+        <v>11.44186823302808</v>
       </c>
       <c r="Z4" t="n">
-        <v>12.77663952929299</v>
+        <v>11.79489860085354</v>
       </c>
       <c r="AA4" t="n">
-        <v>12.94180037205457</v>
+        <v>11.48068374780642</v>
       </c>
       <c r="AB4" t="n">
-        <v>12.83416895773837</v>
+        <v>11.49619033652265</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.97078490580607</v>
+        <v>11.31876285354523</v>
       </c>
       <c r="AD4" t="n">
-        <v>12.94601312097167</v>
+        <v>11.2281702634291</v>
       </c>
       <c r="AE4" t="n">
-        <v>12.71062034688588</v>
+        <v>11.4084031164433</v>
       </c>
       <c r="AF4" t="n">
-        <v>13.00546305448308</v>
+        <v>11.35990098851286</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.00139427353413</v>
+        <v>11.45279289130703</v>
       </c>
       <c r="AH4" t="n">
-        <v>12.85673101590583</v>
+        <v>11.23951780714838</v>
       </c>
       <c r="AI4" t="n">
-        <v>12.79822185539429</v>
+        <v>11.36702641655471</v>
       </c>
       <c r="AJ4" t="n">
-        <v>12.83341058458251</v>
+        <v>11.29062832625537</v>
       </c>
       <c r="AK4" t="n">
-        <v>12.9467808229745</v>
+        <v>11.21206219386012</v>
       </c>
       <c r="AL4" t="n">
-        <v>12.96109806616564</v>
+        <v>11.21269316276663</v>
       </c>
       <c r="AM4" t="n">
-        <v>12.77985127835849</v>
+        <v>11.47456097685492</v>
       </c>
       <c r="AN4" t="n">
-        <v>12.91322265935671</v>
+        <v>11.39558856869337</v>
       </c>
       <c r="AO4" t="n">
-        <v>12.79483862660397</v>
+        <v>11.41038437956357</v>
       </c>
       <c r="AP4" t="n">
-        <v>13.04267626580504</v>
+        <v>11.45236177216054</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.80992586753182</v>
+        <v>11.35757538233304</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.75383882731462</v>
+        <v>11.25902868293706</v>
       </c>
       <c r="AS4" t="n">
-        <v>12.72766586296559</v>
+        <v>11.18909434659647</v>
       </c>
       <c r="AT4" t="n">
-        <v>12.88790429076242</v>
+        <v>11.5913943602924</v>
       </c>
       <c r="AU4" t="n">
-        <v>12.84701847255318</v>
+        <v>11.81725747908258</v>
       </c>
       <c r="AV4" t="n">
-        <v>13.03394059961619</v>
+        <v>11.32385204669757</v>
       </c>
       <c r="AW4" t="n">
-        <v>12.79618935860917</v>
+        <v>11.34056703977041</v>
       </c>
       <c r="AX4" t="n">
-        <v>12.77921711174741</v>
+        <v>11.27155094432428</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.97170690748779</v>
+        <v>11.31618212546037</v>
       </c>
       <c r="AZ4" t="n">
-        <v>12.81714816302593</v>
+        <v>11.14497131454718</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.94659108011701</v>
+        <v>11.3892760622202</v>
       </c>
       <c r="BB4" t="n">
-        <v>12.83805335550365</v>
+        <v>11.60176252728527</v>
       </c>
       <c r="BC4" t="n">
-        <v>13.04596041662425</v>
+        <v>11.4737146123098</v>
       </c>
       <c r="BD4" t="n">
-        <v>12.7841418470257</v>
+        <v>11.24898445913993</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.93110438527078</v>
+        <v>11.43908835092175</v>
       </c>
       <c r="BF4" t="n">
-        <v>12.90308326520506</v>
+        <v>11.46089413170458</v>
       </c>
       <c r="BG4" t="n">
-        <v>12.69588591678122</v>
+        <v>11.44569236269432</v>
       </c>
       <c r="BH4" t="n">
-        <v>12.97433866433001</v>
+        <v>11.32645036841778</v>
       </c>
       <c r="BI4" t="n">
-        <v>13.08814088339861</v>
+        <v>11.40014405240897</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12.90738085103209</v>
+        <v>11.25718819511756</v>
       </c>
       <c r="BK4" t="n">
-        <v>12.8730173785246</v>
+        <v>11.21041904478994</v>
       </c>
       <c r="BL4" t="n">
-        <v>12.86774793175553</v>
+        <v>11.32255108646718</v>
       </c>
       <c r="BM4" t="n">
-        <v>12.61835116102484</v>
+        <v>11.40451293708936</v>
       </c>
       <c r="BN4" t="n">
-        <v>12.76226454878829</v>
+        <v>11.5939858811114</v>
       </c>
       <c r="BO4" t="n">
-        <v>12.74735183703469</v>
+        <v>11.34806524795043</v>
       </c>
       <c r="BP4" t="n">
-        <v>13.05249184050714</v>
+        <v>11.39287626070432</v>
       </c>
       <c r="BQ4" t="n">
-        <v>12.71292216540381</v>
+        <v>11.48495956492633</v>
       </c>
       <c r="BR4" t="n">
-        <v>12.7810107183233</v>
+        <v>11.23844330998768</v>
       </c>
       <c r="BS4" t="n">
-        <v>12.89494943707492</v>
+        <v>11.23916863114634</v>
       </c>
       <c r="BT4" t="n">
-        <v>13.04877764944422</v>
+        <v>11.73849592279705</v>
       </c>
       <c r="BU4" t="n">
-        <v>12.80914282579172</v>
+        <v>11.6605942311846</v>
       </c>
       <c r="BV4" t="n">
-        <v>13.0204808802561</v>
+        <v>11.50010334233167</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.79014844657844</v>
+        <v>11.25322812233109</v>
       </c>
       <c r="BX4" t="n">
-        <v>12.94969712101675</v>
+        <v>11.55310382802407</v>
       </c>
       <c r="BY4" t="n">
-        <v>12.78355332440247</v>
+        <v>11.53247881037611</v>
       </c>
       <c r="BZ4" t="n">
-        <v>12.85461837852178</v>
+        <v>11.92095008140206</v>
       </c>
       <c r="CA4" t="n">
-        <v>12.82002111497146</v>
+        <v>11.53730700140077</v>
       </c>
       <c r="CB4" t="n">
-        <v>12.89613832593422</v>
+        <v>11.3179700138446</v>
       </c>
       <c r="CC4" t="n">
-        <v>12.85183770792546</v>
+        <v>11.32835822682228</v>
       </c>
       <c r="CD4" t="n">
-        <v>12.83796635282824</v>
+        <v>11.79967894034283</v>
       </c>
       <c r="CE4" t="n">
-        <v>12.96980334805973</v>
+        <v>11.44683183173873</v>
       </c>
       <c r="CF4" t="n">
-        <v>12.75166008265865</v>
+        <v>11.49379404537636</v>
       </c>
       <c r="CG4" t="n">
-        <v>12.9873436908312</v>
+        <v>11.37636436548379</v>
       </c>
       <c r="CH4" t="n">
-        <v>12.99179995206576</v>
+        <v>11.27165089115132</v>
       </c>
       <c r="CI4" t="n">
-        <v>12.65994049994158</v>
+        <v>11.62833594348504</v>
       </c>
       <c r="CJ4" t="n">
-        <v>12.86058525538527</v>
+        <v>11.28831114247155</v>
       </c>
       <c r="CK4" t="n">
-        <v>12.98320709062486</v>
+        <v>11.37661100128654</v>
       </c>
       <c r="CL4" t="n">
-        <v>12.91694788249538</v>
+        <v>11.24147950616024</v>
       </c>
       <c r="CM4" t="n">
-        <v>12.7931524765727</v>
+        <v>11.25298113567635</v>
       </c>
       <c r="CN4" t="n">
-        <v>12.92753847644721</v>
+        <v>11.38255275875891</v>
       </c>
       <c r="CO4" t="n">
-        <v>12.81453736483815</v>
+        <v>11.27004761762533</v>
       </c>
       <c r="CP4" t="n">
-        <v>12.83947411800831</v>
+        <v>11.46178489315385</v>
       </c>
       <c r="CQ4" t="n">
-        <v>12.92155879470194</v>
+        <v>11.55770341388705</v>
       </c>
       <c r="CR4" t="n">
-        <v>12.68368709510668</v>
+        <v>11.58231977727669</v>
       </c>
       <c r="CS4" t="n">
-        <v>12.9865748478723</v>
+        <v>11.48835522706031</v>
       </c>
       <c r="CT4" t="n">
-        <v>12.90940672629606</v>
+        <v>11.34275126261653</v>
       </c>
       <c r="CU4" t="n">
-        <v>12.86596568609903</v>
+        <v>11.28437165319508</v>
       </c>
       <c r="CV4" t="n">
-        <v>12.87740370364535</v>
+        <v>11.58250697314481</v>
       </c>
       <c r="CW4" t="n">
-        <v>12.89156647202547</v>
+        <v>11.8082121717671</v>
       </c>
       <c r="CX4" t="n">
-        <v>12.87393661390406</v>
+        <v>11.43177148250323</v>
       </c>
     </row>
     <row r="5">
@@ -1869,307 +1869,307 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.78578821272037</v>
+        <v>12.54915559063692</v>
       </c>
       <c r="C5" t="n">
-        <v>13.76789711591398</v>
+        <v>12.93828171503321</v>
       </c>
       <c r="D5" t="n">
-        <v>13.74642460237573</v>
+        <v>12.40367600267216</v>
       </c>
       <c r="E5" t="n">
-        <v>14.09256335732234</v>
+        <v>12.18463709412456</v>
       </c>
       <c r="F5" t="n">
-        <v>13.84644513146259</v>
+        <v>12.69344031669088</v>
       </c>
       <c r="G5" t="n">
-        <v>13.89739856585876</v>
+        <v>12.5353217029036</v>
       </c>
       <c r="H5" t="n">
-        <v>13.87836609762894</v>
+        <v>12.55793675784369</v>
       </c>
       <c r="I5" t="n">
-        <v>13.7032213777695</v>
+        <v>12.66301258288173</v>
       </c>
       <c r="J5" t="n">
-        <v>14.10215221063437</v>
+        <v>12.81810678588093</v>
       </c>
       <c r="K5" t="n">
-        <v>14.00347144706348</v>
+        <v>12.85324573526833</v>
       </c>
       <c r="L5" t="n">
-        <v>14.2980879128047</v>
+        <v>12.13004379081213</v>
       </c>
       <c r="M5" t="n">
-        <v>14.29822391702174</v>
+        <v>12.82488631040768</v>
       </c>
       <c r="N5" t="n">
-        <v>14.1499529162455</v>
+        <v>12.61960872813696</v>
       </c>
       <c r="O5" t="n">
-        <v>13.72644384463075</v>
+        <v>12.72113065217599</v>
       </c>
       <c r="P5" t="n">
-        <v>14.00261261307835</v>
+        <v>12.50165617156784</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.87784864677321</v>
+        <v>12.71263335826988</v>
       </c>
       <c r="R5" t="n">
-        <v>14.14827008672846</v>
+        <v>12.8029661425286</v>
       </c>
       <c r="S5" t="n">
-        <v>14.16758356503831</v>
+        <v>12.6302115069926</v>
       </c>
       <c r="T5" t="n">
-        <v>13.88126195331348</v>
+        <v>12.84903133223351</v>
       </c>
       <c r="U5" t="n">
-        <v>14.44572975217192</v>
+        <v>12.80093412691011</v>
       </c>
       <c r="V5" t="n">
-        <v>14.36067099758407</v>
+        <v>13.11084954572515</v>
       </c>
       <c r="W5" t="n">
-        <v>13.81181189782659</v>
+        <v>12.38845659112671</v>
       </c>
       <c r="X5" t="n">
-        <v>14.25623368213911</v>
+        <v>12.42498487212794</v>
       </c>
       <c r="Y5" t="n">
-        <v>14.21116973723828</v>
+        <v>12.49079425623171</v>
       </c>
       <c r="Z5" t="n">
-        <v>13.82873079857845</v>
+        <v>13.39198366686483</v>
       </c>
       <c r="AA5" t="n">
-        <v>14.19301331881062</v>
+        <v>12.667487441887</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.05466419901432</v>
+        <v>12.72067352527057</v>
       </c>
       <c r="AC5" t="n">
-        <v>14.09378751076567</v>
+        <v>12.32021974880014</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.17408328966827</v>
+        <v>12.26033936427095</v>
       </c>
       <c r="AE5" t="n">
-        <v>13.74718070240696</v>
+        <v>12.45181379802665</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.3113595735792</v>
+        <v>12.58702530947352</v>
       </c>
       <c r="AG5" t="n">
-        <v>14.21805958724055</v>
+        <v>12.57668516751985</v>
       </c>
       <c r="AH5" t="n">
-        <v>14.0291418574523</v>
+        <v>12.24013313836682</v>
       </c>
       <c r="AI5" t="n">
-        <v>13.92810907805632</v>
+        <v>12.26410968733497</v>
       </c>
       <c r="AJ5" t="n">
-        <v>13.85849820791529</v>
+        <v>12.23915905500587</v>
       </c>
       <c r="AK5" t="n">
-        <v>14.08122998107844</v>
+        <v>12.31985994184179</v>
       </c>
       <c r="AL5" t="n">
-        <v>14.14581665613435</v>
+        <v>12.14947800869591</v>
       </c>
       <c r="AM5" t="n">
-        <v>13.78322316432599</v>
+        <v>12.61496793347335</v>
       </c>
       <c r="AN5" t="n">
-        <v>14.14921210119606</v>
+        <v>12.38453499525307</v>
       </c>
       <c r="AO5" t="n">
-        <v>13.9387808858808</v>
+        <v>12.44398163241358</v>
       </c>
       <c r="AP5" t="n">
-        <v>14.2543775173323</v>
+        <v>12.50170184956092</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.8316803874701</v>
+        <v>12.35921567851046</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.77867589373141</v>
+        <v>12.2390542505636</v>
       </c>
       <c r="AS5" t="n">
-        <v>13.74249373798824</v>
+        <v>12.04596660952224</v>
       </c>
       <c r="AT5" t="n">
-        <v>14.14969086433702</v>
+        <v>12.8731954797022</v>
       </c>
       <c r="AU5" t="n">
-        <v>13.92950890471714</v>
+        <v>13.28611391191663</v>
       </c>
       <c r="AV5" t="n">
-        <v>14.33958049251806</v>
+        <v>12.34550330272391</v>
       </c>
       <c r="AW5" t="n">
-        <v>13.81537948828964</v>
+        <v>12.30722941511528</v>
       </c>
       <c r="AX5" t="n">
-        <v>13.71705144325796</v>
+        <v>12.23278566499493</v>
       </c>
       <c r="AY5" t="n">
-        <v>14.26850373084564</v>
+        <v>12.21180093455133</v>
       </c>
       <c r="AZ5" t="n">
-        <v>14.03563161777291</v>
+        <v>12.11943135296984</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.05035132440706</v>
+        <v>12.3594669144851</v>
       </c>
       <c r="BB5" t="n">
-        <v>13.97937910314508</v>
+        <v>12.78564983178701</v>
       </c>
       <c r="BC5" t="n">
-        <v>14.33509124835243</v>
+        <v>12.60623527776955</v>
       </c>
       <c r="BD5" t="n">
-        <v>13.91199286581892</v>
+        <v>12.21751548230863</v>
       </c>
       <c r="BE5" t="n">
-        <v>14.15338812244696</v>
+        <v>12.49652108350158</v>
       </c>
       <c r="BF5" t="n">
-        <v>14.04409675299519</v>
+        <v>12.57522368748921</v>
       </c>
       <c r="BG5" t="n">
-        <v>13.72135781432416</v>
+        <v>12.6482939120411</v>
       </c>
       <c r="BH5" t="n">
-        <v>14.06527839662087</v>
+        <v>12.29789374196822</v>
       </c>
       <c r="BI5" t="n">
-        <v>14.4468484365479</v>
+        <v>12.55185295226923</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14.08298182858465</v>
+        <v>12.21164453714591</v>
       </c>
       <c r="BK5" t="n">
-        <v>14.089769961163</v>
+        <v>12.14395314136081</v>
       </c>
       <c r="BL5" t="n">
-        <v>13.97181770769922</v>
+        <v>12.37375538851955</v>
       </c>
       <c r="BM5" t="n">
-        <v>13.61417698823961</v>
+        <v>12.6478961080585</v>
       </c>
       <c r="BN5" t="n">
-        <v>13.96517361385324</v>
+        <v>12.77925987252299</v>
       </c>
       <c r="BO5" t="n">
-        <v>13.80152707570422</v>
+        <v>12.30349122582466</v>
       </c>
       <c r="BP5" t="n">
-        <v>14.34814454750968</v>
+        <v>12.48374237020791</v>
       </c>
       <c r="BQ5" t="n">
-        <v>13.74368161023923</v>
+        <v>12.50803711912245</v>
       </c>
       <c r="BR5" t="n">
-        <v>13.87870984769755</v>
+        <v>12.18855770407684</v>
       </c>
       <c r="BS5" t="n">
-        <v>14.1128146937625</v>
+        <v>12.19075680124809</v>
       </c>
       <c r="BT5" t="n">
-        <v>14.18216793903104</v>
+        <v>13.21036940225285</v>
       </c>
       <c r="BU5" t="n">
-        <v>13.80221884289394</v>
+        <v>13.02903124759428</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.22871823633506</v>
+        <v>12.77959973348558</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.89334501570543</v>
+        <v>12.23696902615819</v>
       </c>
       <c r="BX5" t="n">
-        <v>14.136237372157</v>
+        <v>12.79753778628181</v>
       </c>
       <c r="BY5" t="n">
-        <v>13.83604627067639</v>
+        <v>12.70022643471153</v>
       </c>
       <c r="BZ5" t="n">
-        <v>14.02892089701448</v>
+        <v>13.44094109284041</v>
       </c>
       <c r="CA5" t="n">
-        <v>13.87460708641103</v>
+        <v>12.70015892367244</v>
       </c>
       <c r="CB5" t="n">
-        <v>13.94113613139779</v>
+        <v>12.35946613672884</v>
       </c>
       <c r="CC5" t="n">
-        <v>14.08749933235694</v>
+        <v>12.47482628673071</v>
       </c>
       <c r="CD5" t="n">
-        <v>13.91385682631114</v>
+        <v>13.37901651227787</v>
       </c>
       <c r="CE5" t="n">
-        <v>14.18717626048733</v>
+        <v>12.5006266383577</v>
       </c>
       <c r="CF5" t="n">
-        <v>13.84822761601729</v>
+        <v>12.82655107595361</v>
       </c>
       <c r="CG5" t="n">
-        <v>14.12352335581556</v>
+        <v>12.48200058193623</v>
       </c>
       <c r="CH5" t="n">
-        <v>14.15330598563973</v>
+        <v>12.32529125061199</v>
       </c>
       <c r="CI5" t="n">
-        <v>13.72592062226044</v>
+        <v>13.04627191088714</v>
       </c>
       <c r="CJ5" t="n">
-        <v>13.90332957595057</v>
+        <v>12.27565708741396</v>
       </c>
       <c r="CK5" t="n">
-        <v>14.13488007756562</v>
+        <v>12.43493135593975</v>
       </c>
       <c r="CL5" t="n">
-        <v>14.12151957161872</v>
+        <v>12.17525715347556</v>
       </c>
       <c r="CM5" t="n">
-        <v>13.90649639716654</v>
+        <v>12.09593933609521</v>
       </c>
       <c r="CN5" t="n">
-        <v>14.18605942990443</v>
+        <v>12.33489528414678</v>
       </c>
       <c r="CO5" t="n">
-        <v>13.83084984496859</v>
+        <v>12.19685264675132</v>
       </c>
       <c r="CP5" t="n">
-        <v>14.04329424768488</v>
+        <v>12.57685686915882</v>
       </c>
       <c r="CQ5" t="n">
-        <v>13.99136050052902</v>
+        <v>12.87888232929496</v>
       </c>
       <c r="CR5" t="n">
-        <v>13.68396136357542</v>
+        <v>12.79309913898883</v>
       </c>
       <c r="CS5" t="n">
-        <v>14.17563735713113</v>
+        <v>12.62159195880048</v>
       </c>
       <c r="CT5" t="n">
-        <v>14.05891400036713</v>
+        <v>12.37347030502321</v>
       </c>
       <c r="CU5" t="n">
-        <v>14.06255306109441</v>
+        <v>12.29886325107118</v>
       </c>
       <c r="CV5" t="n">
-        <v>14.04543263189624</v>
+        <v>12.92783154116005</v>
       </c>
       <c r="CW5" t="n">
-        <v>13.94641339005546</v>
+        <v>13.350391966637</v>
       </c>
       <c r="CX5" t="n">
-        <v>14.01227285810839</v>
+        <v>12.55352603949959</v>
       </c>
     </row>
     <row r="6">
@@ -2177,307 +2177,307 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.93877268475315</v>
+        <v>13.89032600290141</v>
       </c>
       <c r="C6" t="n">
-        <v>15.04350025257969</v>
+        <v>14.55826690731048</v>
       </c>
       <c r="D6" t="n">
-        <v>14.89799215705186</v>
+        <v>13.69538600205088</v>
       </c>
       <c r="E6" t="n">
-        <v>15.56457015404795</v>
+        <v>13.34429226121786</v>
       </c>
       <c r="F6" t="n">
-        <v>15.23575259232437</v>
+        <v>14.19355841074851</v>
       </c>
       <c r="G6" t="n">
-        <v>15.12290455916427</v>
+        <v>13.97636034737354</v>
       </c>
       <c r="H6" t="n">
-        <v>15.09079469603254</v>
+        <v>13.95629416311793</v>
       </c>
       <c r="I6" t="n">
-        <v>14.89093549091002</v>
+        <v>14.05522469033576</v>
       </c>
       <c r="J6" t="n">
-        <v>15.53936146150848</v>
+        <v>14.30658155069119</v>
       </c>
       <c r="K6" t="n">
-        <v>15.3370431143503</v>
+        <v>14.35697383809411</v>
       </c>
       <c r="L6" t="n">
-        <v>15.76703670098648</v>
+        <v>13.23224250393424</v>
       </c>
       <c r="M6" t="n">
-        <v>15.82767260569998</v>
+        <v>14.39747704767472</v>
       </c>
       <c r="N6" t="n">
-        <v>15.53670984496515</v>
+        <v>13.98129662024197</v>
       </c>
       <c r="O6" t="n">
-        <v>14.86186602094897</v>
+        <v>14.18671684518411</v>
       </c>
       <c r="P6" t="n">
-        <v>15.38683475439337</v>
+        <v>13.7586763164209</v>
       </c>
       <c r="Q6" t="n">
-        <v>15.15638128696609</v>
+        <v>14.12929350754863</v>
       </c>
       <c r="R6" t="n">
-        <v>15.63632708281576</v>
+        <v>14.31589410221214</v>
       </c>
       <c r="S6" t="n">
-        <v>15.64361801889956</v>
+        <v>13.87389546826273</v>
       </c>
       <c r="T6" t="n">
-        <v>15.11245170111511</v>
+        <v>14.4241860365353</v>
       </c>
       <c r="U6" t="n">
-        <v>16.09328172852891</v>
+        <v>14.40123038870626</v>
       </c>
       <c r="V6" t="n">
-        <v>15.91324170689005</v>
+        <v>15.00037593768147</v>
       </c>
       <c r="W6" t="n">
-        <v>15.12946894918428</v>
+        <v>13.56221118732896</v>
       </c>
       <c r="X6" t="n">
-        <v>15.75690343430106</v>
+        <v>13.63929868486833</v>
       </c>
       <c r="Y6" t="n">
-        <v>15.67456467514132</v>
+        <v>13.76798503918345</v>
       </c>
       <c r="Z6" t="n">
-        <v>15.06456780879418</v>
+        <v>15.28473774631981</v>
       </c>
       <c r="AA6" t="n">
-        <v>15.76367982316925</v>
+        <v>14.04818770974879</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.35038677653325</v>
+        <v>14.20851237946828</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.53910825147097</v>
+        <v>13.50407996751998</v>
       </c>
       <c r="AD6" t="n">
-        <v>15.71752501066723</v>
+        <v>13.59157393759088</v>
       </c>
       <c r="AE6" t="n">
-        <v>15.05284958967441</v>
+        <v>13.73065347168433</v>
       </c>
       <c r="AF6" t="n">
-        <v>15.84127033128481</v>
+        <v>14.03314679898099</v>
       </c>
       <c r="AG6" t="n">
-        <v>15.54839300592808</v>
+        <v>13.95079041654553</v>
       </c>
       <c r="AH6" t="n">
-        <v>15.32689400224608</v>
+        <v>13.45135326311844</v>
       </c>
       <c r="AI6" t="n">
-        <v>15.25240895426677</v>
+        <v>13.3523353593091</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15.0998445309834</v>
+        <v>13.46202664359613</v>
       </c>
       <c r="AK6" t="n">
-        <v>15.40023894152754</v>
+        <v>13.60268193516014</v>
       </c>
       <c r="AL6" t="n">
-        <v>15.52733001956049</v>
+        <v>13.25114400257953</v>
       </c>
       <c r="AM6" t="n">
-        <v>14.91820226267163</v>
+        <v>14.06323913015679</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.63957639998981</v>
+        <v>13.5862418036745</v>
       </c>
       <c r="AO6" t="n">
-        <v>15.29024295616673</v>
+        <v>13.69864570205264</v>
       </c>
       <c r="AP6" t="n">
-        <v>15.69753909137868</v>
+        <v>13.86264398647898</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15.10820295483853</v>
+        <v>13.51141880392715</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.96554249902598</v>
+        <v>13.39726627308125</v>
       </c>
       <c r="AS6" t="n">
-        <v>15.02212602689903</v>
+        <v>13.15991189958461</v>
       </c>
       <c r="AT6" t="n">
-        <v>15.59726952817056</v>
+        <v>14.41277848774005</v>
       </c>
       <c r="AU6" t="n">
-        <v>15.34660677715647</v>
+        <v>15.06046949903192</v>
       </c>
       <c r="AV6" t="n">
-        <v>15.94415307674333</v>
+        <v>13.56558346562533</v>
       </c>
       <c r="AW6" t="n">
-        <v>15.03042141279805</v>
+        <v>13.44728774520957</v>
       </c>
       <c r="AX6" t="n">
-        <v>14.97666570650835</v>
+        <v>13.36335998494348</v>
       </c>
       <c r="AY6" t="n">
-        <v>15.71185092565976</v>
+        <v>13.3569244145699</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.36270474441428</v>
+        <v>13.32291557719302</v>
       </c>
       <c r="BA6" t="n">
-        <v>15.33605613654255</v>
+        <v>13.60791459657046</v>
       </c>
       <c r="BB6" t="n">
-        <v>15.33536843744054</v>
+        <v>14.25705042632015</v>
       </c>
       <c r="BC6" t="n">
-        <v>15.82350611420505</v>
+        <v>13.95759594635845</v>
       </c>
       <c r="BD6" t="n">
-        <v>15.19992363460188</v>
+        <v>13.34821852542589</v>
       </c>
       <c r="BE6" t="n">
-        <v>15.52216745432171</v>
+        <v>13.82831211424026</v>
       </c>
       <c r="BF6" t="n">
-        <v>15.42430254148963</v>
+        <v>13.92359594485508</v>
       </c>
       <c r="BG6" t="n">
-        <v>14.91565549179245</v>
+        <v>14.07674942610644</v>
       </c>
       <c r="BH6" t="n">
-        <v>15.4594455119497</v>
+        <v>13.44434155574854</v>
       </c>
       <c r="BI6" t="n">
-        <v>15.96393071396959</v>
+        <v>13.88353311306679</v>
       </c>
       <c r="BJ6" t="n">
-        <v>15.41260322629046</v>
+        <v>13.39646873218827</v>
       </c>
       <c r="BK6" t="n">
-        <v>15.44144217634143</v>
+        <v>13.31278419201253</v>
       </c>
       <c r="BL6" t="n">
-        <v>15.18533029534668</v>
+        <v>13.64248802206718</v>
       </c>
       <c r="BM6" t="n">
-        <v>14.7754668283658</v>
+        <v>14.24174976603118</v>
       </c>
       <c r="BN6" t="n">
-        <v>15.27459556897338</v>
+        <v>14.30826245749088</v>
       </c>
       <c r="BO6" t="n">
-        <v>15.08420447464414</v>
+        <v>13.53125539348388</v>
       </c>
       <c r="BP6" t="n">
-        <v>15.89911837712873</v>
+        <v>13.80456672096095</v>
       </c>
       <c r="BQ6" t="n">
-        <v>14.92821195457004</v>
+        <v>13.80469539766342</v>
       </c>
       <c r="BR6" t="n">
-        <v>15.08005447841571</v>
+        <v>13.25160478177787</v>
       </c>
       <c r="BS6" t="n">
-        <v>15.59870491978094</v>
+        <v>13.38246094721424</v>
       </c>
       <c r="BT6" t="n">
-        <v>15.48569091438209</v>
+        <v>14.95615784921423</v>
       </c>
       <c r="BU6" t="n">
-        <v>14.96090335884902</v>
+        <v>14.73714513366227</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.64307999432036</v>
+        <v>14.28851522776026</v>
       </c>
       <c r="BW6" t="n">
-        <v>15.2110146691519</v>
+        <v>13.50420595887786</v>
       </c>
       <c r="BX6" t="n">
-        <v>15.49037578682639</v>
+        <v>14.34816965724004</v>
       </c>
       <c r="BY6" t="n">
-        <v>15.10841984639862</v>
+        <v>14.15710726468781</v>
       </c>
       <c r="BZ6" t="n">
-        <v>15.50012298975959</v>
+        <v>15.36957398471494</v>
       </c>
       <c r="CA6" t="n">
-        <v>15.12892102597241</v>
+        <v>14.10863671876559</v>
       </c>
       <c r="CB6" t="n">
-        <v>15.17895427177719</v>
+        <v>13.58286635601575</v>
       </c>
       <c r="CC6" t="n">
-        <v>15.47774389183262</v>
+        <v>13.94435362009608</v>
       </c>
       <c r="CD6" t="n">
-        <v>15.25173849276285</v>
+        <v>15.20178376209485</v>
       </c>
       <c r="CE6" t="n">
-        <v>15.62744633013694</v>
+        <v>13.77674951272303</v>
       </c>
       <c r="CF6" t="n">
-        <v>15.18273739968271</v>
+        <v>14.35301997705028</v>
       </c>
       <c r="CG6" t="n">
-        <v>15.42065527361242</v>
+        <v>13.92255061850915</v>
       </c>
       <c r="CH6" t="n">
-        <v>15.69841662965994</v>
+        <v>13.68146294521536</v>
       </c>
       <c r="CI6" t="n">
-        <v>15.00175730300161</v>
+        <v>14.75002686558644</v>
       </c>
       <c r="CJ6" t="n">
-        <v>15.2233130441679</v>
+        <v>13.43146284502703</v>
       </c>
       <c r="CK6" t="n">
-        <v>15.51449805949855</v>
+        <v>13.70121251907197</v>
       </c>
       <c r="CL6" t="n">
-        <v>15.57581885809687</v>
+        <v>13.34907317129906</v>
       </c>
       <c r="CM6" t="n">
-        <v>15.19475257454453</v>
+        <v>13.10763919304145</v>
       </c>
       <c r="CN6" t="n">
-        <v>15.56190591041922</v>
+        <v>13.48240306488977</v>
       </c>
       <c r="CO6" t="n">
-        <v>15.20756211778478</v>
+        <v>13.37394554356832</v>
       </c>
       <c r="CP6" t="n">
-        <v>15.33057453104361</v>
+        <v>13.90363582659955</v>
       </c>
       <c r="CQ6" t="n">
-        <v>15.18450719385833</v>
+        <v>14.47305413082292</v>
       </c>
       <c r="CR6" t="n">
-        <v>14.97351441857786</v>
+        <v>14.28696785699538</v>
       </c>
       <c r="CS6" t="n">
-        <v>15.75670771403733</v>
+        <v>13.98151705088491</v>
       </c>
       <c r="CT6" t="n">
-        <v>15.27486009102417</v>
+        <v>13.67288577862651</v>
       </c>
       <c r="CU6" t="n">
-        <v>15.46190991235683</v>
+        <v>13.52759144090949</v>
       </c>
       <c r="CV6" t="n">
-        <v>15.46198089817643</v>
+        <v>14.60241679165915</v>
       </c>
       <c r="CW6" t="n">
-        <v>15.08664541622784</v>
+        <v>15.12367145286121</v>
       </c>
       <c r="CX6" t="n">
-        <v>15.36090204336198</v>
+        <v>13.91987404442569</v>
       </c>
     </row>
     <row r="7">
@@ -2485,307 +2485,307 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.32550034036187</v>
+        <v>15.39992232456699</v>
       </c>
       <c r="C7" t="n">
-        <v>16.45704194048604</v>
+        <v>16.38127496314447</v>
       </c>
       <c r="D7" t="n">
-        <v>16.14648351572465</v>
+        <v>15.18988180160918</v>
       </c>
       <c r="E7" t="n">
-        <v>17.22857108424953</v>
+        <v>14.70244631317923</v>
       </c>
       <c r="F7" t="n">
-        <v>16.80763395969876</v>
+        <v>15.96927729296148</v>
       </c>
       <c r="G7" t="n">
-        <v>16.53795507678272</v>
+        <v>15.60404166811855</v>
       </c>
       <c r="H7" t="n">
-        <v>16.51641644514479</v>
+        <v>15.51675030833549</v>
       </c>
       <c r="I7" t="n">
-        <v>16.29186705574667</v>
+        <v>15.74468254154744</v>
       </c>
       <c r="J7" t="n">
-        <v>17.08351802822913</v>
+        <v>15.9519562390076</v>
       </c>
       <c r="K7" t="n">
-        <v>16.91206882589447</v>
+        <v>15.97941298761984</v>
       </c>
       <c r="L7" t="n">
-        <v>17.44985483422631</v>
+        <v>14.57637675861913</v>
       </c>
       <c r="M7" t="n">
-        <v>17.58423722728883</v>
+        <v>16.13813957498255</v>
       </c>
       <c r="N7" t="n">
-        <v>17.29957440324499</v>
+        <v>15.52453316634293</v>
       </c>
       <c r="O7" t="n">
-        <v>16.1977310520497</v>
+        <v>15.79411841460215</v>
       </c>
       <c r="P7" t="n">
-        <v>16.9559216193743</v>
+        <v>15.19247245659557</v>
       </c>
       <c r="Q7" t="n">
-        <v>16.6013873207207</v>
+        <v>15.76659893581431</v>
       </c>
       <c r="R7" t="n">
-        <v>17.29249689356832</v>
+        <v>16.14063415117367</v>
       </c>
       <c r="S7" t="n">
-        <v>17.26681628142602</v>
+        <v>15.25056804197609</v>
       </c>
       <c r="T7" t="n">
-        <v>16.51848595699727</v>
+        <v>16.07759343385388</v>
       </c>
       <c r="U7" t="n">
-        <v>17.9560990768451</v>
+        <v>16.20854498507906</v>
       </c>
       <c r="V7" t="n">
-        <v>17.64193855766574</v>
+        <v>17.13293695344996</v>
       </c>
       <c r="W7" t="n">
-        <v>16.61165518165706</v>
+        <v>15.04873854676686</v>
       </c>
       <c r="X7" t="n">
-        <v>17.5089001098805</v>
+        <v>15.14139422768805</v>
       </c>
       <c r="Y7" t="n">
-        <v>17.36374713008448</v>
+        <v>15.26547892076872</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.52986500254458</v>
+        <v>17.40926439207863</v>
       </c>
       <c r="AA7" t="n">
-        <v>17.55153847262796</v>
+        <v>15.66074348598647</v>
       </c>
       <c r="AB7" t="n">
-        <v>16.85572434502104</v>
+        <v>15.92888126280091</v>
       </c>
       <c r="AC7" t="n">
-        <v>17.13699777863708</v>
+        <v>14.96697738713395</v>
       </c>
       <c r="AD7" t="n">
-        <v>17.45223099817974</v>
+        <v>15.19870601116162</v>
       </c>
       <c r="AE7" t="n">
-        <v>16.59913590378865</v>
+        <v>15.27582005497879</v>
       </c>
       <c r="AF7" t="n">
-        <v>17.61259664043386</v>
+        <v>15.68353224271277</v>
       </c>
       <c r="AG7" t="n">
-        <v>17.21209444597232</v>
+        <v>15.59366772342237</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.75112696171224</v>
+        <v>14.76402055454849</v>
       </c>
       <c r="AI7" t="n">
-        <v>16.87575407205998</v>
+        <v>14.55513099680167</v>
       </c>
       <c r="AJ7" t="n">
-        <v>16.56347469593447</v>
+        <v>14.84948201072458</v>
       </c>
       <c r="AK7" t="n">
-        <v>16.97395640793128</v>
+        <v>15.133359804171</v>
       </c>
       <c r="AL7" t="n">
-        <v>17.12332534748323</v>
+        <v>14.56171465642506</v>
       </c>
       <c r="AM7" t="n">
-        <v>16.37694175978301</v>
+        <v>15.71163178495923</v>
       </c>
       <c r="AN7" t="n">
-        <v>17.41965868660078</v>
+        <v>14.9327966692745</v>
       </c>
       <c r="AO7" t="n">
-        <v>16.73918952532193</v>
+        <v>15.11327857852728</v>
       </c>
       <c r="AP7" t="n">
-        <v>17.32803951252657</v>
+        <v>15.37521202107171</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16.55352593576953</v>
+        <v>14.87362282898292</v>
       </c>
       <c r="AR7" t="n">
-        <v>16.3767829825337</v>
+        <v>14.66400509412466</v>
       </c>
       <c r="AS7" t="n">
-        <v>16.46835660643161</v>
+        <v>14.54998751523979</v>
       </c>
       <c r="AT7" t="n">
-        <v>17.28639030199607</v>
+        <v>16.10743507540188</v>
       </c>
       <c r="AU7" t="n">
-        <v>16.96826488091808</v>
+        <v>17.13029725118674</v>
       </c>
       <c r="AV7" t="n">
-        <v>17.71841585783754</v>
+        <v>15.09989071175175</v>
       </c>
       <c r="AW7" t="n">
-        <v>16.405562240457</v>
+        <v>14.84037923216514</v>
       </c>
       <c r="AX7" t="n">
-        <v>16.32060061355209</v>
+        <v>14.72382383057705</v>
       </c>
       <c r="AY7" t="n">
-        <v>17.33001502292652</v>
+        <v>14.59433244225318</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16.9378477504331</v>
+        <v>14.80698420938022</v>
       </c>
       <c r="BA7" t="n">
-        <v>16.77014106532429</v>
+        <v>15.111790050937</v>
       </c>
       <c r="BB7" t="n">
-        <v>16.88119346957389</v>
+        <v>15.88298583819224</v>
       </c>
       <c r="BC7" t="n">
-        <v>17.60790943552689</v>
+        <v>15.41209011054989</v>
       </c>
       <c r="BD7" t="n">
-        <v>16.72424973752763</v>
+        <v>14.63326001837339</v>
       </c>
       <c r="BE7" t="n">
-        <v>17.18784457071861</v>
+        <v>15.2788603764247</v>
       </c>
       <c r="BF7" t="n">
-        <v>16.97601256511388</v>
+        <v>15.47989553851156</v>
       </c>
       <c r="BG7" t="n">
-        <v>16.34839431615858</v>
+        <v>15.77425185726088</v>
       </c>
       <c r="BH7" t="n">
-        <v>17.00652782088109</v>
+        <v>14.79988391140216</v>
       </c>
       <c r="BI7" t="n">
-        <v>17.79622319990631</v>
+        <v>15.49039653675215</v>
       </c>
       <c r="BJ7" t="n">
-        <v>16.87334369265445</v>
+        <v>14.79720598932889</v>
       </c>
       <c r="BK7" t="n">
-        <v>16.94982930256336</v>
+        <v>14.67187756079359</v>
       </c>
       <c r="BL7" t="n">
-        <v>16.62039438494722</v>
+        <v>15.13790214425295</v>
       </c>
       <c r="BM7" t="n">
-        <v>16.1289322643124</v>
+        <v>16.01823259781256</v>
       </c>
       <c r="BN7" t="n">
-        <v>16.82032994316122</v>
+        <v>15.96523113946398</v>
       </c>
       <c r="BO7" t="n">
-        <v>16.54417470263897</v>
+        <v>14.85647873392861</v>
       </c>
       <c r="BP7" t="n">
-        <v>17.72546958777716</v>
+        <v>15.25364018519326</v>
       </c>
       <c r="BQ7" t="n">
-        <v>16.30609956482839</v>
+        <v>15.22728001533169</v>
       </c>
       <c r="BR7" t="n">
-        <v>16.45561482166999</v>
+        <v>14.5243907333494</v>
       </c>
       <c r="BS7" t="n">
-        <v>17.17833657762179</v>
+        <v>14.87265019807862</v>
       </c>
       <c r="BT7" t="n">
-        <v>17.05577959509884</v>
+        <v>16.96816630665516</v>
       </c>
       <c r="BU7" t="n">
-        <v>16.36655973011452</v>
+        <v>16.60921316686504</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.33013899014099</v>
+        <v>15.9780330959047</v>
       </c>
       <c r="BW7" t="n">
-        <v>16.62208634329572</v>
+        <v>15.02806103014051</v>
       </c>
       <c r="BX7" t="n">
-        <v>16.98121014607672</v>
+        <v>16.06993210173813</v>
       </c>
       <c r="BY7" t="n">
-        <v>16.69072483156247</v>
+        <v>15.77830209602026</v>
       </c>
       <c r="BZ7" t="n">
-        <v>17.11891162996782</v>
+        <v>17.54183326184354</v>
       </c>
       <c r="CA7" t="n">
-        <v>16.50141715237275</v>
+        <v>15.68647717057633</v>
       </c>
       <c r="CB7" t="n">
-        <v>16.62694737634551</v>
+        <v>15.01623336127827</v>
       </c>
       <c r="CC7" t="n">
-        <v>17.08016134642977</v>
+        <v>15.61937158848593</v>
       </c>
       <c r="CD7" t="n">
-        <v>16.741956233891</v>
+        <v>17.27180613493879</v>
       </c>
       <c r="CE7" t="n">
-        <v>17.25664468282162</v>
+        <v>15.23813527221459</v>
       </c>
       <c r="CF7" t="n">
-        <v>16.66279833713715</v>
+        <v>16.1983656668003</v>
       </c>
       <c r="CG7" t="n">
-        <v>16.88773109388559</v>
+        <v>15.67082697430124</v>
       </c>
       <c r="CH7" t="n">
-        <v>17.29684030067618</v>
+        <v>15.35912191539594</v>
       </c>
       <c r="CI7" t="n">
-        <v>16.39872950036634</v>
+        <v>16.65543588878308</v>
       </c>
       <c r="CJ7" t="n">
-        <v>16.66582040561686</v>
+        <v>14.70662562502468</v>
       </c>
       <c r="CK7" t="n">
-        <v>17.16874677793543</v>
+        <v>15.14149914997106</v>
       </c>
       <c r="CL7" t="n">
-        <v>17.2725622119449</v>
+        <v>14.78895578260451</v>
       </c>
       <c r="CM7" t="n">
-        <v>16.65705485115829</v>
+        <v>14.36442904581907</v>
       </c>
       <c r="CN7" t="n">
-        <v>17.12493708312708</v>
+        <v>14.79819103481446</v>
       </c>
       <c r="CO7" t="n">
-        <v>16.6067706660671</v>
+        <v>14.76492372369744</v>
       </c>
       <c r="CP7" t="n">
-        <v>16.68738626627005</v>
+        <v>15.43140885928112</v>
       </c>
       <c r="CQ7" t="n">
-        <v>16.57212562895512</v>
+        <v>16.17744206522519</v>
       </c>
       <c r="CR7" t="n">
-        <v>16.39732188581349</v>
+        <v>15.88932636904716</v>
       </c>
       <c r="CS7" t="n">
-        <v>17.45379074410183</v>
+        <v>15.50012742317361</v>
       </c>
       <c r="CT7" t="n">
-        <v>16.75491486097342</v>
+        <v>15.10779689282042</v>
       </c>
       <c r="CU7" t="n">
-        <v>17.04184118993841</v>
+        <v>15.02170729885555</v>
       </c>
       <c r="CV7" t="n">
-        <v>17.09358423991609</v>
+        <v>16.54258451047564</v>
       </c>
       <c r="CW7" t="n">
-        <v>16.42304109321034</v>
+        <v>17.0580369759378</v>
       </c>
       <c r="CX7" t="n">
-        <v>16.90462870884879</v>
+        <v>15.48973426160272</v>
       </c>
     </row>
     <row r="8">
@@ -2793,307 +2793,307 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.39314373563334</v>
+        <v>17.0621131544884</v>
       </c>
       <c r="C8" t="n">
-        <v>11.54660843078557</v>
+        <v>18.33620662608786</v>
       </c>
       <c r="D8" t="n">
-        <v>11.27508371358679</v>
+        <v>16.91234245441979</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43381824804819</v>
+        <v>16.248732235262</v>
       </c>
       <c r="F8" t="n">
-        <v>12.09214918757793</v>
+        <v>17.95937049150368</v>
       </c>
       <c r="G8" t="n">
-        <v>11.56784362755141</v>
+        <v>17.44596008267198</v>
       </c>
       <c r="H8" t="n">
-        <v>11.70460301389568</v>
+        <v>17.25442048460916</v>
       </c>
       <c r="I8" t="n">
-        <v>11.48353208155272</v>
+        <v>17.48891588676145</v>
       </c>
       <c r="J8" t="n">
-        <v>12.32696970692446</v>
+        <v>17.75151767458516</v>
       </c>
       <c r="K8" t="n">
-        <v>11.99147848719198</v>
+        <v>17.72637036985109</v>
       </c>
       <c r="L8" t="n">
-        <v>12.43847617936476</v>
+        <v>16.11742019477116</v>
       </c>
       <c r="M8" t="n">
-        <v>12.82976805487748</v>
+        <v>18.17337743598738</v>
       </c>
       <c r="N8" t="n">
-        <v>12.45499134825943</v>
+        <v>17.21704032681004</v>
       </c>
       <c r="O8" t="n">
-        <v>11.2880370047684</v>
+        <v>17.58264636752817</v>
       </c>
       <c r="P8" t="n">
-        <v>12.1134155430815</v>
+        <v>16.81615188766795</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.87527799234671</v>
+        <v>17.60429578506139</v>
       </c>
       <c r="R8" t="n">
-        <v>12.45251570688528</v>
+        <v>18.12600413862976</v>
       </c>
       <c r="S8" t="n">
-        <v>12.4182114757276</v>
+        <v>16.81920713806417</v>
       </c>
       <c r="T8" t="n">
-        <v>11.79036815733231</v>
+        <v>17.91638956916204</v>
       </c>
       <c r="U8" t="n">
-        <v>13.03679818877306</v>
+        <v>18.14921078736153</v>
       </c>
       <c r="V8" t="n">
-        <v>12.75106349145459</v>
+        <v>19.36573464285264</v>
       </c>
       <c r="W8" t="n">
-        <v>11.71399905132094</v>
+        <v>16.60694212257082</v>
       </c>
       <c r="X8" t="n">
-        <v>12.58583294037493</v>
+        <v>16.72283204759808</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.3351278142363</v>
+        <v>17.08937533227994</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.54101509025963</v>
+        <v>19.73744988682541</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.66865804702538</v>
+        <v>17.40010386884437</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.9468650197602</v>
+        <v>17.77991349785438</v>
       </c>
       <c r="AC8" t="n">
-        <v>12.31060346976124</v>
+        <v>16.63450782475375</v>
       </c>
       <c r="AD8" t="n">
-        <v>12.59730962597576</v>
+        <v>16.89145413846944</v>
       </c>
       <c r="AE8" t="n">
-        <v>11.86130414619682</v>
+        <v>16.94468949873922</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.59121662799715</v>
+        <v>17.51331677642236</v>
       </c>
       <c r="AG8" t="n">
-        <v>12.35595043366381</v>
+        <v>17.37960051713082</v>
       </c>
       <c r="AH8" t="n">
-        <v>11.78267175396731</v>
+        <v>16.40142687148958</v>
       </c>
       <c r="AI8" t="n">
-        <v>12.0733924161892</v>
+        <v>15.9747789919069</v>
       </c>
       <c r="AJ8" t="n">
-        <v>11.70298709392187</v>
+        <v>16.38600206629207</v>
       </c>
       <c r="AK8" t="n">
-        <v>12.03022934006019</v>
+        <v>16.90371541787984</v>
       </c>
       <c r="AL8" t="n">
-        <v>12.16779459072271</v>
+        <v>16.03444392522864</v>
       </c>
       <c r="AM8" t="n">
-        <v>11.39753145173312</v>
+        <v>17.62404487768995</v>
       </c>
       <c r="AN8" t="n">
-        <v>12.62482011017735</v>
+        <v>16.51217638843167</v>
       </c>
       <c r="AO8" t="n">
-        <v>11.872265216321</v>
+        <v>16.68674480224973</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.42857538348728</v>
+        <v>17.08372113531855</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.75765537365135</v>
+        <v>16.442072898806</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.48090816700241</v>
+        <v>16.0696492387926</v>
       </c>
       <c r="AS8" t="n">
-        <v>11.6643565098796</v>
+        <v>16.03505903957947</v>
       </c>
       <c r="AT8" t="n">
-        <v>12.42083769602789</v>
+        <v>18.05488371336993</v>
       </c>
       <c r="AU8" t="n">
-        <v>12.16960510544549</v>
+        <v>19.42649934681551</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.83860301748823</v>
+        <v>16.77818039464064</v>
       </c>
       <c r="AW8" t="n">
-        <v>11.41722769674223</v>
+        <v>16.34608975710697</v>
       </c>
       <c r="AX8" t="n">
-        <v>11.61325302541916</v>
+        <v>16.35004816878453</v>
       </c>
       <c r="AY8" t="n">
-        <v>12.2805860971796</v>
+        <v>16.11671382058608</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12.0727089977013</v>
+        <v>16.48465575225588</v>
       </c>
       <c r="BA8" t="n">
-        <v>11.8242958670911</v>
+        <v>16.7882001504001</v>
       </c>
       <c r="BB8" t="n">
-        <v>12.03239449703791</v>
+        <v>17.68504669972352</v>
       </c>
       <c r="BC8" t="n">
-        <v>12.5819604494736</v>
+        <v>17.03809184061711</v>
       </c>
       <c r="BD8" t="n">
-        <v>11.92922695139741</v>
+        <v>15.99049418842187</v>
       </c>
       <c r="BE8" t="n">
-        <v>12.29603822047059</v>
+        <v>16.80693566210767</v>
       </c>
       <c r="BF8" t="n">
-        <v>12.06191309590737</v>
+        <v>17.27499818611544</v>
       </c>
       <c r="BG8" t="n">
-        <v>11.62572733548905</v>
+        <v>17.67889067597229</v>
       </c>
       <c r="BH8" t="n">
-        <v>12.08166348546796</v>
+        <v>16.3701417450608</v>
       </c>
       <c r="BI8" t="n">
-        <v>12.83723967664008</v>
+        <v>17.26395630182519</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11.99341351247765</v>
+        <v>16.31100539786176</v>
       </c>
       <c r="BK8" t="n">
-        <v>12.03946117285585</v>
+        <v>16.27813207456006</v>
       </c>
       <c r="BL8" t="n">
-        <v>11.81462032842093</v>
+        <v>16.88006361695417</v>
       </c>
       <c r="BM8" t="n">
-        <v>11.36021360409715</v>
+        <v>17.97662965867811</v>
       </c>
       <c r="BN8" t="n">
-        <v>12.04631143777437</v>
+        <v>17.88858432962087</v>
       </c>
       <c r="BO8" t="n">
-        <v>11.77100914674235</v>
+        <v>16.44393477303597</v>
       </c>
       <c r="BP8" t="n">
-        <v>12.88906795328298</v>
+        <v>16.84968098838626</v>
       </c>
       <c r="BQ8" t="n">
-        <v>11.3295744685752</v>
+        <v>16.94088239415584</v>
       </c>
       <c r="BR8" t="n">
-        <v>11.51448358866364</v>
+        <v>16.00317558107644</v>
       </c>
       <c r="BS8" t="n">
-        <v>12.17951535525006</v>
+        <v>16.58706956262423</v>
       </c>
       <c r="BT8" t="n">
-        <v>12.31105606670506</v>
+        <v>19.12925301909613</v>
       </c>
       <c r="BU8" t="n">
-        <v>11.3560220702307</v>
+        <v>18.69673718252821</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.34925084951385</v>
+        <v>17.78487570179301</v>
       </c>
       <c r="BW8" t="n">
-        <v>11.62903755208954</v>
+        <v>16.86640836545363</v>
       </c>
       <c r="BX8" t="n">
-        <v>12.17271580912693</v>
+        <v>17.97472088819348</v>
       </c>
       <c r="BY8" t="n">
-        <v>11.96863696173458</v>
+        <v>17.64106796431834</v>
       </c>
       <c r="BZ8" t="n">
-        <v>12.1380078084252</v>
+        <v>19.89281644091671</v>
       </c>
       <c r="CA8" t="n">
-        <v>11.53373538067712</v>
+        <v>17.49089000103038</v>
       </c>
       <c r="CB8" t="n">
-        <v>11.73425403156823</v>
+        <v>16.64878620689235</v>
       </c>
       <c r="CC8" t="n">
-        <v>12.27849873797169</v>
+        <v>17.57787211716793</v>
       </c>
       <c r="CD8" t="n">
-        <v>11.78072020588715</v>
+        <v>19.38056215060902</v>
       </c>
       <c r="CE8" t="n">
-        <v>12.19827112751591</v>
+        <v>16.91703710457691</v>
       </c>
       <c r="CF8" t="n">
-        <v>11.93951271971934</v>
+        <v>18.18625109612817</v>
       </c>
       <c r="CG8" t="n">
-        <v>11.97851193113704</v>
+        <v>17.6631718740735</v>
       </c>
       <c r="CH8" t="n">
-        <v>12.47746233269036</v>
+        <v>17.15625537556642</v>
       </c>
       <c r="CI8" t="n">
-        <v>11.59178179034206</v>
+        <v>18.77948402361688</v>
       </c>
       <c r="CJ8" t="n">
-        <v>11.8962796693287</v>
+        <v>16.11652046100451</v>
       </c>
       <c r="CK8" t="n">
-        <v>12.19797147615376</v>
+        <v>16.79086726024963</v>
       </c>
       <c r="CL8" t="n">
-        <v>12.53284228640814</v>
+        <v>16.31894329685446</v>
       </c>
       <c r="CM8" t="n">
-        <v>11.8030417977796</v>
+        <v>15.8381671176394</v>
       </c>
       <c r="CN8" t="n">
-        <v>12.06400823992269</v>
+        <v>16.31815804771252</v>
       </c>
       <c r="CO8" t="n">
-        <v>11.66219323832051</v>
+        <v>16.43771712569885</v>
       </c>
       <c r="CP8" t="n">
-        <v>11.59225867066281</v>
+        <v>17.18934064695095</v>
       </c>
       <c r="CQ8" t="n">
-        <v>11.5972555876864</v>
+        <v>18.00497540317932</v>
       </c>
       <c r="CR8" t="n">
-        <v>11.56121993423017</v>
+        <v>17.75152890205916</v>
       </c>
       <c r="CS8" t="n">
-        <v>12.59477222944919</v>
+        <v>17.13259132714626</v>
       </c>
       <c r="CT8" t="n">
-        <v>12.02470920884559</v>
+        <v>16.64223126581371</v>
       </c>
       <c r="CU8" t="n">
-        <v>12.15392177914224</v>
+        <v>16.64657847523081</v>
       </c>
       <c r="CV8" t="n">
-        <v>12.1834596647409</v>
+        <v>18.71115433932723</v>
       </c>
       <c r="CW8" t="n">
-        <v>11.45478240155126</v>
+        <v>19.09894027854924</v>
       </c>
       <c r="CX8" t="n">
-        <v>12.0253236639198</v>
+        <v>17.24324337139425</v>
       </c>
     </row>
     <row r="9">
@@ -3101,307 +3101,307 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.15948427324323</v>
+        <v>18.92556815437303</v>
       </c>
       <c r="C9" t="n">
-        <v>13.42399314840468</v>
+        <v>20.42155648142488</v>
       </c>
       <c r="D9" t="n">
-        <v>12.95867090666482</v>
+        <v>18.85993536809095</v>
       </c>
       <c r="E9" t="n">
-        <v>14.55425996457225</v>
+        <v>17.9367644716417</v>
       </c>
       <c r="F9" t="n">
-        <v>14.29344104268854</v>
+        <v>20.08373491504327</v>
       </c>
       <c r="G9" t="n">
-        <v>13.45026284379102</v>
+        <v>19.41713285919612</v>
       </c>
       <c r="H9" t="n">
-        <v>13.54881794931329</v>
+        <v>19.12730461843174</v>
       </c>
       <c r="I9" t="n">
-        <v>13.35121587549224</v>
+        <v>19.34461870563339</v>
       </c>
       <c r="J9" t="n">
-        <v>14.29575527712166</v>
+        <v>19.66601715571942</v>
       </c>
       <c r="K9" t="n">
-        <v>14.06265298098262</v>
+        <v>19.52343156315776</v>
       </c>
       <c r="L9" t="n">
-        <v>14.47282460322228</v>
+        <v>17.76354834309464</v>
       </c>
       <c r="M9" t="n">
-        <v>15.02177120712996</v>
+        <v>20.29735051784049</v>
       </c>
       <c r="N9" t="n">
-        <v>14.6023325237639</v>
+        <v>19.0612426288647</v>
       </c>
       <c r="O9" t="n">
-        <v>13.05548084750785</v>
+        <v>19.48622281501013</v>
       </c>
       <c r="P9" t="n">
-        <v>14.11443446805032</v>
+        <v>18.68954576364579</v>
       </c>
       <c r="Q9" t="n">
-        <v>13.98870464162028</v>
+        <v>19.44045074253765</v>
       </c>
       <c r="R9" t="n">
-        <v>14.62761942938671</v>
+        <v>20.20795171305245</v>
       </c>
       <c r="S9" t="n">
-        <v>14.57607027336066</v>
+        <v>18.51806028982893</v>
       </c>
       <c r="T9" t="n">
-        <v>13.89316401364993</v>
+        <v>19.92686889987333</v>
       </c>
       <c r="U9" t="n">
-        <v>15.24279302771742</v>
+        <v>20.24806057965144</v>
       </c>
       <c r="V9" t="n">
-        <v>14.89523187558947</v>
+        <v>21.80440911768329</v>
       </c>
       <c r="W9" t="n">
-        <v>13.78857178106163</v>
+        <v>18.3390877034245</v>
       </c>
       <c r="X9" t="n">
-        <v>14.81047058650623</v>
+        <v>18.5272846520166</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.50526463595235</v>
+        <v>19.03136241916674</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.53859981430078</v>
+        <v>22.18919300424418</v>
       </c>
       <c r="AA9" t="n">
-        <v>14.90817888781526</v>
+        <v>19.2392595319021</v>
       </c>
       <c r="AB9" t="n">
-        <v>13.89483909946892</v>
+        <v>19.82223225796585</v>
       </c>
       <c r="AC9" t="n">
-        <v>14.39609716926574</v>
+        <v>18.39583339395753</v>
       </c>
       <c r="AD9" t="n">
-        <v>14.84201095657655</v>
+        <v>18.66148784040695</v>
       </c>
       <c r="AE9" t="n">
-        <v>13.8932678973771</v>
+        <v>18.62798284068007</v>
       </c>
       <c r="AF9" t="n">
-        <v>14.8006178896153</v>
+        <v>19.45687505074595</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.40209870809687</v>
+        <v>19.23625057798155</v>
       </c>
       <c r="AH9" t="n">
-        <v>13.72600383823923</v>
+        <v>18.16413311862469</v>
       </c>
       <c r="AI9" t="n">
-        <v>14.1583721067401</v>
+        <v>17.63013775798846</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13.59838157686974</v>
+        <v>18.14535252092072</v>
       </c>
       <c r="AK9" t="n">
-        <v>14.01143236903662</v>
+        <v>18.93812270028998</v>
       </c>
       <c r="AL9" t="n">
-        <v>14.16288663253381</v>
+        <v>17.66938410486931</v>
       </c>
       <c r="AM9" t="n">
-        <v>13.27360108891492</v>
+        <v>19.71312101437797</v>
       </c>
       <c r="AN9" t="n">
-        <v>14.83230878626572</v>
+        <v>18.36824403141153</v>
       </c>
       <c r="AO9" t="n">
-        <v>13.85588450456671</v>
+        <v>18.37281740730114</v>
       </c>
       <c r="AP9" t="n">
-        <v>14.48447391090476</v>
+        <v>19.01956624383914</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.67388623763624</v>
+        <v>18.27255250657877</v>
       </c>
       <c r="AR9" t="n">
-        <v>13.22899146718139</v>
+        <v>17.74380836415849</v>
       </c>
       <c r="AS9" t="n">
-        <v>13.54286752821091</v>
+        <v>17.7984355673471</v>
       </c>
       <c r="AT9" t="n">
-        <v>14.591396476499</v>
+        <v>20.03395914120529</v>
       </c>
       <c r="AU9" t="n">
-        <v>14.2798385590963</v>
+        <v>21.71241955866265</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.06177160182332</v>
+        <v>18.67489209637852</v>
       </c>
       <c r="AW9" t="n">
-        <v>13.16432539394648</v>
+        <v>17.96090506370247</v>
       </c>
       <c r="AX9" t="n">
-        <v>13.59495207171442</v>
+        <v>18.06680466395155</v>
       </c>
       <c r="AY9" t="n">
-        <v>14.27640352949226</v>
+        <v>17.6257183702718</v>
       </c>
       <c r="AZ9" t="n">
-        <v>14.06672061924416</v>
+        <v>18.45619946705565</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.69671239002546</v>
+        <v>18.61670662848287</v>
       </c>
       <c r="BB9" t="n">
-        <v>14.01035634707787</v>
+        <v>19.59543211670799</v>
       </c>
       <c r="BC9" t="n">
-        <v>14.71818493602703</v>
+        <v>18.79701764128131</v>
       </c>
       <c r="BD9" t="n">
-        <v>13.95296428780148</v>
+        <v>17.69089716991663</v>
       </c>
       <c r="BE9" t="n">
-        <v>14.31838826790546</v>
+        <v>18.58596491452768</v>
       </c>
       <c r="BF9" t="n">
-        <v>14.10004557623502</v>
+        <v>19.2583034094839</v>
       </c>
       <c r="BG9" t="n">
-        <v>13.67063519206997</v>
+        <v>19.81370618539942</v>
       </c>
       <c r="BH9" t="n">
-        <v>13.92701164851305</v>
+        <v>18.11511553384964</v>
       </c>
       <c r="BI9" t="n">
-        <v>15.0570210863032</v>
+        <v>19.06285983248557</v>
       </c>
       <c r="BJ9" t="n">
-        <v>13.83891274375009</v>
+        <v>17.93886353912713</v>
       </c>
       <c r="BK9" t="n">
-        <v>14.03961574893923</v>
+        <v>18.08943094304706</v>
       </c>
       <c r="BL9" t="n">
-        <v>13.88199683953498</v>
+        <v>18.77099521034791</v>
       </c>
       <c r="BM9" t="n">
-        <v>13.2213585254184</v>
+        <v>20.12571312574975</v>
       </c>
       <c r="BN9" t="n">
-        <v>14.0283845659155</v>
+        <v>19.98531964734589</v>
       </c>
       <c r="BO9" t="n">
-        <v>13.76279560873725</v>
+        <v>18.1701668200619</v>
       </c>
       <c r="BP9" t="n">
-        <v>15.18979148985099</v>
+        <v>18.61128017071944</v>
       </c>
       <c r="BQ9" t="n">
-        <v>13.02489210153947</v>
+        <v>18.67839052696905</v>
       </c>
       <c r="BR9" t="n">
-        <v>13.312524542723</v>
+        <v>17.62925889289663</v>
       </c>
       <c r="BS9" t="n">
-        <v>14.14843705271386</v>
+        <v>18.51641015449103</v>
       </c>
       <c r="BT9" t="n">
-        <v>14.34327600563041</v>
+        <v>21.47096313387494</v>
       </c>
       <c r="BU9" t="n">
-        <v>13.12120318217831</v>
+        <v>20.82005034597163</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.43832342693322</v>
+        <v>19.69897203169221</v>
       </c>
       <c r="BW9" t="n">
-        <v>13.43103213459058</v>
+        <v>18.89200403666067</v>
       </c>
       <c r="BX9" t="n">
-        <v>14.14531767758074</v>
+        <v>20.08858398089452</v>
       </c>
       <c r="BY9" t="n">
-        <v>14.04080209030382</v>
+        <v>19.66383191607395</v>
       </c>
       <c r="BZ9" t="n">
-        <v>14.12805875771243</v>
+        <v>22.31132173565848</v>
       </c>
       <c r="CA9" t="n">
-        <v>13.25738857031256</v>
+        <v>19.56181121009136</v>
       </c>
       <c r="CB9" t="n">
-        <v>13.73790633028275</v>
+        <v>18.31570127807276</v>
       </c>
       <c r="CC9" t="n">
-        <v>14.34370728678502</v>
+        <v>19.62070591892214</v>
       </c>
       <c r="CD9" t="n">
-        <v>13.6925509902762</v>
+        <v>21.64414148352776</v>
       </c>
       <c r="CE9" t="n">
-        <v>14.19309965421123</v>
+        <v>18.82756021103426</v>
       </c>
       <c r="CF9" t="n">
-        <v>14.03993864934659</v>
+        <v>20.45631040544618</v>
       </c>
       <c r="CG9" t="n">
-        <v>13.9323617170318</v>
+        <v>19.91663590549518</v>
       </c>
       <c r="CH9" t="n">
-        <v>14.54771847420597</v>
+        <v>19.06531636090937</v>
       </c>
       <c r="CI9" t="n">
-        <v>13.48108231412985</v>
+        <v>20.96449450308505</v>
       </c>
       <c r="CJ9" t="n">
-        <v>13.90832310209306</v>
+        <v>17.74292142575835</v>
       </c>
       <c r="CK9" t="n">
-        <v>14.20413367621072</v>
+        <v>18.72878949648261</v>
       </c>
       <c r="CL9" t="n">
-        <v>14.75386736369813</v>
+        <v>18.05913857522105</v>
       </c>
       <c r="CM9" t="n">
-        <v>13.83596798504671</v>
+        <v>17.45586888572952</v>
       </c>
       <c r="CN9" t="n">
-        <v>14.06234903192361</v>
+        <v>18.00137231690561</v>
       </c>
       <c r="CO9" t="n">
-        <v>13.54029273083878</v>
+        <v>18.39226745261023</v>
       </c>
       <c r="CP9" t="n">
-        <v>13.2598113172176</v>
+        <v>19.15138345176118</v>
       </c>
       <c r="CQ9" t="n">
-        <v>13.34529240522143</v>
+        <v>20.02926232103463</v>
       </c>
       <c r="CR9" t="n">
-        <v>13.47749349126929</v>
+        <v>19.66136729016989</v>
       </c>
       <c r="CS9" t="n">
-        <v>14.75771202472437</v>
+        <v>18.99203312119293</v>
       </c>
       <c r="CT9" t="n">
-        <v>14.23111098949983</v>
+        <v>18.41604417948056</v>
       </c>
       <c r="CU9" t="n">
-        <v>14.16177195884766</v>
+        <v>18.43447910037131</v>
       </c>
       <c r="CV9" t="n">
-        <v>14.28215149780635</v>
+        <v>20.86376847266727</v>
       </c>
       <c r="CW9" t="n">
-        <v>13.28507613494897</v>
+        <v>21.31986504010961</v>
       </c>
       <c r="CX9" t="n">
-        <v>14.02832646820165</v>
+        <v>19.15261996725019</v>
       </c>
     </row>
     <row r="10">
@@ -3409,307 +3409,307 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.17082187996641</v>
+        <v>14.0434100353985</v>
       </c>
       <c r="C10" t="n">
-        <v>15.54821259866379</v>
+        <v>14.98397342345215</v>
       </c>
       <c r="D10" t="n">
-        <v>14.94819484509037</v>
+        <v>14.07845842844011</v>
       </c>
       <c r="E10" t="n">
-        <v>16.84519772623807</v>
+        <v>13.54325866746996</v>
       </c>
       <c r="F10" t="n">
-        <v>16.69308468929327</v>
+        <v>14.80480446742711</v>
       </c>
       <c r="G10" t="n">
-        <v>15.43955277104618</v>
+        <v>14.37667411108212</v>
       </c>
       <c r="H10" t="n">
-        <v>15.59713707989472</v>
+        <v>14.1950606032735</v>
       </c>
       <c r="I10" t="n">
-        <v>15.42460275040458</v>
+        <v>14.47852061792068</v>
       </c>
       <c r="J10" t="n">
-        <v>16.48839257914298</v>
+        <v>14.45381984568183</v>
       </c>
       <c r="K10" t="n">
-        <v>16.31826059875823</v>
+        <v>14.38278058180254</v>
       </c>
       <c r="L10" t="n">
-        <v>16.61969083347012</v>
+        <v>13.34616299836537</v>
       </c>
       <c r="M10" t="n">
-        <v>17.35285839206314</v>
+        <v>15.01303315549786</v>
       </c>
       <c r="N10" t="n">
-        <v>16.92701045394896</v>
+        <v>14.21215283080444</v>
       </c>
       <c r="O10" t="n">
-        <v>15.07537723541303</v>
+        <v>14.4412829274986</v>
       </c>
       <c r="P10" t="n">
-        <v>16.30966115369083</v>
+        <v>13.92748526648104</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.17522071480007</v>
+        <v>14.49923549448029</v>
       </c>
       <c r="R10" t="n">
-        <v>16.89714078442641</v>
+        <v>14.95072162870932</v>
       </c>
       <c r="S10" t="n">
-        <v>16.96658467196474</v>
+        <v>14.03619418977228</v>
       </c>
       <c r="T10" t="n">
-        <v>16.15766838891113</v>
+        <v>14.82964268434456</v>
       </c>
       <c r="U10" t="n">
-        <v>17.56442957743953</v>
+        <v>14.97331164338404</v>
       </c>
       <c r="V10" t="n">
-        <v>17.2248866805208</v>
+        <v>15.87349574836202</v>
       </c>
       <c r="W10" t="n">
-        <v>15.98657893732242</v>
+        <v>13.87354804760971</v>
       </c>
       <c r="X10" t="n">
-        <v>17.17596368000505</v>
+        <v>13.86010792153858</v>
       </c>
       <c r="Y10" t="n">
-        <v>16.97856247787539</v>
+        <v>14.36362668409268</v>
       </c>
       <c r="Z10" t="n">
-        <v>15.84036937365684</v>
+        <v>16.03938165794861</v>
       </c>
       <c r="AA10" t="n">
-        <v>17.31959917710661</v>
+        <v>14.37719443736537</v>
       </c>
       <c r="AB10" t="n">
-        <v>16.01855234936711</v>
+        <v>14.74901174539477</v>
       </c>
       <c r="AC10" t="n">
-        <v>16.63304845412918</v>
+        <v>13.80647504445557</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.17737452610774</v>
+        <v>13.86221867910271</v>
       </c>
       <c r="AE10" t="n">
-        <v>16.1511491694969</v>
+        <v>13.83221646926092</v>
       </c>
       <c r="AF10" t="n">
-        <v>17.16561870802175</v>
+        <v>14.43031680564217</v>
       </c>
       <c r="AG10" t="n">
-        <v>16.68927285174651</v>
+        <v>14.4091503251386</v>
       </c>
       <c r="AH10" t="n">
-        <v>15.95095478093021</v>
+        <v>13.70579681738506</v>
       </c>
       <c r="AI10" t="n">
-        <v>16.36190915662754</v>
+        <v>13.46447341420416</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.65258083438518</v>
+        <v>13.7160462634174</v>
       </c>
       <c r="AK10" t="n">
-        <v>16.19625022450765</v>
+        <v>14.18649976329247</v>
       </c>
       <c r="AL10" t="n">
-        <v>16.37338171175347</v>
+        <v>13.30185672447271</v>
       </c>
       <c r="AM10" t="n">
-        <v>15.42945463086355</v>
+        <v>14.69268887960213</v>
       </c>
       <c r="AN10" t="n">
-        <v>17.209024978409</v>
+        <v>13.94709076813484</v>
       </c>
       <c r="AO10" t="n">
-        <v>16.04189287299039</v>
+        <v>13.70414748124193</v>
       </c>
       <c r="AP10" t="n">
-        <v>16.8466729446357</v>
+        <v>14.26015047606507</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15.97974586473346</v>
+        <v>13.78502385711778</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.06629477084724</v>
+        <v>13.5050784992518</v>
       </c>
       <c r="AS10" t="n">
-        <v>15.682254421939</v>
+        <v>13.47599913225201</v>
       </c>
       <c r="AT10" t="n">
-        <v>16.90771743097217</v>
+        <v>14.76820491301279</v>
       </c>
       <c r="AU10" t="n">
-        <v>16.69884634946983</v>
+        <v>15.84055811288454</v>
       </c>
       <c r="AV10" t="n">
-        <v>17.49667956933639</v>
+        <v>13.96375102667591</v>
       </c>
       <c r="AW10" t="n">
-        <v>15.14952916793046</v>
+        <v>13.45781716476936</v>
       </c>
       <c r="AX10" t="n">
-        <v>15.83258061754338</v>
+        <v>13.66480885073276</v>
       </c>
       <c r="AY10" t="n">
-        <v>16.39947640064932</v>
+        <v>13.3520633020679</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.3092327446649</v>
+        <v>13.86453560368473</v>
       </c>
       <c r="BA10" t="n">
-        <v>15.69806827843304</v>
+        <v>14.11783632885745</v>
       </c>
       <c r="BB10" t="n">
-        <v>16.20453240217947</v>
+        <v>14.48433256432983</v>
       </c>
       <c r="BC10" t="n">
-        <v>17.02283463323858</v>
+        <v>14.12341265581757</v>
       </c>
       <c r="BD10" t="n">
-        <v>16.27190822220788</v>
+        <v>13.52168967040766</v>
       </c>
       <c r="BE10" t="n">
-        <v>16.57770517838298</v>
+        <v>14.12150806527133</v>
       </c>
       <c r="BF10" t="n">
-        <v>16.26503198427742</v>
+        <v>14.46014230089719</v>
       </c>
       <c r="BG10" t="n">
-        <v>15.90793340256015</v>
+        <v>14.64916800387287</v>
       </c>
       <c r="BH10" t="n">
-        <v>15.85970676775382</v>
+        <v>13.61207918153766</v>
       </c>
       <c r="BI10" t="n">
-        <v>17.44276931830925</v>
+        <v>14.23800224785726</v>
       </c>
       <c r="BJ10" t="n">
-        <v>15.83392400638834</v>
+        <v>13.44423959401963</v>
       </c>
       <c r="BK10" t="n">
-        <v>16.34699528057283</v>
+        <v>13.58352995829817</v>
       </c>
       <c r="BL10" t="n">
-        <v>16.26593059823283</v>
+        <v>13.94534325722129</v>
       </c>
       <c r="BM10" t="n">
-        <v>15.36505434471842</v>
+        <v>14.81646763015356</v>
       </c>
       <c r="BN10" t="n">
-        <v>16.24823096276785</v>
+        <v>14.82325150678991</v>
       </c>
       <c r="BO10" t="n">
-        <v>15.85435769397706</v>
+        <v>13.69460489355665</v>
       </c>
       <c r="BP10" t="n">
-        <v>17.63917419897907</v>
+        <v>14.04754319323338</v>
       </c>
       <c r="BQ10" t="n">
-        <v>14.89354790265652</v>
+        <v>14.07350060253366</v>
       </c>
       <c r="BR10" t="n">
-        <v>15.29291341554331</v>
+        <v>13.35903371076805</v>
       </c>
       <c r="BS10" t="n">
-        <v>16.22893988947319</v>
+        <v>13.82031768708545</v>
       </c>
       <c r="BT10" t="n">
-        <v>16.50287222640061</v>
+        <v>15.67970856902074</v>
       </c>
       <c r="BU10" t="n">
-        <v>15.0911387121539</v>
+        <v>15.19172105514782</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.75853654305489</v>
+        <v>14.52657716804357</v>
       </c>
       <c r="BW10" t="n">
-        <v>15.4042583373545</v>
+        <v>14.12148843031725</v>
       </c>
       <c r="BX10" t="n">
-        <v>16.25632711817913</v>
+        <v>14.94684372527754</v>
       </c>
       <c r="BY10" t="n">
-        <v>16.29860745027795</v>
+        <v>14.47837335576505</v>
       </c>
       <c r="BZ10" t="n">
-        <v>16.35671230354162</v>
+        <v>16.15855601176712</v>
       </c>
       <c r="CA10" t="n">
-        <v>15.27022219646649</v>
+        <v>14.62216994200608</v>
       </c>
       <c r="CB10" t="n">
-        <v>15.87659964619957</v>
+        <v>13.63598473813607</v>
       </c>
       <c r="CC10" t="n">
-        <v>16.69643826679723</v>
+        <v>14.4863844170317</v>
       </c>
       <c r="CD10" t="n">
-        <v>15.7932632068024</v>
+        <v>15.65594045710093</v>
       </c>
       <c r="CE10" t="n">
-        <v>16.2489052079243</v>
+        <v>14.06786537071129</v>
       </c>
       <c r="CF10" t="n">
-        <v>16.30929686587801</v>
+        <v>15.21675562160612</v>
       </c>
       <c r="CG10" t="n">
-        <v>16.06645103491506</v>
+        <v>14.77638287138917</v>
       </c>
       <c r="CH10" t="n">
-        <v>16.81447180235786</v>
+        <v>14.20822583998745</v>
       </c>
       <c r="CI10" t="n">
-        <v>15.49369420247682</v>
+        <v>15.34945845878916</v>
       </c>
       <c r="CJ10" t="n">
-        <v>16.03300643917296</v>
+        <v>13.35582339577516</v>
       </c>
       <c r="CK10" t="n">
-        <v>16.30160882901866</v>
+        <v>14.08782430153862</v>
       </c>
       <c r="CL10" t="n">
-        <v>17.145196057764</v>
+        <v>13.52302484728543</v>
       </c>
       <c r="CM10" t="n">
-        <v>16.08297944211911</v>
+        <v>13.35961294191355</v>
       </c>
       <c r="CN10" t="n">
-        <v>16.34249042493629</v>
+        <v>13.66424925454134</v>
       </c>
       <c r="CO10" t="n">
-        <v>15.64000824750292</v>
+        <v>13.89072863243404</v>
       </c>
       <c r="CP10" t="n">
-        <v>15.14760864700648</v>
+        <v>14.24808479677987</v>
       </c>
       <c r="CQ10" t="n">
-        <v>15.28341364860711</v>
+        <v>14.62309278484807</v>
       </c>
       <c r="CR10" t="n">
-        <v>15.70292493141891</v>
+        <v>14.54571143079934</v>
       </c>
       <c r="CS10" t="n">
-        <v>17.0453438775487</v>
+        <v>14.19496242850308</v>
       </c>
       <c r="CT10" t="n">
-        <v>16.64763846203412</v>
+        <v>13.83365963838617</v>
       </c>
       <c r="CU10" t="n">
-        <v>16.3928237614355</v>
+        <v>13.77220223210032</v>
       </c>
       <c r="CV10" t="n">
-        <v>16.49601801621058</v>
+        <v>15.19674760339357</v>
       </c>
       <c r="CW10" t="n">
-        <v>15.30311056887368</v>
+        <v>15.6523276255493</v>
       </c>
       <c r="CX10" t="n">
-        <v>16.22486080538253</v>
+        <v>14.27709809215918</v>
       </c>
     </row>
     <row r="11">
@@ -3717,307 +3717,307 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17.32473208093094</v>
+        <v>14.29335318342269</v>
       </c>
       <c r="C11" t="n">
-        <v>17.80268531705556</v>
+        <v>15.45426984369455</v>
       </c>
       <c r="D11" t="n">
-        <v>17.08653789239716</v>
+        <v>14.36381321615649</v>
       </c>
       <c r="E11" t="n">
-        <v>19.26164481753187</v>
+        <v>13.71194255801365</v>
       </c>
       <c r="F11" t="n">
-        <v>19.13101408841268</v>
+        <v>15.31672699032957</v>
       </c>
       <c r="G11" t="n">
-        <v>17.6249894309466</v>
+        <v>14.83360894506971</v>
       </c>
       <c r="H11" t="n">
-        <v>17.86070083781928</v>
+        <v>14.48571682859281</v>
       </c>
       <c r="I11" t="n">
-        <v>17.70024472152195</v>
+        <v>14.71368846299597</v>
       </c>
       <c r="J11" t="n">
-        <v>18.79036871871827</v>
+        <v>14.78257769940297</v>
       </c>
       <c r="K11" t="n">
-        <v>18.74663705392751</v>
+        <v>14.52787307501317</v>
       </c>
       <c r="L11" t="n">
-        <v>18.76229639836982</v>
+        <v>13.51943165068789</v>
       </c>
       <c r="M11" t="n">
-        <v>19.81421838506598</v>
+        <v>15.50600794770835</v>
       </c>
       <c r="N11" t="n">
-        <v>19.35337524587905</v>
+        <v>14.4539278379293</v>
       </c>
       <c r="O11" t="n">
-        <v>17.25437743964226</v>
+        <v>14.77855253381555</v>
       </c>
       <c r="P11" t="n">
-        <v>18.55459895144904</v>
+        <v>14.19148704163005</v>
       </c>
       <c r="Q11" t="n">
-        <v>18.59408466924196</v>
+        <v>14.78684830191644</v>
       </c>
       <c r="R11" t="n">
-        <v>19.42443736870399</v>
+        <v>15.46763142994935</v>
       </c>
       <c r="S11" t="n">
-        <v>19.47898759290825</v>
+        <v>14.16996713195296</v>
       </c>
       <c r="T11" t="n">
-        <v>18.44439479172244</v>
+        <v>15.2195241501321</v>
       </c>
       <c r="U11" t="n">
-        <v>19.95241066601364</v>
+        <v>15.5204200040067</v>
       </c>
       <c r="V11" t="n">
-        <v>19.71478506261647</v>
+        <v>16.60749941944215</v>
       </c>
       <c r="W11" t="n">
-        <v>18.3724622872764</v>
+        <v>14.02851692272508</v>
       </c>
       <c r="X11" t="n">
-        <v>19.68988045531655</v>
+        <v>14.04811260690184</v>
       </c>
       <c r="Y11" t="n">
-        <v>19.52241692504082</v>
+        <v>14.86511322889899</v>
       </c>
       <c r="Z11" t="n">
-        <v>18.30716266217521</v>
+        <v>16.79169492371294</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.89809159836663</v>
+        <v>14.67040320671572</v>
       </c>
       <c r="AB11" t="n">
-        <v>18.29062798830561</v>
+        <v>15.26566629223169</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.94933122173496</v>
+        <v>13.94487201832325</v>
       </c>
       <c r="AD11" t="n">
-        <v>19.68893598011913</v>
+        <v>14.07644584564641</v>
       </c>
       <c r="AE11" t="n">
-        <v>18.50281714609429</v>
+        <v>13.93935459622538</v>
       </c>
       <c r="AF11" t="n">
-        <v>19.60670968847019</v>
+        <v>14.79034332374356</v>
       </c>
       <c r="AG11" t="n">
-        <v>19.06768848186982</v>
+        <v>14.72470367223762</v>
       </c>
       <c r="AH11" t="n">
-        <v>18.37170623648682</v>
+        <v>13.94984947918378</v>
       </c>
       <c r="AI11" t="n">
-        <v>18.84422335810601</v>
+        <v>13.61954046408994</v>
       </c>
       <c r="AJ11" t="n">
-        <v>17.77197026206296</v>
+        <v>13.89948582195592</v>
       </c>
       <c r="AK11" t="n">
-        <v>18.47887952291174</v>
+        <v>14.66659402562325</v>
       </c>
       <c r="AL11" t="n">
-        <v>18.68195209285287</v>
+        <v>13.42575328474866</v>
       </c>
       <c r="AM11" t="n">
-        <v>17.68659042845275</v>
+        <v>15.18815731098141</v>
       </c>
       <c r="AN11" t="n">
-        <v>19.65664081801448</v>
+        <v>14.20743062434701</v>
       </c>
       <c r="AO11" t="n">
-        <v>18.37863778963598</v>
+        <v>13.82094600561617</v>
       </c>
       <c r="AP11" t="n">
-        <v>19.3365865508589</v>
+        <v>14.69019524043334</v>
       </c>
       <c r="AQ11" t="n">
-        <v>18.33639416674427</v>
+        <v>14.04004264077293</v>
       </c>
       <c r="AR11" t="n">
-        <v>17.04045887812867</v>
+        <v>13.64943468168425</v>
       </c>
       <c r="AS11" t="n">
-        <v>17.93338620774593</v>
+        <v>13.72941766714924</v>
       </c>
       <c r="AT11" t="n">
-        <v>19.41258154623706</v>
+        <v>15.19613891981693</v>
       </c>
       <c r="AU11" t="n">
-        <v>19.28086392761012</v>
+        <v>16.54534497228628</v>
       </c>
       <c r="AV11" t="n">
-        <v>20.10347367822261</v>
+        <v>14.34605340018666</v>
       </c>
       <c r="AW11" t="n">
-        <v>17.21338820245911</v>
+        <v>13.55483347290303</v>
       </c>
       <c r="AX11" t="n">
-        <v>18.31766993636057</v>
+        <v>13.86519337464658</v>
       </c>
       <c r="AY11" t="n">
-        <v>18.7155551587162</v>
+        <v>13.38668954359668</v>
       </c>
       <c r="AZ11" t="n">
-        <v>18.71546680722419</v>
+        <v>14.19820219592709</v>
       </c>
       <c r="BA11" t="n">
-        <v>18.01081068278074</v>
+        <v>14.42269844345721</v>
       </c>
       <c r="BB11" t="n">
-        <v>18.48231510253457</v>
+        <v>14.8531162719531</v>
       </c>
       <c r="BC11" t="n">
-        <v>19.43173081711462</v>
+        <v>14.3462693846816</v>
       </c>
       <c r="BD11" t="n">
-        <v>18.68569384439455</v>
+        <v>13.66719449765408</v>
       </c>
       <c r="BE11" t="n">
-        <v>18.93133327346172</v>
+        <v>14.33124864480662</v>
       </c>
       <c r="BF11" t="n">
-        <v>18.56455051884539</v>
+        <v>14.82756137921155</v>
       </c>
       <c r="BG11" t="n">
-        <v>18.25062275612659</v>
+        <v>15.18135379939098</v>
       </c>
       <c r="BH11" t="n">
-        <v>17.91108642912545</v>
+        <v>13.82982100486256</v>
       </c>
       <c r="BI11" t="n">
-        <v>19.99142669603853</v>
+        <v>14.4616934622699</v>
       </c>
       <c r="BJ11" t="n">
-        <v>18.11251292766253</v>
+        <v>13.56444478292761</v>
       </c>
       <c r="BK11" t="n">
-        <v>18.86572715605343</v>
+        <v>13.89243687343943</v>
       </c>
       <c r="BL11" t="n">
-        <v>18.76919076524149</v>
+        <v>14.27204925824054</v>
       </c>
       <c r="BM11" t="n">
-        <v>17.63338257838989</v>
+        <v>15.40792153457706</v>
       </c>
       <c r="BN11" t="n">
-        <v>18.55486127144223</v>
+        <v>15.24659093433818</v>
       </c>
       <c r="BO11" t="n">
-        <v>18.04498725507843</v>
+        <v>13.87736704617924</v>
       </c>
       <c r="BP11" t="n">
-        <v>20.1428129481793</v>
+        <v>14.29003487618234</v>
       </c>
       <c r="BQ11" t="n">
-        <v>16.85273324734626</v>
+        <v>14.31983091900623</v>
       </c>
       <c r="BR11" t="n">
-        <v>17.388924250801</v>
+        <v>13.42249388237056</v>
       </c>
       <c r="BS11" t="n">
-        <v>18.36843955064852</v>
+        <v>14.14945842241124</v>
       </c>
       <c r="BT11" t="n">
-        <v>18.76569304998928</v>
+        <v>16.37061351588444</v>
       </c>
       <c r="BU11" t="n">
-        <v>17.2767073618061</v>
+        <v>15.72644957721993</v>
       </c>
       <c r="BV11" t="n">
-        <v>19.14441258649152</v>
+        <v>14.83948961381815</v>
       </c>
       <c r="BW11" t="n">
-        <v>17.55024018404357</v>
+        <v>14.53074959578661</v>
       </c>
       <c r="BX11" t="n">
-        <v>18.51032646833216</v>
+        <v>15.52285473831323</v>
       </c>
       <c r="BY11" t="n">
-        <v>18.68544908835423</v>
+        <v>14.84445725720164</v>
       </c>
       <c r="BZ11" t="n">
-        <v>18.74124157078975</v>
+        <v>16.90674593717362</v>
       </c>
       <c r="CA11" t="n">
-        <v>17.35223016208764</v>
+        <v>15.16148322585702</v>
       </c>
       <c r="CB11" t="n">
-        <v>18.18904308154492</v>
+        <v>13.70289084418049</v>
       </c>
       <c r="CC11" t="n">
-        <v>19.13418750199229</v>
+        <v>14.94145393038123</v>
       </c>
       <c r="CD11" t="n">
-        <v>17.98880621438951</v>
+        <v>16.26751037198444</v>
       </c>
       <c r="CE11" t="n">
-        <v>18.37072869572826</v>
+        <v>14.4193212313546</v>
       </c>
       <c r="CF11" t="n">
-        <v>18.8408914889207</v>
+        <v>15.84005742155538</v>
       </c>
       <c r="CG11" t="n">
-        <v>18.28274284243946</v>
+        <v>15.40708704902845</v>
       </c>
       <c r="CH11" t="n">
-        <v>19.17462979368913</v>
+        <v>14.55332979298429</v>
       </c>
       <c r="CI11" t="n">
-        <v>17.75999652642303</v>
+        <v>15.89893283137906</v>
       </c>
       <c r="CJ11" t="n">
-        <v>18.45869975223782</v>
+        <v>13.39034164505648</v>
       </c>
       <c r="CK11" t="n">
-        <v>18.54902222991554</v>
+        <v>14.39622070787368</v>
       </c>
       <c r="CL11" t="n">
-        <v>19.6832972454312</v>
+        <v>13.72167167776274</v>
       </c>
       <c r="CM11" t="n">
-        <v>18.52998780531762</v>
+        <v>13.47559661569327</v>
       </c>
       <c r="CN11" t="n">
-        <v>18.68366787171441</v>
+        <v>13.87159436967826</v>
       </c>
       <c r="CO11" t="n">
-        <v>17.79544249364985</v>
+        <v>14.28340807917867</v>
       </c>
       <c r="CP11" t="n">
-        <v>17.33364432498453</v>
+        <v>14.64653692002548</v>
       </c>
       <c r="CQ11" t="n">
-        <v>17.4559620062714</v>
+        <v>15.00016244309518</v>
       </c>
       <c r="CR11" t="n">
-        <v>18.07751373718585</v>
+        <v>14.85707271520121</v>
       </c>
       <c r="CS11" t="n">
-        <v>19.53333015144519</v>
+        <v>14.4333994934335</v>
       </c>
       <c r="CT11" t="n">
-        <v>19.29226465388023</v>
+        <v>14.00766460148687</v>
       </c>
       <c r="CU11" t="n">
-        <v>18.82067188647517</v>
+        <v>14.00297184746057</v>
       </c>
       <c r="CV11" t="n">
-        <v>18.95885628896854</v>
+        <v>15.72144266392828</v>
       </c>
       <c r="CW11" t="n">
-        <v>17.37215644139649</v>
+        <v>16.2107948071101</v>
       </c>
       <c r="CX11" t="n">
-        <v>18.56155057111637</v>
+        <v>14.6114528895422</v>
       </c>
     </row>
     <row r="12">
@@ -4025,307 +4025,307 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19.53844521585308</v>
+        <v>16.13664340300834</v>
       </c>
       <c r="C12" t="n">
-        <v>20.33796237127201</v>
+        <v>17.56692218089438</v>
       </c>
       <c r="D12" t="n">
-        <v>19.50803187004042</v>
+        <v>16.22789685211808</v>
       </c>
       <c r="E12" t="n">
-        <v>21.64764905315334</v>
+        <v>15.38561622673657</v>
       </c>
       <c r="F12" t="n">
-        <v>21.58049045616213</v>
+        <v>17.41102064545999</v>
       </c>
       <c r="G12" t="n">
-        <v>19.98272903238281</v>
+        <v>16.91841891737711</v>
       </c>
       <c r="H12" t="n">
-        <v>20.10374298642253</v>
+        <v>16.45961876275145</v>
       </c>
       <c r="I12" t="n">
-        <v>20.10311637168496</v>
+        <v>16.48094232288769</v>
       </c>
       <c r="J12" t="n">
-        <v>21.16475728443968</v>
+        <v>16.81758361067392</v>
       </c>
       <c r="K12" t="n">
-        <v>21.21898873642796</v>
+        <v>16.21710744484841</v>
       </c>
       <c r="L12" t="n">
-        <v>20.95545700117064</v>
+        <v>15.29084812084562</v>
       </c>
       <c r="M12" t="n">
-        <v>22.27575372995368</v>
+        <v>17.59365517088103</v>
       </c>
       <c r="N12" t="n">
-        <v>21.80356071930398</v>
+        <v>16.35499390990987</v>
       </c>
       <c r="O12" t="n">
-        <v>19.62812240086195</v>
+        <v>16.77905983075928</v>
       </c>
       <c r="P12" t="n">
-        <v>21.09421695483485</v>
+        <v>15.99332787314239</v>
       </c>
       <c r="Q12" t="n">
-        <v>21.07793959901045</v>
+        <v>16.66969313650618</v>
       </c>
       <c r="R12" t="n">
-        <v>21.96087367256847</v>
+        <v>17.65061617268143</v>
       </c>
       <c r="S12" t="n">
-        <v>22.09651613011599</v>
+        <v>15.81347169372437</v>
       </c>
       <c r="T12" t="n">
-        <v>20.83846484733299</v>
+        <v>17.27442026989109</v>
       </c>
       <c r="U12" t="n">
-        <v>22.35776622800095</v>
+        <v>17.8322885853523</v>
       </c>
       <c r="V12" t="n">
-        <v>22.24951720871741</v>
+        <v>19.01072944214496</v>
       </c>
       <c r="W12" t="n">
-        <v>20.92513761813091</v>
+        <v>15.78347930135963</v>
       </c>
       <c r="X12" t="n">
-        <v>22.37232152631339</v>
+        <v>15.80552935479701</v>
       </c>
       <c r="Y12" t="n">
-        <v>22.10366848361529</v>
+        <v>17.03825104215748</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.82743328784456</v>
+        <v>19.19673136219156</v>
       </c>
       <c r="AA12" t="n">
-        <v>22.46721812098008</v>
+        <v>16.5790091010649</v>
       </c>
       <c r="AB12" t="n">
-        <v>20.67528014277087</v>
+        <v>17.3990236885141</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.50108441779683</v>
+        <v>15.62136330295736</v>
       </c>
       <c r="AD12" t="n">
-        <v>22.09177645423707</v>
+        <v>15.90908410264097</v>
       </c>
       <c r="AE12" t="n">
-        <v>20.99585469949577</v>
+        <v>15.64629969464522</v>
       </c>
       <c r="AF12" t="n">
-        <v>22.08161678710714</v>
+        <v>16.72822493463338</v>
       </c>
       <c r="AG12" t="n">
-        <v>21.51156926345998</v>
+        <v>16.61116133837899</v>
       </c>
       <c r="AH12" t="n">
-        <v>20.85098143460039</v>
+        <v>15.77500681867198</v>
       </c>
       <c r="AI12" t="n">
-        <v>21.25154442924273</v>
+        <v>15.36013987381136</v>
       </c>
       <c r="AJ12" t="n">
-        <v>19.97240443350656</v>
+        <v>15.69777272677888</v>
       </c>
       <c r="AK12" t="n">
-        <v>20.86175821344812</v>
+        <v>16.84013435544048</v>
       </c>
       <c r="AL12" t="n">
-        <v>21.11781683067512</v>
+        <v>15.12081923594712</v>
       </c>
       <c r="AM12" t="n">
-        <v>20.06980032545974</v>
+        <v>17.33901926883053</v>
       </c>
       <c r="AN12" t="n">
-        <v>22.18029908599438</v>
+        <v>16.04655823366665</v>
       </c>
       <c r="AO12" t="n">
-        <v>20.8617659282612</v>
+        <v>15.5618006697407</v>
       </c>
       <c r="AP12" t="n">
-        <v>21.86300241611826</v>
+        <v>16.76199705565947</v>
       </c>
       <c r="AQ12" t="n">
-        <v>20.77745234865662</v>
+        <v>15.90554981090568</v>
       </c>
       <c r="AR12" t="n">
-        <v>19.11067943848652</v>
+        <v>15.39527662414636</v>
       </c>
       <c r="AS12" t="n">
-        <v>20.3060119731866</v>
+        <v>15.60265119171441</v>
       </c>
       <c r="AT12" t="n">
-        <v>21.91871545689737</v>
+        <v>17.27198553558456</v>
       </c>
       <c r="AU12" t="n">
-        <v>21.94169864722109</v>
+        <v>18.88124673743185</v>
       </c>
       <c r="AV12" t="n">
-        <v>22.73844477153779</v>
+        <v>16.30267657475056</v>
       </c>
       <c r="AW12" t="n">
-        <v>19.3747093644828</v>
+        <v>15.22150728049467</v>
       </c>
       <c r="AX12" t="n">
-        <v>20.77225248390826</v>
+        <v>15.62899148261935</v>
       </c>
       <c r="AY12" t="n">
-        <v>20.98316268464937</v>
+        <v>14.98192157075028</v>
       </c>
       <c r="AZ12" t="n">
-        <v>21.22817310625793</v>
+        <v>16.02506777642069</v>
       </c>
       <c r="BA12" t="n">
-        <v>20.48121267864479</v>
+        <v>16.37827114797756</v>
       </c>
       <c r="BB12" t="n">
-        <v>20.90324117110119</v>
+        <v>16.89882323320035</v>
       </c>
       <c r="BC12" t="n">
-        <v>21.90214964915866</v>
+        <v>16.2076041270713</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.23564507349455</v>
+        <v>15.39993010826449</v>
       </c>
       <c r="BE12" t="n">
-        <v>21.43309731564268</v>
+        <v>16.12086671740109</v>
       </c>
       <c r="BF12" t="n">
-        <v>20.93430986406197</v>
+        <v>16.78792501252862</v>
       </c>
       <c r="BG12" t="n">
-        <v>20.69702245934745</v>
+        <v>17.40910623743671</v>
       </c>
       <c r="BH12" t="n">
-        <v>20.11350854670408</v>
+        <v>15.68308578112335</v>
       </c>
       <c r="BI12" t="n">
-        <v>22.50992031098365</v>
+        <v>16.25066358137956</v>
       </c>
       <c r="BJ12" t="n">
-        <v>20.35750926683032</v>
+        <v>15.25101861648433</v>
       </c>
       <c r="BK12" t="n">
-        <v>21.51606887246858</v>
+        <v>15.84076427990243</v>
       </c>
       <c r="BL12" t="n">
-        <v>21.24371272146321</v>
+        <v>16.14288731840735</v>
       </c>
       <c r="BM12" t="n">
-        <v>20.10935281551083</v>
+        <v>17.71561768817961</v>
       </c>
       <c r="BN12" t="n">
-        <v>21.00741274147397</v>
+        <v>17.33759573465938</v>
       </c>
       <c r="BO12" t="n">
-        <v>20.27344679960861</v>
+        <v>15.6080802565189</v>
       </c>
       <c r="BP12" t="n">
-        <v>22.73452318711479</v>
+        <v>16.15047622816117</v>
       </c>
       <c r="BQ12" t="n">
-        <v>18.87752559991513</v>
+        <v>16.15051549806935</v>
       </c>
       <c r="BR12" t="n">
-        <v>19.6973167633841</v>
+        <v>14.97770005562202</v>
       </c>
       <c r="BS12" t="n">
-        <v>20.64626555684159</v>
+        <v>16.12319345946015</v>
       </c>
       <c r="BT12" t="n">
-        <v>21.25057062547378</v>
+        <v>18.82913556929043</v>
       </c>
       <c r="BU12" t="n">
-        <v>19.70133588012172</v>
+        <v>17.94761448817017</v>
       </c>
       <c r="BV12" t="n">
-        <v>21.6608992629692</v>
+        <v>16.77463214861313</v>
       </c>
       <c r="BW12" t="n">
-        <v>19.93034048909908</v>
+        <v>16.46062014540978</v>
       </c>
       <c r="BX12" t="n">
-        <v>20.87985392699836</v>
+        <v>17.73014755420246</v>
       </c>
       <c r="BY12" t="n">
-        <v>21.14087197849853</v>
+        <v>16.86683789299599</v>
       </c>
       <c r="BZ12" t="n">
-        <v>21.25240450943745</v>
+        <v>19.30551882529915</v>
       </c>
       <c r="CA12" t="n">
-        <v>19.5703880151487</v>
+        <v>17.44905355152251</v>
       </c>
       <c r="CB12" t="n">
-        <v>20.6671849749537</v>
+        <v>15.37004570814721</v>
       </c>
       <c r="CC12" t="n">
-        <v>21.65802996729341</v>
+        <v>17.01436512051315</v>
       </c>
       <c r="CD12" t="n">
-        <v>20.27923998273823</v>
+        <v>18.62051418213798</v>
       </c>
       <c r="CE12" t="n">
-        <v>20.53786537507924</v>
+        <v>16.37755447215346</v>
       </c>
       <c r="CF12" t="n">
-        <v>21.47351846691444</v>
+        <v>18.12639074511352</v>
       </c>
       <c r="CG12" t="n">
-        <v>20.59513437152045</v>
+        <v>17.81023853191492</v>
       </c>
       <c r="CH12" t="n">
-        <v>21.59210746443531</v>
+        <v>16.59474651676398</v>
       </c>
       <c r="CI12" t="n">
-        <v>20.11481116630987</v>
+        <v>18.0513950379861</v>
       </c>
       <c r="CJ12" t="n">
-        <v>20.92256150508963</v>
+        <v>14.96293457015015</v>
       </c>
       <c r="CK12" t="n">
-        <v>20.85446904371237</v>
+        <v>16.25290196614525</v>
       </c>
       <c r="CL12" t="n">
-        <v>22.28832860177966</v>
+        <v>15.47502399016233</v>
       </c>
       <c r="CM12" t="n">
-        <v>21.14576139701373</v>
+        <v>15.1428005670452</v>
       </c>
       <c r="CN12" t="n">
-        <v>21.05528335298046</v>
+        <v>15.63353697449002</v>
       </c>
       <c r="CO12" t="n">
-        <v>19.98924112418852</v>
+        <v>16.26296488011377</v>
       </c>
       <c r="CP12" t="n">
-        <v>19.55191472327736</v>
+        <v>16.74842930238678</v>
       </c>
       <c r="CQ12" t="n">
-        <v>19.82891776726756</v>
+        <v>17.04442623521719</v>
       </c>
       <c r="CR12" t="n">
-        <v>20.53514267713928</v>
+        <v>16.82644879244327</v>
       </c>
       <c r="CS12" t="n">
-        <v>22.01105487660168</v>
+        <v>16.23462182389217</v>
       </c>
       <c r="CT12" t="n">
-        <v>22.04068649222968</v>
+        <v>15.83606170839909</v>
       </c>
       <c r="CU12" t="n">
-        <v>21.23793933780056</v>
+        <v>15.9090448327328</v>
       </c>
       <c r="CV12" t="n">
-        <v>21.46000462841031</v>
+        <v>17.89344164984983</v>
       </c>
       <c r="CW12" t="n">
-        <v>19.66227542478277</v>
+        <v>18.48444395032937</v>
       </c>
       <c r="CX12" t="n">
-        <v>20.98819114847069</v>
+        <v>16.56393171434739</v>
       </c>
     </row>
     <row r="13">
@@ -4333,307 +4333,307 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21.86359389987793</v>
+        <v>14.93607395296196</v>
       </c>
       <c r="C13" t="n">
-        <v>22.81328975350561</v>
+        <v>16.29493058536405</v>
       </c>
       <c r="D13" t="n">
-        <v>22.03512308360435</v>
+        <v>15.04567626666407</v>
       </c>
       <c r="E13" t="n">
-        <v>24.07714830633287</v>
+        <v>14.21775861019569</v>
       </c>
       <c r="F13" t="n">
-        <v>24.03836745854796</v>
+        <v>16.12598162294022</v>
       </c>
       <c r="G13" t="n">
-        <v>22.36557604711321</v>
+        <v>15.75620635013566</v>
       </c>
       <c r="H13" t="n">
-        <v>22.45073217434737</v>
+        <v>15.26576446700212</v>
       </c>
       <c r="I13" t="n">
-        <v>22.46327731936486</v>
+        <v>15.24335116691416</v>
       </c>
       <c r="J13" t="n">
-        <v>23.45784364655832</v>
+        <v>15.64792939583428</v>
       </c>
       <c r="K13" t="n">
-        <v>23.77436875506986</v>
+        <v>14.86505432403674</v>
       </c>
       <c r="L13" t="n">
-        <v>23.20128581340657</v>
+        <v>14.17207788951709</v>
       </c>
       <c r="M13" t="n">
-        <v>24.70497924234669</v>
+        <v>16.37966522971759</v>
       </c>
       <c r="N13" t="n">
-        <v>24.12361000706518</v>
+        <v>15.17934121659727</v>
       </c>
       <c r="O13" t="n">
-        <v>22.09671094885641</v>
+        <v>15.58503863790022</v>
       </c>
       <c r="P13" t="n">
-        <v>23.59086328160442</v>
+        <v>14.76711517306108</v>
       </c>
       <c r="Q13" t="n">
-        <v>23.5436339910372</v>
+        <v>15.42652565357253</v>
       </c>
       <c r="R13" t="n">
-        <v>24.44399942797292</v>
+        <v>16.47602376688942</v>
       </c>
       <c r="S13" t="n">
-        <v>24.64006992218229</v>
+        <v>14.63894801027166</v>
       </c>
       <c r="T13" t="n">
-        <v>23.21429097257963</v>
+        <v>16.08473840188481</v>
       </c>
       <c r="U13" t="n">
-        <v>24.68644492354665</v>
+        <v>16.71037676137017</v>
       </c>
       <c r="V13" t="n">
-        <v>24.87948848581139</v>
+        <v>17.72451232238009</v>
       </c>
       <c r="W13" t="n">
-        <v>23.46697149597749</v>
+        <v>14.65921128288731</v>
       </c>
       <c r="X13" t="n">
-        <v>24.93653349485014</v>
+        <v>14.68315610939389</v>
       </c>
       <c r="Y13" t="n">
-        <v>24.79032986480594</v>
+        <v>16.05498162896908</v>
       </c>
       <c r="Z13" t="n">
-        <v>23.4654087059162</v>
+        <v>17.85098106164116</v>
       </c>
       <c r="AA13" t="n">
-        <v>24.95357406008925</v>
+        <v>15.38405524788682</v>
       </c>
       <c r="AB13" t="n">
-        <v>23.1238009032282</v>
+        <v>16.21755904879236</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.89713112796566</v>
+        <v>14.42731265766717</v>
       </c>
       <c r="AD13" t="n">
-        <v>24.40610672293868</v>
+        <v>14.7471464247567</v>
       </c>
       <c r="AE13" t="n">
-        <v>23.43568080141143</v>
+        <v>14.33745329029746</v>
       </c>
       <c r="AF13" t="n">
-        <v>24.63589989287057</v>
+        <v>15.48815977444515</v>
       </c>
       <c r="AG13" t="n">
-        <v>23.89913246712147</v>
+        <v>15.43907238923281</v>
       </c>
       <c r="AH13" t="n">
-        <v>23.38718743743956</v>
+        <v>14.68012250898777</v>
       </c>
       <c r="AI13" t="n">
-        <v>23.77252328610845</v>
+        <v>14.29455091562188</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22.24189938181852</v>
+        <v>14.58136850741758</v>
       </c>
       <c r="AK13" t="n">
-        <v>23.42570783520671</v>
+        <v>15.84931530240642</v>
       </c>
       <c r="AL13" t="n">
-        <v>23.59502613916558</v>
+        <v>13.98411247406199</v>
       </c>
       <c r="AM13" t="n">
-        <v>22.60383070599087</v>
+        <v>16.19934762887858</v>
       </c>
       <c r="AN13" t="n">
-        <v>24.71710739663229</v>
+        <v>14.98308003304129</v>
       </c>
       <c r="AO13" t="n">
-        <v>23.32003999236245</v>
+        <v>14.30837392329767</v>
       </c>
       <c r="AP13" t="n">
-        <v>24.48548144788646</v>
+        <v>15.6611339024564</v>
       </c>
       <c r="AQ13" t="n">
-        <v>23.23384500411574</v>
+        <v>14.86313991601346</v>
       </c>
       <c r="AR13" t="n">
-        <v>21.23608219430443</v>
+        <v>14.33781653694803</v>
       </c>
       <c r="AS13" t="n">
-        <v>22.79452628131305</v>
+        <v>14.53153499395001</v>
       </c>
       <c r="AT13" t="n">
-        <v>24.42154416391282</v>
+        <v>16.08392355129028</v>
       </c>
       <c r="AU13" t="n">
-        <v>24.56431047337731</v>
+        <v>17.5583024360511</v>
       </c>
       <c r="AV13" t="n">
-        <v>25.35977221929273</v>
+        <v>15.13980623654725</v>
       </c>
       <c r="AW13" t="n">
-        <v>21.62654767219792</v>
+        <v>14.00829292001759</v>
       </c>
       <c r="AX13" t="n">
-        <v>23.23645918805875</v>
+        <v>14.51738800953182</v>
       </c>
       <c r="AY13" t="n">
-        <v>23.33232779164595</v>
+        <v>13.80195900501604</v>
       </c>
       <c r="AZ13" t="n">
-        <v>23.72046520750181</v>
+        <v>14.90950786008504</v>
       </c>
       <c r="BA13" t="n">
-        <v>22.97986095278248</v>
+        <v>15.37089001117287</v>
       </c>
       <c r="BB13" t="n">
-        <v>23.30555389572602</v>
+        <v>15.77405452339886</v>
       </c>
       <c r="BC13" t="n">
-        <v>24.40869572280449</v>
+        <v>15.02494175515038</v>
       </c>
       <c r="BD13" t="n">
-        <v>23.75337760691218</v>
+        <v>14.33949532552229</v>
       </c>
       <c r="BE13" t="n">
-        <v>23.92706463244251</v>
+        <v>15.09872991260157</v>
       </c>
       <c r="BF13" t="n">
-        <v>23.27242239352892</v>
+        <v>15.60180688868876</v>
       </c>
       <c r="BG13" t="n">
-        <v>23.26655093322408</v>
+        <v>16.19614713136274</v>
       </c>
       <c r="BH13" t="n">
-        <v>22.40174269019615</v>
+        <v>14.60779715561591</v>
       </c>
       <c r="BI13" t="n">
-        <v>25.07329672057138</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="BJ13" t="n">
-        <v>22.65837035374219</v>
+        <v>14.10475944943688</v>
       </c>
       <c r="BK13" t="n">
-        <v>24.25511983288344</v>
+        <v>14.7547746044187</v>
       </c>
       <c r="BL13" t="n">
-        <v>23.71764178808159</v>
+        <v>14.97648268846875</v>
       </c>
       <c r="BM13" t="n">
-        <v>22.57179380423122</v>
+        <v>16.54451048673767</v>
       </c>
       <c r="BN13" t="n">
-        <v>23.33383350214894</v>
+        <v>16.17827932314544</v>
       </c>
       <c r="BO13" t="n">
-        <v>22.46836105895947</v>
+        <v>14.43525499659453</v>
       </c>
       <c r="BP13" t="n">
-        <v>25.27867153052715</v>
+        <v>15.02462759588501</v>
       </c>
       <c r="BQ13" t="n">
-        <v>20.92006959531266</v>
+        <v>15.04163146612257</v>
       </c>
       <c r="BR13" t="n">
-        <v>22.17063834649706</v>
+        <v>13.79277966398133</v>
       </c>
       <c r="BS13" t="n">
-        <v>23.06194505258051</v>
+        <v>15.08180458218035</v>
       </c>
       <c r="BT13" t="n">
-        <v>23.62213125851835</v>
+        <v>17.63441733556136</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.15533500280426</v>
+        <v>16.67425826333093</v>
       </c>
       <c r="BV13" t="n">
-        <v>24.14587368800943</v>
+        <v>15.44647476692283</v>
       </c>
       <c r="BW13" t="n">
-        <v>22.32307983493873</v>
+        <v>15.27938130766002</v>
       </c>
       <c r="BX13" t="n">
-        <v>23.33400846960346</v>
+        <v>16.56277099403666</v>
       </c>
       <c r="BY13" t="n">
-        <v>23.70494264169785</v>
+        <v>15.61495249044862</v>
       </c>
       <c r="BZ13" t="n">
-        <v>23.72042539591665</v>
+        <v>17.94085024648791</v>
       </c>
       <c r="CA13" t="n">
-        <v>21.84517982410076</v>
+        <v>16.3978373797232</v>
       </c>
       <c r="CB13" t="n">
-        <v>23.03914999867167</v>
+        <v>14.1239035296697</v>
       </c>
       <c r="CC13" t="n">
-        <v>24.04524442626935</v>
+        <v>15.85718891899448</v>
       </c>
       <c r="CD13" t="n">
-        <v>22.61545688853791</v>
+        <v>17.32303641620539</v>
       </c>
       <c r="CE13" t="n">
-        <v>22.75895446173647</v>
+        <v>15.26381078907067</v>
       </c>
       <c r="CF13" t="n">
-        <v>24.19725861252435</v>
+        <v>17.03496218734826</v>
       </c>
       <c r="CG13" t="n">
-        <v>23.01387186420447</v>
+        <v>16.79957835777804</v>
       </c>
       <c r="CH13" t="n">
-        <v>24.01321650148659</v>
+        <v>15.50297434730223</v>
       </c>
       <c r="CI13" t="n">
-        <v>22.46046380103137</v>
+        <v>16.76023972726887</v>
       </c>
       <c r="CJ13" t="n">
-        <v>23.32091094192941</v>
+        <v>13.70642513591578</v>
       </c>
       <c r="CK13" t="n">
-        <v>23.0868876393041</v>
+        <v>15.11483057495121</v>
       </c>
       <c r="CL13" t="n">
-        <v>24.75523171060037</v>
+        <v>14.29444292337441</v>
       </c>
       <c r="CM13" t="n">
-        <v>23.68143070217752</v>
+        <v>14.09246796817971</v>
       </c>
       <c r="CN13" t="n">
-        <v>23.40201247537385</v>
+        <v>14.56269566608281</v>
       </c>
       <c r="CO13" t="n">
-        <v>22.21634125521604</v>
+        <v>15.2278002832789</v>
       </c>
       <c r="CP13" t="n">
-        <v>21.81912001086939</v>
+        <v>15.61760320925009</v>
       </c>
       <c r="CQ13" t="n">
-        <v>22.06599228682633</v>
+        <v>15.73743533403046</v>
       </c>
       <c r="CR13" t="n">
-        <v>22.99422019238985</v>
+        <v>15.59349148563379</v>
       </c>
       <c r="CS13" t="n">
-        <v>24.41766922941993</v>
+        <v>15.04407601790615</v>
       </c>
       <c r="CT13" t="n">
-        <v>24.88172083410633</v>
+        <v>14.7502683824562</v>
       </c>
       <c r="CU13" t="n">
-        <v>23.72245800371309</v>
+        <v>14.77733516666229</v>
       </c>
       <c r="CV13" t="n">
-        <v>23.97793780510482</v>
+        <v>16.52826256223239</v>
       </c>
       <c r="CW13" t="n">
-        <v>22.05417436815121</v>
+        <v>17.20003324634031</v>
       </c>
       <c r="CX13" t="n">
-        <v>23.42765661354625</v>
+        <v>15.39607655217578</v>
       </c>
     </row>
     <row r="14">
@@ -4641,307 +4641,307 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15.57067566898709</v>
+        <v>16.80993579605784</v>
       </c>
       <c r="C14" t="n">
-        <v>16.08700623908162</v>
+        <v>18.36080264445653</v>
       </c>
       <c r="D14" t="n">
-        <v>15.70830687964545</v>
+        <v>16.88502967795568</v>
       </c>
       <c r="E14" t="n">
-        <v>16.89767458838638</v>
+        <v>16.04219927385979</v>
       </c>
       <c r="F14" t="n">
-        <v>16.97022574373022</v>
+        <v>18.15887677664704</v>
       </c>
       <c r="G14" t="n">
-        <v>15.87726565954633</v>
+        <v>17.97763633296604</v>
       </c>
       <c r="H14" t="n">
-        <v>15.90240821825209</v>
+        <v>17.19837409272013</v>
       </c>
       <c r="I14" t="n">
-        <v>15.82485014961659</v>
+        <v>17.04084285609669</v>
       </c>
       <c r="J14" t="n">
-        <v>16.60081371757623</v>
+        <v>17.8248665727082</v>
       </c>
       <c r="K14" t="n">
-        <v>16.8395158543868</v>
+        <v>16.59355860204185</v>
       </c>
       <c r="L14" t="n">
-        <v>16.44100482627893</v>
+        <v>15.96691885989815</v>
       </c>
       <c r="M14" t="n">
-        <v>17.30896797160354</v>
+        <v>18.47766007369303</v>
       </c>
       <c r="N14" t="n">
-        <v>16.97245431101886</v>
+        <v>17.14714649751254</v>
       </c>
       <c r="O14" t="n">
-        <v>15.78088748742042</v>
+        <v>17.68828583209338</v>
       </c>
       <c r="P14" t="n">
-        <v>16.87497658146419</v>
+        <v>16.68683445142234</v>
       </c>
       <c r="Q14" t="n">
-        <v>16.61811211212506</v>
+        <v>17.34287753730822</v>
       </c>
       <c r="R14" t="n">
-        <v>17.43118574330522</v>
+        <v>18.69088585757839</v>
       </c>
       <c r="S14" t="n">
-        <v>17.2648285948206</v>
+        <v>16.32245879099113</v>
       </c>
       <c r="T14" t="n">
-        <v>16.25832121347268</v>
+        <v>18.16426657154336</v>
       </c>
       <c r="U14" t="n">
-        <v>17.42643408441667</v>
+        <v>19.04790822770478</v>
       </c>
       <c r="V14" t="n">
-        <v>17.58006778265425</v>
+        <v>20.0359685696899</v>
       </c>
       <c r="W14" t="n">
-        <v>16.45126408978831</v>
+        <v>16.51519550028886</v>
       </c>
       <c r="X14" t="n">
-        <v>17.61682441670125</v>
+        <v>16.53917959670361</v>
       </c>
       <c r="Y14" t="n">
-        <v>17.32301678125131</v>
+        <v>18.33551282359513</v>
       </c>
       <c r="Z14" t="n">
-        <v>16.45410134065358</v>
+        <v>20.2273799195869</v>
       </c>
       <c r="AA14" t="n">
-        <v>17.36868768445287</v>
+        <v>17.27717898094003</v>
       </c>
       <c r="AB14" t="n">
-        <v>16.36425179076092</v>
+        <v>18.36665386077384</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.93754336265584</v>
+        <v>16.15914506038968</v>
       </c>
       <c r="AD14" t="n">
-        <v>17.19070664314997</v>
+        <v>16.67789072983664</v>
       </c>
       <c r="AE14" t="n">
-        <v>16.471998601302</v>
+        <v>16.09227822425342</v>
       </c>
       <c r="AF14" t="n">
-        <v>17.41475128673613</v>
+        <v>17.44177880103405</v>
       </c>
       <c r="AG14" t="n">
-        <v>16.93170196381557</v>
+        <v>17.32318367836103</v>
       </c>
       <c r="AH14" t="n">
-        <v>16.50476933966976</v>
+        <v>16.58565553302266</v>
       </c>
       <c r="AI14" t="n">
-        <v>16.70883541747451</v>
+        <v>16.08020272749119</v>
       </c>
       <c r="AJ14" t="n">
-        <v>15.75147432620119</v>
+        <v>16.41470380528216</v>
       </c>
       <c r="AK14" t="n">
-        <v>16.52833128457168</v>
+        <v>18.11169398198095</v>
       </c>
       <c r="AL14" t="n">
-        <v>16.69799692281962</v>
+        <v>15.78584531332687</v>
       </c>
       <c r="AM14" t="n">
-        <v>15.99380892951747</v>
+        <v>18.36356135550546</v>
       </c>
       <c r="AN14" t="n">
-        <v>17.33507264305946</v>
+        <v>16.90723681102574</v>
       </c>
       <c r="AO14" t="n">
-        <v>16.47881193036948</v>
+        <v>16.0087511295761</v>
       </c>
       <c r="AP14" t="n">
-        <v>17.3614816563037</v>
+        <v>17.72577877691856</v>
       </c>
       <c r="AQ14" t="n">
-        <v>16.38963978639274</v>
+        <v>16.80307337960516</v>
       </c>
       <c r="AR14" t="n">
-        <v>15.18171704604155</v>
+        <v>16.1641912435895</v>
       </c>
       <c r="AS14" t="n">
-        <v>16.20148783887383</v>
+        <v>16.50870614796379</v>
       </c>
       <c r="AT14" t="n">
-        <v>17.215682304746</v>
+        <v>18.28741700356408</v>
       </c>
       <c r="AU14" t="n">
-        <v>17.2031748389939</v>
+        <v>19.86910091239907</v>
       </c>
       <c r="AV14" t="n">
-        <v>17.91075967935275</v>
+        <v>17.1120686520398</v>
       </c>
       <c r="AW14" t="n">
-        <v>15.29736692560182</v>
+        <v>15.69257928142342</v>
       </c>
       <c r="AX14" t="n">
-        <v>16.28347358965549</v>
+        <v>16.35627999940243</v>
       </c>
       <c r="AY14" t="n">
-        <v>16.50402321141453</v>
+        <v>15.48847393371051</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.67400300892783</v>
+        <v>16.7793641725476</v>
       </c>
       <c r="BA14" t="n">
-        <v>16.38095131921015</v>
+        <v>17.36955162243261</v>
       </c>
       <c r="BB14" t="n">
-        <v>16.48668554695753</v>
+        <v>17.91569787030511</v>
       </c>
       <c r="BC14" t="n">
-        <v>17.21941294602214</v>
+        <v>16.86800617276404</v>
       </c>
       <c r="BD14" t="n">
-        <v>16.84868537794446</v>
+        <v>16.18090058951578</v>
       </c>
       <c r="BE14" t="n">
-        <v>16.89398321701841</v>
+        <v>16.98784811502145</v>
       </c>
       <c r="BF14" t="n">
-        <v>16.41383004982538</v>
+        <v>17.50838056529015</v>
       </c>
       <c r="BG14" t="n">
-        <v>16.45777307706746</v>
+        <v>18.31115566305277</v>
       </c>
       <c r="BH14" t="n">
-        <v>16.02592189692338</v>
+        <v>16.54958612236863</v>
       </c>
       <c r="BI14" t="n">
-        <v>17.54158327264778</v>
+        <v>16.86877193597335</v>
       </c>
       <c r="BJ14" t="n">
-        <v>16.12199572726097</v>
+        <v>15.85321284079228</v>
       </c>
       <c r="BK14" t="n">
-        <v>17.21002743796954</v>
+        <v>16.70875687765816</v>
       </c>
       <c r="BL14" t="n">
-        <v>16.52751643397716</v>
+        <v>16.90888614716888</v>
       </c>
       <c r="BM14" t="n">
-        <v>16.00796573141271</v>
+        <v>18.88361274939908</v>
       </c>
       <c r="BN14" t="n">
-        <v>16.40548519433928</v>
+        <v>18.31289335648928</v>
       </c>
       <c r="BO14" t="n">
-        <v>15.97376164139675</v>
+        <v>16.20871350197709</v>
       </c>
       <c r="BP14" t="n">
-        <v>17.83052143948466</v>
+        <v>16.85268109110075</v>
       </c>
       <c r="BQ14" t="n">
-        <v>14.91094121173323</v>
+        <v>16.86697533767458</v>
       </c>
       <c r="BR14" t="n">
-        <v>15.76174340718761</v>
+        <v>15.37872435785276</v>
       </c>
       <c r="BS14" t="n">
-        <v>16.48019619463246</v>
+        <v>17.14023499367464</v>
       </c>
       <c r="BT14" t="n">
-        <v>16.76308679561118</v>
+        <v>20.04189832582355</v>
       </c>
       <c r="BU14" t="n">
-        <v>15.65647060086122</v>
+        <v>18.94088791046484</v>
       </c>
       <c r="BV14" t="n">
-        <v>17.01101736084167</v>
+        <v>17.36815754069258</v>
       </c>
       <c r="BW14" t="n">
-        <v>15.81670164367134</v>
+        <v>17.24877701985617</v>
       </c>
       <c r="BX14" t="n">
-        <v>16.49406828969347</v>
+        <v>18.73208980872563</v>
       </c>
       <c r="BY14" t="n">
-        <v>16.69811473254413</v>
+        <v>17.60082192912203</v>
       </c>
       <c r="BZ14" t="n">
-        <v>16.86403991203888</v>
+        <v>20.30538959216636</v>
       </c>
       <c r="CA14" t="n">
-        <v>15.44675947375706</v>
+        <v>18.66470264630613</v>
       </c>
       <c r="CB14" t="n">
-        <v>16.30022220548994</v>
+        <v>15.81358950344888</v>
       </c>
       <c r="CC14" t="n">
-        <v>16.8683203320294</v>
+        <v>17.97862789814733</v>
       </c>
       <c r="CD14" t="n">
-        <v>15.93183119694837</v>
+        <v>19.68446362166137</v>
       </c>
       <c r="CE14" t="n">
-        <v>16.18506319978179</v>
+        <v>17.31080383981048</v>
       </c>
       <c r="CF14" t="n">
-        <v>17.07621522588071</v>
+        <v>19.39904992908274</v>
       </c>
       <c r="CG14" t="n">
-        <v>16.41870933591549</v>
+        <v>19.21165392729611</v>
       </c>
       <c r="CH14" t="n">
-        <v>16.9785215118311</v>
+        <v>17.61198440051932</v>
       </c>
       <c r="CI14" t="n">
-        <v>16.07986893327174</v>
+        <v>19.00408301018721</v>
       </c>
       <c r="CJ14" t="n">
-        <v>16.45002708768096</v>
+        <v>15.25974635357509</v>
       </c>
       <c r="CK14" t="n">
-        <v>16.37537499225003</v>
+        <v>17.02511525787466</v>
       </c>
       <c r="CL14" t="n">
-        <v>17.30729900050632</v>
+        <v>16.13335454819911</v>
       </c>
       <c r="CM14" t="n">
-        <v>16.84623100868384</v>
+        <v>15.86737946016456</v>
       </c>
       <c r="CN14" t="n">
-        <v>16.5078520274611</v>
+        <v>16.36081567379605</v>
       </c>
       <c r="CO14" t="n">
-        <v>15.71947916851978</v>
+        <v>17.28606379766346</v>
       </c>
       <c r="CP14" t="n">
-        <v>15.53318272416191</v>
+        <v>17.64906501130872</v>
       </c>
       <c r="CQ14" t="n">
-        <v>15.76099727893238</v>
+        <v>17.82383573761874</v>
       </c>
       <c r="CR14" t="n">
-        <v>16.19344732517606</v>
+        <v>17.56367259599333</v>
       </c>
       <c r="CS14" t="n">
-        <v>17.08087852747587</v>
+        <v>16.90248515213719</v>
       </c>
       <c r="CT14" t="n">
-        <v>17.5724494204693</v>
+        <v>16.68710934077952</v>
       </c>
       <c r="CU14" t="n">
-        <v>16.74236210157454</v>
+        <v>16.67538727319081</v>
       </c>
       <c r="CV14" t="n">
-        <v>16.90036457709601</v>
+        <v>18.75022268882307</v>
       </c>
       <c r="CW14" t="n">
-        <v>15.69890173663877</v>
+        <v>19.40705117287235</v>
       </c>
       <c r="CX14" t="n">
-        <v>16.5575958091885</v>
+        <v>17.38446270108901</v>
       </c>
     </row>
     <row r="15">
@@ -4949,307 +4949,307 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16.25925387379172</v>
+        <v>17.62385373026366</v>
       </c>
       <c r="C15" t="n">
-        <v>16.91287204284812</v>
+        <v>19.25452684954057</v>
       </c>
       <c r="D15" t="n">
-        <v>16.56430252045529</v>
+        <v>17.68904177782565</v>
       </c>
       <c r="E15" t="n">
-        <v>17.65530892670773</v>
+        <v>16.86285199731674</v>
       </c>
       <c r="F15" t="n">
-        <v>17.73317133713154</v>
+        <v>19.00465242385567</v>
       </c>
       <c r="G15" t="n">
-        <v>16.59366659428931</v>
+        <v>19.02473898188456</v>
       </c>
       <c r="H15" t="n">
-        <v>16.57630929487823</v>
+        <v>18.04528856726569</v>
       </c>
       <c r="I15" t="n">
-        <v>16.56487193412375</v>
+        <v>17.79107481672802</v>
       </c>
       <c r="J15" t="n">
-        <v>17.32037587992689</v>
+        <v>18.88520318067996</v>
       </c>
       <c r="K15" t="n">
-        <v>17.64830906557645</v>
+        <v>17.26585942991006</v>
       </c>
       <c r="L15" t="n">
-        <v>16.88986969413762</v>
+        <v>16.7446888436336</v>
       </c>
       <c r="M15" t="n">
-        <v>18.02556525588737</v>
+        <v>19.39333615744403</v>
       </c>
       <c r="N15" t="n">
-        <v>17.66142521490519</v>
+        <v>18.06798657418787</v>
       </c>
       <c r="O15" t="n">
-        <v>16.71690538360341</v>
+        <v>18.65910668439192</v>
       </c>
       <c r="P15" t="n">
-        <v>17.80310122610504</v>
+        <v>17.50547459208558</v>
       </c>
       <c r="Q15" t="n">
-        <v>17.47779912430286</v>
+        <v>18.14472979222885</v>
       </c>
       <c r="R15" t="n">
-        <v>18.24206025962788</v>
+        <v>19.70511959335873</v>
       </c>
       <c r="S15" t="n">
-        <v>18.17023559758518</v>
+        <v>17.01368771459722</v>
       </c>
       <c r="T15" t="n">
-        <v>16.99406257798933</v>
+        <v>19.07718394424543</v>
       </c>
       <c r="U15" t="n">
-        <v>18.09870545985376</v>
+        <v>20.0997723529889</v>
       </c>
       <c r="V15" t="n">
-        <v>18.42675645522783</v>
+        <v>21.05412929628723</v>
       </c>
       <c r="W15" t="n">
-        <v>17.30664122954447</v>
+        <v>17.32261426469257</v>
       </c>
       <c r="X15" t="n">
-        <v>18.55328409935116</v>
+        <v>17.36007775708662</v>
       </c>
       <c r="Y15" t="n">
-        <v>18.25052292483849</v>
+        <v>19.45538261235243</v>
       </c>
       <c r="Z15" t="n">
-        <v>17.36785319890426</v>
+        <v>21.23858987243816</v>
       </c>
       <c r="AA15" t="n">
-        <v>18.14734124112214</v>
+        <v>18.09969702503505</v>
       </c>
       <c r="AB15" t="n">
-        <v>17.1275115434276</v>
+        <v>19.34362045370097</v>
       </c>
       <c r="AC15" t="n">
-        <v>17.77538648841416</v>
+        <v>16.85096303261832</v>
       </c>
       <c r="AD15" t="n">
-        <v>17.91012154334499</v>
+        <v>17.56400639021277</v>
       </c>
       <c r="AE15" t="n">
-        <v>17.21324757043947</v>
+        <v>16.83008125894899</v>
       </c>
       <c r="AF15" t="n">
-        <v>18.27613672244228</v>
+        <v>18.31616257634442</v>
       </c>
       <c r="AG15" t="n">
-        <v>17.7096290271837</v>
+        <v>18.17487926422627</v>
       </c>
       <c r="AH15" t="n">
-        <v>17.3659191559269</v>
+        <v>17.4345335029767</v>
       </c>
       <c r="AI15" t="n">
-        <v>17.54173053480341</v>
+        <v>16.90196482585394</v>
       </c>
       <c r="AJ15" t="n">
-        <v>16.34651160974518</v>
+        <v>17.21990381987426</v>
       </c>
       <c r="AK15" t="n">
-        <v>17.3433585936833</v>
+        <v>19.20812945303786</v>
       </c>
       <c r="AL15" t="n">
-        <v>17.48294348227311</v>
+        <v>16.56917198906836</v>
       </c>
       <c r="AM15" t="n">
-        <v>16.87302290353274</v>
+        <v>19.35475347266713</v>
       </c>
       <c r="AN15" t="n">
-        <v>18.20772854241036</v>
+        <v>17.78567520435466</v>
       </c>
       <c r="AO15" t="n">
-        <v>17.2843162867499</v>
+        <v>16.67972659804359</v>
       </c>
       <c r="AP15" t="n">
-        <v>18.23497204120322</v>
+        <v>18.67628726921624</v>
       </c>
       <c r="AQ15" t="n">
-        <v>17.2543337118622</v>
+        <v>17.71841566913671</v>
       </c>
       <c r="AR15" t="n">
-        <v>15.72605687813823</v>
+        <v>17.0020540043019</v>
       </c>
       <c r="AS15" t="n">
-        <v>17.10861290012085</v>
+        <v>17.43082249665465</v>
       </c>
       <c r="AT15" t="n">
-        <v>18.06709318377701</v>
+        <v>19.31610206555093</v>
       </c>
       <c r="AU15" t="n">
-        <v>18.15228924955155</v>
+        <v>20.8846501901031</v>
       </c>
       <c r="AV15" t="n">
-        <v>18.78532016924989</v>
+        <v>17.97823519906563</v>
       </c>
       <c r="AW15" t="n">
-        <v>15.88966513305097</v>
+        <v>16.39423436564861</v>
       </c>
       <c r="AX15" t="n">
-        <v>17.15920235932069</v>
+        <v>17.15102440094431</v>
       </c>
       <c r="AY15" t="n">
-        <v>17.06986331823423</v>
+        <v>16.20572898895619</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17.58008741760834</v>
+        <v>17.60088083398428</v>
       </c>
       <c r="BA15" t="n">
-        <v>17.27129831219159</v>
+        <v>18.33376531268157</v>
       </c>
       <c r="BB15" t="n">
-        <v>17.2507503327417</v>
+        <v>18.9495469252163</v>
       </c>
       <c r="BC15" t="n">
-        <v>18.0549784171066</v>
+        <v>17.66417410847707</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.7555846372195</v>
+        <v>17.00537231154225</v>
       </c>
       <c r="BE15" t="n">
-        <v>17.75578098676035</v>
+        <v>17.88458628555753</v>
       </c>
       <c r="BF15" t="n">
-        <v>17.13350020442351</v>
+        <v>18.34280720903768</v>
       </c>
       <c r="BG15" t="n">
-        <v>17.32834767128537</v>
+        <v>19.25705975861753</v>
       </c>
       <c r="BH15" t="n">
-        <v>16.71874125181035</v>
+        <v>17.46858051335998</v>
       </c>
       <c r="BI15" t="n">
-        <v>18.43795819653328</v>
+        <v>17.67461990405026</v>
       </c>
       <c r="BJ15" t="n">
-        <v>16.73590220168059</v>
+        <v>16.62862663003754</v>
       </c>
       <c r="BK15" t="n">
-        <v>18.29401434813662</v>
+        <v>17.60232400310953</v>
       </c>
       <c r="BL15" t="n">
-        <v>17.41038250945223</v>
+        <v>17.76369387325657</v>
       </c>
       <c r="BM15" t="n">
-        <v>16.80864970656528</v>
+        <v>19.9292820466694</v>
       </c>
       <c r="BN15" t="n">
-        <v>17.06850850640237</v>
+        <v>19.297625573757</v>
       </c>
       <c r="BO15" t="n">
-        <v>16.57870475927659</v>
+        <v>16.96224413489469</v>
       </c>
       <c r="BP15" t="n">
-        <v>18.71936635847859</v>
+        <v>17.69028859741004</v>
       </c>
       <c r="BQ15" t="n">
-        <v>15.36254515568677</v>
+        <v>17.69441193776788</v>
       </c>
       <c r="BR15" t="n">
-        <v>16.48983695708817</v>
+        <v>16.02487142687984</v>
       </c>
       <c r="BS15" t="n">
-        <v>17.29424175603983</v>
+        <v>18.11798698476516</v>
       </c>
       <c r="BT15" t="n">
-        <v>17.54222140865554</v>
+        <v>21.16648050356124</v>
       </c>
       <c r="BU15" t="n">
-        <v>16.48481040884242</v>
+        <v>19.96439916205031</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.87189228774162</v>
+        <v>18.15942655536142</v>
       </c>
       <c r="BW15" t="n">
-        <v>16.58474250765771</v>
+        <v>18.08760189331873</v>
       </c>
       <c r="BX15" t="n">
-        <v>17.29084490898314</v>
+        <v>19.68751685702158</v>
       </c>
       <c r="BY15" t="n">
-        <v>17.56662765658312</v>
+        <v>18.46271787363439</v>
       </c>
       <c r="BZ15" t="n">
-        <v>17.68758879122336</v>
+        <v>21.32784055623124</v>
       </c>
       <c r="CA15" t="n">
-        <v>16.00014120220986</v>
+        <v>19.76098103773037</v>
       </c>
       <c r="CB15" t="n">
-        <v>17.07972988266191</v>
+        <v>16.5226469653641</v>
       </c>
       <c r="CC15" t="n">
-        <v>17.64272292113928</v>
+        <v>18.97668243176168</v>
       </c>
       <c r="CD15" t="n">
-        <v>16.58251394036906</v>
+        <v>20.70893698599701</v>
       </c>
       <c r="CE15" t="n">
-        <v>16.66251656078814</v>
+        <v>18.24877541392492</v>
       </c>
       <c r="CF15" t="n">
-        <v>18.12901201148386</v>
+        <v>20.5533103399198</v>
       </c>
       <c r="CG15" t="n">
-        <v>17.10573637934741</v>
+        <v>20.38895595675184</v>
       </c>
       <c r="CH15" t="n">
-        <v>17.75807827638828</v>
+        <v>18.62311581355423</v>
       </c>
       <c r="CI15" t="n">
-        <v>16.8221094675905</v>
+        <v>19.98041146710658</v>
       </c>
       <c r="CJ15" t="n">
-        <v>17.19564483410233</v>
+        <v>15.86882262928981</v>
       </c>
       <c r="CK15" t="n">
-        <v>16.99383677601735</v>
+        <v>17.87827364781922</v>
       </c>
       <c r="CL15" t="n">
-        <v>18.11141909262375</v>
+        <v>16.92522242896754</v>
       </c>
       <c r="CM15" t="n">
-        <v>17.78948438544714</v>
+        <v>16.65829504565988</v>
       </c>
       <c r="CN15" t="n">
-        <v>17.16851914503399</v>
+        <v>17.1521534108042</v>
       </c>
       <c r="CO15" t="n">
-        <v>16.28525055300017</v>
+        <v>18.25463644771928</v>
       </c>
       <c r="CP15" t="n">
-        <v>16.17128927949121</v>
+        <v>18.56990508798406</v>
       </c>
       <c r="CQ15" t="n">
-        <v>16.44412678397844</v>
+        <v>18.70403145933826</v>
       </c>
       <c r="CR15" t="n">
-        <v>17.03177150730945</v>
+        <v>18.41081287251086</v>
       </c>
       <c r="CS15" t="n">
-        <v>17.82015418372781</v>
+        <v>17.73391746538677</v>
       </c>
       <c r="CT15" t="n">
-        <v>18.71730468829967</v>
+        <v>17.57150694267322</v>
       </c>
       <c r="CU15" t="n">
-        <v>17.58498633865253</v>
+        <v>17.5416127250789</v>
       </c>
       <c r="CV15" t="n">
-        <v>17.66580380966613</v>
+        <v>19.75039779747859</v>
       </c>
       <c r="CW15" t="n">
-        <v>16.41975980595903</v>
+        <v>20.35788364191243</v>
       </c>
       <c r="CX15" t="n">
-        <v>17.34125362843062</v>
+        <v>18.27269815110816</v>
       </c>
     </row>
     <row r="16">
@@ -5257,307 +5257,307 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>18.55750561447942</v>
+        <v>20.02510062260389</v>
       </c>
       <c r="C16" t="n">
-        <v>19.47429107313622</v>
+        <v>21.73185918895993</v>
       </c>
       <c r="D16" t="n">
-        <v>19.04036840533617</v>
+        <v>19.95086086120875</v>
       </c>
       <c r="E16" t="n">
-        <v>20.14312633160844</v>
+        <v>19.11550155714218</v>
       </c>
       <c r="F16" t="n">
-        <v>20.17109632370244</v>
+        <v>21.49223420930737</v>
       </c>
       <c r="G16" t="n">
-        <v>18.94385278853166</v>
+        <v>21.61434398876159</v>
       </c>
       <c r="H16" t="n">
-        <v>18.86280951554609</v>
+        <v>20.33672697888591</v>
       </c>
       <c r="I16" t="n">
-        <v>18.96620718375736</v>
+        <v>19.92142806503543</v>
       </c>
       <c r="J16" t="n">
-        <v>19.76756856482587</v>
+        <v>21.53027693284693</v>
       </c>
       <c r="K16" t="n">
-        <v>20.15369975438318</v>
+        <v>19.35448840078698</v>
       </c>
       <c r="L16" t="n">
-        <v>19.04418740390569</v>
+        <v>19.08397763835881</v>
       </c>
       <c r="M16" t="n">
-        <v>20.48810265740373</v>
+        <v>21.76968592800456</v>
       </c>
       <c r="N16" t="n">
-        <v>20.09976253551186</v>
+        <v>20.55662864716016</v>
       </c>
       <c r="O16" t="n">
-        <v>19.3929140059312</v>
+        <v>21.12819234309561</v>
       </c>
       <c r="P16" t="n">
-        <v>20.40057984957012</v>
+        <v>19.80506150965105</v>
       </c>
       <c r="Q16" t="n">
-        <v>20.03052968740838</v>
+        <v>20.38890686936663</v>
       </c>
       <c r="R16" t="n">
-        <v>20.73046671315114</v>
+        <v>22.26059905003613</v>
       </c>
       <c r="S16" t="n">
-        <v>20.77031585246652</v>
+        <v>19.11906530130859</v>
       </c>
       <c r="T16" t="n">
-        <v>19.42247442930607</v>
+        <v>21.4062232929383</v>
       </c>
       <c r="U16" t="n">
-        <v>20.53979167403232</v>
+        <v>22.72862763308172</v>
       </c>
       <c r="V16" t="n">
-        <v>21.12756402456489</v>
+        <v>23.60689912930091</v>
       </c>
       <c r="W16" t="n">
-        <v>19.83143125298712</v>
+        <v>19.60559982857923</v>
       </c>
       <c r="X16" t="n">
-        <v>21.24788702319738</v>
+        <v>19.63689794539062</v>
       </c>
       <c r="Y16" t="n">
-        <v>20.95949863507488</v>
+        <v>22.05468728654741</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.09936983643016</v>
+        <v>23.88708010661591</v>
       </c>
       <c r="AA16" t="n">
-        <v>20.63977286023282</v>
+        <v>20.36327343680875</v>
       </c>
       <c r="AB16" t="n">
-        <v>19.6084370794445</v>
+        <v>21.79908927174675</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.24644546000338</v>
+        <v>18.94957637764742</v>
       </c>
       <c r="AD16" t="n">
-        <v>20.40431049084626</v>
+        <v>19.92865372813868</v>
       </c>
       <c r="AE16" t="n">
-        <v>19.57892574345484</v>
+        <v>19.03160139833724</v>
       </c>
       <c r="AF16" t="n">
-        <v>20.96813801487225</v>
+        <v>20.66310900316276</v>
       </c>
       <c r="AG16" t="n">
-        <v>20.26971288059402</v>
+        <v>20.56796783314421</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.9549645666125</v>
+        <v>19.67074860623305</v>
       </c>
       <c r="AI16" t="n">
-        <v>20.0595697845</v>
+        <v>19.16154552447135</v>
       </c>
       <c r="AJ16" t="n">
-        <v>18.55482544324683</v>
+        <v>19.49287555717761</v>
       </c>
       <c r="AK16" t="n">
-        <v>19.91718691495308</v>
+        <v>21.76725119369802</v>
       </c>
       <c r="AL16" t="n">
-        <v>19.96744257993348</v>
+        <v>18.82861524300717</v>
       </c>
       <c r="AM16" t="n">
-        <v>19.48778028659257</v>
+        <v>21.86066448775711</v>
       </c>
       <c r="AN16" t="n">
-        <v>20.84631294225226</v>
+        <v>20.03653798335836</v>
       </c>
       <c r="AO16" t="n">
-        <v>19.79688355127468</v>
+        <v>18.8423302584355</v>
       </c>
       <c r="AP16" t="n">
-        <v>20.82722776688171</v>
+        <v>21.12820216057265</v>
       </c>
       <c r="AQ16" t="n">
-        <v>19.75125191798129</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="AR16" t="n">
-        <v>17.88222027359029</v>
+        <v>19.24018351558152</v>
       </c>
       <c r="AS16" t="n">
-        <v>19.72125952561655</v>
+        <v>19.72448947556352</v>
       </c>
       <c r="AT16" t="n">
-        <v>20.69494708121149</v>
+        <v>21.85677676684829</v>
       </c>
       <c r="AU16" t="n">
-        <v>20.83541554273512</v>
+        <v>23.44477331342159</v>
       </c>
       <c r="AV16" t="n">
-        <v>21.42372785450502</v>
+        <v>20.31049468022844</v>
       </c>
       <c r="AW16" t="n">
-        <v>18.16020213604778</v>
+        <v>18.5129539036607</v>
       </c>
       <c r="AX16" t="n">
-        <v>19.5327737838782</v>
+        <v>19.35430186872317</v>
       </c>
       <c r="AY16" t="n">
-        <v>19.37812888550524</v>
+        <v>18.2554512983138</v>
       </c>
       <c r="AZ16" t="n">
-        <v>20.18039347446165</v>
+        <v>19.81178648142514</v>
       </c>
       <c r="BA16" t="n">
-        <v>19.78341397277241</v>
+        <v>20.80597292908476</v>
       </c>
       <c r="BB16" t="n">
-        <v>19.64156124698579</v>
+        <v>21.50548780331469</v>
       </c>
       <c r="BC16" t="n">
-        <v>20.71368864488556</v>
+        <v>19.82860381959889</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.30899260624094</v>
+        <v>19.32261105283008</v>
       </c>
       <c r="BE16" t="n">
-        <v>20.37374868481306</v>
+        <v>20.20424012619781</v>
       </c>
       <c r="BF16" t="n">
-        <v>19.45979065954449</v>
+        <v>20.58873179708903</v>
       </c>
       <c r="BG16" t="n">
-        <v>19.82448047924106</v>
+        <v>21.66742708713021</v>
       </c>
       <c r="BH16" t="n">
-        <v>19.11001358747544</v>
+        <v>19.83707630228654</v>
       </c>
       <c r="BI16" t="n">
-        <v>21.18327820678089</v>
+        <v>19.91331882899835</v>
       </c>
       <c r="BJ16" t="n">
-        <v>19.00686135619023</v>
+        <v>18.79022890777113</v>
       </c>
       <c r="BK16" t="n">
-        <v>21.04507758245407</v>
+        <v>19.92767198043444</v>
       </c>
       <c r="BL16" t="n">
-        <v>20.02531660709882</v>
+        <v>20.14049524776106</v>
       </c>
       <c r="BM16" t="n">
-        <v>19.20381958061622</v>
+        <v>22.55975721047422</v>
       </c>
       <c r="BN16" t="n">
-        <v>19.34606500548454</v>
+        <v>21.78389181728501</v>
       </c>
       <c r="BO16" t="n">
-        <v>18.77276361611257</v>
+        <v>19.12479870790139</v>
       </c>
       <c r="BP16" t="n">
-        <v>21.37196029806009</v>
+        <v>19.90552375222663</v>
       </c>
       <c r="BQ16" t="n">
-        <v>17.4724682342688</v>
+        <v>19.86528191382955</v>
       </c>
       <c r="BR16" t="n">
-        <v>18.90749867104341</v>
+        <v>18.08956538872722</v>
       </c>
       <c r="BS16" t="n">
-        <v>19.81835437356656</v>
+        <v>20.61305950520027</v>
       </c>
       <c r="BT16" t="n">
-        <v>19.96169935586363</v>
+        <v>23.89763389443656</v>
       </c>
       <c r="BU16" t="n">
-        <v>19.03651013685848</v>
+        <v>22.57497429989005</v>
       </c>
       <c r="BV16" t="n">
-        <v>20.58709227842294</v>
+        <v>20.39822365507993</v>
       </c>
       <c r="BW16" t="n">
-        <v>19.0258581742674</v>
+        <v>20.34958787381154</v>
       </c>
       <c r="BX16" t="n">
-        <v>19.8113839648664</v>
+        <v>22.17163307307728</v>
       </c>
       <c r="BY16" t="n">
-        <v>20.01618635344933</v>
+        <v>20.82327132363359</v>
       </c>
       <c r="BZ16" t="n">
-        <v>20.32424896556493</v>
+        <v>24.05953390834391</v>
       </c>
       <c r="CA16" t="n">
-        <v>18.19173587230818</v>
+        <v>22.42147804633106</v>
       </c>
       <c r="CB16" t="n">
-        <v>19.49563426822655</v>
+        <v>18.64341835607805</v>
       </c>
       <c r="CC16" t="n">
-        <v>20.14909535765026</v>
+        <v>21.53206371366866</v>
       </c>
       <c r="CD16" t="n">
-        <v>18.97784089405269</v>
+        <v>23.38099898255372</v>
       </c>
       <c r="CE16" t="n">
-        <v>18.91878876964224</v>
+        <v>20.72131682454756</v>
       </c>
       <c r="CF16" t="n">
-        <v>20.83091913824967</v>
+        <v>23.33313878197169</v>
       </c>
       <c r="CG16" t="n">
-        <v>19.39502476349533</v>
+        <v>23.14502610436096</v>
       </c>
       <c r="CH16" t="n">
-        <v>20.27643785236812</v>
+        <v>21.0961284630749</v>
       </c>
       <c r="CI16" t="n">
-        <v>19.19915627902105</v>
+        <v>22.56181888065314</v>
       </c>
       <c r="CJ16" t="n">
-        <v>19.48812389828905</v>
+        <v>17.84582688619387</v>
       </c>
       <c r="CK16" t="n">
-        <v>19.35563704560095</v>
+        <v>20.23034479765373</v>
       </c>
       <c r="CL16" t="n">
-        <v>20.65223123859971</v>
+        <v>19.15918932998116</v>
       </c>
       <c r="CM16" t="n">
-        <v>20.37634049875227</v>
+        <v>18.92538611421478</v>
       </c>
       <c r="CN16" t="n">
-        <v>19.52211200381008</v>
+        <v>19.49858932881633</v>
       </c>
       <c r="CO16" t="n">
-        <v>18.48696704192929</v>
+        <v>20.71131281544128</v>
       </c>
       <c r="CP16" t="n">
-        <v>18.52596206074197</v>
+        <v>21.02495175451701</v>
       </c>
       <c r="CQ16" t="n">
-        <v>18.74247669943656</v>
+        <v>21.21798298812602</v>
       </c>
       <c r="CR16" t="n">
-        <v>19.53128152736775</v>
+        <v>20.74630230362064</v>
       </c>
       <c r="CS16" t="n">
-        <v>20.30745126234527</v>
+        <v>20.00967736617017</v>
       </c>
       <c r="CT16" t="n">
-        <v>21.47094010160225</v>
+        <v>19.86702942474311</v>
       </c>
       <c r="CU16" t="n">
-        <v>20.1658636084388</v>
+        <v>19.8087234285879</v>
       </c>
       <c r="CV16" t="n">
-        <v>20.10262923880826</v>
+        <v>22.35083148153346</v>
       </c>
       <c r="CW16" t="n">
-        <v>18.76986746038505</v>
+        <v>22.88135812343139</v>
       </c>
       <c r="CX16" t="n">
-        <v>19.82018307501525</v>
+        <v>20.64686804906617</v>
       </c>
     </row>
     <row r="17">
@@ -5565,307 +5565,307 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16.97798155059377</v>
+        <v>15.44423638215715</v>
       </c>
       <c r="C17" t="n">
-        <v>17.77885205781015</v>
+        <v>16.56142599968185</v>
       </c>
       <c r="D17" t="n">
-        <v>17.54462669053094</v>
+        <v>15.32932281337506</v>
       </c>
       <c r="E17" t="n">
-        <v>18.36668331320497</v>
+        <v>14.89124735278605</v>
       </c>
       <c r="F17" t="n">
-        <v>18.39370101002584</v>
+        <v>16.28483821896439</v>
       </c>
       <c r="G17" t="n">
-        <v>17.29810002451752</v>
+        <v>16.45671278954688</v>
       </c>
       <c r="H17" t="n">
-        <v>17.23335376342245</v>
+        <v>15.56511897698106</v>
       </c>
       <c r="I17" t="n">
-        <v>17.31461302090296</v>
+        <v>15.43626459079866</v>
       </c>
       <c r="J17" t="n">
-        <v>18.10334912649484</v>
+        <v>16.55087221186119</v>
       </c>
       <c r="K17" t="n">
-        <v>18.36499470715366</v>
+        <v>14.87699237612038</v>
       </c>
       <c r="L17" t="n">
-        <v>17.15378311199325</v>
+        <v>14.74894302305547</v>
       </c>
       <c r="M17" t="n">
-        <v>18.69781699637037</v>
+        <v>16.74083057515591</v>
       </c>
       <c r="N17" t="n">
-        <v>18.25029712286651</v>
+        <v>15.98820315012622</v>
       </c>
       <c r="O17" t="n">
-        <v>17.96479507299449</v>
+        <v>16.19620603622499</v>
       </c>
       <c r="P17" t="n">
-        <v>18.92201871958922</v>
+        <v>15.20342348778245</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.36641824132482</v>
+        <v>15.73707208737989</v>
       </c>
       <c r="R17" t="n">
-        <v>19.04704428972505</v>
+        <v>17.00197546448556</v>
       </c>
       <c r="S17" t="n">
-        <v>18.94187947564613</v>
+        <v>15.02122093135128</v>
       </c>
       <c r="T17" t="n">
-        <v>17.75640930529106</v>
+        <v>16.47714295927226</v>
       </c>
       <c r="U17" t="n">
-        <v>18.57100464541281</v>
+        <v>17.38662421500946</v>
       </c>
       <c r="V17" t="n">
-        <v>19.22970826757721</v>
+        <v>17.80486837197269</v>
       </c>
       <c r="W17" t="n">
-        <v>18.0792963077408</v>
+        <v>15.41962396721168</v>
       </c>
       <c r="X17" t="n">
-        <v>19.42349544691849</v>
+        <v>15.16430084176821</v>
       </c>
       <c r="Y17" t="n">
-        <v>19.01255549287486</v>
+        <v>16.91167431064894</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.3716607740655</v>
+        <v>17.92966814013654</v>
       </c>
       <c r="AA17" t="n">
-        <v>18.64969172390819</v>
+        <v>15.67013652890434</v>
       </c>
       <c r="AB17" t="n">
-        <v>17.89893943699362</v>
+        <v>16.53963120064757</v>
       </c>
       <c r="AC17" t="n">
-        <v>18.55125188160337</v>
+        <v>14.73721113798972</v>
       </c>
       <c r="AD17" t="n">
-        <v>18.62942845129254</v>
+        <v>15.3288712094311</v>
       </c>
       <c r="AE17" t="n">
-        <v>17.75791137927856</v>
+        <v>14.66660384310029</v>
       </c>
       <c r="AF17" t="n">
-        <v>19.06775916628466</v>
+        <v>15.82005922081987</v>
       </c>
       <c r="AG17" t="n">
-        <v>18.56519269900367</v>
+        <v>16.00431362995291</v>
       </c>
       <c r="AH17" t="n">
-        <v>18.26435574999132</v>
+        <v>15.16377069800792</v>
       </c>
       <c r="AI17" t="n">
-        <v>18.29681232909372</v>
+        <v>14.96413230234933</v>
       </c>
       <c r="AJ17" t="n">
-        <v>16.88225133195266</v>
+        <v>15.16344672126552</v>
       </c>
       <c r="AK17" t="n">
-        <v>18.11116383822065</v>
+        <v>16.69311763672951</v>
       </c>
       <c r="AL17" t="n">
-        <v>18.1561377005522</v>
+        <v>14.51346101871483</v>
       </c>
       <c r="AM17" t="n">
-        <v>17.85696972263706</v>
+        <v>16.74083057515591</v>
       </c>
       <c r="AN17" t="n">
-        <v>18.92498359765604</v>
+        <v>15.59127273582219</v>
       </c>
       <c r="AO17" t="n">
-        <v>18.11899818490054</v>
+        <v>14.54792036313389</v>
       </c>
       <c r="AP17" t="n">
-        <v>19.12664439358538</v>
+        <v>16.17811242603572</v>
       </c>
       <c r="AQ17" t="n">
-        <v>18.15911239609606</v>
+        <v>15.62492704712377</v>
       </c>
       <c r="AR17" t="n">
-        <v>16.34504880566585</v>
+        <v>15.0830415842877</v>
       </c>
       <c r="AS17" t="n">
-        <v>18.26131233210815</v>
+        <v>15.21061969845458</v>
       </c>
       <c r="AT17" t="n">
-        <v>18.92875350884035</v>
+        <v>16.76328314515203</v>
       </c>
       <c r="AU17" t="n">
-        <v>19.04138942294859</v>
+        <v>17.73742230469093</v>
       </c>
       <c r="AV17" t="n">
-        <v>19.53416786561823</v>
+        <v>15.46475490917591</v>
       </c>
       <c r="AW17" t="n">
-        <v>16.51179865323217</v>
+        <v>14.31575666603361</v>
       </c>
       <c r="AX17" t="n">
-        <v>17.91729811906303</v>
+        <v>14.97004242352889</v>
       </c>
       <c r="AY17" t="n">
-        <v>17.50709447579759</v>
+        <v>14.33572541433799</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18.48510172129122</v>
+        <v>15.20834204378072</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.08957520620426</v>
+        <v>16.25258780687988</v>
       </c>
       <c r="BB17" t="n">
-        <v>17.91760246085135</v>
+        <v>16.46622592480103</v>
       </c>
       <c r="BC17" t="n">
-        <v>18.82875268768577</v>
+        <v>15.32839015305602</v>
       </c>
       <c r="BD17" t="n">
-        <v>18.66765770689591</v>
+        <v>15.24405802526122</v>
       </c>
       <c r="BE17" t="n">
-        <v>18.65458082747534</v>
+        <v>15.92588180586063</v>
       </c>
       <c r="BF17" t="n">
-        <v>17.72686851687028</v>
+        <v>15.83790739408307</v>
       </c>
       <c r="BG17" t="n">
-        <v>18.19946222674061</v>
+        <v>16.35492518757057</v>
       </c>
       <c r="BH17" t="n">
-        <v>17.53024408666373</v>
+        <v>15.29378354648133</v>
       </c>
       <c r="BI17" t="n">
-        <v>19.1761441128335</v>
+        <v>15.45563447300345</v>
       </c>
       <c r="BJ17" t="n">
-        <v>17.27006131008424</v>
+        <v>14.54014492131626</v>
       </c>
       <c r="BK17" t="n">
-        <v>19.41642686344791</v>
+        <v>15.15517058811872</v>
       </c>
       <c r="BL17" t="n">
-        <v>18.35506923786373</v>
+        <v>15.3958656727689</v>
       </c>
       <c r="BM17" t="n">
-        <v>17.65332579634515</v>
+        <v>17.04626210342413</v>
       </c>
       <c r="BN17" t="n">
-        <v>17.53807843334362</v>
+        <v>16.79673128943572</v>
       </c>
       <c r="BO17" t="n">
-        <v>17.19008814209629</v>
+        <v>14.75572689969182</v>
       </c>
       <c r="BP17" t="n">
-        <v>19.45936850803167</v>
+        <v>15.44454072394546</v>
       </c>
       <c r="BQ17" t="n">
-        <v>15.83780921931265</v>
+        <v>15.38020679688617</v>
       </c>
       <c r="BR17" t="n">
-        <v>17.23787962033903</v>
+        <v>14.09495178987146</v>
       </c>
       <c r="BS17" t="n">
-        <v>18.11790844494882</v>
+        <v>15.91187226612103</v>
       </c>
       <c r="BT17" t="n">
-        <v>18.30168179770678</v>
+        <v>18.11707395940022</v>
       </c>
       <c r="BU17" t="n">
-        <v>17.43569196526771</v>
+        <v>17.11545568161945</v>
       </c>
       <c r="BV17" t="n">
-        <v>18.82974425286706</v>
+        <v>15.54409975863313</v>
       </c>
       <c r="BW17" t="n">
-        <v>17.36993450403726</v>
+        <v>15.51728822883015</v>
       </c>
       <c r="BX17" t="n">
-        <v>18.18697439594259</v>
+        <v>16.86477622281707</v>
       </c>
       <c r="BY17" t="n">
-        <v>18.29451503946579</v>
+        <v>15.87529234666079</v>
       </c>
       <c r="BZ17" t="n">
-        <v>18.45230153049233</v>
+        <v>18.11832077898461</v>
       </c>
       <c r="CA17" t="n">
-        <v>16.50077362651348</v>
+        <v>17.18507141132759</v>
       </c>
       <c r="CB17" t="n">
-        <v>17.89338274498758</v>
+        <v>14.43002228133089</v>
       </c>
       <c r="CC17" t="n">
-        <v>18.41632047713168</v>
+        <v>16.4882268908532</v>
       </c>
       <c r="CD17" t="n">
-        <v>17.19237561424719</v>
+        <v>17.56272030072022</v>
       </c>
       <c r="CE17" t="n">
-        <v>17.04210931063517</v>
+        <v>15.84250197333895</v>
       </c>
       <c r="CF17" t="n">
-        <v>19.20551800414457</v>
+        <v>17.9484293387647</v>
       </c>
       <c r="CG17" t="n">
-        <v>17.66189645380322</v>
+        <v>17.66284874907634</v>
       </c>
       <c r="CH17" t="n">
-        <v>18.50974358866781</v>
+        <v>16.19265210953562</v>
       </c>
       <c r="CI17" t="n">
-        <v>17.72829205104144</v>
+        <v>17.19022558677489</v>
       </c>
       <c r="CJ17" t="n">
-        <v>17.82480766784594</v>
+        <v>13.82772006477547</v>
       </c>
       <c r="CK17" t="n">
-        <v>17.58478998911168</v>
+        <v>15.6850394590548</v>
       </c>
       <c r="CL17" t="n">
-        <v>18.69909326838589</v>
+        <v>14.6959875518884</v>
       </c>
       <c r="CM17" t="n">
-        <v>18.70464996039193</v>
+        <v>14.86646804073086</v>
       </c>
       <c r="CN17" t="n">
-        <v>17.65001730658184</v>
+        <v>15.24942818520345</v>
       </c>
       <c r="CO17" t="n">
-        <v>16.79556300966767</v>
+        <v>15.90548108856638</v>
       </c>
       <c r="CP17" t="n">
-        <v>16.92291532186256</v>
+        <v>16.09849268722131</v>
       </c>
       <c r="CQ17" t="n">
-        <v>17.26420027628988</v>
+        <v>16.02884750508204</v>
       </c>
       <c r="CR17" t="n">
-        <v>17.81200567778256</v>
+        <v>15.91743877560411</v>
       </c>
       <c r="CS17" t="n">
-        <v>18.37754144281394</v>
+        <v>15.50369102312633</v>
       </c>
       <c r="CT17" t="n">
-        <v>19.80899831794508</v>
+        <v>15.36901487305776</v>
       </c>
       <c r="CU17" t="n">
-        <v>18.32417363761108</v>
+        <v>15.19672796843948</v>
       </c>
       <c r="CV17" t="n">
-        <v>18.23671955211677</v>
+        <v>16.92931631689425</v>
       </c>
       <c r="CW17" t="n">
-        <v>17.22004126455286</v>
+        <v>17.44851359028518</v>
       </c>
       <c r="CX17" t="n">
-        <v>18.09827682880608</v>
+        <v>15.87223655875655</v>
       </c>
     </row>
     <row r="18">
@@ -5873,307 +5873,307 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>19.19855741292146</v>
+        <v>13.92442221364379</v>
       </c>
       <c r="C18" t="n">
-        <v>20.2355382430092</v>
+        <v>14.8855041287162</v>
       </c>
       <c r="D18" t="n">
-        <v>19.91217018418438</v>
+        <v>13.6957044509854</v>
       </c>
       <c r="E18" t="n">
-        <v>20.77469444722746</v>
+        <v>13.36396208424337</v>
       </c>
       <c r="F18" t="n">
-        <v>20.65388057474285</v>
+        <v>14.54754729900628</v>
       </c>
       <c r="G18" t="n">
-        <v>19.52385951472364</v>
+        <v>14.83105640103867</v>
       </c>
       <c r="H18" t="n">
-        <v>19.34699766580358</v>
+        <v>13.89784630328982</v>
       </c>
       <c r="I18" t="n">
-        <v>19.69072717201447</v>
+        <v>13.75806506515916</v>
       </c>
       <c r="J18" t="n">
-        <v>20.48490215988788</v>
+        <v>15.05546429127541</v>
       </c>
       <c r="K18" t="n">
-        <v>20.81066568311106</v>
+        <v>13.15055958577124</v>
       </c>
       <c r="L18" t="n">
-        <v>19.20653902175698</v>
+        <v>13.2561269164089</v>
       </c>
       <c r="M18" t="n">
-        <v>21.04907329561036</v>
+        <v>15.07747507480462</v>
       </c>
       <c r="N18" t="n">
-        <v>20.5736521523518</v>
+        <v>14.51560122871009</v>
       </c>
       <c r="O18" t="n">
-        <v>20.53945787981288</v>
+        <v>14.56536601983836</v>
       </c>
       <c r="P18" t="n">
-        <v>21.41179961989842</v>
+        <v>13.62051239431714</v>
       </c>
       <c r="Q18" t="n">
-        <v>20.80495191147235</v>
+        <v>14.06294681471301</v>
       </c>
       <c r="R18" t="n">
-        <v>21.36295767161215</v>
+        <v>15.32532710021877</v>
       </c>
       <c r="S18" t="n">
-        <v>21.41916272768028</v>
+        <v>13.51657476486854</v>
       </c>
       <c r="T18" t="n">
-        <v>20.02437412930275</v>
+        <v>14.7642779221958</v>
       </c>
       <c r="U18" t="n">
-        <v>20.84723578509426</v>
+        <v>15.73689537279312</v>
       </c>
       <c r="V18" t="n">
-        <v>21.81634839638741</v>
+        <v>15.9386347085388</v>
       </c>
       <c r="W18" t="n">
-        <v>20.57297474643587</v>
+        <v>14.00745843446898</v>
       </c>
       <c r="X18" t="n">
-        <v>21.96740991563987</v>
+        <v>13.54880554199896</v>
       </c>
       <c r="Y18" t="n">
-        <v>21.62973779276417</v>
+        <v>15.31061070213211</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.01736284476318</v>
+        <v>16.09929772033879</v>
       </c>
       <c r="AA18" t="n">
-        <v>21.01598839797724</v>
+        <v>13.94960404225772</v>
       </c>
       <c r="AB18" t="n">
-        <v>20.25510447475483</v>
+        <v>14.74942407943055</v>
       </c>
       <c r="AC18" t="n">
-        <v>20.95366705371165</v>
+        <v>13.1428528662929</v>
       </c>
       <c r="AD18" t="n">
-        <v>21.0555331955043</v>
+        <v>13.7242536742249</v>
       </c>
       <c r="AE18" t="n">
-        <v>20.05111693676643</v>
+        <v>13.07637872923835</v>
       </c>
       <c r="AF18" t="n">
-        <v>21.66004434439428</v>
+        <v>14.16900501920279</v>
       </c>
       <c r="AG18" t="n">
-        <v>20.96449573088949</v>
+        <v>14.51141898349</v>
       </c>
       <c r="AH18" t="n">
-        <v>20.75301745791769</v>
+        <v>13.56437606058831</v>
       </c>
       <c r="AI18" t="n">
-        <v>20.71794942992199</v>
+        <v>13.48285173122765</v>
       </c>
       <c r="AJ18" t="n">
-        <v>19.01188790443597</v>
+        <v>13.58217514646631</v>
       </c>
       <c r="AK18" t="n">
-        <v>20.61604401822117</v>
+        <v>15.12102540296501</v>
       </c>
       <c r="AL18" t="n">
-        <v>20.53171189042637</v>
+        <v>12.97084085103182</v>
       </c>
       <c r="AM18" t="n">
-        <v>20.35247421206203</v>
+        <v>15.11082504431789</v>
       </c>
       <c r="AN18" t="n">
-        <v>21.4942762445322</v>
+        <v>14.04985030033836</v>
       </c>
       <c r="AO18" t="n">
-        <v>20.55823871339512</v>
+        <v>12.9827887205925</v>
       </c>
       <c r="AP18" t="n">
-        <v>21.54575909414291</v>
+        <v>14.55649102059197</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20.49723291105322</v>
+        <v>14.19319528263544</v>
       </c>
       <c r="AR18" t="n">
-        <v>18.44290620496269</v>
+        <v>13.61576073542859</v>
       </c>
       <c r="AS18" t="n">
-        <v>20.8167328839233</v>
+        <v>13.65251736947559</v>
       </c>
       <c r="AT18" t="n">
-        <v>21.44338244354405</v>
+        <v>15.16595999538839</v>
       </c>
       <c r="AU18" t="n">
-        <v>21.51706260874777</v>
+        <v>15.9593495850984</v>
       </c>
       <c r="AV18" t="n">
-        <v>22.04433966574464</v>
+        <v>13.76932571132687</v>
       </c>
       <c r="AW18" t="n">
-        <v>18.74929984598108</v>
+        <v>12.79388082734133</v>
       </c>
       <c r="AX18" t="n">
-        <v>20.26627676362916</v>
+        <v>13.36742765363936</v>
       </c>
       <c r="AY18" t="n">
-        <v>19.72501961932381</v>
+        <v>12.85064547960088</v>
       </c>
       <c r="AZ18" t="n">
-        <v>20.90264562552195</v>
+        <v>13.52729544979891</v>
       </c>
       <c r="BA18" t="n">
-        <v>20.56479678805949</v>
+        <v>14.70858337493388</v>
       </c>
       <c r="BB18" t="n">
-        <v>20.22794933325537</v>
+        <v>14.85681746079811</v>
       </c>
       <c r="BC18" t="n">
-        <v>21.41810244015969</v>
+        <v>13.71255124159028</v>
       </c>
       <c r="BD18" t="n">
-        <v>21.0883137513491</v>
+        <v>13.85100712032021</v>
       </c>
       <c r="BE18" t="n">
-        <v>21.19844620881151</v>
+        <v>14.50388897859842</v>
       </c>
       <c r="BF18" t="n">
-        <v>19.96256329384337</v>
+        <v>14.12158660508767</v>
       </c>
       <c r="BG18" t="n">
-        <v>20.64293408784049</v>
+        <v>14.57556637848548</v>
       </c>
       <c r="BH18" t="n">
-        <v>19.79247550408261</v>
+        <v>13.72656078132988</v>
       </c>
       <c r="BI18" t="n">
-        <v>21.74560365681938</v>
+        <v>13.86562534363645</v>
       </c>
       <c r="BJ18" t="n">
-        <v>19.455284437582</v>
+        <v>12.9767313372573</v>
       </c>
       <c r="BK18" t="n">
-        <v>22.09788418553427</v>
+        <v>13.49729323995713</v>
       </c>
       <c r="BL18" t="n">
-        <v>20.84294554762669</v>
+        <v>13.79638267805592</v>
       </c>
       <c r="BM18" t="n">
-        <v>19.98634122324023</v>
+        <v>15.32576888668568</v>
       </c>
       <c r="BN18" t="n">
-        <v>19.74433059666634</v>
+        <v>15.23822644389799</v>
       </c>
       <c r="BO18" t="n">
-        <v>19.37169843804243</v>
+        <v>13.10202197927327</v>
       </c>
       <c r="BP18" t="n">
-        <v>22.00699398307509</v>
+        <v>13.82552094991796</v>
       </c>
       <c r="BQ18" t="n">
-        <v>17.91276244466941</v>
+        <v>13.7189129667138</v>
       </c>
       <c r="BR18" t="n">
-        <v>19.53352972961047</v>
+        <v>12.51075460691359</v>
       </c>
       <c r="BS18" t="n">
-        <v>20.56536620172795</v>
+        <v>14.43217230880319</v>
       </c>
       <c r="BT18" t="n">
-        <v>20.57392704170899</v>
+        <v>16.42156622173485</v>
       </c>
       <c r="BU18" t="n">
-        <v>19.83485755247495</v>
+        <v>15.47220637425114</v>
       </c>
       <c r="BV18" t="n">
-        <v>21.43679491644855</v>
+        <v>13.74217056982741</v>
       </c>
       <c r="BW18" t="n">
-        <v>19.73125371724578</v>
+        <v>13.82219282520057</v>
       </c>
       <c r="BX18" t="n">
-        <v>20.58282167590946</v>
+        <v>15.10477747845973</v>
       </c>
       <c r="BY18" t="n">
-        <v>20.61036951649062</v>
+        <v>14.20799022053843</v>
       </c>
       <c r="BZ18" t="n">
-        <v>21.03838206311111</v>
+        <v>16.35983392609181</v>
       </c>
       <c r="CA18" t="n">
-        <v>18.58382627043028</v>
+        <v>15.65460528022316</v>
       </c>
       <c r="CB18" t="n">
-        <v>20.32494600643495</v>
+        <v>12.81785510627904</v>
       </c>
       <c r="CC18" t="n">
-        <v>20.86235469973965</v>
+        <v>14.93023255412169</v>
       </c>
       <c r="CD18" t="n">
-        <v>19.58739822614249</v>
+        <v>15.74654595272587</v>
       </c>
       <c r="CE18" t="n">
-        <v>19.26268517296286</v>
+        <v>14.20581074063501</v>
       </c>
       <c r="CF18" t="n">
-        <v>21.78496192228264</v>
+        <v>16.41421293143004</v>
       </c>
       <c r="CG18" t="n">
-        <v>19.89614806165107</v>
+        <v>16.04716691724328</v>
       </c>
       <c r="CH18" t="n">
-        <v>20.92411644781383</v>
+        <v>14.55272110940766</v>
       </c>
       <c r="CI18" t="n">
-        <v>20.02214556201411</v>
+        <v>15.52198098285645</v>
       </c>
       <c r="CJ18" t="n">
-        <v>20.05202996213138</v>
+        <v>12.21200878051129</v>
       </c>
       <c r="CK18" t="n">
-        <v>19.96704006337474</v>
+        <v>14.16311453297731</v>
       </c>
       <c r="CL18" t="n">
-        <v>21.12117284701024</v>
+        <v>13.08231830284904</v>
       </c>
       <c r="CM18" t="n">
-        <v>21.18071584527281</v>
+        <v>13.42311238342424</v>
       </c>
       <c r="CN18" t="n">
-        <v>20.02629835480307</v>
+        <v>13.83632999214172</v>
       </c>
       <c r="CO18" t="n">
-        <v>18.94292012821263</v>
+        <v>14.30041194941623</v>
       </c>
       <c r="CP18" t="n">
-        <v>19.22601689620924</v>
+        <v>14.50303485809573</v>
       </c>
       <c r="CQ18" t="n">
-        <v>19.43027932355484</v>
+        <v>14.2907417345294</v>
       </c>
       <c r="CR18" t="n">
-        <v>20.23855220846123</v>
+        <v>14.18795274989476</v>
       </c>
       <c r="CS18" t="n">
-        <v>20.80182995377284</v>
+        <v>13.97697516825212</v>
       </c>
       <c r="CT18" t="n">
-        <v>22.41612752134291</v>
+        <v>13.80159575836547</v>
       </c>
       <c r="CU18" t="n">
-        <v>20.84311244473642</v>
+        <v>13.52727581484483</v>
       </c>
       <c r="CV18" t="n">
-        <v>20.53585486573829</v>
+        <v>15.19255554069643</v>
       </c>
       <c r="CW18" t="n">
-        <v>19.47350567497282</v>
+        <v>15.7032999663538</v>
       </c>
       <c r="CX18" t="n">
-        <v>20.48288005414144</v>
+        <v>14.25664131707101</v>
       </c>
     </row>
     <row r="19">
@@ -6181,307 +6181,307 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>20.11989818092596</v>
+        <v>16.61370406493299</v>
       </c>
       <c r="C19" t="n">
-        <v>21.27897897299088</v>
+        <v>17.73626384239992</v>
       </c>
       <c r="D19" t="n">
-        <v>20.84797209587244</v>
+        <v>16.21801065273631</v>
       </c>
       <c r="E19" t="n">
-        <v>21.73390122418476</v>
+        <v>15.83297902060776</v>
       </c>
       <c r="F19" t="n">
-        <v>21.49014308669732</v>
+        <v>17.33576968392947</v>
       </c>
       <c r="G19" t="n">
-        <v>20.37163792724893</v>
+        <v>17.74483449985799</v>
       </c>
       <c r="H19" t="n">
-        <v>20.13036361145323</v>
+        <v>16.50179464412589</v>
       </c>
       <c r="I19" t="n">
-        <v>20.62914053259582</v>
+        <v>16.17165252614178</v>
       </c>
       <c r="J19" t="n">
-        <v>21.4546529071888</v>
+        <v>18.06881124225944</v>
       </c>
       <c r="K19" t="n">
-        <v>21.81169491226928</v>
+        <v>15.45675366538629</v>
       </c>
       <c r="L19" t="n">
-        <v>19.93505472317037</v>
+        <v>15.84196201210161</v>
       </c>
       <c r="M19" t="n">
-        <v>21.9703060713674</v>
+        <v>17.77965709092763</v>
       </c>
       <c r="N19" t="n">
-        <v>21.44783957812133</v>
+        <v>17.26829416421659</v>
       </c>
       <c r="O19" t="n">
-        <v>21.62035228471157</v>
+        <v>17.29822765171908</v>
       </c>
       <c r="P19" t="n">
-        <v>22.50847071040437</v>
+        <v>16.17119110472078</v>
       </c>
       <c r="Q19" t="n">
-        <v>21.82065826880905</v>
+        <v>16.53924831904291</v>
       </c>
       <c r="R19" t="n">
-        <v>22.26901262786153</v>
+        <v>18.22101158884882</v>
       </c>
       <c r="S19" t="n">
-        <v>22.36969085493204</v>
+        <v>15.97311368791195</v>
       </c>
       <c r="T19" t="n">
-        <v>20.90312668189703</v>
+        <v>17.39540103948542</v>
       </c>
       <c r="U19" t="n">
-        <v>21.7094066189638</v>
+        <v>18.64305510942749</v>
       </c>
       <c r="V19" t="n">
-        <v>22.81146750436606</v>
+        <v>18.76080592907485</v>
       </c>
       <c r="W19" t="n">
-        <v>21.53888686021318</v>
+        <v>16.6057322735745</v>
       </c>
       <c r="X19" t="n">
-        <v>22.98383294880067</v>
+        <v>16.00968378989514</v>
       </c>
       <c r="Y19" t="n">
-        <v>22.65197277233413</v>
+        <v>18.23416700808573</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.10398083877764</v>
+        <v>19.16197749346122</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.88965549746352</v>
+        <v>16.41809083486181</v>
       </c>
       <c r="AB19" t="n">
-        <v>21.22746667094904</v>
+        <v>17.39679512122546</v>
       </c>
       <c r="AC19" t="n">
-        <v>21.91828326051935</v>
+        <v>15.45024467810713</v>
       </c>
       <c r="AD19" t="n">
-        <v>22.00937962999642</v>
+        <v>16.3745110542703</v>
       </c>
       <c r="AE19" t="n">
-        <v>20.91966913071358</v>
+        <v>15.53179845989892</v>
       </c>
       <c r="AF19" t="n">
-        <v>22.69710371429835</v>
+        <v>16.86713241730726</v>
       </c>
       <c r="AG19" t="n">
-        <v>21.94537949715657</v>
+        <v>17.2431221530797</v>
       </c>
       <c r="AH19" t="n">
-        <v>21.79314969813606</v>
+        <v>16.05136879741746</v>
       </c>
       <c r="AI19" t="n">
-        <v>21.70109121590884</v>
+        <v>16.04901260292727</v>
       </c>
       <c r="AJ19" t="n">
-        <v>19.83456302816367</v>
+        <v>15.94904123420381</v>
       </c>
       <c r="AK19" t="n">
-        <v>21.6491862147853</v>
+        <v>17.9495387136705</v>
       </c>
       <c r="AL19" t="n">
-        <v>21.43134621668998</v>
+        <v>15.50703878279781</v>
       </c>
       <c r="AM19" t="n">
-        <v>21.37896015919137</v>
+        <v>17.86367505945707</v>
       </c>
       <c r="AN19" t="n">
-        <v>22.45957967473288</v>
+        <v>16.54978247190948</v>
       </c>
       <c r="AO19" t="n">
-        <v>21.55898323571911</v>
+        <v>15.41409672763677</v>
       </c>
       <c r="AP19" t="n">
-        <v>22.49372485988658</v>
+        <v>17.27533329525604</v>
       </c>
       <c r="AQ19" t="n">
-        <v>21.37394342842267</v>
+        <v>16.92235572567114</v>
       </c>
       <c r="AR19" t="n">
-        <v>19.29463124325905</v>
+        <v>16.07653099107731</v>
       </c>
       <c r="AS19" t="n">
-        <v>21.93194918856247</v>
+        <v>16.17664962195639</v>
       </c>
       <c r="AT19" t="n">
-        <v>22.4289785987915</v>
+        <v>18.12441743222798</v>
       </c>
       <c r="AU19" t="n">
-        <v>22.4795582405143</v>
+        <v>18.89795608335812</v>
       </c>
       <c r="AV19" t="n">
-        <v>23.06863631549351</v>
+        <v>16.30481678474581</v>
       </c>
       <c r="AW19" t="n">
-        <v>19.64511517367516</v>
+        <v>15.21833623540996</v>
       </c>
       <c r="AX19" t="n">
-        <v>21.20481775141207</v>
+        <v>15.77763790251936</v>
       </c>
       <c r="AY19" t="n">
-        <v>20.58237007196551</v>
+        <v>15.13650756426098</v>
       </c>
       <c r="AZ19" t="n">
-        <v>21.83563973877586</v>
+        <v>15.98996047851682</v>
       </c>
       <c r="BA19" t="n">
-        <v>21.57905015879392</v>
+        <v>17.3565336478743</v>
       </c>
       <c r="BB19" t="n">
-        <v>21.1582436403226</v>
+        <v>17.76154384578428</v>
       </c>
       <c r="BC19" t="n">
-        <v>22.46149408275616</v>
+        <v>16.07746365139634</v>
       </c>
       <c r="BD19" t="n">
-        <v>22.0296723550432</v>
+        <v>16.40103787723904</v>
       </c>
       <c r="BE19" t="n">
-        <v>22.25362864133598</v>
+        <v>17.05581450858645</v>
       </c>
       <c r="BF19" t="n">
-        <v>20.793082581728</v>
+        <v>16.61309538135636</v>
       </c>
       <c r="BG19" t="n">
-        <v>21.60612676047704</v>
+        <v>17.26047945249079</v>
       </c>
       <c r="BH19" t="n">
-        <v>20.68585609747016</v>
+        <v>16.33533932087085</v>
       </c>
       <c r="BI19" t="n">
-        <v>22.70130559447253</v>
+        <v>16.39310535578873</v>
       </c>
       <c r="BJ19" t="n">
-        <v>20.26160364455695</v>
+        <v>15.40607584889307</v>
       </c>
       <c r="BK19" t="n">
-        <v>23.20582573968496</v>
+        <v>16.07856320882509</v>
       </c>
       <c r="BL19" t="n">
-        <v>21.85687494161872</v>
+        <v>16.47575869500927</v>
       </c>
       <c r="BM19" t="n">
-        <v>20.96416193667005</v>
+        <v>18.24514294741921</v>
       </c>
       <c r="BN19" t="n">
-        <v>20.55418409537658</v>
+        <v>18.09253026679405</v>
       </c>
       <c r="BO19" t="n">
-        <v>20.21989900208055</v>
+        <v>15.44775103893835</v>
       </c>
       <c r="BP19" t="n">
-        <v>23.05192696956723</v>
+        <v>16.33561421022804</v>
       </c>
       <c r="BQ19" t="n">
-        <v>18.74714981850877</v>
+        <v>16.23502434045091</v>
       </c>
       <c r="BR19" t="n">
-        <v>20.43173070422588</v>
+        <v>14.70517671040015</v>
       </c>
       <c r="BS19" t="n">
-        <v>21.55642087421102</v>
+        <v>17.2789068568995</v>
       </c>
       <c r="BT19" t="n">
-        <v>21.46041576621273</v>
+        <v>19.50698327168764</v>
       </c>
       <c r="BU19" t="n">
-        <v>20.81882400653335</v>
+        <v>18.46533914000473</v>
       </c>
       <c r="BV19" t="n">
-        <v>22.55901108221899</v>
+        <v>16.20422691496869</v>
       </c>
       <c r="BW19" t="n">
-        <v>20.68109462110457</v>
+        <v>16.403570786316</v>
       </c>
       <c r="BX19" t="n">
-        <v>21.5774989974212</v>
+        <v>17.90941468499793</v>
       </c>
       <c r="BY19" t="n">
-        <v>21.49699568567296</v>
+        <v>16.86790799799362</v>
       </c>
       <c r="BZ19" t="n">
-        <v>22.14402632763387</v>
+        <v>19.53493362882754</v>
       </c>
       <c r="CA19" t="n">
-        <v>19.40369359572383</v>
+        <v>18.7253550194745</v>
       </c>
       <c r="CB19" t="n">
-        <v>21.36522550880896</v>
+        <v>15.20989320515343</v>
       </c>
       <c r="CC19" t="n">
-        <v>21.85412604804682</v>
+        <v>17.83990694753726</v>
       </c>
       <c r="CD19" t="n">
-        <v>20.57309255616038</v>
+        <v>18.70888129299724</v>
       </c>
       <c r="CE19" t="n">
-        <v>20.14086831188867</v>
+        <v>16.99391531583369</v>
       </c>
       <c r="CF19" t="n">
-        <v>22.82600718786595</v>
+        <v>19.49756831120391</v>
       </c>
       <c r="CG19" t="n">
-        <v>20.76713498990476</v>
+        <v>18.98874811104687</v>
       </c>
       <c r="CH19" t="n">
-        <v>21.87721675405071</v>
+        <v>17.3009372753828</v>
       </c>
       <c r="CI19" t="n">
-        <v>20.97978154264462</v>
+        <v>18.45963518584305</v>
       </c>
       <c r="CJ19" t="n">
-        <v>20.93591705521887</v>
+        <v>14.43005173376202</v>
       </c>
       <c r="CK19" t="n">
-        <v>20.91540834567715</v>
+        <v>16.85450714183065</v>
       </c>
       <c r="CL19" t="n">
-        <v>22.04305357625208</v>
+        <v>15.54008441052276</v>
       </c>
       <c r="CM19" t="n">
-        <v>22.19355549931312</v>
+        <v>15.92641194962092</v>
       </c>
       <c r="CN19" t="n">
-        <v>20.97261478440361</v>
+        <v>16.47191024400862</v>
       </c>
       <c r="CO19" t="n">
-        <v>19.78886267253098</v>
+        <v>17.01685875968194</v>
       </c>
       <c r="CP19" t="n">
-        <v>20.15343468250303</v>
+        <v>17.25715132777339</v>
       </c>
       <c r="CQ19" t="n">
-        <v>20.27912784107775</v>
+        <v>17.05763074183931</v>
       </c>
       <c r="CR19" t="n">
-        <v>21.23660674207558</v>
+        <v>16.70008804542967</v>
       </c>
       <c r="CS19" t="n">
-        <v>21.70781618768292</v>
+        <v>16.57915636322054</v>
       </c>
       <c r="CT19" t="n">
-        <v>23.49595182124398</v>
+        <v>16.32349944355763</v>
       </c>
       <c r="CU19" t="n">
-        <v>21.89134410351482</v>
+        <v>16.0077104770096</v>
       </c>
       <c r="CV19" t="n">
-        <v>21.40309151776176</v>
+        <v>18.18996872644054</v>
       </c>
       <c r="CW19" t="n">
-        <v>20.36995913867467</v>
+        <v>18.51098059077516</v>
       </c>
       <c r="CX19" t="n">
-        <v>21.43295598840063</v>
+        <v>16.91138037538629</v>
       </c>
     </row>
     <row r="20">
@@ -6489,307 +6489,307 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>22.59633712993446</v>
+        <v>19.51846971982732</v>
       </c>
       <c r="C20" t="n">
-        <v>23.93791500274181</v>
+        <v>20.75247749668035</v>
       </c>
       <c r="D20" t="n">
-        <v>23.35460960426357</v>
+        <v>18.80494530585779</v>
       </c>
       <c r="E20" t="n">
-        <v>24.29973811914197</v>
+        <v>18.45660158543693</v>
       </c>
       <c r="F20" t="n">
-        <v>23.969399651617</v>
+        <v>20.290280494998</v>
       </c>
       <c r="G20" t="n">
-        <v>22.82600718786596</v>
+        <v>20.79937558451222</v>
       </c>
       <c r="H20" t="n">
-        <v>22.5045240846333</v>
+        <v>19.16069140396866</v>
       </c>
       <c r="I20" t="n">
-        <v>23.15933016841183</v>
+        <v>18.59565633026645</v>
       </c>
       <c r="J20" t="n">
-        <v>23.99569085513674</v>
+        <v>21.16941592919693</v>
       </c>
       <c r="K20" t="n">
-        <v>24.38526797913595</v>
+        <v>17.96432383409645</v>
       </c>
       <c r="L20" t="n">
-        <v>22.21029429767053</v>
+        <v>18.59163116467904</v>
       </c>
       <c r="M20" t="n">
-        <v>24.59752183279411</v>
+        <v>20.53212422446216</v>
       </c>
       <c r="N20" t="n">
-        <v>23.98227036401968</v>
+        <v>20.14374483266212</v>
       </c>
       <c r="O20" t="n">
-        <v>24.24707717228617</v>
+        <v>20.1031004777063</v>
       </c>
       <c r="P20" t="n">
-        <v>25.0837912881846</v>
+        <v>18.83954209495544</v>
       </c>
       <c r="Q20" t="n">
-        <v>24.4165562784703</v>
+        <v>19.18900500775914</v>
       </c>
       <c r="R20" t="n">
-        <v>24.70181289141625</v>
+        <v>21.20888218690765</v>
       </c>
       <c r="S20" t="n">
-        <v>24.94846718463122</v>
+        <v>18.4785338291498</v>
       </c>
       <c r="T20" t="n">
-        <v>23.30734826978112</v>
+        <v>20.08311209444783</v>
       </c>
       <c r="U20" t="n">
-        <v>24.168900602597</v>
+        <v>21.69143081849904</v>
       </c>
       <c r="V20" t="n">
-        <v>25.39764621175527</v>
+        <v>21.63061154822095</v>
       </c>
       <c r="W20" t="n">
-        <v>24.26713427788393</v>
+        <v>19.33567811477361</v>
       </c>
       <c r="X20" t="n">
-        <v>25.57812089222695</v>
+        <v>18.66382889084935</v>
       </c>
       <c r="Y20" t="n">
-        <v>25.34655606122626</v>
+        <v>21.29918334074427</v>
       </c>
       <c r="Z20" t="n">
-        <v>24.89123129347363</v>
+        <v>22.2210149826009</v>
       </c>
       <c r="AA20" t="n">
-        <v>24.47942740145027</v>
+        <v>19.02216680289943</v>
       </c>
       <c r="AB20" t="n">
-        <v>23.82589758968724</v>
+        <v>20.11729654950971</v>
       </c>
       <c r="AC20" t="n">
-        <v>24.40933061536704</v>
+        <v>17.87360052874701</v>
       </c>
       <c r="AD20" t="n">
-        <v>24.5887351908411</v>
+        <v>19.1766055342545</v>
       </c>
       <c r="AE20" t="n">
-        <v>23.44037508370657</v>
+        <v>18.2022111203125</v>
       </c>
       <c r="AF20" t="n">
-        <v>25.45162270053475</v>
+        <v>19.57579396827829</v>
       </c>
       <c r="AG20" t="n">
-        <v>24.5351710360974</v>
+        <v>20.22620182234181</v>
       </c>
       <c r="AH20" t="n">
-        <v>24.48131235704242</v>
+        <v>18.63421938008926</v>
       </c>
       <c r="AI20" t="n">
-        <v>24.29450540387833</v>
+        <v>18.74383151126842</v>
       </c>
       <c r="AJ20" t="n">
-        <v>22.17601166783823</v>
+        <v>18.42004130093078</v>
       </c>
       <c r="AK20" t="n">
-        <v>24.43176355040908</v>
+        <v>20.7339715524553</v>
       </c>
       <c r="AL20" t="n">
-        <v>24.06028003659913</v>
+        <v>18.09313895037068</v>
       </c>
       <c r="AM20" t="n">
-        <v>23.97908950145792</v>
+        <v>20.70426386692479</v>
       </c>
       <c r="AN20" t="n">
-        <v>25.05881562658856</v>
+        <v>19.11223233728704</v>
       </c>
       <c r="AO20" t="n">
-        <v>24.24180518711437</v>
+        <v>17.97666440273884</v>
       </c>
       <c r="AP20" t="n">
-        <v>24.94804503311839</v>
+        <v>20.17217624617711</v>
       </c>
       <c r="AQ20" t="n">
-        <v>23.974946526146</v>
+        <v>19.73264779898581</v>
       </c>
       <c r="AR20" t="n">
-        <v>21.57785242659473</v>
+        <v>18.76187603407248</v>
       </c>
       <c r="AS20" t="n">
-        <v>24.73266922176073</v>
+        <v>18.78346466608886</v>
       </c>
       <c r="AT20" t="n">
-        <v>25.03436029127577</v>
+        <v>21.11133573501369</v>
       </c>
       <c r="AU20" t="n">
-        <v>25.15579266481406</v>
+        <v>21.99523264557822</v>
       </c>
       <c r="AV20" t="n">
-        <v>25.74509654176525</v>
+        <v>18.99760347533918</v>
       </c>
       <c r="AW20" t="n">
-        <v>22.1849063020387</v>
+        <v>17.76928983517078</v>
       </c>
       <c r="AX20" t="n">
-        <v>23.61805178322115</v>
+        <v>18.33648475382233</v>
       </c>
       <c r="AY20" t="n">
-        <v>22.98461834696407</v>
+        <v>17.5297532128116</v>
       </c>
       <c r="AZ20" t="n">
-        <v>24.43402157012885</v>
+        <v>18.57859355516664</v>
       </c>
       <c r="BA20" t="n">
-        <v>24.27851273377616</v>
+        <v>20.06546027072548</v>
       </c>
       <c r="BB20" t="n">
-        <v>23.57357861221877</v>
+        <v>20.79029441824794</v>
       </c>
       <c r="BC20" t="n">
-        <v>25.13947601796948</v>
+        <v>18.5748629138905</v>
       </c>
       <c r="BD20" t="n">
-        <v>24.57924169054104</v>
+        <v>19.06026843130125</v>
       </c>
       <c r="BE20" t="n">
-        <v>24.98180733666744</v>
+        <v>19.73614282081293</v>
       </c>
       <c r="BF20" t="n">
-        <v>23.21183403563495</v>
+        <v>19.15728473943492</v>
       </c>
       <c r="BG20" t="n">
-        <v>24.13981141812016</v>
+        <v>20.06702124957523</v>
       </c>
       <c r="BH20" t="n">
-        <v>23.14018608817902</v>
+        <v>19.03923939547629</v>
       </c>
       <c r="BI20" t="n">
-        <v>25.3740744493763</v>
+        <v>19.01336052599234</v>
       </c>
       <c r="BJ20" t="n">
-        <v>22.72774406014789</v>
+        <v>18.01487402338812</v>
       </c>
       <c r="BK20" t="n">
-        <v>25.9649982100395</v>
+        <v>18.74279085870192</v>
       </c>
       <c r="BL20" t="n">
-        <v>24.50145781993356</v>
+        <v>19.25406542811957</v>
       </c>
       <c r="BM20" t="n">
-        <v>23.53875602114914</v>
+        <v>21.21120892896671</v>
       </c>
       <c r="BN20" t="n">
-        <v>22.99556483386642</v>
+        <v>21.0720167394586</v>
       </c>
       <c r="BO20" t="n">
-        <v>22.6085991587605</v>
+        <v>17.91417616136353</v>
       </c>
       <c r="BP20" t="n">
-        <v>25.74988747056198</v>
+        <v>18.90565298535942</v>
       </c>
       <c r="BQ20" t="n">
-        <v>21.05846862114</v>
+        <v>18.82627868347107</v>
       </c>
       <c r="BR20" t="n">
-        <v>22.9361003754202</v>
+        <v>17.02674495906371</v>
       </c>
       <c r="BS20" t="n">
-        <v>24.18674877586021</v>
+        <v>20.3107401171545</v>
       </c>
       <c r="BT20" t="n">
-        <v>23.88016860277801</v>
+        <v>22.57261810539985</v>
       </c>
       <c r="BU20" t="n">
-        <v>23.42305705420366</v>
+        <v>21.574445762061</v>
       </c>
       <c r="BV20" t="n">
-        <v>25.2715505366218</v>
+        <v>18.86626526746504</v>
       </c>
       <c r="BW20" t="n">
-        <v>23.15772010217687</v>
+        <v>19.12673275087876</v>
       </c>
       <c r="BX20" t="n">
-        <v>24.16463981756057</v>
+        <v>20.74770620283771</v>
       </c>
       <c r="BY20" t="n">
-        <v>24.00354483677071</v>
+        <v>19.6052463994057</v>
       </c>
       <c r="BZ20" t="n">
-        <v>25.0511972644036</v>
+        <v>22.80941565166419</v>
       </c>
       <c r="CA20" t="n">
-        <v>21.68591339640118</v>
+        <v>21.78949759667626</v>
       </c>
       <c r="CB20" t="n">
-        <v>24.0204407147608</v>
+        <v>17.65539728400111</v>
       </c>
       <c r="CC20" t="n">
-        <v>24.51132438436124</v>
+        <v>20.78283313569566</v>
       </c>
       <c r="CD20" t="n">
-        <v>23.13104601705248</v>
+        <v>21.71025092198946</v>
       </c>
       <c r="CE20" t="n">
-        <v>22.58100223079412</v>
+        <v>19.86719632185283</v>
       </c>
       <c r="CF20" t="n">
-        <v>25.51691874034421</v>
+        <v>22.69590598209917</v>
       </c>
       <c r="CG20" t="n">
-        <v>23.31542805338708</v>
+        <v>22.04708855931654</v>
       </c>
       <c r="CH20" t="n">
-        <v>24.39956222570979</v>
+        <v>20.09162384704365</v>
       </c>
       <c r="CI20" t="n">
-        <v>23.52319532003683</v>
+        <v>21.37793914157895</v>
       </c>
       <c r="CJ20" t="n">
-        <v>23.36443689878308</v>
+        <v>16.76047534671789</v>
       </c>
       <c r="CK20" t="n">
-        <v>23.48392541186696</v>
+        <v>19.65517808764369</v>
       </c>
       <c r="CL20" t="n">
-        <v>24.71937635784523</v>
+        <v>18.15082644547222</v>
       </c>
       <c r="CM20" t="n">
-        <v>24.84959537333653</v>
+        <v>18.50609148720801</v>
       </c>
       <c r="CN20" t="n">
-        <v>23.55017374694953</v>
+        <v>19.15817812984579</v>
       </c>
       <c r="CO20" t="n">
-        <v>22.15336274830125</v>
+        <v>19.83078329950232</v>
       </c>
       <c r="CP20" t="n">
-        <v>22.60060773244793</v>
+        <v>20.09566864758515</v>
       </c>
       <c r="CQ20" t="n">
-        <v>22.61156403682732</v>
+        <v>20.03152125258966</v>
       </c>
       <c r="CR20" t="n">
-        <v>23.82142082015588</v>
+        <v>19.30384985420193</v>
       </c>
       <c r="CS20" t="n">
-        <v>24.31649655245346</v>
+        <v>19.28340004952247</v>
       </c>
       <c r="CT20" t="n">
-        <v>26.23051187665304</v>
+        <v>18.91967234257607</v>
       </c>
       <c r="CU20" t="n">
-        <v>24.56266978929335</v>
+        <v>18.66119780700197</v>
       </c>
       <c r="CV20" t="n">
-        <v>23.89417814251761</v>
+        <v>21.38674541848605</v>
       </c>
       <c r="CW20" t="n">
-        <v>22.88732714947321</v>
+        <v>21.35087235737287</v>
       </c>
       <c r="CX20" t="n">
-        <v>23.99387256021369</v>
+        <v>19.67101465986089</v>
       </c>
     </row>
     <row r="21">
@@ -6797,307 +6797,307 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17.08945900241099</v>
+        <v>22.35041914749767</v>
       </c>
       <c r="C21" t="n">
-        <v>17.91807369974939</v>
+        <v>23.73135528576828</v>
       </c>
       <c r="D21" t="n">
-        <v>17.57716180944968</v>
+        <v>21.36397868922456</v>
       </c>
       <c r="E21" t="n">
-        <v>18.38550341669538</v>
+        <v>21.06597899107749</v>
       </c>
       <c r="F21" t="n">
-        <v>18.12239503195723</v>
+        <v>23.25835905933921</v>
       </c>
       <c r="G21" t="n">
-        <v>17.13057459626485</v>
+        <v>23.69847655515305</v>
       </c>
       <c r="H21" t="n">
-        <v>16.99014540464939</v>
+        <v>21.94460391647021</v>
       </c>
       <c r="I21" t="n">
-        <v>17.33369819627351</v>
+        <v>21.09496018330685</v>
       </c>
       <c r="J21" t="n">
-        <v>18.28030915018533</v>
+        <v>24.15518558716867</v>
       </c>
       <c r="K21" t="n">
-        <v>18.40629683307133</v>
+        <v>20.46681836717566</v>
       </c>
       <c r="L21" t="n">
-        <v>16.86364721295718</v>
+        <v>21.3669926546766</v>
       </c>
       <c r="M21" t="n">
-        <v>18.71313226055662</v>
+        <v>23.39512633201783</v>
       </c>
       <c r="N21" t="n">
-        <v>18.15564682670007</v>
+        <v>22.96292172270022</v>
       </c>
       <c r="O21" t="n">
-        <v>18.32788464393314</v>
+        <v>22.91254824799531</v>
       </c>
       <c r="P21" t="n">
-        <v>19.20290655525127</v>
+        <v>21.4372465203925</v>
       </c>
       <c r="Q21" t="n">
-        <v>18.4367604643341</v>
+        <v>21.71085960556609</v>
       </c>
       <c r="R21" t="n">
-        <v>18.89300807492872</v>
+        <v>24.13015102071038</v>
       </c>
       <c r="S21" t="n">
-        <v>18.55485489567795</v>
+        <v>20.98148978365001</v>
       </c>
       <c r="T21" t="n">
-        <v>17.48345399107933</v>
+        <v>22.84674169937965</v>
       </c>
       <c r="U21" t="n">
-        <v>18.15421347505188</v>
+        <v>24.62679754933475</v>
       </c>
       <c r="V21" t="n">
-        <v>19.09021173628078</v>
+        <v>24.56870753767447</v>
       </c>
       <c r="W21" t="n">
-        <v>18.18097591746964</v>
+        <v>22.21682291990377</v>
       </c>
       <c r="X21" t="n">
-        <v>19.14692730115512</v>
+        <v>21.32366812848819</v>
       </c>
       <c r="Y21" t="n">
-        <v>18.6877442649248</v>
+        <v>24.24638013141615</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.56487853973831</v>
+        <v>25.16913461611477</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.19365028033146</v>
+        <v>21.5419204606193</v>
       </c>
       <c r="AB21" t="n">
-        <v>17.99580848297165</v>
+        <v>22.87257148147838</v>
       </c>
       <c r="AC21" t="n">
-        <v>18.45763242052639</v>
+        <v>20.29022159013574</v>
       </c>
       <c r="AD21" t="n">
-        <v>18.63715480572496</v>
+        <v>21.99443742993778</v>
       </c>
       <c r="AE21" t="n">
-        <v>17.55699671160445</v>
+        <v>20.87349753618286</v>
       </c>
       <c r="AF21" t="n">
-        <v>18.98593049513568</v>
+        <v>22.26938569198914</v>
       </c>
       <c r="AG21" t="n">
-        <v>18.61628284953267</v>
+        <v>23.14300370409021</v>
       </c>
       <c r="AH21" t="n">
-        <v>18.382872332848</v>
+        <v>21.2144192439596</v>
       </c>
       <c r="AI21" t="n">
-        <v>18.16354007824222</v>
+        <v>21.38476228812347</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16.77067570536501</v>
+        <v>20.97666940242215</v>
       </c>
       <c r="AK21" t="n">
-        <v>18.36015469097173</v>
+        <v>23.42217348126983</v>
       </c>
       <c r="AL21" t="n">
-        <v>18.07410286238533</v>
+        <v>20.77104234576766</v>
       </c>
       <c r="AM21" t="n">
-        <v>17.82644718651203</v>
+        <v>23.41339665679386</v>
       </c>
       <c r="AN21" t="n">
-        <v>18.55352953627722</v>
+        <v>21.60483085350743</v>
       </c>
       <c r="AO21" t="n">
-        <v>18.29349402185337</v>
+        <v>20.47726416274885</v>
       </c>
       <c r="AP21" t="n">
-        <v>18.96052286454978</v>
+        <v>23.17664819791474</v>
       </c>
       <c r="AQ21" t="n">
-        <v>18.16887096827628</v>
+        <v>22.49394084438152</v>
       </c>
       <c r="AR21" t="n">
-        <v>16.41999542540805</v>
+        <v>21.38197412464341</v>
       </c>
       <c r="AS21" t="n">
-        <v>18.7338176846851</v>
+        <v>21.40287553326682</v>
       </c>
       <c r="AT21" t="n">
-        <v>18.80701679351375</v>
+        <v>24.06663194424561</v>
       </c>
       <c r="AU21" t="n">
-        <v>18.87526789391299</v>
+        <v>24.95889334525032</v>
       </c>
       <c r="AV21" t="n">
-        <v>19.46904854039554</v>
+        <v>21.60406509029812</v>
       </c>
       <c r="AW21" t="n">
-        <v>16.71448046677392</v>
+        <v>20.257686471217</v>
       </c>
       <c r="AX21" t="n">
-        <v>17.72361893196922</v>
+        <v>20.85719070681532</v>
       </c>
       <c r="AY21" t="n">
-        <v>17.32123981790662</v>
+        <v>20.02312730971835</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18.25102361616765</v>
+        <v>21.27167477007128</v>
       </c>
       <c r="BA21" t="n">
-        <v>18.26503315590725</v>
+        <v>22.71351853591336</v>
       </c>
       <c r="BB21" t="n">
-        <v>17.75307136309662</v>
+        <v>23.77395331865555</v>
       </c>
       <c r="BC21" t="n">
-        <v>18.78334685636436</v>
+        <v>21.00093820567113</v>
       </c>
       <c r="BD21" t="n">
-        <v>18.57699330640872</v>
+        <v>21.74557420438826</v>
       </c>
       <c r="BE21" t="n">
-        <v>18.79235930028934</v>
+        <v>22.45710567051817</v>
       </c>
       <c r="BF21" t="n">
-        <v>17.50869472455551</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="BG21" t="n">
-        <v>18.23336197496825</v>
+        <v>22.79382549812075</v>
       </c>
       <c r="BH21" t="n">
-        <v>17.58339590737165</v>
+        <v>21.72643012415544</v>
       </c>
       <c r="BI21" t="n">
-        <v>18.77570885922531</v>
+        <v>21.61523737917245</v>
       </c>
       <c r="BJ21" t="n">
-        <v>17.24842359068264</v>
+        <v>20.78175321322099</v>
       </c>
       <c r="BK21" t="n">
-        <v>19.57694261309226</v>
+        <v>21.35312055961559</v>
       </c>
       <c r="BL21" t="n">
-        <v>18.28742682104112</v>
+        <v>22.13491570893846</v>
       </c>
       <c r="BM21" t="n">
-        <v>17.85984624341051</v>
+        <v>24.17594955111349</v>
       </c>
       <c r="BN21" t="n">
-        <v>17.30414759037568</v>
+        <v>23.96980216817575</v>
       </c>
       <c r="BO21" t="n">
-        <v>17.31038168829765</v>
+        <v>20.49942220843369</v>
       </c>
       <c r="BP21" t="n">
-        <v>19.30109114315299</v>
+        <v>21.56274332942638</v>
       </c>
       <c r="BQ21" t="n">
-        <v>15.97222029750108</v>
+        <v>21.51165317889737</v>
       </c>
       <c r="BR21" t="n">
-        <v>17.19576264382684</v>
+        <v>19.35772816821099</v>
       </c>
       <c r="BS21" t="n">
-        <v>18.21257837606935</v>
+        <v>23.42186913948152</v>
       </c>
       <c r="BT21" t="n">
-        <v>18.11213576844785</v>
+        <v>25.6158592739782</v>
       </c>
       <c r="BU21" t="n">
-        <v>17.48057747030588</v>
+        <v>24.63437664161154</v>
       </c>
       <c r="BV21" t="n">
-        <v>18.93493851937711</v>
+        <v>21.50134482800278</v>
       </c>
       <c r="BW21" t="n">
-        <v>17.2693348167831</v>
+        <v>21.76648543048871</v>
       </c>
       <c r="BX21" t="n">
-        <v>18.355825183596</v>
+        <v>23.73243520824295</v>
       </c>
       <c r="BY21" t="n">
-        <v>17.97968818566792</v>
+        <v>22.37597404023922</v>
       </c>
       <c r="BZ21" t="n">
-        <v>18.81786510564567</v>
+        <v>26.08365223757476</v>
       </c>
       <c r="CA21" t="n">
-        <v>16.31117850986934</v>
+        <v>24.85501462066396</v>
       </c>
       <c r="CB21" t="n">
-        <v>18.18923241566236</v>
+        <v>20.17211734131485</v>
       </c>
       <c r="CC21" t="n">
-        <v>18.51775464993447</v>
+        <v>23.71828822382475</v>
       </c>
       <c r="CD21" t="n">
-        <v>17.25556089649251</v>
+        <v>24.59860175526878</v>
       </c>
       <c r="CE21" t="n">
-        <v>17.01170458423465</v>
+        <v>22.6923520554098</v>
       </c>
       <c r="CF21" t="n">
-        <v>19.20533147208076</v>
+        <v>25.67627602769755</v>
       </c>
       <c r="CG21" t="n">
-        <v>17.81177005833354</v>
+        <v>25.03759024122274</v>
       </c>
       <c r="CH21" t="n">
-        <v>18.44250368840395</v>
+        <v>22.98721997838032</v>
       </c>
       <c r="CI21" t="n">
-        <v>18.04380612823228</v>
+        <v>24.27350582048449</v>
       </c>
       <c r="CJ21" t="n">
-        <v>17.81705186098239</v>
+        <v>19.11750432245884</v>
       </c>
       <c r="CK21" t="n">
-        <v>17.77023231296686</v>
+        <v>22.40156820288893</v>
       </c>
       <c r="CL21" t="n">
-        <v>18.43901848405387</v>
+        <v>20.82963304875711</v>
       </c>
       <c r="CM21" t="n">
-        <v>18.79872102541286</v>
+        <v>21.23384803102665</v>
       </c>
       <c r="CN21" t="n">
-        <v>17.70338511178469</v>
+        <v>21.97882764144025</v>
       </c>
       <c r="CO21" t="n">
-        <v>16.76191851584313</v>
+        <v>22.74896944551371</v>
       </c>
       <c r="CP21" t="n">
-        <v>17.06742858392769</v>
+        <v>23.00398822916886</v>
       </c>
       <c r="CQ21" t="n">
-        <v>17.25385265548712</v>
+        <v>22.95333004762973</v>
       </c>
       <c r="CR21" t="n">
-        <v>17.82133228097291</v>
+        <v>21.88031907679613</v>
       </c>
       <c r="CS21" t="n">
-        <v>18.18235036425559</v>
+        <v>21.98154708258102</v>
       </c>
       <c r="CT21" t="n">
-        <v>19.83178468216065</v>
+        <v>21.63018939670813</v>
       </c>
       <c r="CU21" t="n">
-        <v>18.24872632653971</v>
+        <v>21.22074169917495</v>
       </c>
       <c r="CV21" t="n">
-        <v>17.97309084109538</v>
+        <v>24.49375110045522</v>
       </c>
       <c r="CW21" t="n">
-        <v>17.3178135184188</v>
+        <v>24.05457608243746</v>
       </c>
       <c r="CX21" t="n">
-        <v>18.07269739237193</v>
+        <v>22.42253175614203</v>
       </c>
     </row>
   </sheetData>
